--- a/소방설비기사_필기_문제은행.xlsx
+++ b/소방설비기사_필기_문제은행.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4425E7D-4DF9-4FC4-9DCA-4D8C385AF689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF940335-EB9D-4E13-AB04-EDE046AF19FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{FB57838C-1CAD-4D08-9B84-85A2A61E99B1}"/>
   </bookViews>
@@ -39,33 +39,787 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
   <si>
     <t>문제</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>정답</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부촉매소화에 관한 설명으로 옳은 것은?</t>
+  </si>
+  <si>
+    <t>이산화탄소의 증기비중은 약 얼마인가?</t>
+  </si>
+  <si>
+    <t>축압식 분말소화기의 충전압력이 정상인 것은?</t>
+  </si>
+  <si>
+    <t>착화에너지가 충분하지 않아 가연물이 발화되지 못하고 다량 의 연기가 발생되는 연소형태는?</t>
+  </si>
+  <si>
+    <t>가연성 액화가스의 용기가 과열로 파손되어 가스가 분출된 후 불이 폭발하는 현상은?</t>
+  </si>
+  <si>
+    <t>소방안전관리대상물에 대한 소방안전관리자의 업무가 아닌 것은?</t>
+  </si>
+  <si>
+    <t>불활성가스 청정소화약제인 IG-541의 성분이 아닌 것은?</t>
+  </si>
+  <si>
+    <t>위험물안전관리법령상 옥외 탱크저장소에 설치하는 방유제의 면적기준으로 옳은 것은?</t>
+  </si>
+  <si>
+    <t>건축물의 주요 구조부에 해당되지 않는 것은?</t>
+  </si>
+  <si>
+    <t>가연물이 되기 쉬운 조건이 아닌 것은?</t>
+  </si>
+  <si>
+    <t>할로겐화합물 소화약제에 관한 설명으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>유류탱크 화재 시 발생하는 슬롭오버(Slop over) 현상에 관 한 설명으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>마그네슘에 관한 설명으로 옳지 않은 것은?</t>
+  </si>
+  <si>
+    <t>할로겐화합물 소화약제의 분자식이 틀린 것은?</t>
+  </si>
+  <si>
+    <t>그림에서 내화조 건물의 표준 화재 온도-시간 곡선은?</t>
+  </si>
+  <si>
+    <t>가연성물질별 소화에 필요한 이산화탄소 소화약제의 설계농 도로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>다음 중 등전위면의 성질로 적당치 않은 것은?</t>
+  </si>
+  <si>
+    <t>3상 전원에서 6상 전압을 얻을 수 있는 변압기의 결선방법 은?</t>
+  </si>
+  <si>
+    <t>계측방법이 잘못된 것은?</t>
+  </si>
+  <si>
+    <t>그림과 같은 논리회로의 출력 L을 간략화한 것은?</t>
+  </si>
+  <si>
+    <t>소형이면서 대전력용 정류기로 사용하는데 적당한 것은?</t>
+  </si>
+  <si>
+    <t>단상교류회로에 연결되어 있는 부하의 역률을 측정하는 경 우 필요한 계측기의 구성은?</t>
+  </si>
+  <si>
+    <t>제어량이 온도, 압력, 유량 및 액면 등과 같은 일반 공업량 일 때의 제어방식은?</t>
+  </si>
+  <si>
+    <t>다음 중 피드백제어계에서 반드시 필요한 장치는?</t>
+  </si>
+  <si>
+    <t>다음 중 회로의 단락과 같이 이상 상태에서 자동적으로 회 로를 차단하여 피해를 최소화하는 기능을 가진 것은?</t>
+  </si>
+  <si>
+    <t>그림과 같은 논리회로의 출력 Y를 간략화한 것은?</t>
+  </si>
+  <si>
+    <t>제3고조파 전류가 나타나는 결선방식은?</t>
+  </si>
+  <si>
+    <t>축전지의 부동충전 방식에 대한 일반적인 회로계통은?</t>
+  </si>
+  <si>
+    <t>옥내 배선의 굵기를 결정하는 요소가 아닌 것은?</t>
+  </si>
+  <si>
+    <t>위험물안전관리법령에서 규정하는 제3류 위험물의 품명에 속하는 것은?</t>
+  </si>
+  <si>
+    <t>소방시설관리사 시험을 시행하고자 하는 때에는 응시자격등 필요한 사항을 시험 시행일 며칠 전까지 일간신문에 공고하 여야 하는가?</t>
+  </si>
+  <si>
+    <t>소방대장은 화재, 재난·재해, 그 밖의 위급한 상황이 발생한 현장에 소방활동구역을 정하여 지정한 사람 외에는 그 구역 에 출입하는 것을 제한 할 수 있다. 소방활동구역을 출입할 수 없는 사람은?</t>
+  </si>
+  <si>
+    <t>소방공사업자가 소방시설공사를 마친 때에는 완공검사를 받 아야하는데 완공검사를 위한 현장 확인을 할 수 있는 특정 소방대상물의 범위에 속하지 않는 것은? (단, 가스계소화설 비를 설치하지 않는 경우이다.)</t>
+  </si>
+  <si>
+    <t>제조소 등의 위치·구조 또는 설비의 변경 없이 당해 제조소 등에서 저장하거나 취급하는 위험물의 품명·수량 또는 지정 수량의 배수를 변경하고자 할 때는 누구에게 신고해야 하는 가?</t>
+  </si>
+  <si>
+    <t>하자를 보수하여야 하는 소방시설에 따른 하자보수 보증기 간의 연결이 옳은 것은?</t>
+  </si>
+  <si>
+    <t>1급 소방안전관리 대상물에 해당하는 건축물은?</t>
+  </si>
+  <si>
+    <t>다음의 위험물 중에서 위험물안전관리법령에서 정하고 있는 지정수량이 가장 적은 것은?</t>
+  </si>
+  <si>
+    <t>무창층 여부 판단 시 개구부 요건기준으로 옳은 것은?</t>
+  </si>
+  <si>
+    <t>소방시설업을 등록할 수 있는 사람은?</t>
+  </si>
+  <si>
+    <t>소방시설 설치·유지 및 안전관리에 관한 법률에서 규정하는 소방용품 중 경보설비를 구성하는 제품 또는 기기에 해당하 지 않는 것은?</t>
+  </si>
+  <si>
+    <t>제4류 위험물을 저장하는 위험물제조소의 주의사항을 표시 한 게시판의 내용으로 적합한 것은?</t>
+  </si>
+  <si>
+    <t>위험물안전관리법령에 의하여 자체소방대에 배치해야 하는 화학소방자동차의 구분에 속하지 않는 것은?</t>
+  </si>
+  <si>
+    <t>소방력의 기준에 따라 관할구역 안의 소방력을 확충하기 위 한 필요 계획을 수립하여 시행하는 사람은?</t>
+  </si>
+  <si>
+    <t>다음 소방시설 중 소화활동설비가 아닌 것은?</t>
+  </si>
+  <si>
+    <t>차동식감지기에 리크구멍을 이용하는 목적으로 가장 적합한 것은?</t>
+  </si>
+  <si>
+    <t>다음 중 객석유도등을 설치하여야 할 장소는?</t>
+  </si>
+  <si>
+    <t>경계 전류의 정격전류는 최대 몇 A를 초과할 때 1급 누전경 보기를 설치해야 하는가?</t>
+  </si>
+  <si>
+    <t>열반도체 감지기의 구성 부분이 아닌 것은?</t>
+  </si>
+  <si>
+    <t>불꽃감지기 중 도로형의 최대시야각은?</t>
+  </si>
+  <si>
+    <t>자동화재탐지설비의 음향장치 설치기준 중 옳은 것은?</t>
+  </si>
+  <si>
+    <t>무선통신보조서리의 무선기기 접속단자 중 지상에 설치하는 접속단자는 보행거리 최대 몇 m 이내마다 설치하여야 하는 가?</t>
+  </si>
+  <si>
+    <t>무선통신보조시설의 주요 구성요소가 아닌 것은?</t>
+  </si>
+  <si>
+    <t>경계전로의 누설전류를 자동적으로 검출하여 이를 누전경보 기의 수신부에 송신하는 것은?</t>
+  </si>
+  <si>
+    <t>공기관식 차동식분포형감지기의 설치기준으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>휴대용비상조명등을 설치하여야 하는 특정소방대상물에 해 당하는 것은?</t>
+  </si>
+  <si>
+    <t>자동화재탐지설비의 경계구역에 대한 설명 중 옳은 것은?</t>
+  </si>
+  <si>
+    <t>비상콘센트의 플러그접속기는 단상교류 220[V]일 경우 접 지형 및 극 플러그 접속기를 사용해야 하는가?</t>
+  </si>
+  <si>
+    <t>비상콘세트설비의 전원부와 외함사이의 절연저항은 전원부 와 외함사이를 500V 절연저항계로 측정할 때 몇 MΩ 이상 이어야 하는가?</t>
+  </si>
+  <si>
+    <t>소방시설용 비상전원수전설비에서 전력수급용 계기용 변성 기 - 주차단장치 및 그 부속기기로 정의되는 것은?</t>
+  </si>
+  <si>
+    <t>용량 0.02 ㎌ 콘덴서 2개와 0.01㎌의 콘덴서 1개를 병렬로 접속하여 24V 의 전압을 가하였다. 합성용량은 몇 ㎌ 이며, 0.01㎌의 콘덴서에 축적되는 전하량은 몇 C 인가?</t>
+  </si>
+  <si>
     <t>객관식보기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>정답</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>해설</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 소방안전관리대상물에 대한 소방안전관리자의 업무가 아닌 
-것은?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>① 소방계획서의 작성
 ② 자위소방대의 구성
 ③ 소방훈련 및 교육
 ④ 소방용수시설의 지정</t>
+  </si>
+  <si>
+    <t>① 지시압력계의 지침이 노란색부분을 가리키면 정상이다.
+② 지시압력계의 지침이 흰색부분을 가리키면 정상이다.
+③ 지시압력계의 지침이 빨간색부분을 가리키면 정상이다.
+④ 지시압력계의 지침이 녹색부분을 가리키면 정상이다.</t>
+  </si>
+  <si>
+    <t>① 훈소
+② 표면연소
+③ 분해연소
+④ 증발연소</t>
+  </si>
+  <si>
+    <t>① 블레비(BLEVE)
+② 보일오버(Boil over)
+③ 슬롭오버(Slop over)
+④ 플래시오버(Flash over)</t>
+  </si>
+  <si>
+    <t>① 질소
+② 아르곤
+③ 헬륨
+④ 이산화탄소</t>
+  </si>
+  <si>
+    <t>① 비화
+② 전도
+③ 대류
+④ 복사</t>
+  </si>
+  <si>
+    <t>① 소화 시 외부에서 방사하는 포에 의해 발생한다.
+② 연소유가 비산되어 탱크 외부까지 화재가 확산된다.
+③ 탱크의 바닥에 고인 물의 비등 팽창에 의해 발생한다.
+④ 연소면의 온도가 100℃ 이상일 때 물을 주수하면 발생한 다.</t>
+  </si>
+  <si>
+    <t>① 마그네슘의 지정수량은 500kg이다.
+② 마그네슘 화재 시 주수하면 폭발이 일어날 수도 있다.
+③ 마그네슘 화재 시 이산화탄소 소화약제를 사용하여 소화 한다.
+④ 마그네슘의 저장·취급 시 산화제와의 접촉을 피한다.</t>
+  </si>
+  <si>
+    <t>① 13.2
+② 14.5
+③ 15.5
+④ 16.5</t>
+  </si>
+  <si>
+    <t>① 메탄 : 34 vol%
+② 천연가스 : 37 vol%
+③ 에틸렌 : 49 vol%
+④ 아세틸렌 : 53 vol%</t>
+  </si>
+  <si>
+    <t>① 온.오프동작
+② 미분동작
+③ 적분동작
+④ 비례동작</t>
+  </si>
+  <si>
+    <t>① 우드브릿지 결선
+② 메이어 결선
+③ 스코트 결선
+④ 환상 결선</t>
+  </si>
+  <si>
+    <t>① 훅크온 메타에 의한 전류 측정
+② 회로시험기에 의한 저항 측정
+③ 메거에 의한 접지저항 측정
+④ 전류계, 전압계, 전력계에 의한 역률 측정</t>
+  </si>
+  <si>
+    <t>① L=X
+② L=Y
+③ L=X'
+④ L=Y'</t>
+  </si>
+  <si>
+    <t>① 게르마늄 정류기
+② CdS
+③ 셀렌정류기
+④ SCR</t>
+  </si>
+  <si>
+    <t>① 전압계, 전력계, 회전계
+② 상순계, 전력계, 전류계
+③ 전압계, 전류계, 전력계
+④ 전류계, 전압계, 주파수계</t>
+  </si>
+  <si>
+    <t>① 추종제어
+② 공정제어
+③ 프로그램제어
+④ 시퀀스제어</t>
+  </si>
+  <si>
+    <t>① 증폭도를 향상시키는 장치
+② 응답속도를 개선시키는 장치
+③ 기어장치
+④ 입력과 출력을 비교하는 장치</t>
+  </si>
+  <si>
+    <t>① 5
+② 6
+③ 7
+④ 8</t>
+  </si>
+  <si>
+    <t>① 10.17
+② 9.6
+③ 8.8
+④ 5.08</t>
+  </si>
+  <si>
+    <t>① 나이프 스위치
+② 금속함 개폐기
+③ 컷아웃 스위치
+④ 서킷 브레이커</t>
+  </si>
+  <si>
+    <t>① Y - Y
+② Y - △
+③ △ - △
+④ △ - Y</t>
+  </si>
+  <si>
+    <t>① 기계적 강도
+② 허용 전류
+③ 전압 강하
+④ 역률</t>
+  </si>
+  <si>
+    <t>① 나트륨
+② 염소산염류
+③ 무기과산화물
+④ 유기과산화물</t>
+  </si>
+  <si>
+    <t>① 소방서장
+② 소방본부장
+③ 국민안전처장관
+④ 시·도지사</t>
+  </si>
+  <si>
+    <t>① 15
+② 30
+③ 60
+④ 90</t>
+  </si>
+  <si>
+    <t>① 의사·간호사 그 밖의 구조·구급업무에 종사하는 사람
+② 수사업무에 종사하는 사람
+③ 소방활동구역 밖의 소방대상물을 소유한 사람
+④ 전기·가스 등의 업무에 종사하는 사람으로서 원활한 소 방활동을 위하여 필요한 사람</t>
+  </si>
+  <si>
+    <t>① 국무총리
+② 시·도지사
+③ 국민안전처장관
+④ 관할소방서장</t>
+  </si>
+  <si>
+    <t>① 2백만원
+② 3백만원
+③ 5백만원
+④ 1천만원</t>
+  </si>
+  <si>
+    <t>① 10
+② 100
+③ 150
+④ 200</t>
+  </si>
+  <si>
+    <t>① 브롬산염류
+② 유황
+③ 알칼리토금속
+④ 과염소산</t>
+  </si>
+  <si>
+    <t>① 해당 층의 바닥면으로부터 개구부 밑부분까지의 높이가 1.5m 이내일 것
+② 개구부의 크기가 지름 50cm 이상의 원이 내접할 수 있 을 것
+③ 개구부는 도로 또는 차량이 진입할 수 없는 빈터를 향할 것
+④ 내부 또는 외부에서 쉽게 파괴 또는 개방할 수 없을 것</t>
+  </si>
+  <si>
+    <t>① 비상조명등
+② 누전경보기
+③ 발신기
+④ 감지기</t>
+  </si>
+  <si>
+    <t>① 화기엄금
+② 물기엄금
+③ 화기주의
+④ 물기주의</t>
+  </si>
+  <si>
+    <t>① 포수용액 방사차
+② 고가 사다리차
+③ 제독차
+④ 할로겐화합물 방사차</t>
+  </si>
+  <si>
+    <t>① 소방서장
+② 소방본부장
+③ 시·도지사
+④ 자치소방대장</t>
+  </si>
+  <si>
+    <t>① 제연설비
+② 연결송수관설비
+③ 무선통신보조설비
+④ 자동화재탐지설비</t>
+  </si>
+  <si>
+    <t>① 비화재보를 방지하기 위하여
+② 완만한 온도 상승을 감지하기 위해서
+③ 감지기의 감도를 예민하게 하기 위해서
+④ 급격한 전류변화를 방지하기 위해서</t>
+  </si>
+  <si>
+    <t>① 위락시설
+② 근린생활시설
+③ 의료시설
+④ 운동시설</t>
+  </si>
+  <si>
+    <t>① 30
+② 60
+③ 90
+④ 120</t>
+  </si>
+  <si>
+    <t>① 수열관
+② 미터릴레이
+③ 열반도체 소자
+④ 열전대</t>
+  </si>
+  <si>
+    <t>① 30˚ 이상
+② 45˚ 이상
+③ 90˚ 이상
+④ 180˚ 이상</t>
+  </si>
+  <si>
+    <t>① 5
+② 50
+③ 150
+④ 300</t>
+  </si>
+  <si>
+    <t>① 누설동축케이블
+② 증폭기
+③ 음향장치
+④ 분배기</t>
+  </si>
+  <si>
+    <t>① 10
+② 20
+③ 30
+④ 40</t>
+  </si>
+  <si>
+    <t>① 100
+② 200
+③ 300
+④ 400</t>
+  </si>
+  <si>
+    <t>① 변류기
+② 중계기
+③ 검지기
+④ 발신기</t>
+  </si>
+  <si>
+    <t>① 지상 1층
+② 지하 전층, 지상 1층, 지상 2층
+③ 지상 1층, 지상 2층
+④ 지하 전층, 지상 1층</t>
+  </si>
+  <si>
+    <t>① 종합병원
+② 숙박시설
+③ 노유자시설
+④ 집회장</t>
+  </si>
+  <si>
+    <t>① 1극
+② 2극
+③ 3극
+④ 4극</t>
+  </si>
+  <si>
+    <t>① 50
+② 40
+③ 30
+④ 20</t>
+  </si>
+  <si>
+    <t>① 0.81
+② 1.52
+③ 2.02
+④ 2.51</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 산소의 농도를 낮추어 소화하는 방법이다.
+② 화학반응으로 발생한 탄산가스에 의한 소화방법이다.
+③ 활성기(Free radical)의 생성을 억제하는 소화방법이다.
+④ 용융잠열에 의한 냉각효과를 이용하여 소화하는 방법이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 30000[m²] 이하
+② 50000[m²] 이하
+③ 80000[m²] 이하
+④ 100000[m²] 이하</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위험물안전관리법령상 제4류 위험물인 알코올류에 속하지 않는 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 이산화탄소소화기
+② 마른모래
+③ 팽창질석
+④ 팽창진주암</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 발열량이 커야 한다.
+② 열전도율이 커야 한다.
+③ 산소와 친화력이 좋아야 한다.
+④ 활성화에너지가 작아야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>간이소화용구에 해당되지 않는 것은?</t>
+  </si>
+  <si>
+    <t>① 기둥
+② 작은 보
+③ 지붕틀
+④ 바닥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화재 시 불티가 바람에 날리거나 상승하는 열기류에 휩쓸려 멀리 있는 가연물에 착화되는 현상은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 비열, 기화열이 작기 때문에 냉각효과는 물보다 작다.
+② 할로겐 원자는 활성기의 생성을 억제하여 연쇄반응을 차 단한다.
+③ 사용 후에도 화재현장을 오염시키지 않기 때문에 통신 기기실 등에 적합하다.
+④ 약제의 분자 중에 포함되어 있는 할로겐 원자의 소화 효 과는 F &gt;Cl &gt;Br &gt;I 의 순이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① a
+② b
+③ c
+④ d</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>문제이미지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>벤젠의 소화에 필요한 CO₂ 의 이론소화농도가 공기 중에서 37 vol% 일 때 한계산소농도는 약 몇 vol% 인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 전위가 같은 점틀을 연결해 형성된 면이다.
+② 등전위명간의 밀도가 크면 전기장의 세기는 커진다.
+③ 항상 전기력선과 수평을 이룬다.
+④ 유전체의 유전률이 일정하면 등전위면은 동심원을 이룬다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진동이 발생되는 장치의 진동을 억제시키는데 가장 효과적인 제어동작은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>논리식을 간략화 한 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1517.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15117.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15118a.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15124a.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15124.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">① 0
+② 0.2
+③ 12
+④ 24
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① R/(CL)
+② L/(CR)
+③ 1/(LR)
+④ 1/(RC)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그림과 같은 1[kΩ] 의 저항과 실리콘다이오드의 직렬회로 에서 양단간의 전압 VD 는 약 몇 V인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15125a.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그림의 회로에서 공진상태의 임피던스는 몇 Ω 인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15126a.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15128a.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그림과 같은 회로에서 R₁ 과 R₂ 가 각각 2 Ω 및 3 Ω 이었다. 합성저항이 4 Ω이면 R₃는 몇 Ω 인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15133a.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3상3선식 전원으로부터 80m 떨어진 장소에 50A 전류가 필 요해서 14 mm² 전선으로 배선하였을 경우 전압강하는 몇 V 인가? (단, 리액턴스 및 역률은 무시한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15136a.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소방특별조사 결과 화재예방을 위하여 필요한 때 관계인에 게 소방대상물의 개수·이전·제거, 사용의 금지 또는 제한 등 의 필요한 조치를 명할 수 있는 사람이 아닌 것은?(관련 규 정 개정전 문제)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 문화 및 집회시설
+② 노유자시설
+③ 지하상가
+④ 의료시설</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 무선통신보조설비 : 3년
+② 상수도소화용수설비 : 3년
+③ 피난기구 : 3년
+④ 자동화재탐지설비 : 2년</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 연면적 15000 m² 이상인 동물원
+② 층수가 15층인 업무시설
+③ 층수가 20층인 아파트
+④ 지하구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>피난시설, 방화구획 및 방화시설을 폐쇄·훼손·변경등의 행위 를 3차 이상 위반한 자에 대한 과태료는?(관련 규정 개정전 문제)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>관계인이 예방규정을 정하여야 하는 옥외저장소는 지정 수량의 몇 배 이상의 위험물을 저장하는 것을 말하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소방기본법에서 규정하는 소방용수시설에 대한 설명으로 틀린 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 시·도지사는 소방활동에 필요한 소화전·급수탑·저수조를 설치하고 유지·관리하여야 한다.
+② 소방본부장 또는 소방서장은 원활한 소방활동을 위하여 소방용수시설에 대한 조사를 월 1회 이상 실시하여야 한다.
+③ 소방용수시설 조사의 결과는 2년간 보관하여야 한다.
+④ 수도법의 규정에 따라 설치된 소화전도 시·도지사가 유지·관리해야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 6층
+② 11층
+③ 16층
+④ 전층</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아파트로서 층수가 20층인 특정소방대상물에는 몇 층이상의 층에 스프링클러설비를 설치해야 하는가?(관련 규정이 개정 되었습니다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 한정치산자
+② 소방기본법에 따른 금고 이상의 실형을 선고 받고 그 집 행이 종료된 후 1년이 경과한 사람
+③ 위험물안전관리법에 따른 금고 이상의 형의 집행유예를 과한 사람
+④ 등록하려는 소방시설업 등록이 취소된 날부터 2년이 경과한 사람</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포지 등을 사용하여 자루형태로 만든 것으로서 화재시 사용 자가 그 내부에 들어가서 내려옴으로써 대피할 수 있는 피난기구는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연면적 2000 m² 미만의 교육연구시설 내에 있는 합숙소 또는 기숙사에 설치하는 단독경보형감지기 설치기준으로 틀린 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 피난사다리
+② 완강기
+③ 간이완강기
+④ 구조대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 각 실 마다 설치하되, 바닥면적이 150 m² 를 초과하는 경우에는 150 m²마다 1개 이상 설치 할 것
+② 외기가 상통하는 최상층의 계단실의 천장에 설치할 것
+③ 건전지를 주전원으로 사용하는 단독경보형감지기는 정상 적인 작동상태를 유지할 수 있도록 건전지를 교환할 것
+④ 상용전원을 주전원으로 사용하는 단독경보형감지기의 2차전지는 제품검사에 합격한 것을 사용할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 지구음향장치는 당해 소방대상물의 각 부분으로부터 하 나의 음향장치까지의 수평거리가 30m 이하가 되도록 한 다.
+② 정격전압의 80% 전압에서 음향을 발할 수 있어야 한다.
+③ 용량은 부착된 음향장치의 중심으로부터 1m 떨어진 위 치에서 80dB 이상이 되도록 하여야 한다.
+④ 8층으로서 연면적이 3000 m² 를 초과하는 소방대상물에 있어서는 2층 이상의 층에서 발화시 발화층 및 직하층에 경보를 발하여야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상방송설비의 설치기준에서 기동장치에 따른 화재신고를 수신한 후 필요한 음량으로 화재발생 상황 및 피난에 유요 한 방송이 자동으로 개시될 때까지의 소요시간은 몇 초 이 하인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>누전경보기에 사용하는 변압기의 정격 1차 전압은 몇 V 이하 인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 공기관의 노출부분은 감지구역마다 20 m 이상이 되도록 할 것
+② 하나의 검출부분에 접속하는 공기관의 길이는 100m 이하로 할 것
+③ 검출부는 15º 이상 경사되지 아니하도록 부착할 것
+④ 검출부는 바닥으로부터 0.8m 이상 1.5m 이하의 위치에 설치할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연면적 15000 m², 지하3층 지상 20층인 소방대상물의 1층 에서 화재가 발생한 경우 비상방송설비에서 경보를 발하여 야 하는 층은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 하나의 경계구역이 2개 이상의 건축물에 미치지 아니하 도록 하여야 한다.
+② 600 m² 이하의 범위 안에서는 2개의 층을 하나의 경계 구역으로 할 수 있다.
+③ 하나의 경계구역의 면적은 600 m², 한 변의 길이는 최 대 30m 이하로 한다.
+④ 지하구에 있어서는 경계구역의 길이는 최대 500 m 이하로 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 큐비클설비
+② 배전반설비
+③ 수전설비
+④ 변전설비</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -73,7 +827,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,6 +843,13 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -98,12 +859,36 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -112,11 +897,32 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -453,38 +1259,936 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54917824-7461-42B7-AA25-E5AF0FCA2A08}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="39.796875" customWidth="1"/>
-    <col min="2" max="2" width="38.796875" customWidth="1"/>
-    <col min="3" max="3" width="6.5" customWidth="1"/>
+    <col min="1" max="1" width="39.796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="6.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.69921875" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="4" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
+      <c r="B6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A8" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>120</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A14" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C15" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="1">
+        <v>4</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A20" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="8" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A21" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A23" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A25" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C25" s="1">
+        <v>1</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="87" x14ac:dyDescent="0.4">
+      <c r="A26" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C26" s="1">
+        <v>4</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A27" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A34" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" s="1">
+        <v>2</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A35" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C35" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A36" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A37" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B37" s="2">
+        <v>15136</v>
+      </c>
+      <c r="C37" s="1">
+        <v>2</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A38" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C38" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A39" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B39" s="2">
+        <v>15138</v>
+      </c>
+      <c r="C39" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A40" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40" s="2">
+        <v>15139</v>
+      </c>
+      <c r="C40" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" s="8" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A41" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C41" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A43" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A44" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A45" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C45" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="87" x14ac:dyDescent="0.4">
+      <c r="A46" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C46" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A47" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C47" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A48" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C48" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A49" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C49" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A50" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C50" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A51" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C51" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A52" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C52" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="106.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C53" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A54" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C54" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A55" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C55" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="87" x14ac:dyDescent="0.4">
+      <c r="A56" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C56" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A57" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C57" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A58" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C58" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A59" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C59" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A60" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C60" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" s="8" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A61" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C61" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A62" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C62" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A63" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C63" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A64" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C64" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A65" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C65" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A66" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C66" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A67" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C67" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A68" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C68" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A69" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C69" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A70" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C70" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A71" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C71" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A72" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C72" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A73" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C73" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A74" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C74" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A75" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C75" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A76" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C76" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A77" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C77" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A78" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C78" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A79" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C79" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A80" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C80" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A81" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C81" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A82" s="3"/>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A83" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/소방설비기사_필기_문제은행.xlsx
+++ b/소방설비기사_필기_문제은행.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF940335-EB9D-4E13-AB04-EDE046AF19FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5587C42C-5B5D-4E13-AC7C-A664D6E205FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{FB57838C-1CAD-4D08-9B84-85A2A61E99B1}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="3" xr2:uid="{FB57838C-1CAD-4D08-9B84-85A2A61E99B1}"/>
   </bookViews>
   <sheets>
     <sheet name="15년 1회" sheetId="1" r:id="rId1"/>
+    <sheet name="15년 2회" sheetId="2" r:id="rId2"/>
+    <sheet name="15년 3회" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="605">
   <si>
     <t>문제</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -822,12 +825,2080 @@
 ④ 변전설비</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>분진폭발을 일으키는 물질이 아닌 것은?</t>
+  </si>
+  <si>
+    <t>① 시멘트 분말
+② 마그네슘 분말
+③ 석탄 분말
+④ 알루미늄 분말</t>
+  </si>
+  <si>
+    <t>화재강도(Fire intensity)와 관계가 없는 것은?</t>
+  </si>
+  <si>
+    <t>① 가연물의 비표면적
+② 발화원의 온도
+③ 화재실의 구조
+④ 가연물의 발열량</t>
+  </si>
+  <si>
+    <t>화재 시 분말 소화약제와 병용하여 사용할 수 있는 포 소화 약제는?</t>
+  </si>
+  <si>
+    <t>① 수성막포 소화약제
+② 단백포 소화약제
+③ 알콜형포 소화약제
+④ 합성계면활성제포 소화약제</t>
+  </si>
+  <si>
+    <t>표준상태에서 메탄가스의 밀도는 몇 g/L인가?</t>
+  </si>
+  <si>
+    <t>① 0.21
+② 0.41
+③ 0.71
+④ 0.91</t>
+  </si>
+  <si>
+    <t>플래시 오버(Flash over)현상에 대한 설명으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>① 산소의 농도와 무관하다.
+② 화재공간의 개구율과 관계가 있다.
+③ 화재공간내의 가연물의 양과 관계가 있다.
+④ 화재실내의 가연물의 종류와 관계가 있다.</t>
+  </si>
+  <si>
+    <t>유류탱크 화재 시 기름 표면에 물을 살수하면 기름이 탱크 밖으로 비산하여 화재가 확대되는 현상은?</t>
+  </si>
+  <si>
+    <t>① 스롭 오버(Slop over)
+② 보일 오버(Boil over)
+③ 프로스 오버(Froth over)
+④ 블레비(BLEVE)</t>
+  </si>
+  <si>
+    <t>이산화탄소 소화약제의 주된 소화효과는?</t>
+  </si>
+  <si>
+    <t>① 제거소화
+② 억제소화
+③ 질식소화
+④ 냉각소화</t>
+  </si>
+  <si>
+    <t>버너의 불꽃을 제거한 때부터 불꽃을 올리며 연소하는 상태 가 끝날 때까지의 시간은?</t>
+  </si>
+  <si>
+    <t>① 10초 이내
+② 20초 이내
+③ 30초 이내
+④ 40초 이내</t>
+  </si>
+  <si>
+    <t>위험물안전관리법령상 가연성 고체는 제 몇 류 위험물인가?</t>
+  </si>
+  <si>
+    <t>① 제1류
+② 제2류
+③ 제3류
+④ 제4류</t>
+  </si>
+  <si>
+    <t>전기에너지에 의하여 발생되는 열원이 아닌 것은?</t>
+  </si>
+  <si>
+    <t>① 저항가열
+② 마찰 스파크
+③ 유도가열
+④ 유전가열</t>
+  </si>
+  <si>
+    <t>가연물이 공기 중에서 산화되어 산화열의 축적으로 발화되 는 현상은?</t>
+  </si>
+  <si>
+    <t>① 분해연소
+② 자기연소
+③ 자연발화
+④ 폭굉</t>
+  </si>
+  <si>
+    <t>① 9.5
+② 25.8
+③ 38.1
+④ 61.5</t>
+  </si>
+  <si>
+    <t>① 단백포 소화약제
+② 수성막포 소화약제
+③ 불화단백포 소화약제
+④ 합성계면활성제포 소화약제</t>
+  </si>
+  <si>
+    <t>방화구조의 기준으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>① 심벽에 흙으로 맞벽치기한 것
+② 철망모르타르로서 그 바름 두께가 2cm 이상인 것
+③ 시멘트모르타르 위에 타일을 붙인 것으로서 그 두께의 합계가 1.5cm 이상인 것
+④ 석고판 위에 시멘트모르타르 또는 회반죽을 바른 것으로 서 그 두께의 합계가 2.5cm 이상인 것</t>
+  </si>
+  <si>
+    <t>이산화탄소 소화설비의 적용대상이 아닌 것은?</t>
+  </si>
+  <si>
+    <t>① 가솔린
+② 전기설비
+③ 인화성 고체 위험물
+④ 니트로셀로로오스</t>
+  </si>
+  <si>
+    <t>목조건축물에서 발생하는 옥내출화 시기를 나타낸 것으로 옳지 않은 것은?</t>
+  </si>
+  <si>
+    <t>① 천장 속, 벽속 등에서 발염 착화할 때
+② 창, 출입구 등에 발염 착화할 때
+③ 가옥의 구조에는 천장면에 발염 착화할 때
+④ 불연 벽체나 불연 천장인 경우 실내의 그 뒷면에 발염 착화할 때</t>
+  </si>
+  <si>
+    <t>소화약제로서 물에 관한 설명으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>① 수소결합을 하므로 증발잠열이 작다.
+② 가스계 소화약제에 비해 사용 후 오염이 크다.
+③ 무상으로 주수하면 중질유 화재에도 사용할 수 있다.
+④ 타 소화약제에 비해 비열이 크기 때문에 냉각효과가 우 수하다.</t>
+  </si>
+  <si>
+    <t>건축물의 방재계획 중에서 공간적 대응 계획에 해당되지 않 는 것은?</t>
+  </si>
+  <si>
+    <t>① 도피성 대응
+② 대항성 대응
+③ 회피성 대응
+④ 소방시설방재 대응</t>
+  </si>
+  <si>
+    <t>제6류 위험물의 공통성질이 아닌 것은?</t>
+  </si>
+  <si>
+    <t>① 산화성 액체이다.
+② 모두 유기화합물이다.
+③ 불연성 물질이다.
+④ 대부분 비중이 1보다 크다.</t>
+  </si>
+  <si>
+    <t>분말 소화약제의 열분해 반응식 중 옳은 것은?</t>
+  </si>
+  <si>
+    <t>개루프 제어계를 동작시키는 기준으로 직접제어계에 가해지 는 신호는?</t>
+  </si>
+  <si>
+    <t>반파 정류 정현파의 최대값이 1일 때, 실효값과 평균값은?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 
+② 
+③ 
+④ </t>
+  </si>
+  <si>
+    <t>한 코일의 전류가 매초 150A 의 비율로 변화할 때 다른 코 일에 10V 기전력이 발생하였다면 두 코일 상호 인덕턴스(H) 는?</t>
+  </si>
+  <si>
+    <t>① 1/3
+② 1/5
+③ 1/10
+④ 1/15</t>
+  </si>
+  <si>
+    <t>반도체의 특징을 설명 한 것 중 틀린 것은?</t>
+  </si>
+  <si>
+    <t>① 진성 반도체의 경우 온도가 올라 갈수록 양(+)의 온도 계수를 나타낸다.
+② 열전현상, 광전현상, 홀효과 등이 심하다.
+③ 반도체와 금속의 접촉면 또는 P형, N형 반도체외 접합면 에서 정류작용을 한다.
+④ 전류와 전압의 관계는 비직선형이다.</t>
+  </si>
+  <si>
+    <t>서보 기구에 있어서의 제어량은?</t>
+  </si>
+  <si>
+    <t>① 유량
+② 위치
+③ 주파수
+④ 전압</t>
+  </si>
+  <si>
+    <t>온도, 유량, 압력 등의 공업프로세스 상태량을 제어량으로 하는 제어계로서 외란의 억제를 주된 목적으로 하는 제어방 식은?</t>
+  </si>
+  <si>
+    <t>① 서보기구
+② 자동제어
+③ 정치제어
+④ 프로세스제어</t>
+  </si>
+  <si>
+    <t>Y-△ 기동방식인 3상 농형 유도전동기는 직입기동방식에 비해 기동전류는 어떻게 되는가?</t>
+  </si>
+  <si>
+    <t>① 1/√3 로 줄어든다.
+② 1/3 로 줄어든다.
+③ √3 배로 증가한다.
+④ 3 배로 증가한다.</t>
+  </si>
+  <si>
+    <t>주파수 60Hz, 인덕턴스 50mH인 코일의 유도리액턴스는 몇 Ω 인가?</t>
+  </si>
+  <si>
+    <t>① 14.14
+② 18.85
+③ 22.12
+④ 26.86</t>
+  </si>
+  <si>
+    <t>주로 정전압 회로용으로 사용되는 소자는?</t>
+  </si>
+  <si>
+    <t>① 터널다이오드
+② 포토다이오드
+③ 제너다이오드
+④ 매트릭스다이오드</t>
+  </si>
+  <si>
+    <t>논리식 (AㆍA)' 를 간략화한 것은?</t>
+  </si>
+  <si>
+    <t>① A'
+② A
+③ 0
+④ ø</t>
+  </si>
+  <si>
+    <t>실리콘 정류기(SCR)의 애노드 전류가 5A 일 때 게이트 전 류를 2배로 증가시키면 애노드 전류[A]는?</t>
+  </si>
+  <si>
+    <t>3상 유도전동기의 회전차 철손이 작은 이유는?</t>
+  </si>
+  <si>
+    <t>① 효율, 역률이 나쁘다.
+② 성층 철심을 사용한다.
+③ 주파수가 낮다.
+④ 2차가 권선형이다.</t>
+  </si>
+  <si>
+    <t>그림과 같은 게이트의 명칭은?</t>
+  </si>
+  <si>
+    <t>① AND
+② OR
+③ NOR
+④ NAND</t>
+  </si>
+  <si>
+    <t>피드백제어계의 일반적인 특성으로 옳은 것은?</t>
+  </si>
+  <si>
+    <t>① 계의 정확성이 떨어진다.
+② 계의 특성변화에 대한 입력 대 출력비의 감도가 감소된 다.
+③ 비선형과 왜형에 대한 효과가 증대된다.
+④ 대역폭이 감소된다.</t>
+  </si>
+  <si>
+    <t>선간전압이 일정한 경우 △ 결선된 부하를 Y결선으로 바꾸 면 소비전력은 어떻게 되는가?</t>
+  </si>
+  <si>
+    <t>① 1/3
+② 1/9
+③ 3 배로 증가한다.
+④ 9 배로 증가한다.</t>
+  </si>
+  <si>
+    <t>저항이 있는 도체에 전류를 흘리면 열이 발생되는 법칙은?</t>
+  </si>
+  <si>
+    <t>① 옴의 법칙
+② 플레밍의 법칙
+③ 줄의 법칙
+④ 키르히호프의 법칙</t>
+  </si>
+  <si>
+    <t>반도체를 사용한 화재감지기 중 서미스터(Thermistor)는 무 엇을 측정, 제어하기 위한 반도체 소자인가?</t>
+  </si>
+  <si>
+    <t>① 온도
+② 연기 농도
+③ 가스 농도
+④ 불꽃의 스펙트럼 강도</t>
+  </si>
+  <si>
+    <t>A, B 두 개의 코일에 동일 주파수, 동일 전압을 가하면 두 코일의 전류는 같고, 코일 A는 역률이 0.96, 코일 B는 역률 이 0.80인 경우 코일 A에 대한 코일 B의 저항비는 얼마인 가?</t>
+  </si>
+  <si>
+    <t>① 0.833
+② 1.544
+③ 3.211
+④ 7.621</t>
+  </si>
+  <si>
+    <t>2 Ω 의 저항 5개를 직렬로 연결하면 병렬연결 때의 몇 배 가 되는가?</t>
+  </si>
+  <si>
+    <t>① 2
+② 5
+③ 10
+④ 25</t>
+  </si>
+  <si>
+    <t>단상전력을 간접적으로 측정하기 위해 3전압계법을 사용하 는 경우 단상교류전력 P[W]는?</t>
+  </si>
+  <si>
+    <t>① 1천5백만원
+② 2천만원
+③ 3천만원
+④ 5천만원</t>
+  </si>
+  <si>
+    <t>제4류 위험물로서 제1석유류인 수용성 액체의 지정수량은 몇 리터인가?</t>
+  </si>
+  <si>
+    <t>고형알코올 그 밖에 1기압 상태에서 인화점이 40 ℃ 미만인 고체에 해당하는 것은?</t>
+  </si>
+  <si>
+    <t>① 가연성고체
+② 산화성고체
+③ 인화성고체
+④ 자연발화성물질</t>
+  </si>
+  <si>
+    <t>소방대상물이 아닌 것은?</t>
+  </si>
+  <si>
+    <t>① 산림
+② 항해중인 선박
+③ 건축물
+④ 차량</t>
+  </si>
+  <si>
+    <t>비상경보설비를 설치하여야 할 특정소방대상물이 아닌 것 은?</t>
+  </si>
+  <si>
+    <t>시·도지사가 소방시설업의 등록취소처분이나 영업정지처분 을 하고자 할 경우 실시하여야 하는 것은?</t>
+  </si>
+  <si>
+    <t>다음은 소방기본법의 목적을 기술한 것이다. (가), (나), (다) 에 들어갈 내용으로 알맞은 것은?</t>
+  </si>
+  <si>
+    <t>① (가) 예방, (나) 경계, (다) 복구
+② (가) 경보, (나) 소화, (다) 복구
+③ (가) 예방, (나) 경계, (다) 진압
+④ (가) 경계, (나) 통제, (다) 진압</t>
+  </si>
+  <si>
+    <t>위험물 제조소 등에 자동화재탐지설비를 설치하여야 할 대 상은?</t>
+  </si>
+  <si>
+    <t>소방시설 중 화재를 진압하거나 인명구조활동을 위하여 사 용하는 설비로 나열된 것은?</t>
+  </si>
+  <si>
+    <t>① 상수도소화용설비, 연결송수관설비
+② 연결살수설비, 제연설비
+③ 연소방지설비, 피난설비
+④ 무선통신보조설비, 통합감시시설</t>
+  </si>
+  <si>
+    <t>다음 중 스프링클러설비를 의무적으로 설치하여야 하는 기 준으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>"무창층"이라 함은 지상층 중 개구부 면적의 합계가 해당 층 의 바닥면적의 얼마 이하가 되는 층을 말하는가?</t>
+  </si>
+  <si>
+    <t>① 1/3
+② 1/10
+③ 1/30
+④ 1/300</t>
+  </si>
+  <si>
+    <t>다음 중 특수가연물에 해당되지 않는 것은?</t>
+  </si>
+  <si>
+    <t>소화활동을 위한 소방용수시설 및 지리조사의 실시 횟수는?</t>
+  </si>
+  <si>
+    <t>① 주 1회 이상
+② 주 2회 이상
+③ 월 1회 이상
+④ 분기별 1회 이상</t>
+  </si>
+  <si>
+    <t>인접하고 있는 시 · 도간 소방업무의 상호응원협정 사항이 아닌 것은?</t>
+  </si>
+  <si>
+    <t>제1류 위험물 산화성고체에 해당하는 것은?</t>
+  </si>
+  <si>
+    <t>① 질산염류
+② 특수인화물
+③ 과염소산
+④ 유기과산화물</t>
+  </si>
+  <si>
+    <t>소방대상물에 대한 개수 명령권자는?</t>
+  </si>
+  <si>
+    <t>① 소방본부장 또는 소방서장
+② 한국소방안전협회장
+③ 시 · 도지사
+④ 국무총리</t>
+  </si>
+  <si>
+    <t>다음 중 소방용품에 해당되지 않는 것은?</t>
+  </si>
+  <si>
+    <t>① 방염도료
+② 소방호스
+③ 공기호흡기
+④ 휴대용비상조명등</t>
+  </si>
+  <si>
+    <t>다음 소방시설 중 하자보수보증기간이 다른 것은?</t>
+  </si>
+  <si>
+    <t>① 옥내소화전설비
+② 비상방송설비
+③ 자동화재탐지설비
+④ 상수도소화용수설비</t>
+  </si>
+  <si>
+    <t>소방시설업자가 특정소방대상물의 관계인에 대한 통보 의무 사항이 아닌 것은?</t>
+  </si>
+  <si>
+    <t>① 지위를 승계한 때
+② 등록취소 또는 영업정지 처분을 받은 때
+③ 휴업 또는 폐업한 때
+④ 주소지가 변경된 때</t>
+  </si>
+  <si>
+    <t>특정소방대상물 중 노유자시설에 해당되지 않는 것은?</t>
+  </si>
+  <si>
+    <t>① 요양병원
+② 아동복지시설
+③ 장애인직업재활시설
+④ 노인의료복지시설</t>
+  </si>
+  <si>
+    <t>① (가) 750 (나) 600 (다) 7
+② (가) 600 (나) 750 (다) 7
+③ (가) 600 (나) 700 (다) 10
+④ (가) 700 (나) 600 (다) 10</t>
+  </si>
+  <si>
+    <t>유도표지의 설치기준 중 틀린 것은?</t>
+  </si>
+  <si>
+    <t>① 계단에 설치하는 것을 제외하고는 각 층마다 복도 및 통 로의 각 부분으로부터 하나의 유도표지까지의 보행거리 가 15m 이하가 되는 곳에 설치한다.
+② 피난구유도표지는 출입구 상단에 설치한다.
+③ 통로유도표지는 바닥으로부터 높이 1.5m 이하의 위치에 설치한다.
+④ 주위에는 이와 유사한 등화 · 광고물 · 게시물 등을 설치 하지 않는다.</t>
+  </si>
+  <si>
+    <t>정온식 스포트형 감지기의 구조 및 작동원리에 대한 형식이 아닌 것은?</t>
+  </si>
+  <si>
+    <t>① 큐비클(Cubicle)형
+② 옥내개방형
+③ 옥외개방형
+④ 방화구획형</t>
+  </si>
+  <si>
+    <t>피난통로가 되는 계단이나 경사로에 설치하는 통로유도등으 로 바닥면 및 디딤 바닥면을 비추어 주는 유도등은?</t>
+  </si>
+  <si>
+    <t>① 계단통로유도등
+② 피난통로유도등
+③ 복도통로유도등
+④ 바닥통로유도등</t>
+  </si>
+  <si>
+    <t>비상방송설비의 음향장치 설치기준으로 옳은 것은?</t>
+  </si>
+  <si>
+    <t>① 음량조정기의 배선은 2선식으로 할 것
+② 5층 건물 중 2층에서 화재발생시 1층, 2층, 3층에서 경 보를 발할 수 있을 것
+③ 기동장치에 의한 화재신고 수신 후 피난에 유효한 방송 이 자동으로 개시될 때까지의 소요시간은 10초 이하로 할 것
+④ 음향장치는 자동화재탐지설비의 작동과 별도로 작동하는 방식의 성능으로 할 것</t>
+  </si>
+  <si>
+    <t>휴대용 비상조명등의 적합한 기준이 아닌 것은?</t>
+  </si>
+  <si>
+    <t>① 설치높이는 바닥으로부터 0.8 m 이상 1.5m 이하의 높이 에 설치할 것
+② 사용 시 자동으로 점등되는 구조일 것
+③ 외함은 난연성능이 있을 것
+④ 충전식 밧데리의 용량은 10분 이상 유효하게 사용할 수 있는 것으로 할 것</t>
+  </si>
+  <si>
+    <t>비상콘센트설비에 자가발전설비를 비상전원으로 설치할 때 의 기준으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>연기감지기를 설치하지 않아도 되는 장소는?</t>
+  </si>
+  <si>
+    <t>① 계단 및 경사로
+② 엘리베이터 승강로
+③ 파이프 피트 및 덕트
+④ 20m 인 복도</t>
+  </si>
+  <si>
+    <t>감지기 설치기준 중 틀린 것은?</t>
+  </si>
+  <si>
+    <t>① 15
+② 20
+③ 25
+④ 30</t>
+  </si>
+  <si>
+    <t>비상콘센트보호함의 설치기준으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>① 보호함 상부에 적색의 표시등을 설치하여야 한다.
+② 보호함에는 쉽게 개폐할 수 있는 문을 설치하여야 한다.
+③ 보호함 표면에 "비상콘센트" 라고 표시한 표지를 하여야 한다.
+④ 비상콘센트의 보호함을 옥내소화전함 등과 접속하여 설 치하는 경우에는 옥내소화전함의 표시등과 분리하여야 한다.</t>
+  </si>
+  <si>
+    <t>자동화재속보설비 설치기준으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>① 화재 시 자동으로 소방관서에 연락되는 설비여야 한다.
+② 자동화재탐지설비와 연동되어야 한다.
+③ 스위치는 바닥으로터 0.8m 이상 1.5m 이하의 높이에 설 치한다.
+④ 관계인이 24시간 상주하고 있는 경우에는 설치하지 않을 수 있다.</t>
+  </si>
+  <si>
+    <t>수신기를 나타내는 소방시설 도시기호로 옳은 것은?</t>
+  </si>
+  <si>
+    <t>다음 ( ) 에 들어갈 내용으로 옳은 것은?</t>
+  </si>
+  <si>
+    <t>① (가) 400 m (나) 5 m
+② (가) 300 m (나) 5 m
+③ (가) 400 m (나) 3 m
+④ (가) 300 m (나) 3 m</t>
+  </si>
+  <si>
+    <t>① 제1종 접지선측의 점검이 쉬운 위치에 설치
+② 옥외 인입선의 제1지점의 부하측에 설치
+③ 인입구에 근접한 옥외에 설치
+④ 제3종 접지선측의 점검이 쉬운 위치에 설치</t>
+  </si>
+  <si>
+    <t>감도조정장치를 갖는 누전경보기에 있어서 감도조정장치의 조정범위는 최대치가 몇 A 이어야 하는가?</t>
+  </si>
+  <si>
+    <t>다음 ( )에 들어갈 내용으로 옳은 것은?</t>
+  </si>
+  <si>
+    <t>① 사용전압 220V
+② 사용전압 380V
+③ 사용전압 600V
+④ 사용전압 750V</t>
+  </si>
+  <si>
+    <t>부착높이 20m 이상에 설치되는 광전식 중 아날로그방식의 감지기 공칭감지농도 하한값의 기준은?</t>
+  </si>
+  <si>
+    <t>화재 시 이산화탄소를 방출하여 산소농도를 13vol%로 낮추 어 소화하기 위한 공기 중의 이산화탄소의 농도는 약 몇 [vol%]인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저팽창포의 고팽창포에 모두 사용할 수 있는 포 소화약제는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 기준입력신호
+② 피드백신호
+③ 제어편차신호
+④ 동작신호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 2.5
+② 5
+③ 10
+④ 20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15233a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15240a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소방자동차의 출동을 방해한 자는 5년 이하의 징역 또는 얼마 이하의 벌금에 처하는가?(2018년 03월 27일 개정된 규정 적용됨)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 지하가 중 터널로서 길이가 1000m 이상인 것
+② 사람이 거주하고 있는 연면적 400m² 이상인 건축물
+③ 지하층의 바닥면적이 100m² 이상으로 공연장인 건축물
+④ 35명의 근로자가 작업하는 옥내작업장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 청문을 실시하여야 한다.
+② 징계위원회의 개최를 요구하여야 한다.
+③ 직권으로 취소 처분을 결정하여야 한다.
+④ 소방기술심의위원회의 개최를 요구하여야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15247a</t>
+  </si>
+  <si>
+    <t>① 옥내에서 지정수량 50배의 위험물을 저장·취급하고 있는 일반취급소
+② 하루에 지정수량 50배의 위험물을 제조하고 있는 제조소
+③ 지정수량의 100배의 위험물을 저장·취급하고 있는 옥내 저장소
+④ 연면적 100m² 이상의 제조소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 숙박시설로 11층 이상인 것
+② 지하가로 연면적이 1000 m² 이상인 것
+③ 판매시설로 수용인원이 300인 이상인 것
+④ 복합건축물로 연면적 5000 m² 이상인 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 나무껍질 500kg
+② 가연성고체류 2000kg
+③ 목재가공품 15m³
+④ 가연성액체류 3m³</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 화재조사 활동
+② 응원출동의 요청방법
+③ 소방교육 및 응원출동훈련
+④ 응원출동대상지역 및 규모</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"고압이라 함은 직류는 (가) V를, 교류는 (나) V를 초과하고 (다) kV 이하인 것을 말한다. "의 문장에서 괄호안에 들어갈 내용으로 옳은 것은?(관련 규정 개정전 문제)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 가용절연물을 이용한 방식
+② 줄열을 이용한 방식
+③ 바이메탈의 반전을 이용한 방식
+④ 금속의 팽창계수차를 이용한 방식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반전기사업자로부터 특별고압 또는 고압으로 수전하는 비상전원수전설비의 형식 중 틀린 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 상용전원으로부터 전력의 공급이 중단된 때에는 자동으로 비상전원으로부터 전력을 공급받도록 할 것
+② 비상콘센트설비를 유효하게 10분 이상 작동실킬 수 있는 용량으로 할 것
+③ 점검이 편리하고 화재 및 침수 등의 재해로인한 피해를 받을 우려가 없는 곳에 설치할 것
+④ 비상전원을 실내에 설치하는 때에는 그 실내에 비상조명 등을 설치할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 30분, 20mcd/m²
+② 30분, 7mcd/m²
+③ 60분, 20mcd/m²
+④ 60분, 7mcd/m²</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>축광유도표지의 표지면의 휘도는 주위조도 01x에서 몇 분간 발광 후 몇 mcd/m² 이상이어야 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 감지기는 천장 또는 반자의 옥내에 면하는 부분에 설치 할 것
+② 차동식분포형의 것을 제외하고 감지기는 실내로의 공기유입구로부터 1.5m 이상 떨어진 위치에 설치할 것
+③ 정온식감지기는 주방 · 보일러실 등으로서 다량의 화기 를 취급하는 장소에 설치하되, 공칭작동온도가 주위온도 보다 10℃ 이상 높은 것으로 설치할 것
+④ 스포트형감지기는 45˚ 이상 경사되지 아니하도록 부착할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상방송설비에 사용되는 확성기는 각층마다 설치하되 그 층의 각 부분으로부터 하나의 확성기까지의 수평거리는 최대 몇 m 이하인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15276a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 0.2
+② 1.0
+③ 1.5
+④ 2.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>누전경보기의 화재안전기준에서 변류기의 설치위치 기준으로 옳은 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15279a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 감광율 5%/m 미만
+② 감광율 10%/m 미만
+③ 감광율 15%/m 미만
+④ 감광율 20%/m 미만</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>할로겐화합물 소화약제의 구성 원소가 아닌 것은?</t>
+  </si>
+  <si>
+    <t>제1인산암모늄이 주성분인 분말 소화약제는?</t>
+  </si>
+  <si>
+    <t>다음 중 방염대상물품이 아닌 것은?</t>
+  </si>
+  <si>
+    <t>공기 중에서 연소상한값이 가장 큰 물질은?</t>
+  </si>
+  <si>
+    <t>제2류 위험물에 해당하지 않는 것은?</t>
+  </si>
+  <si>
+    <t>다음 물질 중 공기에서 위험도(H)가 가장 큰 것은?</t>
+  </si>
+  <si>
+    <t>고비점유 화재 시 무상주수하여 가연성 중기의 발생을 억제 함으로써 기름의 연소성을 상실시키는 소화효과는?</t>
+  </si>
+  <si>
+    <t>건축물 화재에서 플래시 오버(Flash over) 현상이 일어나는 시기는?</t>
+  </si>
+  <si>
+    <t>다음 중 인화점이 가장 낮은 물질은?</t>
+  </si>
+  <si>
+    <t>같은 원액으로 만들어진 포의 특성에 관한 설명으로 옳지 않은 것은?</t>
+  </si>
+  <si>
+    <t>물리적 소화방법이 아닌 것은?</t>
+  </si>
+  <si>
+    <t>갑종방화문의 을종방화문의 비차열 성능은 각각 얼마 이상 이어야 하는가?</t>
+  </si>
+  <si>
+    <t>마그네슘의 화재에 주수하였을 때 물과 마그네슘의 반응으 로 인하여 생성되는 가스는?</t>
+  </si>
+  <si>
+    <t>비수용성 유류의 화재 시 물로 소화할 수 없는 이유는?</t>
+  </si>
+  <si>
+    <t>가연물의 종류에 따른 화제의 분류방법 중 유류화재의 나타 내는 것은?</t>
+  </si>
+  <si>
+    <t>건물 내에서 화재가 발생하여 실내온도가 20℃에서 600℃ 까지 상승했다면 온도 상승만으로 건물의 내의 공기 부피는 처음의 약 몇 배 정도 팽창하는가? (단, 화재로 인한 압력의 변화는 없다고 가정한다.)</t>
+  </si>
+  <si>
+    <t>화재의 일반적 특성이 아닌 것은?</t>
+  </si>
+  <si>
+    <t>화재에 대한 건축물의 손실정도에 따른 화재형태를 설명한 것으로 옳지 않은 것은?</t>
+  </si>
+  <si>
+    <t>위험물의 유별에 따른 대표적인 성질의 연결이 옳지 않은 것은?</t>
+  </si>
+  <si>
+    <t>60Hz의 3상 전압을 전파정류하면 맥동주파수는?</t>
+  </si>
+  <si>
+    <t>제어요소의 구성으로 옳은 것은?</t>
+  </si>
+  <si>
+    <t>제어량에 따라 분류되어 자동제어로 옳은 것은?</t>
+  </si>
+  <si>
+    <t>온도보상장치에 사용되는 소자인 NCT형 서미스터의 저항값 과 온도의 관계를 옳게 설명한 것은?</t>
+  </si>
+  <si>
+    <t>반지름 1m 인 원형 코일에서 중심점에서의 자계의 세기가 1AT/m 라면 흐르는 전류는 몇 A 인가?</t>
+  </si>
+  <si>
+    <t>조작량(manipulated varible)은 제어요소에서 무엇에 인가되 는 양인가?</t>
+  </si>
+  <si>
+    <t>전원을 넣자마자 곧바로 점등되는 형광등용의 안정기는?</t>
+  </si>
+  <si>
+    <t>다음 중 3상 유도전동기에 속하는 것은?</t>
+  </si>
+  <si>
+    <t>확산형 트랜지스터에 관한 설명으로 옳지 않은 것은?</t>
+  </si>
+  <si>
+    <t>다음중 직류전동기의 제동법이 아닌 것은?</t>
+  </si>
+  <si>
+    <t>A급 싱글 전력증폭기에 관한 설명으로 옳지 않은 것은?</t>
+  </si>
+  <si>
+    <t>전류계의 오차율 ±2%, 전압게의 오차율 ±1%인 계기로 저 항을 측정하면 저항의 오차율은 몇 %인가?</t>
+  </si>
+  <si>
+    <t>다음 그림을 논리식으로 표현한 것은?</t>
+  </si>
+  <si>
+    <t>지멘스(siemens)는 무엇의 단위인가?</t>
+  </si>
+  <si>
+    <t>소방시설공사업의 상호ㆍ영업소 소재지가 변경된 경우 제출 하여야 하는 서류는?</t>
+  </si>
+  <si>
+    <t>소방기술자의 자격의 정지 및 취소에 관한 기준 중 1차 행 정처분기준이 자격정지 1년 해당 되는 경우는?</t>
+  </si>
+  <si>
+    <t>소방본부장 또는 소장서장이 원활한 소방 활동을 위하여 행 하는 지리 조사의 내용에 속하지 않은 것은?</t>
+  </si>
+  <si>
+    <t>소방시설 중 연결살수설비는 어떤 설비에 속하는가?</t>
+  </si>
+  <si>
+    <t>소방시설관리업 등록의 결격사유에 해당되지 않은 것은?</t>
+  </si>
+  <si>
+    <t>다음 중 위험물의 성질이 자기반응성 물질에 속하지 않은 것은?</t>
+  </si>
+  <si>
+    <t>소방기본법상 화재의 예방조치 명령이 아닌 것은?</t>
+  </si>
+  <si>
+    <t>방염성능기준 이상의 실내장식물 등을 설치하여야 하는 특 정소방대상물에 해당하지 않은 것은?</t>
+  </si>
+  <si>
+    <t>형식승인대상 소방용품에 해당하지 않은 것은?</t>
+  </si>
+  <si>
+    <t>화재예방강화지구구에 대한 화재안전조사권자는 누구인가?</t>
+  </si>
+  <si>
+    <t>다음 중 특수가연물에 해당 하지 않는 것은?</t>
+  </si>
+  <si>
+    <t>점포에서 위험물을 용기에 담아 판매하기 위하여 위험물을 취급하는 판매취급소는 위험물안전관리법상 지정수량의 몇 배 이하의 위험물까지 취급할 수 있는가?</t>
+  </si>
+  <si>
+    <t>소방안전관리자가 작성하는 소방계획서의 내용에 포함되지 않는 것은?</t>
+  </si>
+  <si>
+    <t>소방시설 중 화재를 진압하거나 인명구조활동을 위하여 사 용하는 설비로 정의되는 것은?</t>
+  </si>
+  <si>
+    <t>다음 비상전원 및 배터리 중 최소용량이 가장 큰 것은?</t>
+  </si>
+  <si>
+    <t>비상경보설비함 상부에 설치하는 발신기 위치표시등의 불빛 은 부착지점으로부터 몇 m이내 떨어진 위치에서 쉽게 식별 할 수 있어야 하는가?</t>
+  </si>
+  <si>
+    <t>P형 1급 발신기에 연결해야 하는 회선은?</t>
+  </si>
+  <si>
+    <t>누전경보기의 기능검사 항목이 아닌 것은?</t>
+  </si>
+  <si>
+    <t>휴대용비상조명등의 설치기준으로 옳지 않은 것은?</t>
+  </si>
+  <si>
+    <t>비상콘센트설비의 전원공급회로의 설치기준으로 옳지 않은 것은?</t>
+  </si>
+  <si>
+    <t>비상방송설비의 설치기준으로 옳지않은 것은?</t>
+  </si>
+  <si>
+    <t>자동화재탐지설비에 있어서 지하구의 경우 하나의 경계구역 의 길이는?</t>
+  </si>
+  <si>
+    <t>무선통신보조설비에 사용되는 용어의 설명이 틀린 것은?</t>
+  </si>
+  <si>
+    <t>누전경보기의 수신부는 그 정격전압에서 최소 몇 회의 누전 작동 반복시험을 실시하는 경우 구보 및 기능에 이상이 생 기지 않아야 하는가?</t>
+  </si>
+  <si>
+    <t>피난기구의 설치기준으로 옳지 않은 것은?</t>
+  </si>
+  <si>
+    <t>열전대식 감지기의 구성요소가 아닌 것은?</t>
+  </si>
+  <si>
+    <t>부착높이가 15m 이상 20m미만에 적응성이 있는 감지기가 아닌 것은?</t>
+  </si>
+  <si>
+    <t>비상콘센트 풀 박스 등의 두께의 최소 몇 mm이상의 철판을 사용하여야 하는가?</t>
+  </si>
+  <si>
+    <t>다음 ( ㉠ ), ( ㉡ )에 들어갈 내용으로 옳은 것은?</t>
+  </si>
+  <si>
+    <t>① 염소
+② 브롬
+③ 네온
+④ 탄소</t>
+  </si>
+  <si>
+    <t>① 1종 분말소화약제
+② 2종 분말소화약제
+③ 3종 분말소화약제
+④ 4종 분말소화약제</t>
+  </si>
+  <si>
+    <t>① 카펫
+② 무대용 합판
+③ 창문에 설치하는 커튼
+④ 두께 2mm 미만인 종이벽지</t>
+  </si>
+  <si>
+    <t>① 아세틸렌
+② 수소
+③ 가솔린
+④ 프로판</t>
+  </si>
+  <si>
+    <t>① 유황
+② 황화린
+③ 적린
+④ 황린</t>
+  </si>
+  <si>
+    <t>① 에테르
+② 수소
+③ 에틸렌
+④ 프로판</t>
+  </si>
+  <si>
+    <t>① 억제효과
+② 제거효과
+③ 유화효과
+④ 파괴효과</t>
+  </si>
+  <si>
+    <t>① 초기에서 성장기로 넘어가는 시기
+② 성장에서 최성기로 넘어가는 시기
+③ 최성기에서 감쇠기로 넘어가는 시기
+④ 감쇠기에서 종기로 넘어가는 시기</t>
+  </si>
+  <si>
+    <t>① 경유
+② 메틸알코올
+③ 이황화탄소
+④ 등유</t>
+  </si>
+  <si>
+    <t>① 발포배율이 커지면 환원시간은 짧아진다.
+② 환원시간이 길면 내열성이 떨어진다.
+③ 유동성이 좋으면 내열성이 떨어진다.
+④ 발포배율이 작으면 유동성이 떨어진다.</t>
+  </si>
+  <si>
+    <t>① 갑종 : 90분, 을종 : 40분
+② 갑종 : 60분, 을종 : 30분
+③ 갑종 : 45분, 을종 : 20분
+④ 갑종 : 30분, 을종 : 10분</t>
+  </si>
+  <si>
+    <t>① 산소
+② 수소
+③ 일산화탄소
+④ 이산화탄소</t>
+  </si>
+  <si>
+    <t>① 인화점이 변하기 때문
+② 발화점이 변하기 때문
+③ 연소면이 확대되기 때문
+④ 수용성으로 변하여 인화점이 상승하기 때문</t>
+  </si>
+  <si>
+    <t>① A급 화재
+② B급 화재
+③ C급 화재
+④ D급 화재</t>
+  </si>
+  <si>
+    <t>① 3
+② 9
+③ 15
+④ 30</t>
+  </si>
+  <si>
+    <t>① 확대성
+② 정형성
+③ 우발성
+④ 불안정성</t>
+  </si>
+  <si>
+    <t>① 제1류 : 산화성 고체
+② 제2류 : 가연성 고체
+③ 제4류 : 인화성 액체
+④ 제5류 : 산화성 액체</t>
+  </si>
+  <si>
+    <t>① 120Hz
+② 240Hz
+③ 360Hz
+④ 720Hz</t>
+  </si>
+  <si>
+    <t>① 30°
+② 45°
+③ 50°
+④ 60°</t>
+  </si>
+  <si>
+    <t>① 검출부와 비교부
+② 조작부와 검출부
+③ 검출부와 조절부
+④ 조작부와 조절부</t>
+  </si>
+  <si>
+    <t>① 50
+② 100
+③ 150
+④ 200</t>
+  </si>
+  <si>
+    <t>① 정치(fixed value)제어
+② 비율(ration)제어
+③ 프로세스(process)제어
+④ 시퀸스(sequence)제어</t>
+  </si>
+  <si>
+    <t>① 저항값은 온도에 비례한다.
+② 저항값은 온도에 반비례한다.
+③ 저항값은 온도의 제곱에 비례한다.
+④ 저항값은 온도의 제곱에 반비례한다.</t>
+  </si>
+  <si>
+    <t>① 조작대상
+② 제어대상
+③ 측정대상
+④ 입력대상</t>
+  </si>
+  <si>
+    <t>① 글로우 스타트식
+② 필라멘트 단락식
+③ 래피드 스타트식
+④ 점등관식</t>
+  </si>
+  <si>
+    <t>① 권선형 유동전동기
+② 세이딩코일형 전동기
+③ 뷴상기동형 전동기
+④ 콘텐서기동형 전동기</t>
+  </si>
+  <si>
+    <t>① 불활성 가스 속에서 확산시킨다.
+② 단일 확산형과 2중 확산형이다.
+③ 이미터, 베이스의 순으로 확산시킨다.
+④ 기체반도체가 용해하는 것보다 낮은 온도에서 불순불을 확산시킨다.</t>
+  </si>
+  <si>
+    <t>① 19.2
+② 20.3
+③ 21.6
+④ 22.6</t>
+  </si>
+  <si>
+    <t>① 펠티에 효과
+② 제벡 효과
+③ 톰슨 효과
+④ 홀 효과</t>
+  </si>
+  <si>
+    <t>① 회생제동
+② 정상제동
+③ 발전제동
+④ 역전제동</t>
+  </si>
+  <si>
+    <t>① 바이어스점은 부하선이 거의 가운데인 중앙점에 취한다.
+② 회로의 구성이 매우 복잡하다.
+③ 출력용의 트랜지스터가 1개이다.
+④ 찌그러짐이 적다.</t>
+  </si>
+  <si>
+    <t>① ±0.5%
+② ±1%
+③ ±3%
+④ ±7%</t>
+  </si>
+  <si>
+    <t>① X(Y+Z)
+② XYZ
+③ XY+ZY
+④ (X+Y)(X+Z)</t>
+  </si>
+  <si>
+    <t>① 접기계전기
+② 영상변류기
+③ 계기용변압기
+④ 과전류계전기</t>
+  </si>
+  <si>
+    <t>① 비저항
+② 도전률
+③ 컨덕턴스
+④ 자속</t>
+  </si>
+  <si>
+    <t>① 소방기술인력의 자격증 및 자격수첩
+② 소방시설업 등록증 및 등록수첩
+③ 법인등기부등본 및 소방기술인력 연명부
+④ 사업자등록증 및 소방기술인력의 자격증</t>
+  </si>
+  <si>
+    <t>① 자격수첩을 다른 자에게 빌려준 경우
+② 동시에 둘 이상의 업체에 취업한 경우
+③ 거짓이나 그 밖의 부정한 방법으로 자격수첩을 발급받은 경우
+④ 업무수행 중 해당 자격과 관련하여 중대한 과실로 다른 자에게 손해를 입히고 형의 선고를 받은 경우</t>
+  </si>
+  <si>
+    <t>① 소방대상물에 인접한 도로의 폭
+② 소방대상물에 인접한 도로의 교통상황
+③ 소방대상물에 인접한 도로주변의 토지의 고저
+④ 소방대상물에 인접한 지역에 대한 유동인원의 현황</t>
+  </si>
+  <si>
+    <t>① 소화설비
+② 구조설비
+③ 피난설비
+④ 소화활동설비</t>
+  </si>
+  <si>
+    <t>① 2
+② 3
+③ 5
+④ 10</t>
+  </si>
+  <si>
+    <t>① 유기과산화물
+② 무기과산화물
+③ 히드라진 유도체
+④ 니트로화합물</t>
+  </si>
+  <si>
+    <t>① 10배
+② 20배
+③ 30배
+④ 50배</t>
+  </si>
+  <si>
+    <t>① 불장난ㆍ모닥불ㆍ흡연 및 화기 취급의 금지 또는 제한
+② 타고남은 불 또는 화기의 우려가 있는 재의 처리
+③ 함부로 버려두거나 그냥 둔 위험물, 그 밖에 탈 수 있는 물건을 옮기거나 치우게 하는 등의 조치
+④ 불이 번지는 것을 막기 위하여 불이 번질 우려가 있는 소방대상물의 사용 제한</t>
+  </si>
+  <si>
+    <t>① 숙박시설
+② 노유자시설
+③ 층수가 11층 이상의 아파트
+④ 건축물의 옥내에 있는 종교시설</t>
+  </si>
+  <si>
+    <t>① 100만원 이하
+② 200만원 이하
+③ 300만원 이하
+④ 500만원 이하</t>
+  </si>
+  <si>
+    <t>① 소방시설유지업
+② 소방시설설계업
+③ 소방시설공사업
+④ 소방공사감리업</t>
+  </si>
+  <si>
+    <t>① 관창
+② 안전매트
+③ 피난사다리
+④ 가스누설경보기</t>
+  </si>
+  <si>
+    <t>① 시ㆍ도지사
+② 소방본부장ㆍ소방서장
+③ 한국소방안전협회장
+④ 국민안전처장관</t>
+  </si>
+  <si>
+    <t>① 사류 1000kg
+② 면화류 200kg
+③ 나무껍질 및 대팻밥 400kg
+④ 넝마 및 종이부스러기 500kg</t>
+  </si>
+  <si>
+    <t>① 지정수량의 5배 이하
+② 지정수량의 10배 이하
+③ 지정수량의 20배 이하
+④ 지정수량의 40배이하</t>
+  </si>
+  <si>
+    <t>① 소방시설공사 하자의 판단기준에 관한 사항
+② 소방시설ㆍ피난시설 및 방화시설의 점검ㆍ정비계획
+③ 공동 및 분임 소방안전관리에 관한사항
+④ 소화 및 연소 방지에 관한 사항</t>
+  </si>
+  <si>
+    <t>① 소화활동설비
+② 피난설비
+③ 소화용수설비
+④ 소화설비</t>
+  </si>
+  <si>
+    <t>① 지하층을 제외한 11층 미만의 유도등 비상전원
+② 비상조명등의 비상전원
+③ 휴대용지상조명등의 충전식 배터리용량
+④ 무선통신보조설비 증폭기의 비상전원</t>
+  </si>
+  <si>
+    <t>① 5
+② 10
+③ 15
+④ 20</t>
+  </si>
+  <si>
+    <t>① 단락전압시험
+② 절연저항시험
+③ 온도특성시험
+④ 단락전류강도시험</t>
+  </si>
+  <si>
+    <t>① 숙박시설 또는 다중이용업소에는 객실 또는 영업장 안의 구획된 실마다 잘 보이는 곳에 1개 이상 설치
+② 대규모점포에는 보행거리 30m이내 마다 2개이상 설치
+③ 영화상영관에는 보행거리 50m이내 마다 3개이상 설치
+④ 지하역사에는 보행거리 25m이내 마다 3개 이상 설치</t>
+  </si>
+  <si>
+    <t>① 전용분전반
+② 공용분전반
+③ 전용큐비클식
+④ 공용큐비클식</t>
+  </si>
+  <si>
+    <t>① 전원회로는 단상 교류 220V인 것으로 한다.
+② 전원회로의 공급용량은 1.5kVA 이상의 것으로 한다.
+③ 전원회로는 주배전반에서 전용회로로 한다.
+④ 하나의 전용회로에 설치하는 비상콘센트는 10개 이상으 로 한다.</t>
+  </si>
+  <si>
+    <t>① 음량조정기의 배선은 3선식으로 할 것
+② 확성기 음성입력은 5W 이상일 것
+③ 다른 전기회로에 따라 유도장애가 생기지 아니하도록 할 것
+④ 조작스위치는 바닥으로부터 0.8m 이상 1.5m이하의 높이 에 설치할 것</t>
+  </si>
+  <si>
+    <t>① 700m 이하
+② 800m 이하
+③ 900m 이하
+④ 1000m 이하</t>
+  </si>
+  <si>
+    <t>① 1.5
+② 4.0
+③ 100
+④ 300</t>
+  </si>
+  <si>
+    <t>① 1만회
+② 2만회
+③ 3만회
+④ 5만회</t>
+  </si>
+  <si>
+    <t>① 25m
+② 50m
+③ 100m
+④ 150m</t>
+  </si>
+  <si>
+    <t>① 열전대
+② 미터릴레이
+③ 접속전선
+④ 공기관</t>
+  </si>
+  <si>
+    <t>① 5
+② 15
+③ 25
+④ 35</t>
+  </si>
+  <si>
+    <t>① 이온화식 1종 감지기
+② 연기복합형감지기
+③ 불꽃감지기
+④ 차동식분포형감지기</t>
+  </si>
+  <si>
+    <t>① 1.2mm
+② 1.5mm
+③ 1.6mm
+④ 20.mm</t>
+  </si>
+  <si>
+    <t>① 연쇄반응의 억제에 의한 방법
+② 냉각에 의한 방법
+③ 공기와의 접촉 차단에 의한 방법
+④ 가연물 제거에 의한 방법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>① 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>π</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/w
+② 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>π</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/w
+③ w2/2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>π</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+④ 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>π</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>f2</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 3000
+② 4500
+③ 9000
+④ 12000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화재하중 계산 시 목재의 단위발열량은 약 몇 kcal/kg 인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>그림과 같은 정현파에서 v=Vm(sin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>ω</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>t+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>θ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>)의 주기를 T로 옳은 것은?</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15421a</t>
+  </si>
+  <si>
+    <t>i=Im sinwt인 정현파에서 순시값과 실효값이 같아지는 위상은 몇 도인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그림과 같이 전압계 V₁ , V₂ , V₃ 와 5Ω의 저항 R을 접속하였다. 전압계의 지시가 V₁ =20V, V₂ =40V, V₃ =50V 라면 부하전력은 몇 W인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15425a</t>
+  </si>
+  <si>
+    <t>① 1
+② 2
+③ 3
+④ 4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전압변동율이 25%인 정류회로에서 무부하 전압이 24V인 경우 부하 전압은 몇 V인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>두 종류의 금속으로 폐회로를 만들어 전류를 흘리면 양 접 속점에서 한 쪽은 온도가 올라가고 다른 쪽은 온도가 내려가는 현상은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15438a</t>
+  </si>
+  <si>
+    <t>전기화재의 원인이 되는 누전전류를 검출하기 위해 사용되 는것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제4류 위험물 제조소의 경우 사용전압이 22kV인 특고압 가공전선이 지니갈 때 제조소의 외벽과 가공전선 사이의 수평 거리(안전거리)는 몇 m 이상이어야 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반음식점에서 조리를 위해 불을 사용하는 설비를 설치할 때 지켜야 할 사항의 기준으로 옳지 않은 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 주방시설에는 동물 또는 식물의 기름을 제거할 수 있는 필터 등을 설치할 것
+② 열을 발생하는 조리기구는 반자 또는 선반에서 50cm 이 상 떨어지게 할 것
+③ 주방시설에 부속된 배기덕트는 0.5mm 이상의 아연도금 강판 또는 이와 동등 이상의 내식성 불연재료로 설치할 것
+④ 열을 발생하는 조리기구로 부터 15cm 이내의 거리에 있 는 가연성 주요구조부터는 석면판 또는 단열성이 있는 불연재료로 덮어 씌울 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지정수량의 몇 배 이상의 위험물을 취급하는 제조소에는 화재예방을 윈한 예방규정을 정하여야 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정소방대상물의 관계인이 피난시설 또는 방화시설의 폐쇄 ㆍ훼손ㆍ변경 등의 행위를 했을 때 과태료 처분으로 옳은 것은?(관련규정 개정으로 정답이 바뀌었습니다. 시험 출제당 시 기존 정답은 2번이었습니다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소방시설공사업법상 소방시설공사에 관한 발주자의 권한을 대행하여 소방시설공사가 설계도서 및 관계 법령에 따라 적법하게 시공되는지 여부의 확인과 품질ㆍ시공 관리에 대한 기술지도를 수행하는 영업은 무엇인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소방기존법상 5년 이하의 징역 또는 3천만원 이하의 벌금에 해당하는 위반사항이 아닌 것은?(관련 규정 개정전 문제로 여기서는 기존 정답인 3번을 누르면 정답 처리됩니다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 정당한 사유 없이 소방용수시설을 사용하거나 소방용수 시설의 효용을 해하거나 그 정당한 사용을 방해한 자
+② 화재현장에서 사람을 구출하는 일 또는 불을 끄거나 불이 번지지 아니하도록 하는 일을 방해한 자
+③ 불이 번질 우려가 있는 소방대상물 및 토지를 일시적으로 사용하거나 그 사용의 제한 또는 소방활동에 필요한 처분을 방해한 자
+④ 화재 진압을 위하여 출동하는 소방자동차의 출동을 방해 한 자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 지구선, 공통선, 소화선, 전화선
+② 지구선, 공통선, 응답선, 전화선
+③ 지구선, 공통선, 발신기선, 응답선
+④ 신호선, 공통선, 발신기선, 응답선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 1시간 이내
+② 2시간 이내
+③ 3시간 이내
+④ 5시간 이내</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화재속보설비 속보기의 예비전원에 대한 안전장치시험 을 할 경우 1/5C이상 1C이하의 전류로 역충전하는 경우 안전장치가 작동해야 하는 시간의 기준은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소방회로용으로 수전설비, 변전설비, 그 밖의 기기 및 배선을 금속제 외함에 수납한 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무선통신보조설비의 누설동축케이블 및 공중선은 고압의 전로로부터 몇 m 이상 떨어진 위치에 설치해야 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화재탐지설비의 발신기는 건축물의 각 부분으로부터 하나의 발신기까지 수평거리는 최대 몇 m 이하인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 숙박시설ㆍ노유자시설 및 의료시설은 그 층의 바닥면적 500m² 마다 1개 이상 설치
+② 계단실형 아파트이 경우는 각 층마다 1개 이상 설치
+③ 복합용도의 층은 그 층의 바닥면적 800m² 머더 1개 이 상 설치
+④ 주택법 시행령 제48조으 따른 아파트의 경우 하나의 관 리주체가 관리하는 아파트 구역마다 공기안전매트 1개 이상 설치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>누전경보기의전원은 분전반으로부터 전용회로로 하고 각 극에는 최대 몇 A 이하의 과전류 차단기를 설치해야 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① ㉠ 30분, ㉡ 30분
+② ㉠ 30분, ㉡ 10분
+③ ㉠ 60분, ㉡ 60분
+④ ㉠ 60분, ㉡ 10분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15480a</t>
+  </si>
+  <si>
+    <t>① 부분소 화재란 전소화재, 반소화재에 해당하지 않는 것을 말한다.
+② 반소화재란 건축물에 화재가 발생하여 건축물의 30%이상 70%미만 소실된 상태를 말한다.
+③ 전소화재란 건축물에 화재가 발생하여 건축물의 70%이상이 소실된 상태를 말한다.
+④ 훈소화재란 건축물에 화재가 발생하여 건물물의 10%이하가 소실된 상태를 말한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 금치산자
+② 한정치산자
+③ 소방시설관리업의 등록의 취소된 날로 부터 2년이 지난 자
+④ 금고 이상의 형의 집행유예를 선고 받고 그 유예기간 중에 있는자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 분파기 : 임피던스 매칭과 신호 균등분배를 위해 사용하는 장치
+② 혼합기 : 두 개 이상의 입력신호를 원하는 비율로 조합한 출력이 발생하도록 하는 장치
+③ 증폭기 : 신호 전송 시 신호가 약해져 수신이 불가능해지는 것을 방지하기 위해서 증폭하는 장치
+④ 누설동축케이블 : 동축케이블의 외부도체에 가느다란 홈을 만들어서 전파기 외부로 새어나갈 수 있도록 한 케이블</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반적인 자연발화의 방지법으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>위험물안전관리법령상 제4류 위험물의 화재에 적응성이 있는 것은?</t>
+  </si>
+  <si>
+    <t>화학적 소화방법에 해당하는 것은?</t>
+  </si>
+  <si>
+    <t>목조건축물에서 발생하는 옥외출화 시기를 나타낸 것으로 옳 은 것은?</t>
+  </si>
+  <si>
+    <t>무창층 여부를 판단하는 개구부로서 갖추어야 할 조건으로 옳은 것은?</t>
+  </si>
+  <si>
+    <t>건물화재 시 패닉(panic)의 발생원인과 직접적인 관계가 없는 것은?</t>
+  </si>
+  <si>
+    <t>공기 중에서 수소의 연소범위로 옳은 것은?</t>
+  </si>
+  <si>
+    <t>가연성가스나 산소의 농도를 낮추어 소화하는 방법은?</t>
+  </si>
+  <si>
+    <t>이산화탄소(CO2)에 대한 설명으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>분말 소화약제 중 A급, B급, C급 화재에 모두 사용할 수 있 는 것은?</t>
+  </si>
+  <si>
+    <t>증기비중의 정의로 옳은 것은? (단, 보기에서 분자, 분모의 단위는 모두 g/mol 이다.)</t>
+  </si>
+  <si>
+    <t>화재발생 시 건축물의 화재를 확대시키는 주요인이 아닌 것 은?</t>
+  </si>
+  <si>
+    <t>위험물안전관리법령상 위험물 유별에 따른 성질이 잘못 연 결된 것은?</t>
+  </si>
+  <si>
+    <t>가연성 가스가 아닌 것은?</t>
+  </si>
+  <si>
+    <t>화재 최성기 때의 농도로 유도등이 보이지 않을 정도의 연 기농도는? (단, 감광계수로 나타낸다.)</t>
+  </si>
+  <si>
+    <t>황린의 보관 방법으로 옳은 것은?</t>
+  </si>
+  <si>
+    <t>공기 중의 산소의 농도는 약 몇 vol% 인가?</t>
+  </si>
+  <si>
+    <t>제거소화의 예가 아닌 것은?</t>
+  </si>
+  <si>
+    <t>제2종 분말 소화약제가 열분해되었을 때 생성되는 물질이 아닌 것은?</t>
+  </si>
+  <si>
+    <t>저항 6 Ω 과 유도리액턴스 8 Ω 이 직렬로 접속된 회로에 100V의 교류전압을 가할 때 흐르는 전류의 크기는 몇 A인 가?</t>
+  </si>
+  <si>
+    <t>다음과 같은 블록선도의 전달 함수는?</t>
+  </si>
+  <si>
+    <t>콘덴서와 정전유도에 관한 설명으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>그림과 같은 브리지 회로의 평형조건은?</t>
+  </si>
+  <si>
+    <t>작동 신호를 조작량으로 변환하는 요소이며, 조절부와 조작 부로 이루어진 것은?</t>
+  </si>
+  <si>
+    <t>어떤 측정계기의 참값을 T, 지시값을 M 이라 할 때 보정율 과 오차율이 옳은 것은?</t>
+  </si>
+  <si>
+    <t>R=9 Ω, XL = 10 Ω, XC = 5 Ω 인 직렬부하회로에 220V 의 정현파 전압을 인가시켰을 때의 유효 전력은 약 몇 kW 인가?</t>
+  </si>
+  <si>
+    <t>금속이나 반도체에 압력이 가해진 경우 전기저항이 변화하 는 성질을 이용한 압력센서는?</t>
+  </si>
+  <si>
+    <t>변압기의 내부고장 보호에 사용되는 계전기는 다음 중 어느 것인가?</t>
+  </si>
+  <si>
+    <t>알칼리 축전지의 음극 재료는?</t>
+  </si>
+  <si>
+    <t>PNPN 4층 구조로 되어 있는 사이리스터 소자가 아닌 것은?</t>
+  </si>
+  <si>
+    <t>미지의 임의 시간적 변화를 목표값에 제어량을 추종시키는 것을 목적으로 하는 제어는?</t>
+  </si>
+  <si>
+    <t>무한장 솔레노이드 자계의 세기에 대한 설명으로 틀린 것 은?</t>
+  </si>
+  <si>
+    <t>저항 R1 , R2 와 인덕턴스 L이 직렬로 연결된 회로에서 시 정수[sec] 는?</t>
+  </si>
+  <si>
+    <t>아날로그와 디지털 통신에서 데시벨의 단위로 나타내는 SN 비를 올바르게 풀어 쓴 것은?</t>
+  </si>
+  <si>
+    <t>분류기를 써서 배율을 9로 하기 위한 분류기의 저항은 전류 계 내부저항의 몇 배인가?</t>
+  </si>
+  <si>
+    <t>전지의 자기 방전을 보충함과 동시에 상용 부하에 대한 전 력 공급은 충전기가 부담하도록 하되, 충전기가 부담하기 어려운 일시적인 내전류 부하는 축전지로 하여금 부담하게 하는 충전방식은?</t>
+  </si>
+  <si>
+    <t>그림과 같은 R-C 필터회로에서 리플 함유율을 가장 효과적 으로 줄일 수 있는 방법은?</t>
+  </si>
+  <si>
+    <t>그림과 같은 릴레이 스퀀스회로의 출력식을 간략화한 것은?</t>
+  </si>
+  <si>
+    <t>특정소방대상물의 관계인이 소방안전관리자를 해임한 경우 재선임 신고를 해야 하는 기준은? (단, 해임한 날부터를 기 준일로 한다.)</t>
+  </si>
+  <si>
+    <t>시·도지사가 설치하고 유지·관리하여야 하는 소방용수시설이 아니 것은?</t>
+  </si>
+  <si>
+    <t>( )안의 내용으로 알맞은 것은?</t>
+  </si>
+  <si>
+    <t>소방시설공사업자의 시공능력평가 방법에 대한 설명 중 틀 린 것은?</t>
+  </si>
+  <si>
+    <t>소방시설의 자체점검에 관한 설명으로 옳지 않은 것은?</t>
+  </si>
+  <si>
+    <t>소방시설공사의 착공신고 시 첨부서류가 아닌 것은?</t>
+  </si>
+  <si>
+    <t>시·도의 조례가 정하는 바에 따라 지정수량 이상의 위험물 을 임시로 저장·취급할 수 있는 기간 (㉠)과 임시저장 승인 권자 (㉡)는?</t>
+  </si>
+  <si>
+    <t>연면적이 500m2 이상인 위험물 제조소 및 일반취급소에 설 치하여야 하는 경보설비는?</t>
+  </si>
+  <si>
+    <t>소방서의 종합상황실 실장이 서면 모사전송 또는 컴퓨터통 신 등으로 소방본부의 종합상황실에 보고하여야 하는 화재 가 아닌 것은?</t>
+  </si>
+  <si>
+    <t>소방시설업의 등록권자로 옳은 것은?</t>
+  </si>
+  <si>
+    <t>제3류 위험물 중 금수성 물품에 적응성이 있는 소화약제는?</t>
+  </si>
+  <si>
+    <t>소방시설관리업의 등록을 반드시 취소해야 하는 사유에 해 당하지 않는 것은?</t>
+  </si>
+  <si>
+    <t>가연성가스를 저장·취급하는 시설로서 1급 소방안전관리대 상물의 가연성가스 저장·취급 기준으로 옳은 것은?</t>
+  </si>
+  <si>
+    <t>소방기본법상 소방용수시설·소화기구 및 설비등의 설치명령 을 위반한 자의 과태료는?</t>
+  </si>
+  <si>
+    <t>방염처리업의 종류가 아닌 것은?</t>
+  </si>
+  <si>
+    <t>자동화재탐지설비를 설치하여야 하는 특정소방 대상물의 기 준으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>소방용수시설 저수조의 설치기준으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>화재현장에서 피난 등을 체험할 수 있는 소방체험관의 설립 · 운영권자는?</t>
+  </si>
+  <si>
+    <t>공동 소방안전관리자를 선임하여야 할 특정 소방대상물의 기준으로 틀린 것은?(2021년 11월 30일 개정된 규정 적용 됨)</t>
+  </si>
+  <si>
+    <t>종합정밀점검의 경우 점검인력 1단위가 하루 동안 점검할 수 있는 특정소방대상물의 연면적 기준으로 옳은 것은?</t>
+  </si>
+  <si>
+    <t>비상방송설비의 특징에 대한 설명으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>자동화재탐지설비의 수신기 설치기준에 관한 사항 중, 최소 몇 층 이상의 특정소방대상물에는 발신기와 전화통화가 가 능한 수신기를 설치하여야 하는가?</t>
+  </si>
+  <si>
+    <t>지하층을 제외한 층수가 11층 이상의 층에서 피난층에 이르 는 부분의 소방시설에 있어 비상 전원을 60분 이상 유효하 게 작동시킬 수 있는 용량으로 하여야 하는 설비들로 옳게 나열된 것은?</t>
+  </si>
+  <si>
+    <t>화재안전기준에서 정하고 있는 연기감지기를 설치하지 않아 도 되는 장소는?</t>
+  </si>
+  <si>
+    <t>누전경보기의 수신부 설치 제외 장소로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>상용전원이 서로 다른 소방시설은?</t>
+  </si>
+  <si>
+    <t>노유자시설로서 바닥면적이 몇 m2 이상인 층이 있는 경우에 자동화재속보설비를 설치하는가?</t>
+  </si>
+  <si>
+    <t>절연저항시험에 관한 기준에서 ( )에 알맞은 것은?</t>
+  </si>
+  <si>
+    <t>축광표지의 식별도시험에 관련한 기준에서 ( )에 알맞은 것 은?</t>
+  </si>
+  <si>
+    <t>환경상태가 현저하게 고온으로 되어 연기감지기를 설치할 수 없는 건조실 또는 살균실 등에 적응성 있는 열감지기가 아닌 것은?</t>
+  </si>
+  <si>
+    <t>누전경보기의 화재안전기준에서 규정한 용어, 설치방법, 전 원 등에 관한 설명으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>누전경보기에서 감도조정장치의 조정범위는 최대 몇 mA인 가?</t>
+  </si>
+  <si>
+    <t>자동화재탐지설비의 GP형 수신기에 감지기 회로의 배선을 접속하려고 할 때 경계구역이 15개인 경우 필요한 공통선의 최소 개수는?</t>
+  </si>
+  <si>
+    <t>무선통신보조설비에 대한 설명으로 틀린 것은? 용량은 30분 이상이다.</t>
+  </si>
+  <si>
+    <t>비상방송설비가 기동장치에 의한 화재신고를 수신한 후 필 요한 음량으로 화재발생 상황 및 피난에 유효한 방송이 자 동으로 개시될 때까지의 소요시간은 최대 몇 초 이하인가?</t>
+  </si>
+  <si>
+    <t>지하층으로서 특정소방대상물의 바닥부분 중 최소 몇 면이 지표면과 동일한 경우에 무선통신 보조설비의 설치를 제외 할 수 있는가?</t>
+  </si>
+  <si>
+    <t>무창층의 도매시장에 설치하는 비상조명등용 비상전원은 당 해 비상조명등을 몇 분 이상 유효하게 작동시킬 수 있는 용 량으로 하여야 하는가?</t>
+  </si>
+  <si>
+    <t>청각장애인용 시각경보장치는 천장의 높이가 2m 이하인 경 우 천장으로부터 몇 m 이내의 장소에 설치해야 하는가?</t>
+  </si>
+  <si>
+    <t>신호의 전송로가 분기되는 장소에 설치하는 것으로 임피던 스 매칭과 신호 균등분배를 위해 사용되는 장치는?</t>
+  </si>
+  <si>
+    <t>① 습도를 높일 것
+② 저장실의 온도를 낮출 것
+③ 정촉매 작용을 하는 물질을 피할 것
+④ 통풍을 원활하게 하여 열축적을 방지할것</t>
+  </si>
+  <si>
+    <t>① 옥내소화전설비
+② 옥외소화전설비
+③ 봉상수소화기
+④ 물분무소화설비</t>
+  </si>
+  <si>
+    <t>① 모닥불에 물을 뿌려 소화한다.
+② 모닥불을 모래로 덮어 소화한다.
+③ 유류화재를 할론 1301로 소화한다.
+④ 지하실 화재를 이산화탄소로 소화한다.</t>
+  </si>
+  <si>
+    <t>① 창, 출입구 등에 발염 착화한 때
+② 천장 속, 벽 속 등에서 발염 착화한 때
+③ 가옥 구조에서는 천장면에 발염 착화한 때
+④ 불연 천장인 경우 실내의 그 뒷면에 발염 착화한 때</t>
+  </si>
+  <si>
+    <t>① 개구부 크기가 지름 30cm 의 원이 내접할 수 있는 것
+② 해당 층의 바닥면으로부터 개구부 밑 부분까지의 높이가 1.5m 인 것
+③ 내부 또는 외부에서 쉽게 파괴 또는 개방할 수 있을 것
+④ 창에 방범을 위하여 40cm 간격으로 창살을 설치한 것</t>
+  </si>
+  <si>
+    <t>① 연기에 의한 시계 제한
+② 유독가스에 의한 호흡 장애
+③ 외부와 단절되어 고립
+④ 불연내장재의 사용</t>
+  </si>
+  <si>
+    <t>① 적린
+② 마그네슘 분말
+③ 과염소산칼륨
+④ 유황</t>
+  </si>
+  <si>
+    <t>① 0.4 ~ 4 vol%
+② 1 ~ 12.5 vol%
+③ 4 ~ 75 vol%
+④ 67 ~ 92 vol%</t>
+  </si>
+  <si>
+    <t>① 질식소화
+② 냉각소화
+③ 제거소화
+④ 억제소화</t>
+  </si>
+  <si>
+    <t>① 임계온도는 97.5℃ 이다.
+③ 불연성가스로 공기보다 무겁다.
+④ 상온, 상압에서 기체 상태로 존재한다.</t>
+  </si>
+  <si>
+    <t>① Na CO
+② NH H PO 2 3 4 2 4
+③ KHCO
+④ NaHCO 3 3</t>
+  </si>
+  <si>
+    <t>① 분자량/22.4
+② 분자량/29
+③ 분자량/44.8
+④ 분자량/100</t>
+  </si>
+  <si>
+    <t>① 비화
+② 복사열
+③ 화염의 접촉(접염)
+④ 흡착열에 의한 발화</t>
+  </si>
+  <si>
+    <t>① 제1류 위험물 - 산화성고체
+② 제2류 위험물 - 가연성고체
+③ 제4류 위험물 - 인화성액체
+④ 제6류 위험물 - 자기반응성물질</t>
+  </si>
+  <si>
+    <t>① 일산화탄소
+② 프로판
+③ 수소
+④ 아르곤</t>
+  </si>
+  <si>
+    <t>① 0.1m-1
+② 1m-1
+③ 10m-1
+④ 30m-1</t>
+  </si>
+  <si>
+    <t>① 물 속에 보관
+② 이황화탄소 속에 보관
+③ 수산화칼륨 속에 보관
+④ 통풍이 잘 되는 공기 중에 보관</t>
+  </si>
+  <si>
+    <t>① 10
+② 13
+③ 17
+④ 21</t>
+  </si>
+  <si>
+    <t>① 유류화재 시 다량의 포를 방사한다.
+② 전기화재 시 신속하게 전원을 차단한다.
+③ 가연성가스 화재 시 가스의 밸브를 닫는다.
+④ 산림화재 시 확산을 막기 위하여 산림의 일부를 벌목한 다.</t>
+  </si>
+  <si>
+    <t>① CO
+② H O 2 2</t>
+  </si>
+  <si>
+    <t>① 10
+② 20
+③ 50
+④ 80</t>
+  </si>
+  <si>
+    <t>① G/(1+G)
+② G/(1-G)
+③ 1+G
+④ 1-G</t>
+  </si>
+  <si>
+    <t>① 정전용량이란 콘덴서가 전하를 축적하는 능력을 말한다.
+② 콘덴서에서 전압을 가하는 순간 콘덴서는 단락상태가 된 다.
+③ 정전 유도에 의하여 작용하는 힘은 반발력이다.
+④ 같은 부호의 전하끼리는 반발력이 생긴다.</t>
+  </si>
+  <si>
+    <t>① R C = R C , R R = C L 1 1 2 2 2 3 1
+② R C = R C , R R = C = L 1 1 2 2 2 3 1
+③ R C = R C , R R = C L 1 2 2 1 2 3 1
+④ R C = R C , L=R R C 1 2 2 1 2 3 1</t>
+  </si>
+  <si>
+    <t>① 제어요소
+② 제어대상
+③ 피드백요소
+④ 기준입력요소</t>
+  </si>
+  <si>
+    <t>① 보정율 = (T-M)/T , 오차율 = (M-T)/M
+② 보정율 = (M-T)/M, 오차율 = (T-M)/T
+③ 보정율 = (T-M)/M, 오차율 =(M-T)/T
+④ 보정율 = (M-T)/T, 오차율 = (T-M)/M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 1.98
+② 2.41
+③ 2.77
+④ 4.1
+① 
+② 
+③ 
+④ </t>
+  </si>
+  <si>
+    <t>① 벨로우즈
+② 다이어프램
+③ 가변저항기
+④ 스트레인 게이지</t>
+  </si>
+  <si>
+    <t>① 비율차등 계전기
+② 저전압 계전기
+③ 고전압 계전기
+④ 압력 계전기</t>
+  </si>
+  <si>
+    <t>① 수산화니켈
+② 카드뮴
+③ 이산화연
+④ 연</t>
+  </si>
+  <si>
+    <t>① SCR
+② TRIAC
+③ Diode
+④ GTO</t>
+  </si>
+  <si>
+    <t>① 추종제어
+② 정치제어
+③ 비율제어
+④ 프로그래밍제어</t>
+  </si>
+  <si>
+    <t>① 전류의 세기에 비례한다.
+② 코일의 권수에 비례한다.
+③ 솔레노이드 내부에서의 자계의 세기는 위치에 관계없이 일정한 평등자계이다.
+④ 자계의 방향과 암페어 경로 간에 서로 수직인 경우 자계 의 세기가 최고이다.</t>
+  </si>
+  <si>
+    <t>① SIGN TO NUMBER RATING
+② SIGNAL TO NOISE RATIO
+③ SOURCE NULL RESISTANCE
+④ SOURCE NETWORK RANGE</t>
+  </si>
+  <si>
+    <t>화재 발생 시 주수소화가 적합하지 않은 물질은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -848,6 +2919,20 @@
       <sz val="11"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="161"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
     </font>
   </fonts>
@@ -897,7 +2982,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -924,6 +3009,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1269,7 +3369,7 @@
     <col min="5" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2189,6 +4289,2457 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A83" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18C66A0B-3427-4A38-9BD1-EE9765A72F55}">
+  <dimension ref="A1:D81"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="37" customWidth="1"/>
+    <col min="2" max="2" width="42.19921875" customWidth="1"/>
+    <col min="3" max="3" width="5.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.3984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A3" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C3" s="4">
+        <v>2</v>
+      </c>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A5" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C5" s="4">
+        <v>3</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A6" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A7" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A8" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C8" s="4">
+        <v>3</v>
+      </c>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A9" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C9" s="4">
+        <v>2</v>
+      </c>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A10" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C10" s="4">
+        <v>2</v>
+      </c>
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A11" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C11" s="4">
+        <v>2</v>
+      </c>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A12" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C12" s="4">
+        <v>3</v>
+      </c>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A13" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C13" s="4">
+        <v>3</v>
+      </c>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A14" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C14" s="4">
+        <v>4</v>
+      </c>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="1:4" ht="136.80000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C15" s="4">
+        <v>3</v>
+      </c>
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A16" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C16" s="4">
+        <v>4</v>
+      </c>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" ht="87" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C17" s="4">
+        <v>2</v>
+      </c>
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A18" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1</v>
+      </c>
+      <c r="D18" s="4"/>
+    </row>
+    <row r="19" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C19" s="4">
+        <v>4</v>
+      </c>
+      <c r="D19" s="4"/>
+    </row>
+    <row r="20" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A20" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C20" s="4">
+        <v>2</v>
+      </c>
+      <c r="D20" s="4"/>
+    </row>
+    <row r="21" spans="1:4" s="11" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A21" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="B21" s="10">
+        <v>15220</v>
+      </c>
+      <c r="C21" s="10">
+        <v>3</v>
+      </c>
+      <c r="D21" s="10"/>
+    </row>
+    <row r="22" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A22" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C22" s="4">
+        <v>1</v>
+      </c>
+      <c r="D22" s="4"/>
+    </row>
+    <row r="23" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A23" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B23" s="4">
+        <v>15222</v>
+      </c>
+      <c r="C23" s="4">
+        <v>4</v>
+      </c>
+      <c r="D23" s="4"/>
+    </row>
+    <row r="24" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A24" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C24" s="4">
+        <v>4</v>
+      </c>
+      <c r="D24" s="4"/>
+    </row>
+    <row r="25" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A25" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C25" s="4">
+        <v>1</v>
+      </c>
+      <c r="D25" s="4"/>
+    </row>
+    <row r="26" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A26" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C26" s="4">
+        <v>2</v>
+      </c>
+      <c r="D26" s="4"/>
+    </row>
+    <row r="27" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A27" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C27" s="4">
+        <v>4</v>
+      </c>
+      <c r="D27" s="4"/>
+    </row>
+    <row r="28" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A28" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C28" s="4">
+        <v>2</v>
+      </c>
+      <c r="D28" s="4"/>
+    </row>
+    <row r="29" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A29" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C29" s="4">
+        <v>2</v>
+      </c>
+      <c r="D29" s="4"/>
+    </row>
+    <row r="30" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A30" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C30" s="4">
+        <v>3</v>
+      </c>
+      <c r="D30" s="4"/>
+    </row>
+    <row r="31" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A31" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C31" s="4">
+        <v>1</v>
+      </c>
+      <c r="D31" s="4"/>
+    </row>
+    <row r="32" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A32" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C32" s="4">
+        <v>2</v>
+      </c>
+      <c r="D32" s="4"/>
+    </row>
+    <row r="33" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A33" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C33" s="4">
+        <v>3</v>
+      </c>
+      <c r="D33" s="4"/>
+    </row>
+    <row r="34" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A34" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="C34" s="4">
+        <v>2</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="87" x14ac:dyDescent="0.4">
+      <c r="A35" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C35" s="4">
+        <v>2</v>
+      </c>
+      <c r="D35" s="4"/>
+    </row>
+    <row r="36" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A36" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C36" s="4">
+        <v>1</v>
+      </c>
+      <c r="D36" s="4"/>
+    </row>
+    <row r="37" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A37" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C37" s="4">
+        <v>3</v>
+      </c>
+      <c r="D37" s="4"/>
+    </row>
+    <row r="38" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A38" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C38" s="4">
+        <v>1</v>
+      </c>
+      <c r="D38" s="4"/>
+    </row>
+    <row r="39" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A39" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C39" s="4">
+        <v>1</v>
+      </c>
+      <c r="D39" s="4"/>
+    </row>
+    <row r="40" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A40" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C40" s="4">
+        <v>4</v>
+      </c>
+      <c r="D40" s="4"/>
+    </row>
+    <row r="41" spans="1:4" s="11" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A41" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B41" s="10">
+        <v>15240</v>
+      </c>
+      <c r="C41" s="10">
+        <v>3</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A42" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C42" s="4">
+        <v>4</v>
+      </c>
+      <c r="D42" s="4"/>
+    </row>
+    <row r="43" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A43" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C43" s="4">
+        <v>4</v>
+      </c>
+      <c r="D43" s="4"/>
+    </row>
+    <row r="44" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A44" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C44" s="4">
+        <v>3</v>
+      </c>
+      <c r="D44" s="4"/>
+    </row>
+    <row r="45" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A45" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C45" s="4">
+        <v>2</v>
+      </c>
+      <c r="D45" s="4"/>
+    </row>
+    <row r="46" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A46" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="C46" s="4">
+        <v>4</v>
+      </c>
+      <c r="D46" s="4"/>
+    </row>
+    <row r="47" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A47" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C47" s="4">
+        <v>1</v>
+      </c>
+      <c r="D47" s="4"/>
+    </row>
+    <row r="48" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A48" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C48" s="4">
+        <v>3</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A49" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C49" s="4">
+        <v>3</v>
+      </c>
+      <c r="D49" s="4"/>
+    </row>
+    <row r="50" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A50" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C50" s="4">
+        <v>2</v>
+      </c>
+      <c r="D50" s="4"/>
+    </row>
+    <row r="51" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A51" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C51" s="4">
+        <v>3</v>
+      </c>
+      <c r="D51" s="4"/>
+    </row>
+    <row r="52" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A52" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C52" s="4">
+        <v>3</v>
+      </c>
+      <c r="D52" s="4"/>
+    </row>
+    <row r="53" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A53" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C53" s="4">
+        <v>2</v>
+      </c>
+      <c r="D53" s="4"/>
+    </row>
+    <row r="54" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A54" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C54" s="4">
+        <v>3</v>
+      </c>
+      <c r="D54" s="4"/>
+    </row>
+    <row r="55" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A55" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C55" s="4">
+        <v>3</v>
+      </c>
+      <c r="D55" s="4"/>
+    </row>
+    <row r="56" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A56" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C56" s="4">
+        <v>1</v>
+      </c>
+      <c r="D56" s="4"/>
+    </row>
+    <row r="57" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A57" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="C57" s="4">
+        <v>1</v>
+      </c>
+      <c r="D57" s="4"/>
+    </row>
+    <row r="58" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A58" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C58" s="4">
+        <v>4</v>
+      </c>
+      <c r="D58" s="4"/>
+    </row>
+    <row r="59" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A59" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C59" s="4">
+        <v>2</v>
+      </c>
+      <c r="D59" s="4"/>
+    </row>
+    <row r="60" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A60" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C60" s="4">
+        <v>4</v>
+      </c>
+      <c r="D60" s="4"/>
+    </row>
+    <row r="61" spans="1:4" s="11" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A61" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="C61" s="10">
+        <v>1</v>
+      </c>
+      <c r="D61" s="10"/>
+    </row>
+    <row r="62" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A62" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C62" s="4">
+        <v>1</v>
+      </c>
+      <c r="D62" s="4"/>
+    </row>
+    <row r="63" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A63" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C63" s="4">
+        <v>3</v>
+      </c>
+      <c r="D63" s="4"/>
+    </row>
+    <row r="64" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A64" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="C64" s="4">
+        <v>2</v>
+      </c>
+      <c r="D64" s="4"/>
+    </row>
+    <row r="65" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A65" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C65" s="4">
+        <v>2</v>
+      </c>
+      <c r="D65" s="4"/>
+    </row>
+    <row r="66" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A66" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="C66" s="4">
+        <v>1</v>
+      </c>
+      <c r="D66" s="4"/>
+    </row>
+    <row r="67" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A67" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C67" s="4">
+        <v>3</v>
+      </c>
+      <c r="D67" s="4"/>
+    </row>
+    <row r="68" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A68" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="C68" s="4">
+        <v>4</v>
+      </c>
+      <c r="D68" s="4"/>
+    </row>
+    <row r="69" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A69" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C69" s="4">
+        <v>2</v>
+      </c>
+      <c r="D69" s="4"/>
+    </row>
+    <row r="70" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A70" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C70" s="4">
+        <v>4</v>
+      </c>
+      <c r="D70" s="4"/>
+    </row>
+    <row r="71" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A71" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C71" s="4">
+        <v>4</v>
+      </c>
+      <c r="D71" s="4"/>
+    </row>
+    <row r="72" spans="1:4" ht="191.4" x14ac:dyDescent="0.4">
+      <c r="A72" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C72" s="4">
+        <v>3</v>
+      </c>
+      <c r="D72" s="4"/>
+    </row>
+    <row r="73" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A73" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C73" s="4">
+        <v>3</v>
+      </c>
+      <c r="D73" s="4"/>
+    </row>
+    <row r="74" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A74" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C74" s="4">
+        <v>4</v>
+      </c>
+      <c r="D74" s="4"/>
+    </row>
+    <row r="75" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A75" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C75" s="4">
+        <v>4</v>
+      </c>
+      <c r="D75" s="4"/>
+    </row>
+    <row r="76" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A76" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B76" s="4">
+        <v>15275</v>
+      </c>
+      <c r="C76" s="4">
+        <v>1</v>
+      </c>
+      <c r="D76" s="4"/>
+    </row>
+    <row r="77" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A77" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C77" s="4">
+        <v>2</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A78" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="C78" s="4">
+        <v>2</v>
+      </c>
+      <c r="D78" s="4"/>
+    </row>
+    <row r="79" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A79" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="C79" s="4">
+        <v>2</v>
+      </c>
+      <c r="D79" s="4"/>
+    </row>
+    <row r="80" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A80" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="C80" s="4">
+        <v>3</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A81" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C81" s="4">
+        <v>1</v>
+      </c>
+      <c r="D81" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3745CDB7-6D76-40BD-A4ED-5DCE928E6506}">
+  <dimension ref="A1:D81"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="37.8984375" customWidth="1"/>
+    <col min="2" max="2" width="35.796875" customWidth="1"/>
+    <col min="3" max="3" width="5.59765625" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="1" customFormat="1" ht="16.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A3" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A5" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A6" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A7" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A8" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A9" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A10" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A11" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A12" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A13" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A14" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="87" x14ac:dyDescent="0.4">
+      <c r="A15" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A16" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="87" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A18" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A20" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="13" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A21" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="C21" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A22" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A23" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="C23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A24" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A25" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A26" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A27" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="C27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A28" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A29" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A30" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A31" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A32" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A33" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="C33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A34" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A35" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A36" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="87" x14ac:dyDescent="0.4">
+      <c r="A37" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A38" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="C38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A39" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="C39">
+        <v>4</v>
+      </c>
+      <c r="D39" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A40" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" s="11" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A41" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="C41" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A42" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A43" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A44" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="C44">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A45" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C45">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A46" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="C46">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A47" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="243.6" x14ac:dyDescent="0.4">
+      <c r="A48" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A49" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="C49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A50" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="174" x14ac:dyDescent="0.4">
+      <c r="A51" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C51">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A52" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="C52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="87" x14ac:dyDescent="0.4">
+      <c r="A53" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="C53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="87" x14ac:dyDescent="0.4">
+      <c r="A54" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C54">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="208.8" x14ac:dyDescent="0.4">
+      <c r="A55" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="C55">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A56" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="C56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A57" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="C57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A58" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="C58">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A59" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="C59">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A60" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" s="11" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A61" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="C61" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A62" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="C62">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A63" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="C63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A64" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A65" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="C65">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A66" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A67" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="C67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A68" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="C68">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A69" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="C69">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A70" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="C70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A71" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A72" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="191.4" x14ac:dyDescent="0.4">
+      <c r="A73" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A74" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A75" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A76" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A77" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C77">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A78" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="C78">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A79" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="C79">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A80" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="C80">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A81" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="C81">
+        <v>4</v>
+      </c>
+      <c r="D81" t="s">
+        <v>489</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EA50D89-9007-423F-AC0E-48A3655CC170}">
+  <dimension ref="A1:D79"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="39.69921875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="33.296875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="5.69921875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="10" style="4" customWidth="1"/>
+    <col min="5" max="16384" width="8.796875" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="1" customFormat="1" ht="16.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="87" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A3" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="87" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A5" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A6" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A7" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A8" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A9" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A10" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A11" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A12" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A13" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A14" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A15" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A16" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A18" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A20" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A21" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A22" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A23" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A24" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="87" x14ac:dyDescent="0.4">
+      <c r="A25" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A26" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="87" x14ac:dyDescent="0.4">
+      <c r="A27" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A28" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A29" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A30" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A31" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A32" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A33" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A34" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A35" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A36" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A37" s="4" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A38" s="4" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A39" s="4" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A40" s="4" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A41" s="4" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A42" s="4" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A43" s="4" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A44" s="4" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A45" s="4" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A46" s="4" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A47" s="4" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A48" s="4" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A49" s="4" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A50" s="4" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A51" s="4" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A52" s="4" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A53" s="4" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A54" s="4" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A55" s="4" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A56" s="4" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A57" s="4" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A58" s="4" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A59" s="4" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A60" s="4" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A61" s="4" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A62" s="4" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A63" s="4" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A64" s="4" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A65" s="4" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A66" s="4" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A67" s="4" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A68" s="4" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A69" s="4" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A70" s="4" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A71" s="4" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A72" s="4" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A73" s="4" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A74" s="4" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A75" s="4" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A76" s="4" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A77" s="4" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A78" s="4" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A79" s="4" t="s">
+        <v>569</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/소방설비기사_필기_문제은행.xlsx
+++ b/소방설비기사_필기_문제은행.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5587C42C-5B5D-4E13-AC7C-A664D6E205FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C600692-0BB1-4027-A1C5-50A3C02517A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="3" xr2:uid="{FB57838C-1CAD-4D08-9B84-85A2A61E99B1}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="2" activeTab="4" xr2:uid="{FB57838C-1CAD-4D08-9B84-85A2A61E99B1}"/>
   </bookViews>
   <sheets>
     <sheet name="15년 1회" sheetId="1" r:id="rId1"/>
     <sheet name="15년 2회" sheetId="2" r:id="rId2"/>
     <sheet name="15년 3회" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="4" r:id="rId4"/>
+    <sheet name="16년 1회" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet4" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="651">
   <si>
     <t>문제</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -998,12 +999,6 @@
   </si>
   <si>
     <t>반파 정류 정현파의 최대값이 1일 때, 실효값과 평균값은?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">① 
-② 
-③ 
-④ </t>
   </si>
   <si>
     <t>한 코일의 전류가 매초 150A 의 비율로 변화할 때 다른 코 일에 10V 기전력이 발생하였다면 두 코일 상호 인덕턴스(H) 는?</t>
@@ -2326,6 +2321,12 @@
 ② 2
 ③ 3
 ④ 4</t>
+  </si>
+  <si>
+    <t>① 1
+② 2
+③ 3
+④ 4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2463,9 +2464,6 @@
     <t>화학적 소화방법에 해당하는 것은?</t>
   </si>
   <si>
-    <t>목조건축물에서 발생하는 옥외출화 시기를 나타낸 것으로 옳 은 것은?</t>
-  </si>
-  <si>
     <t>무창층 여부를 판단하는 개구부로서 갖추어야 할 조건으로 옳은 것은?</t>
   </si>
   <si>
@@ -2478,27 +2476,15 @@
     <t>가연성가스나 산소의 농도를 낮추어 소화하는 방법은?</t>
   </si>
   <si>
-    <t>이산화탄소(CO2)에 대한 설명으로 틀린 것은?</t>
-  </si>
-  <si>
     <t>분말 소화약제 중 A급, B급, C급 화재에 모두 사용할 수 있 는 것은?</t>
   </si>
   <si>
     <t>증기비중의 정의로 옳은 것은? (단, 보기에서 분자, 분모의 단위는 모두 g/mol 이다.)</t>
   </si>
   <si>
-    <t>화재발생 시 건축물의 화재를 확대시키는 주요인이 아닌 것 은?</t>
-  </si>
-  <si>
-    <t>위험물안전관리법령상 위험물 유별에 따른 성질이 잘못 연 결된 것은?</t>
-  </si>
-  <si>
     <t>가연성 가스가 아닌 것은?</t>
   </si>
   <si>
-    <t>화재 최성기 때의 농도로 유도등이 보이지 않을 정도의 연 기농도는? (단, 감광계수로 나타낸다.)</t>
-  </si>
-  <si>
     <t>황린의 보관 방법으로 옳은 것은?</t>
   </si>
   <si>
@@ -2526,15 +2512,9 @@
     <t>작동 신호를 조작량으로 변환하는 요소이며, 조절부와 조작 부로 이루어진 것은?</t>
   </si>
   <si>
-    <t>어떤 측정계기의 참값을 T, 지시값을 M 이라 할 때 보정율 과 오차율이 옳은 것은?</t>
-  </si>
-  <si>
     <t>R=9 Ω, XL = 10 Ω, XC = 5 Ω 인 직렬부하회로에 220V 의 정현파 전압을 인가시켰을 때의 유효 전력은 약 몇 kW 인가?</t>
   </si>
   <si>
-    <t>금속이나 반도체에 압력이 가해진 경우 전기저항이 변화하 는 성질을 이용한 압력센서는?</t>
-  </si>
-  <si>
     <t>변압기의 내부고장 보호에 사용되는 계전기는 다음 중 어느 것인가?</t>
   </si>
   <si>
@@ -2547,9 +2527,6 @@
     <t>미지의 임의 시간적 변화를 목표값에 제어량을 추종시키는 것을 목적으로 하는 제어는?</t>
   </si>
   <si>
-    <t>무한장 솔레노이드 자계의 세기에 대한 설명으로 틀린 것 은?</t>
-  </si>
-  <si>
     <t>저항 R1 , R2 와 인덕턴스 L이 직렬로 연결된 회로에서 시 정수[sec] 는?</t>
   </si>
   <si>
@@ -2568,54 +2545,30 @@
     <t>그림과 같은 릴레이 스퀀스회로의 출력식을 간략화한 것은?</t>
   </si>
   <si>
-    <t>특정소방대상물의 관계인이 소방안전관리자를 해임한 경우 재선임 신고를 해야 하는 기준은? (단, 해임한 날부터를 기 준일로 한다.)</t>
-  </si>
-  <si>
     <t>시·도지사가 설치하고 유지·관리하여야 하는 소방용수시설이 아니 것은?</t>
   </si>
   <si>
     <t>( )안의 내용으로 알맞은 것은?</t>
   </si>
   <si>
-    <t>소방시설공사업자의 시공능력평가 방법에 대한 설명 중 틀 린 것은?</t>
-  </si>
-  <si>
     <t>소방시설의 자체점검에 관한 설명으로 옳지 않은 것은?</t>
   </si>
   <si>
     <t>소방시설공사의 착공신고 시 첨부서류가 아닌 것은?</t>
   </si>
   <si>
-    <t>시·도의 조례가 정하는 바에 따라 지정수량 이상의 위험물 을 임시로 저장·취급할 수 있는 기간 (㉠)과 임시저장 승인 권자 (㉡)는?</t>
-  </si>
-  <si>
-    <t>연면적이 500m2 이상인 위험물 제조소 및 일반취급소에 설 치하여야 하는 경보설비는?</t>
-  </si>
-  <si>
-    <t>소방서의 종합상황실 실장이 서면 모사전송 또는 컴퓨터통 신 등으로 소방본부의 종합상황실에 보고하여야 하는 화재 가 아닌 것은?</t>
-  </si>
-  <si>
     <t>소방시설업의 등록권자로 옳은 것은?</t>
   </si>
   <si>
     <t>제3류 위험물 중 금수성 물품에 적응성이 있는 소화약제는?</t>
   </si>
   <si>
-    <t>소방시설관리업의 등록을 반드시 취소해야 하는 사유에 해 당하지 않는 것은?</t>
-  </si>
-  <si>
-    <t>가연성가스를 저장·취급하는 시설로서 1급 소방안전관리대 상물의 가연성가스 저장·취급 기준으로 옳은 것은?</t>
-  </si>
-  <si>
     <t>소방기본법상 소방용수시설·소화기구 및 설비등의 설치명령 을 위반한 자의 과태료는?</t>
   </si>
   <si>
     <t>방염처리업의 종류가 아닌 것은?</t>
   </si>
   <si>
-    <t>자동화재탐지설비를 설치하여야 하는 특정소방 대상물의 기 준으로 틀린 것은?</t>
-  </si>
-  <si>
     <t>소방용수시설 저수조의 설치기준으로 틀린 것은?</t>
   </si>
   <si>
@@ -2631,58 +2584,22 @@
     <t>비상방송설비의 특징에 대한 설명으로 틀린 것은?</t>
   </si>
   <si>
-    <t>자동화재탐지설비의 수신기 설치기준에 관한 사항 중, 최소 몇 층 이상의 특정소방대상물에는 발신기와 전화통화가 가 능한 수신기를 설치하여야 하는가?</t>
-  </si>
-  <si>
-    <t>지하층을 제외한 층수가 11층 이상의 층에서 피난층에 이르 는 부분의 소방시설에 있어 비상 전원을 60분 이상 유효하 게 작동시킬 수 있는 용량으로 하여야 하는 설비들로 옳게 나열된 것은?</t>
-  </si>
-  <si>
-    <t>화재안전기준에서 정하고 있는 연기감지기를 설치하지 않아 도 되는 장소는?</t>
-  </si>
-  <si>
     <t>누전경보기의 수신부 설치 제외 장소로 틀린 것은?</t>
   </si>
   <si>
     <t>상용전원이 서로 다른 소방시설은?</t>
   </si>
   <si>
-    <t>노유자시설로서 바닥면적이 몇 m2 이상인 층이 있는 경우에 자동화재속보설비를 설치하는가?</t>
-  </si>
-  <si>
     <t>절연저항시험에 관한 기준에서 ( )에 알맞은 것은?</t>
   </si>
   <si>
-    <t>축광표지의 식별도시험에 관련한 기준에서 ( )에 알맞은 것 은?</t>
-  </si>
-  <si>
     <t>환경상태가 현저하게 고온으로 되어 연기감지기를 설치할 수 없는 건조실 또는 살균실 등에 적응성 있는 열감지기가 아닌 것은?</t>
   </si>
   <si>
-    <t>누전경보기의 화재안전기준에서 규정한 용어, 설치방법, 전 원 등에 관한 설명으로 틀린 것은?</t>
-  </si>
-  <si>
     <t>누전경보기에서 감도조정장치의 조정범위는 최대 몇 mA인 가?</t>
   </si>
   <si>
     <t>자동화재탐지설비의 GP형 수신기에 감지기 회로의 배선을 접속하려고 할 때 경계구역이 15개인 경우 필요한 공통선의 최소 개수는?</t>
-  </si>
-  <si>
-    <t>무선통신보조설비에 대한 설명으로 틀린 것은? 용량은 30분 이상이다.</t>
-  </si>
-  <si>
-    <t>비상방송설비가 기동장치에 의한 화재신고를 수신한 후 필 요한 음량으로 화재발생 상황 및 피난에 유효한 방송이 자 동으로 개시될 때까지의 소요시간은 최대 몇 초 이하인가?</t>
-  </si>
-  <si>
-    <t>지하층으로서 특정소방대상물의 바닥부분 중 최소 몇 면이 지표면과 동일한 경우에 무선통신 보조설비의 설치를 제외 할 수 있는가?</t>
-  </si>
-  <si>
-    <t>무창층의 도매시장에 설치하는 비상조명등용 비상전원은 당 해 비상조명등을 몇 분 이상 유효하게 작동시킬 수 있는 용 량으로 하여야 하는가?</t>
-  </si>
-  <si>
-    <t>청각장애인용 시각경보장치는 천장의 높이가 2m 이하인 경 우 천장으로부터 몇 m 이내의 장소에 설치해야 하는가?</t>
-  </si>
-  <si>
-    <t>신호의 전송로가 분기되는 장소에 설치하는 것으로 임피던 스 매칭과 신호 균등분배를 위해 사용되는 장치는?</t>
   </si>
   <si>
     <t>① 습도를 높일 것
@@ -2721,176 +2638,567 @@
 ④ 불연내장재의 사용</t>
   </si>
   <si>
+    <t>① 0.4 ~ 4 vol%
+② 1 ~ 12.5 vol%
+③ 4 ~ 75 vol%
+④ 67 ~ 92 vol%</t>
+  </si>
+  <si>
+    <t>① 질식소화
+② 냉각소화
+③ 제거소화
+④ 억제소화</t>
+  </si>
+  <si>
+    <t>① 분자량/22.4
+② 분자량/29
+③ 분자량/44.8
+④ 분자량/100</t>
+  </si>
+  <si>
+    <t>① 비화
+② 복사열
+③ 화염의 접촉(접염)
+④ 흡착열에 의한 발화</t>
+  </si>
+  <si>
+    <t>① 제1류 위험물 - 산화성고체
+② 제2류 위험물 - 가연성고체
+③ 제4류 위험물 - 인화성액체
+④ 제6류 위험물 - 자기반응성물질</t>
+  </si>
+  <si>
+    <t>① 일산화탄소
+② 프로판
+③ 수소
+④ 아르곤</t>
+  </si>
+  <si>
+    <t>① 물 속에 보관
+② 이황화탄소 속에 보관
+③ 수산화칼륨 속에 보관
+④ 통풍이 잘 되는 공기 중에 보관</t>
+  </si>
+  <si>
+    <t>① 10
+② 13
+③ 17
+④ 21</t>
+  </si>
+  <si>
+    <t>① 유류화재 시 다량의 포를 방사한다.
+② 전기화재 시 신속하게 전원을 차단한다.
+③ 가연성가스 화재 시 가스의 밸브를 닫는다.
+④ 산림화재 시 확산을 막기 위하여 산림의 일부를 벌목한 다.</t>
+  </si>
+  <si>
+    <t>① 10
+② 20
+③ 50
+④ 80</t>
+  </si>
+  <si>
+    <t>① G/(1+G)
+② G/(1-G)
+③ 1+G
+④ 1-G</t>
+  </si>
+  <si>
+    <t>① 정전용량이란 콘덴서가 전하를 축적하는 능력을 말한다.
+② 콘덴서에서 전압을 가하는 순간 콘덴서는 단락상태가 된 다.
+③ 정전 유도에 의하여 작용하는 힘은 반발력이다.
+④ 같은 부호의 전하끼리는 반발력이 생긴다.</t>
+  </si>
+  <si>
+    <t>① 제어요소
+② 제어대상
+③ 피드백요소
+④ 기준입력요소</t>
+  </si>
+  <si>
+    <t>① 보정율 = (T-M)/T , 오차율 = (M-T)/M
+② 보정율 = (M-T)/M, 오차율 = (T-M)/T
+③ 보정율 = (T-M)/M, 오차율 =(M-T)/T
+④ 보정율 = (M-T)/T, 오차율 = (T-M)/M</t>
+  </si>
+  <si>
+    <t>① 벨로우즈
+② 다이어프램
+③ 가변저항기
+④ 스트레인 게이지</t>
+  </si>
+  <si>
+    <t>① 비율차등 계전기
+② 저전압 계전기
+③ 고전압 계전기
+④ 압력 계전기</t>
+  </si>
+  <si>
+    <t>① 수산화니켈
+② 카드뮴
+③ 이산화연
+④ 연</t>
+  </si>
+  <si>
+    <t>① SCR
+② TRIAC
+③ Diode
+④ GTO</t>
+  </si>
+  <si>
+    <t>① 추종제어
+② 정치제어
+③ 비율제어
+④ 프로그래밍제어</t>
+  </si>
+  <si>
+    <t>① 전류의 세기에 비례한다.
+② 코일의 권수에 비례한다.
+③ 솔레노이드 내부에서의 자계의 세기는 위치에 관계없이 일정한 평등자계이다.
+④ 자계의 방향과 암페어 경로 간에 서로 수직인 경우 자계 의 세기가 최고이다.</t>
+  </si>
+  <si>
+    <t>① SIGN TO NUMBER RATING
+② SIGNAL TO NOISE RATIO
+③ SOURCE NULL RESISTANCE
+④ SOURCE NETWORK RANGE</t>
+  </si>
+  <si>
+    <t>화재 발생 시 주수소화가 적합하지 않은 물질은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>① 적린
 ② 마그네슘 분말
 ③ 과염소산칼륨
 ④ 유황</t>
-  </si>
-  <si>
-    <t>① 0.4 ~ 4 vol%
-② 1 ~ 12.5 vol%
-③ 4 ~ 75 vol%
-④ 67 ~ 92 vol%</t>
-  </si>
-  <si>
-    <t>① 질식소화
-② 냉각소화
-③ 제거소화
-④ 억제소화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>목조건축물에서 발생하는 옥외출화 시기를 나타낸 것으로 옳은 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>① 임계온도는 97.5℃ 이다.
+② 고체의 형태로 존재할 수 있다.
 ③ 불연성가스로 공기보다 무겁다.
 ④ 상온, 상압에서 기체 상태로 존재한다.</t>
-  </si>
-  <si>
-    <t>① Na CO
-② NH H PO 2 3 4 2 4
-③ KHCO
-④ NaHCO 3 3</t>
-  </si>
-  <si>
-    <t>① 분자량/22.4
-② 분자량/29
-③ 분자량/44.8
-④ 분자량/100</t>
-  </si>
-  <si>
-    <t>① 비화
-② 복사열
-③ 화염의 접촉(접염)
-④ 흡착열에 의한 발화</t>
-  </si>
-  <si>
-    <t>① 제1류 위험물 - 산화성고체
-② 제2류 위험물 - 가연성고체
-③ 제4류 위험물 - 인화성액체
-④ 제6류 위험물 - 자기반응성물질</t>
-  </si>
-  <si>
-    <t>① 일산화탄소
-② 프로판
-③ 수소
-④ 아르곤</t>
-  </si>
-  <si>
-    <t>① 0.1m-1
-② 1m-1
-③ 10m-1
-④ 30m-1</t>
-  </si>
-  <si>
-    <t>① 물 속에 보관
-② 이황화탄소 속에 보관
-③ 수산화칼륨 속에 보관
-④ 통풍이 잘 되는 공기 중에 보관</t>
-  </si>
-  <si>
-    <t>① 10
-② 13
-③ 17
-④ 21</t>
-  </si>
-  <si>
-    <t>① 유류화재 시 다량의 포를 방사한다.
-② 전기화재 시 신속하게 전원을 차단한다.
-③ 가연성가스 화재 시 가스의 밸브를 닫는다.
-④ 산림화재 시 확산을 막기 위하여 산림의 일부를 벌목한 다.</t>
-  </si>
-  <si>
-    <t>① CO
-② H O 2 2</t>
-  </si>
-  <si>
-    <t>① 10
-② 20
-③ 50
-④ 80</t>
-  </si>
-  <si>
-    <t>① G/(1+G)
-② G/(1-G)
-③ 1+G
-④ 1-G</t>
-  </si>
-  <si>
-    <t>① 정전용량이란 콘덴서가 전하를 축적하는 능력을 말한다.
-② 콘덴서에서 전압을 가하는 순간 콘덴서는 단락상태가 된 다.
-③ 정전 유도에 의하여 작용하는 힘은 반발력이다.
-④ 같은 부호의 전하끼리는 반발력이 생긴다.</t>
-  </si>
-  <si>
-    <t>① R C = R C , R R = C L 1 1 2 2 2 3 1
-② R C = R C , R R = C = L 1 1 2 2 2 3 1
-③ R C = R C , R R = C L 1 2 2 1 2 3 1
-④ R C = R C , L=R R C 1 2 2 1 2 3 1</t>
-  </si>
-  <si>
-    <t>① 제어요소
-② 제어대상
-③ 피드백요소
-④ 기준입력요소</t>
-  </si>
-  <si>
-    <t>① 보정율 = (T-M)/T , 오차율 = (M-T)/M
-② 보정율 = (M-T)/M, 오차율 = (T-M)/T
-③ 보정율 = (T-M)/M, 오차율 =(M-T)/T
-④ 보정율 = (M-T)/T, 오차율 = (T-M)/M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이산화탄소(CO₂)에 대한 설명으로 틀린 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화재발생 시 건축물의 화재를 확대시키는 주요인이 아닌 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위험물안전관리법령상 위험물 유별에 따른 성질이 잘못 연결된 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화재 최성기 때의 농도로 유도등이 보이지 않을 정도의 연기농도는? (단, 감광계수로 나타낸다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① CO₂
+② H₂O
+③ H₃PO₄
+④ K₂CO₃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① R₁C₁ = R₂C₂ , R₂R₃ = C₁L 
+② R₁C₁ = R₂C₂ , R₂R₃ = C₁ = L
+③ R₁C₂ = R₂C₁ , R₂R₃ = C₁L
+④ R₁C₂ = R₂C₁ , L=R₂R₃C₁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어떤 측정계기의 참값을 T, 지시값을 M 이라 할 때 보정율과 오차율이 옳은 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>논리식을 간략화한 것 중 그 값이 다른 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">① 1.98
 ② 2.41
 ③ 2.77
 ④ 4.1
-① 
-② 
-③ 
-④ </t>
-  </si>
-  <si>
-    <t>① 벨로우즈
-② 다이어프램
-③ 가변저항기
-④ 스트레인 게이지</t>
-  </si>
-  <si>
-    <t>① 비율차등 계전기
-② 저전압 계전기
-③ 고전압 계전기
-④ 압력 계전기</t>
-  </si>
-  <si>
-    <t>① 수산화니켈
-② 카드뮴
-③ 이산화연
-④ 연</t>
-  </si>
-  <si>
-    <t>① SCR
-② TRIAC
-③ Diode
-④ GTO</t>
-  </si>
-  <si>
-    <t>① 추종제어
-② 정치제어
-③ 비율제어
-④ 프로그래밍제어</t>
-  </si>
-  <si>
-    <t>① 전류의 세기에 비례한다.
-② 코일의 권수에 비례한다.
-③ 솔레노이드 내부에서의 자계의 세기는 위치에 관계없이 일정한 평등자계이다.
-④ 자계의 방향과 암페어 경로 간에 서로 수직인 경우 자계 의 세기가 최고이다.</t>
-  </si>
-  <si>
-    <t>① SIGN TO NUMBER RATING
-② SIGNAL TO NOISE RATIO
-③ SOURCE NULL RESISTANCE
-④ SOURCE NETWORK RANGE</t>
-  </si>
-  <si>
-    <t>화재 발생 시 주수소화가 적합하지 않은 물질은?</t>
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16122a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금속이나 반도체에 압력이 가해진 경우 전기저항이 변화하는 성질을 이용한 압력센서는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무한장 솔레노이드 자계의 세기에 대한 설명으로 틀린 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 급속충전
+② 부동충전
+③ 균등충전
+④ 세류충전</t>
+  </si>
+  <si>
+    <t>① C를 크게 한다.
+② R을 크게 한다.
+③ C와 R을 크게 한다.
+④ C와 R을 적게 한다.</t>
+  </si>
+  <si>
+    <t>① 10일 이내
+② 20일 이내
+③ 30일 이내
+④ 40일 이내</t>
+  </si>
+  <si>
+    <t>① 저수조
+② 상수도
+③ 소화전
+④ 급수탑</t>
+  </si>
+  <si>
+    <t>① ㉠ 30일 이내, ㉡ 시·도지사
+② ㉠ 60일 이내, ㉡ 소방본부장
+③ ㉠ 90일 이내, ㉡ 관할소방서장
+④ ㉠ 120일 이내, ㉡ 국민안전처장관</t>
+  </si>
+  <si>
+    <t>① 자동화재탐지설비
+② 확성장치
+③ 비상경보설비
+④ 비상방송설비</t>
+  </si>
+  <si>
+    <t>① 사상자가 10인 발생한 화재
+② 이재민이 100인 발생한 화재
+③ 관공서·학교·정부미도정공장의 화재
+④ 재산피해액이 10억원 발생한 일반화재</t>
+  </si>
+  <si>
+    <t>① 물
+② 강화액
+③ 팽창질석
+④ 인산염류분말</t>
+  </si>
+  <si>
+    <t>① 거짓으로 등록을 한 경우
+② 등록기준 미달하게 된 경우
+③ 다른 사람에게 등록증을 빌려준 경우
+④ 등록의 결격사유에 해당하게 된 경우</t>
+  </si>
+  <si>
+    <t>① 100톤 미만
+② 100톤 이상 ~ 1000톤 미만
+③ 500톤 이상 ~ 1000톤 미만
+④ 1000톤 이상</t>
+  </si>
+  <si>
+    <t>① 섬유류 방염업
+② 합성수지류 방염업
+③ 합판·목재류 방염업
+④ 실내장식물류 방염업</t>
+  </si>
+  <si>
+    <t>① 지면으로부터의 낙차가 4.5m 이하일 것
+② 흡수부분의 수심이 0.3m 이상일 것
+③ 흡수관의 투입구가 사각형의 경우에는 한 변의 길이가 60cm 이상일 것
+④ 흡수관의 투입구가 원형의 경우에는 지름이 60 cm 이상 일 것</t>
+  </si>
+  <si>
+    <t>① 시 · 도지사
+② 국민안전처장관
+③ 소방본부장 또는 소방서장
+④ 한국소방안전협회장</t>
+  </si>
+  <si>
+    <t>① 3
+② 4
+③ 5
+④ 7</t>
+  </si>
+  <si>
+    <t>① 비상조명등설비, 유도등설비
+② 비상조명등설비, 비상경보설비
+③ 비상방송설비, 유도등설비
+④ 비상방송설비, 비상경보설비</t>
+  </si>
+  <si>
+    <t>① 에스컬레이터 경사로
+② 길이가 15m인 복도
+③ 엘리베이터 권상기실
+④ 천장의 높이가 15m 이상 20 m 미만의 장소</t>
+  </si>
+  <si>
+    <t>① 옥내소화전설비
+② 비상방송설비
+③ 비상콘센트설비
+④ 스프링클러설비</t>
+  </si>
+  <si>
+    <t>① 0.1
+② 3
+③ 5
+④ 10</t>
+  </si>
+  <si>
+    <t>① 20
+② 10
+③ 5
+④ 3</t>
+  </si>
+  <si>
+    <t>① 정온식 1종
+② 정온식 특종
+③ 열아날로그식
+④ 보상식 스포트형 1종</t>
+  </si>
+  <si>
+    <t>① 1
+② 20
+③ 1000
+④ 1500</t>
+  </si>
+  <si>
+    <t>① 5
+② 10
+③ 20
+④ 30</t>
+  </si>
+  <si>
+    <t>① 1면 이상
+② 2면 이상
+③ 3면 이상
+④ 4면 이상</t>
+  </si>
+  <si>
+    <t>① 10
+② 20
+③ 40
+④ 60</t>
+  </si>
+  <si>
+    <t>① 0.1
+② 0.15
+③ 2.0
+④ 2.5</t>
+  </si>
+  <si>
+    <t>① 1/8
+② 1/9
+③ 8
+④ 9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16140a</t>
+  </si>
+  <si>
+    <t>특정소방대상물의 관계인이 소방안전관리자를 해임한 경우 재선임 신고를 해야 하는 기준은? (단, 해임한 날부터를 기준일로 한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16143a</t>
+  </si>
+  <si>
+    <t>소방시설공사업자의 시공능력평가 방법에 대한 설명 중 틀린 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 시공능력평가액은 실적평가액 + 자본금평가액 + 기술력 평가액 ± 신인도평가액으로 산출한다.
+② 신인도평가액 산정 시 최근 1년간 국가기관으로 부터 우수시공업자로 선정된 경우에는 3% 가산 한다.
+③ 신인도평가액 산정 시 최근 1년간 부도가 발생된 사실이 있는 경우에는 2%를 감산한다.
+④ 실적평가액은 최근 5년간의 연평균공사실적액을 의미한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 작동기능점검은 소방시설 등을 인위적으로 조작하여 정상적으로 작동하는 것을 점검하는 것이다.
+② 종합정밀점검은 설비별 주요 구성부품의 구조기준이 화재안전기준 및 관련 법령에 적합한지 여부를 점검하는 것이다.
+③ 종합정밀점검에는 작동기능점검의 사항이 해당되지 않는다.
+④ 종합정밀점검은 소방시설관리사가 참여한 경우 소방시설 관리업자 또는 소방안전 관리자로 선임된 소방시설관리 사·소방기술사 1명 이상을 점검자로 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 공사업자의 소방시설공사업 등록증 사본
+② 공사업자의 소방시설공사업 등록수첩 사본
+③ 해당 소방시설공사의 책임시공 및 기술관리를 하는 기술인력의 기술등급을 증명하는 서류 사본
+④ 해당 소방시설을 설계한 기술인력자의 기술자격증 사본</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시·도의 조례가 정하는 바에 따라 지정수량 이상의 위험물을 임시로 저장·취급할 수 있는 기간 (㉠)과 임시저장 승인 권자 (㉡)는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연면적이 500m2 이상인 위험물 제조소 및 일반취급소에 설치하여야 하는 경보설비는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소방서의 종합상황실 실장이 서면 모사전송 또는 컴퓨터통신 등으로 소방본부의 종합상황실에 보고하여야 하는 화재 가 아닌 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 국무총리
+② 시·도지사
+③ 소방서장
+④ 한국소방안전협회장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소방시설관리업의 등록을 반드시 취소해야 하는 사유에 해당하지 않는 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가연성가스를 저장·취급하는 시설로서 1급 소방안전관리대상물의 가연성가스 저장·취급 기준으로 옳은 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 지하구
+② 지하가 중 터널로서 길이 700m 이상인 것
+③ 교정시설로서 연면적 2000m² 이상인 것
+④ 복합건축물로서 연면적 600m² 이상인 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화재탐지설비를 설치하여야 하는 특정소방 대상물의 기준으로 틀린 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 지하가
+② 지하층을 포함한 층수가 16층 이상인 건축물
+③ 지하층을 제외한 층수가 11층 이상인 건축물
+④ 복합건축물로써 연면적 3만제곱미터 이상인 건축물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 12000 m²
+② 10000 m²
+③ 8000 m²
+④ 6000 m²</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 다른 방송설비와 공용하는 경우에는 화재 시 비상경보외의 방송을 차단 할 수 있는 구조로 하여야 한다.
+② 비상방송설비의 축전지는 감시상태를 10분간 지속한 후 유효하게 60분 이상 경보할 수 있어야 한다.
+③ 확성기의 음성입력은 실외에 설치한 경우 3W 이상이어야 한다.
+④ 음량조정기의 배선은 3선식으로 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화재탐지설비의 수신기 설치기준에 관한 사항 중, 최소 몇 층 이상의 특정소방대상물에는 발신기와 전화통화가 가능한 수신기를 설치하여야 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지하층을 제외한 층수가 11층 이상의 층에서 피난층에 이르는 부분의 소방시설에 있어 비상 전원을 60분 이상 유효하게 작동시킬 수 있는 용량으로 하여야 하는 설비들로 옳게 나열된 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화재안전기준에서 정하고 있는 연기감지기를 설치하지 않아도 되는 장소는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 습도가 높은 장소
+② 온도의 변화가 급격한 장소
+③ 고주파 발생회로 등에 따른 영향을 받을 우려가 있는 장소
+④ 부식성의 증기·가스 등이 체류하지 않는 장소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">① 200
+② 300
+③ 500
+④ 600
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 3
+② 5
+③ 7
+④ 10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경계구역에 관한 다음 내용 중 ( )안에 맞는 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>노유자시설로서 바닥면적이 몇 m² 이상인 층이 있는 경우에 자동화재속보설비를 설치하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16168a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16169a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16170a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>축광표지의 식별도시험에 관련한 기준에서 ( )에 알맞은 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>누전경보기의 화재안전기준에서 규정한 용어, 설치방법, 전원 등에 관한 설명으로 틀린 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 경계전로의 정격전류가 60A 를 초과하는 전로에 있어서는 1급 누전경보기를 설치한다.
+② 변류기는 옥외 인입선 제1지점의 전원측에 설치한다.
+③ 누전경보기 전원은 분전반으로부터 전용으로 하고, 각 극에 개폐기 및 15A 이하의 과전류차단기를 설치한다.
+④ 누전경보기는 변류기와 수신부로 구성되어 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 소화활동설비이다.
+② 증폭기에는 비상전원이 부착된 것으로 하고 비상전원의 용량은 30분 이상이다.
+③ 누설동축케이블의 끝부분에는 무반사 종단저항을 부착한다.
+④ 누설동축케이블 또는 동축케이블의 임피던스는 100 Ω 의 것으로 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무선통신보조설비에 대한 설명으로 틀린 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상방송설비가 기동장치에 의한 화재신고를 수신한 후 필요한 음량으로 화재발생 상황 및 피난에 유효한 방송이 자동으로 개시될 때까지의 소요시간은 최대 몇 초 이하인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지하층으로서 특정소방대상물의 바닥부분 중 최소 몇 면이 지표면과 동일한 경우에 무선통신 보조설비의 설치를 제외할 수 있는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무창층의 도매시장에 설치하는 비상조명등용 비상전원은 당해 비상조명등을 몇 분 이상 유효하게 작동시킬 수 있는 용량으로 하여야 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>청각장애인용 시각경보장치는 천장의 높이가 2m 이하인 경우 천장으로부터 몇 m 이내의 장소에 설치해야 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신호의 전송로가 분기되는 장소에 설치하는 것으로 임피던스 매칭과 신호 균등분배를 위해 사용되는 장치는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">① 분배기
+② 혼합기
+③ 증폭기
+④ 분파기 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4455,7 +4763,7 @@
     </row>
     <row r="13" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>190</v>
@@ -4467,7 +4775,7 @@
     </row>
     <row r="14" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>191</v>
@@ -4566,7 +4874,7 @@
         <v>205</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C22" s="4">
         <v>1</v>
@@ -4587,10 +4895,10 @@
     </row>
     <row r="24" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>208</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>209</v>
       </c>
       <c r="C24" s="4">
         <v>4</v>
@@ -4599,10 +4907,10 @@
     </row>
     <row r="25" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A25" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>210</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>211</v>
       </c>
       <c r="C25" s="4">
         <v>1</v>
@@ -4611,10 +4919,10 @@
     </row>
     <row r="26" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A26" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>212</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>213</v>
       </c>
       <c r="C26" s="4">
         <v>2</v>
@@ -4623,10 +4931,10 @@
     </row>
     <row r="27" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A27" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>214</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>215</v>
       </c>
       <c r="C27" s="4">
         <v>4</v>
@@ -4635,10 +4943,10 @@
     </row>
     <row r="28" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A28" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>216</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>217</v>
       </c>
       <c r="C28" s="4">
         <v>2</v>
@@ -4647,10 +4955,10 @@
     </row>
     <row r="29" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A29" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>218</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>219</v>
       </c>
       <c r="C29" s="4">
         <v>2</v>
@@ -4659,10 +4967,10 @@
     </row>
     <row r="30" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A30" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>220</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>221</v>
       </c>
       <c r="C30" s="4">
         <v>3</v>
@@ -4671,10 +4979,10 @@
     </row>
     <row r="31" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A31" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>222</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>223</v>
       </c>
       <c r="C31" s="4">
         <v>1</v>
@@ -4683,10 +4991,10 @@
     </row>
     <row r="32" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A32" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C32" s="4">
         <v>2</v>
@@ -4695,10 +5003,10 @@
     </row>
     <row r="33" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A33" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B33" s="4" t="s">
         <v>225</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>226</v>
       </c>
       <c r="C33" s="4">
         <v>3</v>
@@ -4707,24 +5015,24 @@
     </row>
     <row r="34" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A34" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B34" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>228</v>
-      </c>
       <c r="C34" s="4">
         <v>2</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A35" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>229</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>230</v>
       </c>
       <c r="C35" s="4">
         <v>2</v>
@@ -4733,10 +5041,10 @@
     </row>
     <row r="36" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A36" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>231</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>232</v>
       </c>
       <c r="C36" s="4">
         <v>1</v>
@@ -4745,10 +5053,10 @@
     </row>
     <row r="37" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A37" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B37" s="4" t="s">
         <v>233</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>234</v>
       </c>
       <c r="C37" s="4">
         <v>3</v>
@@ -4757,10 +5065,10 @@
     </row>
     <row r="38" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A38" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B38" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>236</v>
       </c>
       <c r="C38" s="4">
         <v>1</v>
@@ -4769,10 +5077,10 @@
     </row>
     <row r="39" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A39" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B39" s="4" t="s">
         <v>237</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>238</v>
       </c>
       <c r="C39" s="4">
         <v>1</v>
@@ -4781,10 +5089,10 @@
     </row>
     <row r="40" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A40" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B40" s="4" t="s">
         <v>239</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>240</v>
       </c>
       <c r="C40" s="4">
         <v>4</v>
@@ -4793,7 +5101,7 @@
     </row>
     <row r="41" spans="1:4" s="11" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A41" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B41" s="10">
         <v>15240</v>
@@ -4802,15 +5110,15 @@
         <v>3</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A42" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C42" s="4">
         <v>4</v>
@@ -4819,7 +5127,7 @@
     </row>
     <row r="43" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A43" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>108</v>
@@ -4831,10 +5139,10 @@
     </row>
     <row r="44" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A44" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>244</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>245</v>
       </c>
       <c r="C44" s="4">
         <v>3</v>
@@ -4843,10 +5151,10 @@
     </row>
     <row r="45" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A45" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B45" s="4" t="s">
         <v>246</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>247</v>
       </c>
       <c r="C45" s="4">
         <v>2</v>
@@ -4855,10 +5163,10 @@
     </row>
     <row r="46" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A46" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C46" s="4">
         <v>4</v>
@@ -4867,10 +5175,10 @@
     </row>
     <row r="47" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A47" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C47" s="4">
         <v>1</v>
@@ -4879,24 +5187,24 @@
     </row>
     <row r="48" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A48" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B48" s="4" t="s">
         <v>250</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>251</v>
       </c>
       <c r="C48" s="4">
         <v>3</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A49" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C49" s="4">
         <v>3</v>
@@ -4905,10 +5213,10 @@
     </row>
     <row r="50" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A50" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>253</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>254</v>
       </c>
       <c r="C50" s="4">
         <v>2</v>
@@ -4917,10 +5225,10 @@
     </row>
     <row r="51" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A51" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C51" s="4">
         <v>3</v>
@@ -4929,10 +5237,10 @@
     </row>
     <row r="52" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A52" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B52" s="4" t="s">
         <v>256</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>257</v>
       </c>
       <c r="C52" s="4">
         <v>3</v>
@@ -4941,10 +5249,10 @@
     </row>
     <row r="53" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A53" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C53" s="4">
         <v>2</v>
@@ -4953,10 +5261,10 @@
     </row>
     <row r="54" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A54" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B54" s="4" t="s">
         <v>259</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>260</v>
       </c>
       <c r="C54" s="4">
         <v>3</v>
@@ -4965,10 +5273,10 @@
     </row>
     <row r="55" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A55" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C55" s="4">
         <v>3</v>
@@ -4977,10 +5285,10 @@
     </row>
     <row r="56" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A56" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B56" s="4" t="s">
         <v>262</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>263</v>
       </c>
       <c r="C56" s="4">
         <v>1</v>
@@ -4989,10 +5297,10 @@
     </row>
     <row r="57" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A57" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B57" s="4" t="s">
         <v>264</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>265</v>
       </c>
       <c r="C57" s="4">
         <v>1</v>
@@ -5001,10 +5309,10 @@
     </row>
     <row r="58" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A58" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B58" s="4" t="s">
         <v>266</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>267</v>
       </c>
       <c r="C58" s="4">
         <v>4</v>
@@ -5013,10 +5321,10 @@
     </row>
     <row r="59" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A59" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B59" s="4" t="s">
         <v>268</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>269</v>
       </c>
       <c r="C59" s="4">
         <v>2</v>
@@ -5025,10 +5333,10 @@
     </row>
     <row r="60" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A60" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B60" s="4" t="s">
         <v>270</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>271</v>
       </c>
       <c r="C60" s="4">
         <v>4</v>
@@ -5037,10 +5345,10 @@
     </row>
     <row r="61" spans="1:4" s="11" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A61" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="B61" s="10" t="s">
         <v>272</v>
-      </c>
-      <c r="B61" s="10" t="s">
-        <v>273</v>
       </c>
       <c r="C61" s="10">
         <v>1</v>
@@ -5049,10 +5357,10 @@
     </row>
     <row r="62" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A62" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C62" s="4">
         <v>1</v>
@@ -5061,10 +5369,10 @@
     </row>
     <row r="63" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A63" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B63" s="4" t="s">
         <v>275</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>276</v>
       </c>
       <c r="C63" s="4">
         <v>3</v>
@@ -5073,10 +5381,10 @@
     </row>
     <row r="64" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A64" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C64" s="4">
         <v>2</v>
@@ -5085,10 +5393,10 @@
     </row>
     <row r="65" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A65" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C65" s="4">
         <v>2</v>
@@ -5097,10 +5405,10 @@
     </row>
     <row r="66" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A66" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B66" s="4" t="s">
         <v>279</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>280</v>
       </c>
       <c r="C66" s="4">
         <v>1</v>
@@ -5109,10 +5417,10 @@
     </row>
     <row r="67" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A67" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B67" s="4" t="s">
         <v>281</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>282</v>
       </c>
       <c r="C67" s="4">
         <v>3</v>
@@ -5121,10 +5429,10 @@
     </row>
     <row r="68" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A68" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B68" s="4" t="s">
         <v>283</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>284</v>
       </c>
       <c r="C68" s="4">
         <v>4</v>
@@ -5133,10 +5441,10 @@
     </row>
     <row r="69" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A69" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C69" s="4">
         <v>2</v>
@@ -5145,10 +5453,10 @@
     </row>
     <row r="70" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A70" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C70" s="4">
         <v>4</v>
@@ -5157,10 +5465,10 @@
     </row>
     <row r="71" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A71" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B71" s="4" t="s">
         <v>286</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>287</v>
       </c>
       <c r="C71" s="4">
         <v>4</v>
@@ -5169,10 +5477,10 @@
     </row>
     <row r="72" spans="1:4" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A72" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C72" s="4">
         <v>3</v>
@@ -5181,10 +5489,10 @@
     </row>
     <row r="73" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A73" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C73" s="4">
         <v>3</v>
@@ -5193,10 +5501,10 @@
     </row>
     <row r="74" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A74" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B74" s="4" t="s">
         <v>290</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>291</v>
       </c>
       <c r="C74" s="4">
         <v>4</v>
@@ -5205,10 +5513,10 @@
     </row>
     <row r="75" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A75" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="B75" s="4" t="s">
         <v>292</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>293</v>
       </c>
       <c r="C75" s="4">
         <v>4</v>
@@ -5217,7 +5525,7 @@
     </row>
     <row r="76" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A76" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B76" s="4">
         <v>15275</v>
@@ -5229,24 +5537,24 @@
     </row>
     <row r="77" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A77" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B77" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="B77" s="4" t="s">
-        <v>296</v>
-      </c>
       <c r="C77" s="4">
         <v>2</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A78" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C78" s="4">
         <v>2</v>
@@ -5255,10 +5563,10 @@
     </row>
     <row r="79" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A79" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C79" s="4">
         <v>2</v>
@@ -5267,24 +5575,24 @@
     </row>
     <row r="80" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A80" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="B80" s="4" t="s">
         <v>299</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>300</v>
       </c>
       <c r="C80" s="4">
         <v>3</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A81" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C81" s="4">
         <v>1</v>
@@ -5324,10 +5632,10 @@
     </row>
     <row r="2" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -5335,10 +5643,10 @@
     </row>
     <row r="3" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -5346,10 +5654,10 @@
     </row>
     <row r="4" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -5357,10 +5665,10 @@
     </row>
     <row r="5" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -5368,10 +5676,10 @@
     </row>
     <row r="6" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -5379,10 +5687,10 @@
     </row>
     <row r="7" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -5390,10 +5698,10 @@
     </row>
     <row r="8" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -5401,10 +5709,10 @@
     </row>
     <row r="9" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -5412,10 +5720,10 @@
     </row>
     <row r="10" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -5423,10 +5731,10 @@
     </row>
     <row r="11" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -5434,10 +5742,10 @@
     </row>
     <row r="12" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -5445,10 +5753,10 @@
     </row>
     <row r="13" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -5456,10 +5764,10 @@
     </row>
     <row r="14" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -5467,10 +5775,10 @@
     </row>
     <row r="15" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A15" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -5478,10 +5786,10 @@
     </row>
     <row r="16" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C16">
         <v>2</v>
@@ -5489,10 +5797,10 @@
     </row>
     <row r="17" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -5500,10 +5808,10 @@
     </row>
     <row r="18" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -5511,7 +5819,7 @@
     </row>
     <row r="19" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>490</v>
@@ -5522,10 +5830,10 @@
     </row>
     <row r="20" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C20">
         <v>4</v>
@@ -5533,10 +5841,10 @@
     </row>
     <row r="21" spans="1:4" s="13" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A21" s="12" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C21" s="13">
         <v>2</v>
@@ -5544,24 +5852,24 @@
     </row>
     <row r="22" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22" t="s">
         <v>462</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>459</v>
-      </c>
-      <c r="C22">
-        <v>2</v>
-      </c>
-      <c r="D22" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A23" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C23">
         <v>3</v>
@@ -5569,10 +5877,10 @@
     </row>
     <row r="24" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -5580,10 +5888,10 @@
     </row>
     <row r="25" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A25" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C25">
         <v>4</v>
@@ -5591,24 +5899,24 @@
     </row>
     <row r="26" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A26" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A27" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C27">
         <v>3</v>
@@ -5616,10 +5924,10 @@
     </row>
     <row r="28" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A28" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C28">
         <v>2</v>
@@ -5627,7 +5935,7 @@
     </row>
     <row r="29" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A29" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>467</v>
@@ -5638,10 +5946,10 @@
     </row>
     <row r="30" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A30" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C30">
         <v>2</v>
@@ -5649,10 +5957,10 @@
     </row>
     <row r="31" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A31" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C31">
         <v>3</v>
@@ -5660,10 +5968,10 @@
     </row>
     <row r="32" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A32" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -5671,10 +5979,10 @@
     </row>
     <row r="33" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A33" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C33">
         <v>3</v>
@@ -5685,7 +5993,7 @@
         <v>468</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -5696,7 +6004,7 @@
         <v>469</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -5704,10 +6012,10 @@
     </row>
     <row r="36" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A36" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -5715,10 +6023,10 @@
     </row>
     <row r="37" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A37" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C37">
         <v>2</v>
@@ -5726,10 +6034,10 @@
     </row>
     <row r="38" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A38" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C38">
         <v>3</v>
@@ -5737,10 +6045,10 @@
     </row>
     <row r="39" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A39" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C39">
         <v>4</v>
@@ -5754,7 +6062,7 @@
         <v>471</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C40">
         <v>2</v>
@@ -5762,10 +6070,10 @@
     </row>
     <row r="41" spans="1:4" s="11" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A41" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C41" s="11">
         <v>3</v>
@@ -5773,10 +6081,10 @@
     </row>
     <row r="42" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A42" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -5784,10 +6092,10 @@
     </row>
     <row r="43" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A43" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C43">
         <v>2</v>
@@ -5795,10 +6103,10 @@
     </row>
     <row r="44" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A44" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C44">
         <v>4</v>
@@ -5806,10 +6114,10 @@
     </row>
     <row r="45" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A45" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C45">
         <v>4</v>
@@ -5817,7 +6125,7 @@
     </row>
     <row r="46" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A46" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>491</v>
@@ -5831,7 +6139,7 @@
         <v>472</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C47">
         <v>2</v>
@@ -5850,10 +6158,10 @@
     </row>
     <row r="49" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A49" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C49">
         <v>2</v>
@@ -5864,7 +6172,7 @@
         <v>475</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -5872,10 +6180,10 @@
     </row>
     <row r="51" spans="1:3" ht="174" x14ac:dyDescent="0.4">
       <c r="A51" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C51">
         <v>4</v>
@@ -5883,10 +6191,10 @@
     </row>
     <row r="52" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A52" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C52">
         <v>3</v>
@@ -5897,7 +6205,7 @@
         <v>476</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C53">
         <v>2</v>
@@ -5908,7 +6216,7 @@
         <v>477</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C54">
         <v>4</v>
@@ -5927,10 +6235,10 @@
     </row>
     <row r="56" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A56" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C56">
         <v>2</v>
@@ -5938,10 +6246,10 @@
     </row>
     <row r="57" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A57" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C57">
         <v>2</v>
@@ -5949,10 +6257,10 @@
     </row>
     <row r="58" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A58" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C58">
         <v>4</v>
@@ -5960,10 +6268,10 @@
     </row>
     <row r="59" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A59" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C59">
         <v>4</v>
@@ -5971,10 +6279,10 @@
     </row>
     <row r="60" spans="1:3" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A60" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -5982,10 +6290,10 @@
     </row>
     <row r="61" spans="1:3" s="11" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A61" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C61" s="11">
         <v>1</v>
@@ -5993,10 +6301,10 @@
     </row>
     <row r="62" spans="1:3" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A62" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C62">
         <v>4</v>
@@ -6004,10 +6312,10 @@
     </row>
     <row r="63" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A63" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C63">
         <v>2</v>
@@ -6015,7 +6323,7 @@
     </row>
     <row r="64" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A64" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>480</v>
@@ -6037,10 +6345,10 @@
     </row>
     <row r="66" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A66" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -6048,10 +6356,10 @@
     </row>
     <row r="67" spans="1:3" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A67" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C67">
         <v>2</v>
@@ -6062,7 +6370,7 @@
         <v>483</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C68">
         <v>3</v>
@@ -6070,10 +6378,10 @@
     </row>
     <row r="69" spans="1:3" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A69" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C69">
         <v>4</v>
@@ -6081,10 +6389,10 @@
     </row>
     <row r="70" spans="1:3" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A70" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C70">
         <v>2</v>
@@ -6092,10 +6400,10 @@
     </row>
     <row r="71" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A71" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -6106,7 +6414,7 @@
         <v>484</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -6114,7 +6422,7 @@
     </row>
     <row r="73" spans="1:3" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A73" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>492</v>
@@ -6125,10 +6433,10 @@
     </row>
     <row r="74" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A74" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -6139,7 +6447,7 @@
         <v>485</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -6147,7 +6455,7 @@
     </row>
     <row r="76" spans="1:3" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A76" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>486</v>
@@ -6158,10 +6466,10 @@
     </row>
     <row r="77" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A77" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C77">
         <v>4</v>
@@ -6172,7 +6480,7 @@
         <v>487</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C78">
         <v>2</v>
@@ -6180,10 +6488,10 @@
     </row>
     <row r="79" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A79" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C79">
         <v>4</v>
@@ -6191,10 +6499,10 @@
     </row>
     <row r="80" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A80" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C80">
         <v>3</v>
@@ -6202,7 +6510,7 @@
     </row>
     <row r="81" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A81" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>488</v>
@@ -6222,7 +6530,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EA50D89-9007-423F-AC0E-48A3655CC170}">
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="39.69921875" style="4" customWidth="1"/>
@@ -6251,7 +6559,10 @@
         <v>493</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>570</v>
+        <v>542</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
@@ -6259,7 +6570,10 @@
         <v>494</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>571</v>
+        <v>543</v>
+      </c>
+      <c r="C3" s="4">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="87" x14ac:dyDescent="0.4">
@@ -6267,478 +6581,903 @@
         <v>495</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>572</v>
+        <v>544</v>
+      </c>
+      <c r="C4" s="4">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
-        <v>496</v>
+        <v>571</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>573</v>
+        <v>545</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>574</v>
+        <v>546</v>
+      </c>
+      <c r="C6" s="4">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>575</v>
+        <v>547</v>
+      </c>
+      <c r="C7" s="4">
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
-        <v>604</v>
+        <v>569</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>576</v>
+        <v>570</v>
+      </c>
+      <c r="C8" s="4">
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>577</v>
+        <v>548</v>
+      </c>
+      <c r="C9" s="4">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A11" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A12" s="4" t="s">
         <v>500</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="52.2" x14ac:dyDescent="0.4">
-      <c r="A11" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A12" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>580</v>
+      <c r="B12" s="4">
+        <v>16111</v>
+      </c>
+      <c r="C12" s="4">
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>581</v>
+        <v>550</v>
+      </c>
+      <c r="C13" s="4">
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
-        <v>504</v>
+        <v>574</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>582</v>
+        <v>551</v>
+      </c>
+      <c r="C14" s="4">
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A15" s="4" t="s">
-        <v>505</v>
+        <v>575</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>583</v>
+        <v>552</v>
+      </c>
+      <c r="C15" s="4">
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="C16" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="B17" s="4">
+        <v>16116</v>
+      </c>
+      <c r="C17" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A18" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="C19" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A20" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="C20" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A21" s="4" t="s">
         <v>506</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B21" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="C21" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A22" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="C22" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A23" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="C23" s="4">
+        <v>1</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A24" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="C24" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A25" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="C25" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A26" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="C26" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="87" x14ac:dyDescent="0.4">
+      <c r="A27" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="C27" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="87" x14ac:dyDescent="0.4">
+      <c r="A28" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="C28" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A29" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="B29" s="4">
+        <v>16128</v>
+      </c>
+      <c r="C29" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A30" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="C30" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A31" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="C31" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A32" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="C32" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A33" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="C33" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A34" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="C34" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A35" s="4" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A17" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="B17" s="4" t="s">
+      <c r="B35" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="C35" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A36" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="B36" s="4">
+        <v>16135</v>
+      </c>
+      <c r="C36" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A37" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="C37" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A38" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="C38" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A39" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>585</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A18" s="4" t="s">
-        <v>508</v>
-      </c>
-      <c r="B18" s="4" t="s">
+      <c r="C39" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A40" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A19" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="B19" s="4" t="s">
+      <c r="C40" s="4">
+        <v>3</v>
+      </c>
+      <c r="D40" s="4">
+        <v>16139</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A41" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="B41" s="4">
+        <v>16140</v>
+      </c>
+      <c r="C41" s="4">
+        <v>4</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A42" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="121.8" x14ac:dyDescent="0.4">
-      <c r="A20" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="B20" s="4" t="s">
+      <c r="C42" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A43" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A21" s="4" t="s">
-        <v>511</v>
-      </c>
-      <c r="B21" s="4" t="s">
+      <c r="C43" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A44" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C44" s="4">
+        <v>4</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="191.4" x14ac:dyDescent="0.4">
+      <c r="A45" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="C45" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="226.2" x14ac:dyDescent="0.4">
+      <c r="A46" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="C46" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A47" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="C47" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A48" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A22" s="4" t="s">
-        <v>512</v>
-      </c>
-      <c r="B22" s="4" t="s">
+      <c r="C48" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A49" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>590</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A23" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="B23" s="4" t="s">
+      <c r="C49" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="87" x14ac:dyDescent="0.4">
+      <c r="A50" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" ht="139.19999999999999" x14ac:dyDescent="0.4">
-      <c r="A24" s="4" t="s">
-        <v>514</v>
-      </c>
-      <c r="B24" s="4" t="s">
+      <c r="C50" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A51" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="C51" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A52" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" ht="87" x14ac:dyDescent="0.4">
-      <c r="A25" s="4" t="s">
-        <v>515</v>
-      </c>
-      <c r="B25" s="4" t="s">
+      <c r="C52" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A53" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>593</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A26" s="4" t="s">
-        <v>516</v>
-      </c>
-      <c r="B26" s="4" t="s">
+      <c r="C53" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A54" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>594</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" ht="87" x14ac:dyDescent="0.4">
-      <c r="A27" s="4" t="s">
-        <v>517</v>
-      </c>
-      <c r="B27" s="4" t="s">
+      <c r="C54" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A55" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="C55" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A56" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" ht="139.19999999999999" x14ac:dyDescent="0.4">
-      <c r="A28" s="4" t="s">
-        <v>518</v>
-      </c>
-      <c r="B28" s="4" t="s">
+      <c r="C56" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A57" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="C57" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A58" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>596</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A29" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="B29" s="4" t="s">
+      <c r="C58" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A59" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A30" s="4" t="s">
-        <v>520</v>
-      </c>
-      <c r="B30" s="4" t="s">
+      <c r="C59" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A60" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="C60" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A61" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="C61" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A62" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="C62" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A63" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A31" s="4" t="s">
-        <v>521</v>
-      </c>
-      <c r="B31" s="4" t="s">
+      <c r="C63" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A64" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>599</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A32" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="B32" s="4" t="s">
+      <c r="C64" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="87" x14ac:dyDescent="0.4">
+      <c r="A65" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A33" s="4" t="s">
-        <v>523</v>
-      </c>
-      <c r="B33" s="4" t="s">
+      <c r="C65" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A66" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="C66" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A67" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" ht="121.8" x14ac:dyDescent="0.4">
-      <c r="A34" s="4" t="s">
-        <v>524</v>
-      </c>
-      <c r="B34" s="4" t="s">
+      <c r="C67" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="87" x14ac:dyDescent="0.4">
+      <c r="A68" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="C68" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A69" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="C69" s="4">
+        <v>2</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A70" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A35" s="4" t="s">
-        <v>525</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A36" s="4" t="s">
-        <v>526</v>
-      </c>
-      <c r="B36" s="4" t="s">
+      <c r="C70" s="4">
+        <v>3</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A71" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="B71" s="2" t="s">
         <v>603</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A37" s="4" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A38" s="4" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A39" s="4" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A40" s="4" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="52.2" x14ac:dyDescent="0.4">
-      <c r="A41" s="4" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A42" s="4" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A43" s="4" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A44" s="4" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A45" s="4" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A46" s="4" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" ht="52.2" x14ac:dyDescent="0.4">
-      <c r="A47" s="4" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A48" s="4" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" ht="52.2" x14ac:dyDescent="0.4">
-      <c r="A49" s="4" t="s">
+      <c r="C71" s="4">
+        <v>1</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A72" s="4" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A50" s="4" t="s">
+      <c r="B72" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="C72" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="174" x14ac:dyDescent="0.4">
+      <c r="A73" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="C73" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A74" s="4" t="s">
         <v>540</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A51" s="4" t="s">
+      <c r="B74" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="C74" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A75" s="4" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="52" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A52" s="4" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" ht="52.2" x14ac:dyDescent="0.4">
-      <c r="A53" s="4" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A54" s="4" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A55" s="4" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A56" s="4" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A57" s="4" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A58" s="4" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" ht="52.2" x14ac:dyDescent="0.4">
-      <c r="A59" s="4" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" ht="52.2" x14ac:dyDescent="0.4">
-      <c r="A60" s="4" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A61" s="4" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A62" s="4" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A63" s="4" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A64" s="4" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A65" s="4" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A66" s="4" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A67" s="4" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A68" s="4" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A69" s="4" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" ht="52.2" x14ac:dyDescent="0.4">
-      <c r="A70" s="4" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A71" s="4" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A72" s="4" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" ht="52.2" x14ac:dyDescent="0.4">
-      <c r="A73" s="4" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A74" s="4" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A75" s="4" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="B75" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C75" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A76" s="4" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" ht="52.2" x14ac:dyDescent="0.4">
+        <v>644</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="C76" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A77" s="4" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" ht="52.2" x14ac:dyDescent="0.4">
+        <v>645</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C77" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A78" s="4" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" ht="52.2" x14ac:dyDescent="0.4">
+        <v>646</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C78" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A79" s="4" t="s">
-        <v>569</v>
+        <v>647</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="C79" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A80" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="C80" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A81" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="C81" s="4">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B064E4E4-586D-4AE9-88BE-75A9B8DB12F8}">
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:4" s="1" customFormat="1" ht="16.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/소방설비기사_필기_문제은행.xlsx
+++ b/소방설비기사_필기_문제은행.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C600692-0BB1-4027-A1C5-50A3C02517A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40C7E04-E3B8-49F4-BD87-E428F93BC6A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="2" activeTab="4" xr2:uid="{FB57838C-1CAD-4D08-9B84-85A2A61E99B1}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="3" activeTab="5" xr2:uid="{FB57838C-1CAD-4D08-9B84-85A2A61E99B1}"/>
   </bookViews>
   <sheets>
     <sheet name="15년 1회" sheetId="1" r:id="rId1"/>
     <sheet name="15년 2회" sheetId="2" r:id="rId2"/>
     <sheet name="15년 3회" sheetId="3" r:id="rId3"/>
     <sheet name="16년 1회" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheet4" sheetId="5" r:id="rId5"/>
+    <sheet name="16년 2회" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet5" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="966">
   <si>
     <t>문제</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -999,6 +1000,12 @@
   </si>
   <si>
     <t>반파 정류 정현파의 최대값이 1일 때, 실효값과 평균값은?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 
+② 
+③ 
+④ </t>
   </si>
   <si>
     <t>한 코일의 전류가 매초 150A 의 비율로 변화할 때 다른 코 일에 10V 기전력이 발생하였다면 두 코일 상호 인덕턴스(H) 는?</t>
@@ -3126,6 +3133,12 @@
 ② 5
 ③ 7
 ④ 10</t>
+  </si>
+  <si>
+    <t>① 3
+② 5
+③ 7
+④ 10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3200,6 +3213,1530 @@
 ③ 증폭기
 ④ 분파기 </t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위험물안전관리법상 위험물의 지정수량이 틀린것은?</t>
+  </si>
+  <si>
+    <t>① 과산화나트륨 - 50kg
+② 적린 - 100kg
+③ 트리니트로톨루엔 - 200kg
+④ 탄화알루미늄 - 400kg</t>
+  </si>
+  <si>
+    <t>블레비(BLEVE) 현상과 관계가 없는 것은?</t>
+  </si>
+  <si>
+    <t>① 핵분열
+② 가연성액체
+③ 화구(Fire ball)의 형성
+④ 복사열의 대량 방출</t>
+  </si>
+  <si>
+    <t>화재 발생 시 인간의 피난 특성으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>① 수소화 분해반응
+② 탄화반응
+③ 비누화반응
+④ 할로겐화반응</t>
+  </si>
+  <si>
+    <t>① 4
+② 5
+③ 7
+④ 10</t>
+  </si>
+  <si>
+    <t>스테판-볼쯔만의 법칙에 의해 복사열과 절대온도와의 관계를 옳게 설명한 것은?</t>
+  </si>
+  <si>
+    <t>① 복사열은 절대온도의 제곱에 비례한다.
+② 복사열은 절대온도의 4제곱에 비례한다.
+③ 복사열은 절대온도의 제곱에 반비례한다.
+④ 복사열은 절대온도의 4제곱에 반비례한다.</t>
+  </si>
+  <si>
+    <t>물을 사용하여 소화가 가능한 물질은?</t>
+  </si>
+  <si>
+    <t>① 트리메틸알루미늄
+② 나트륨
+③ 칼륨
+④ 적린</t>
+  </si>
+  <si>
+    <t>연쇄반응을 차단하여 소화하는 약제는?</t>
+  </si>
+  <si>
+    <t>① 물
+② 포
+③ 할론 1301
+④ 이산화탄소</t>
+  </si>
+  <si>
+    <t>화재의 종류에 따른 표시 색 연결이 틀린 것은?</t>
+  </si>
+  <si>
+    <t>① 일반화재 - 백색
+② 전기화재 - 청색
+③ 금속화재 - 흑색
+④ 유류화재 - 황색</t>
+  </si>
+  <si>
+    <t>제4류 위험물의 화재시 사용되는 주된 소화방법은?</t>
+  </si>
+  <si>
+    <t>① 물을 뿌려 냉각한다.
+② 연소물을 제거한다.
+③ 포를 사용하여 질식 소화한다.
+④ 인화점 이하로 냉각한다.</t>
+  </si>
+  <si>
+    <t>화씨 95도를 켈빈(Kelvin)온도로 나타내면 약 몇 K인가?</t>
+  </si>
+  <si>
+    <t>① 0.5
+② 1.0
+③ 1.5
+④ 2.0</t>
+  </si>
+  <si>
+    <t>폭굉(Detonation)에 관한 설명으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>① 연소속도가 음속보다 느릴 때 나타난다.
+② 온도의 상승과 충격파의 압력에 기인한다.
+③ 압력상승은 폭연의 경우보다 크다.
+④ 폭굉의 유도거리는 배관의 지름과 관계가 있다.</t>
+  </si>
+  <si>
+    <t>제1종 분말 소화약제의 열분해 반응식으로 옳은 것은?</t>
+  </si>
+  <si>
+    <t>굴뚝효과에 관한 설명으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>분말소화약제 중 담홍색 또는 황색으로 착색하여 사용하는 것은?</t>
+  </si>
+  <si>
+    <t>① 탄산수소나트륨
+② 탄산수소칼륨
+③ 제1인산암모늄
+④ 탄산수소칼륨과 요소와의 반응물</t>
+  </si>
+  <si>
+    <t>화재 및 폭발에 관한 설명으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>위험물에 관한 설명으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>① 유기금속화합물인 사에틸납은 물로 소화할 수 없다.
+② 황린은 자연발화를 막기 위해 통상 물 속에 저장한다.
+③ 칼륨, 나트륨은 등유 속에 보관한다.
+④ 유황은 자연발화를 일으킬 가능성이 없다.</t>
+  </si>
+  <si>
+    <t>알킬알루미늄 화재에 적합한 소화약제는?</t>
+  </si>
+  <si>
+    <t>제어계가 부정확하고 신뢰성은 없으나 출력과 입력이 서로 독립인 제어계는?</t>
+  </si>
+  <si>
+    <t>① 자동 제어계
+② 개회로 제어계
+③ 폐회로 제어계
+④ 피드백 제어계</t>
+  </si>
+  <si>
+    <t>제어량을 어떤 일정한 목표값으로 유지하는 것을 목적으로 하는 제어방식은?</t>
+  </si>
+  <si>
+    <t>① 정치 제어
+② 추종 제어
+③ 프로그램 제어
+④ 비율 제어</t>
+  </si>
+  <si>
+    <t>① 톰슨 효과
+② 제어백 효과
+③ 펠티에 효과
+④ 펀치 효과</t>
+  </si>
+  <si>
+    <t>① 0.05
+② 0.83
+③ 1.25
+④ 1.5</t>
+  </si>
+  <si>
+    <t>① 제어량
+② 주 피드백신호
+③ 기준입력
+④ 조작량</t>
+  </si>
+  <si>
+    <t>변압기의 내부회로 고장검출용으로 사용되는 계전기는?</t>
+  </si>
+  <si>
+    <t>① 비율차동계전기
+② 과전류계전기
+③ 온도계전기
+④ 접지계전기</t>
+  </si>
+  <si>
+    <t>단상 반파정류회로에서 출력되는 전력은?</t>
+  </si>
+  <si>
+    <t>① 입력전압의 제곱에 비례한다.
+② 입력전압에 비례한다.
+③ 부하저항에 비례한다.
+④ 부하임피던스에 비례한다.</t>
+  </si>
+  <si>
+    <t>100Ω인 저항 3개를 같은 전원에 △결선으로 접속할 때와 Y 결선으로 접속할 때, 선전류의 크기의 비는?</t>
+  </si>
+  <si>
+    <t>① 3
+② 1/3
+③ √3
+④ 1/√3</t>
+  </si>
+  <si>
+    <t>① 포토 트랜지스터
+② 서미스터
+③ 바리스터
+④ IC</t>
+  </si>
+  <si>
+    <t>변류기에 결선된 전류계가 고장이 나서 교환하는 경우 옳은 방법은?</t>
+  </si>
+  <si>
+    <t>① 6.19
+② 6.29
+③ 6.39
+④ 6.88</t>
+  </si>
+  <si>
+    <t>전류에 의한 자계의 세기를 구하는 법칙은?</t>
+  </si>
+  <si>
+    <t>① 쿨롱의 법칙
+② 페러데이의 법칙
+③ 비오사바르의 법칙
+④ 렌츠의 법칙</t>
+  </si>
+  <si>
+    <t>그림과 같은 회로에서 2Ω에 흐르는 전류는 몇 A인가? (단, 저항의 단위는 모두 Ω이다.)</t>
+  </si>
+  <si>
+    <t>① 0.8
+② 1.0
+③ 1.2
+④ 2.0</t>
+  </si>
+  <si>
+    <t>논리식 Xㆍ(X+Y)를 간략화 하면?</t>
+  </si>
+  <si>
+    <t>① X
+② Y
+③ X+Y
+④ XㆍY</t>
+  </si>
+  <si>
+    <t>그림과 같은 다이오드 논리회로의 명칭은?</t>
+  </si>
+  <si>
+    <t>① NOT 회로
+② AND 회로
+③ OR 회로
+④ NAND 회로</t>
+  </si>
+  <si>
+    <t>i=50sin⍵t인 교류전류의 평균값은 약 몇 A 인가?</t>
+  </si>
+  <si>
+    <t>① 25
+② 31.8
+③ 35.9
+④ 50</t>
+  </si>
+  <si>
+    <t>그림과 같은 계전기 접점회로를 논리식으로 나타내면?</t>
+  </si>
+  <si>
+    <t>연소 우려가 있는 건축물의 구조에 대한 기준중 다음 보기 (㉠),(㉡)에 들어갈 수치로 알맞은 것은?</t>
+  </si>
+  <si>
+    <t>① 길이가 1.3km 인 지하가 중 터널
+② 연면적 600m2인 볼링장
+③ 연면적 500m2인 산후조리원
+④ 지정수량 100배의 특수가연물을 저장하는 창고</t>
+  </si>
+  <si>
+    <t>① 2.5m 이하
+② 3.5m 이하
+③ 4.5m 이하
+④ 5.5m 이하</t>
+  </si>
+  <si>
+    <t>소방시설업 등록사항의 변경신고 사항이 아닌 것은?</t>
+  </si>
+  <si>
+    <t>① 상호
+② 대표자
+③ 보유설비
+④ 기술인력</t>
+  </si>
+  <si>
+    <t>다음 중 그 성질이 자연발화성 물질 및 금수성물질인 제3류 위험물에 속하지 않는 것은?</t>
+  </si>
+  <si>
+    <t>① 황린
+② 황화린
+③ 칼륨
+④ 나트륨</t>
+  </si>
+  <si>
+    <t>① 유도등
+② 구조대
+③ 피난사다리
+④ 완강기</t>
+  </si>
+  <si>
+    <t>완공된 소방시설 등의 성능시험을 수행하는 자는?</t>
+  </si>
+  <si>
+    <t>① 소방시설공사업자
+② 소방공사감리업자
+③ 소방시설설계업자
+④ 소방기구제조업자</t>
+  </si>
+  <si>
+    <t>소방본부장 또는 소방서장이 소방특별조사를 하고자 하는 때에는 며칠 전에 관계인에게 서면으로 알려야 하는가?</t>
+  </si>
+  <si>
+    <t>① 1일
+② 3일
+③ 5일
+④ 7일</t>
+  </si>
+  <si>
+    <t>소방시설공사업자가 소방시설공사를 하고자 하는 경우 소방 시설공사 착공신고서를 누구에게 제출해야 하는가?</t>
+  </si>
+  <si>
+    <t>① 시ㆍ도지사
+② 국민안전처장관
+③ 한국소방시설협회장
+④ 소방본부장 또는 소방서장</t>
+  </si>
+  <si>
+    <t>① 시ㆍ도지사
+② 국민안전처장관
+③ 소방서장
+④ 소방본부장</t>
+  </si>
+  <si>
+    <t>① 0.5
+② 0.6
+③ 1
+④ 2</t>
+  </si>
+  <si>
+    <t>① 200만원 이하의 벌금
+② 300만원 이하의 벌금
+③ 3년 이하의 징역 또는 1500만원 이하의 벌금
+④ 5년 이하의 징역 또는 3000만원 이하의 벌금</t>
+  </si>
+  <si>
+    <t>형식승인을 얻어야 할 소방용품이 아닌 것은?</t>
+  </si>
+  <si>
+    <t>① 감지기
+② 휴대용 비상조명등
+③ 소화기
+④ 방염액</t>
+  </si>
+  <si>
+    <t>특정소방대상물의 근린생활시설에 해당되는 것은?</t>
+  </si>
+  <si>
+    <t>① 7일
+② 14일
+③ 30일
+④ 60일</t>
+  </si>
+  <si>
+    <t>① 역충전 방지 조치
+② 자동 직류전환 조치
+③ 계속충전 유지조치
+④ 접지 조치</t>
+  </si>
+  <si>
+    <t>① 직류는 1500V 이하, 교류는 1000V 이하인 것
+② 직류는 15000V 이하, 교류는 750V 이하인 것
+③ 직류는 1500V 를, 교류는 1000V 를 넘고 7000V 이하인 것
+④ 직류는 1500V 를, 교류는 750V 를 넘고 7000V 이하인 것</t>
+  </si>
+  <si>
+    <t>① 15
+② 25
+③ 35
+④ 45</t>
+  </si>
+  <si>
+    <t>누전경보기의 수신부의 설치 장소로서 옳은 것은?</t>
+  </si>
+  <si>
+    <t>자동화재탐지설비 감지기의 구조 및 기능에 대한 설명으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>자동화재탐지설비의 연기복합형 감지기를 설치할 수 없는 부착높이는?</t>
+  </si>
+  <si>
+    <t>① 4m 이상 8m 미만
+② 8m 이상 15m 미만
+③ 15m 이상 20m 미만
+④ 20m 이상</t>
+  </si>
+  <si>
+    <t>3종 연기감지기의 설치기준 중 다음 ( )안에 알맞은 것으로 연결된 것은?</t>
+  </si>
+  <si>
+    <t>① ㉠ 15, ㉡ 10
+② ㉠ 20, ㉡ 10
+③ ㉠ 30, ㉡ 15
+④ ㉠ 30, ㉡ 20</t>
+  </si>
+  <si>
+    <t>비상방송설비의 배선에 대한 설치기준으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>무선통신보조설비의 설치기준으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>① 0.5
+② 5
+③ 10
+④ 20</t>
+  </si>
+  <si>
+    <t>지상 4층인 교육연구시설에 적응성이 없는 피난기구는?</t>
+  </si>
+  <si>
+    <t>① 완강기
+② 구조대
+③ 피난교
+④ 미끄럼대</t>
+  </si>
+  <si>
+    <t>대형피난구유도등의 설치장소가 아닌 것은?</t>
+  </si>
+  <si>
+    <t>① 위락시설
+② 판매시설
+③ 지하철역사
+④ 아파트</t>
+  </si>
+  <si>
+    <t>① 2
+② 3
+③ 10
+④ 20</t>
+  </si>
+  <si>
+    <t>비상조명등의 설치제외 장소가 아닌 것은?</t>
+  </si>
+  <si>
+    <t>① 의원의 거실
+② 경기장의 거실
+③ 의료시설의 거실
+④ 종교시설의 거실</t>
+  </si>
+  <si>
+    <t>1개 층에 계단참이 4개 있을 경우 계단통로 유도등은 최소 몇 개 이상 설치해야 하는가?</t>
+  </si>
+  <si>
+    <t>① 1개
+② 2개
+③ 3개
+④ 4개</t>
+  </si>
+  <si>
+    <t>① 본능적으로 평상시 사용하는 출입구를 사용한다.
+② 최초로 행동을 개시한 사람을 따라서 움직인다.
+③ 공포감으로 인해서 빛을 피하여 어두운 곳으로 몸을 숨긴다.
+④ 무의식 중에 발화 장소의 반대쪽으로 이동한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>에스테르가 알칼리의 작용으로 가수분해 되어 알코올과 산의알칼리염이 생성되는 반응은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>건축물이 내화구조 바닥이 철근콘크리트조 또는 철골철근콘크리트조인 경우 두께가 몇 cm 이상이어야 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 178
+② 252
+③ 308
+④ 368</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소화기구는 바닥으로부터 높이 몇 m 이하의 곳에 비치하여야 하는가? (단, 자동소화장치를 제외한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>증발잠열을 이용하여 가연물의 온도를 떨어뜨려 화재를 진압하는 소화방법은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 건물내ㆍ외부의 온도차에 따른 공기의 흐름현상이다.
+② 굴뚝효과는 고층건물에서는 잘 나타나지 않고 저층건물에서 주로 나타난다.
+③ 평상시 건물 내의 기류분포를 지배하는 중요요소이며 화재 시 연기의 이동에 큰 영향을 미친다.
+④ 건물외부의 온도가 내부의 온도보다 높은 경우 저층부에서는 내부에서 외부로 공기의 흐름이 생긴다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 메탄가스는 공기보다 무거우므로 가스 탐지부는 가스기구의 직하부에 설치한다.
+② 옥외저장탱크의 방유제는 화재 시 화재의 확대를 방지하기 위한 것이다.
+③ 가연성 분진이 공기 중에 부유하면 폭발할 수도 있다.
+④ 마그네슘의 화재 시 주수 소화는 화재를 확대할 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 물
+② 이산화탄소
+③ 팽창질석
+④ 할로겐화합물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서로 다른 두 개의 금속도선 양끝을 연결하여 폐회로를 구성한 후, 양단에 온도차를 주었을 때 두 접점사이에서 기전력이 발생하는 효과는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일정전압의 직류전원에 저항을 접속하고 전류를 흘릴 때 전류의 값을 20% 감소시키기 위한 저항값은 처음의 몇 배인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제어량을 조절하기 위하여 제어 대상에 주어지는 양으로 제어부의 출력이 되는 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한 조각의 실리콘 속에 많은 트랜지스터, 다이오드, 저항 등을 넣고 상호배선을 하여 하나의 회로에서의 기능을 갖게한 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 변류기의 2차를 개방시키고 한다.
+② 변류기의 2차를 단락시키고 한다.
+③ 변류기의 2차를 접지시키고 한다.
+④ 변류기에 피뢰기를 달고 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단상변압기 권수비 a = 8이고, 1차 교류전압은 110V 이다. 변압기 2차 전압을 단상 반파 정류회로를 이용하여 정류했을 때 발생하는 직류전압의 평균치는 약 몇 V 인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 1×10⁴
+② 2×10⁴
+③ 3×10⁴
+④ 4×10⁴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공기 중에 1×10^-7C의 (+)전하가 있을 때, 이 전하로부터 15cm의 거리에 있는 점의 전장의 세기는 몇 V/m 인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16234a</t>
+  </si>
+  <si>
+    <t>16235a</t>
+  </si>
+  <si>
+    <t>선간전압 E[V]의 3상 평형전원에 대칠 3상 저항부하 R[Ω] 이 그림과 같이 접속되었을 때 a, b 두 상간에 접속된 전력계의 지시값이 W[W]라면 C상의 전류는 몇 A 인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단상 변압기 3대를 △결선하여 부하에 전력을 공급하고 있는데, 변압기 1대의 고장으로 V결선을 한 경우 고장 전의 몇 % 출력을 낼 수 있는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 51.6
+② 53.6
+③ 55.7
+④ 57.7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16238a</t>
+  </si>
+  <si>
+    <t>16240a</t>
+  </si>
+  <si>
+    <t>① 청색
+② 적색
+③ 흑색
+④ 백색</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① ㉠5, ㉡ 10
+② ㉠6, ㉡ 10
+③ ㉠10, ㉡ 5
+④ ㉠10, ㉡ 6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16241a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위험물 제조소에서 저장 또는 취급하는 위험물에 따른 주의사항을 표시한 게시판 중 화기엄금을 표시하는 게시판의 바탕색은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 중 자동화재탐지설비를 설치해야 하는 특정소방대상물은?(관련 규정 개정전 문제로 여기서는 기존 정답인 1번을 누르면 정답 처리됩니다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소방요수시설 중 저수조 설치 시 지면으로부터 낙차 기준은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>옥내주유취급소에 있어서 당해 사무소 등의 출입구 및 피난구와 당해 피난구로 통하는 통로ㆍ계단 및 출입구에 설치해야 하는 피난설비는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 제1류 : 산화성 고체
+② 제2류 : 가연성 고체
+③ 제4류 : 인화성 액체
+④ 제6류 : 인화성 고체</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① ㉠ : 소방청장, ㉡ : 소방청장
+② ㉠ : 소방청장, ㉡ : 시ㆍ도지사
+③ ㉠ : 시ㆍ도지사, ㉡ : 시ㆍ도지사
+④ ㉠ : 소방본부장, ㉡ : 시ㆍ도지사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소방의 역사와 안전문화를 발전시키고 국민의 안전위식을 높이기 위하여 ㉠소방박물관과 ㉡소방체험관을 설립 및 운영할 수 있는 사람은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 중 위험물별 성질로서 틀린 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도시의 건물 밀집지역 등 화재가 발생할 우려가 높거나 화재가 발생하는 경우 그로 인하여 피해가 클 것으로 예상되는 일정한 구역을 화재예방강화지구로 지정할 수 있는 권한을 가진 사람은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1급 소방안전관리대상물의 소방안전관리에 관한 시험응시 자격자의 기준으로 옳은 것은?(관련 규정 개정전 문제로 여기서는 기존 정답인 3번을 누르면 정답 처리됩니다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 1급 소방안전관리대상물의 소방안전관리에 관한 강습교육을 수료한 후 1년이 경과되지 아니한 자
+② 1급 소방안전관리대상물의 소방안전관리에 관한 강습교육을 수료한 후 1년 6개월이 경과되지 아니한 자
+③ 1급 소방안전관리대상물의 소방안전관리에 관한 강습 육을 수료한 후 2년이 경과되지 아니한 자
+④ 1급 소방안전관리대상물의 소방안전관리에 관한 강습교육을 수료한 후 3년이 경과되지 아니한 자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화재예방, 소방시설 설치ㆍ유지 및 안전관리에 관한 법률상 소방시설 등에 대한 자체점검 중 종합정밀점검 대상기준으로 옳지 않은 것은?(2021년 07월 12일 개정된 규정 적용 됨)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 제연설비가 설치된 터널
+② 노래연습장으로서 연면적이 2000m² 이상인 것
+③ 물분무등소화설비가 설치된 아파트로서 연면적 3000m² 이상이고 11층 이상인 것
+④ 소방대가 근무하지 않는 국공립학교 중 연면적이 1000m²이상인 것으로서 자동화재탐지설비가 설치된 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보일러 등의 위치ㆍ구조 및 관리와 화재예방을 위하여 불의 사용에 있어서 지켜야 하는 사항 중 보일러에 경유ㆍ등유 등 액체연료를 사용하는 경우에 연료탱크는 보일러 본체로부터 수평거리 최소 몇 m 이상의 간격을 두어 설치해야 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위력을 사용하여 출동한 소방대의 화재진압ㆍ인명구조 또는 구급활동을 방해하는 행위를 한 자에 대한 벌칙 기준은?(관련 규정 개정전 문제로 여기서는 기존 정답인 4번을 누르면 정답 처리됩니다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 전시장
+② 기숙사
+③ 유치원
+④ 의원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신축ㆍ증축ㆍ개축ㆍ재축ㆍ대수선 또는 용도변경으로 해당 특정소방대상물의 소방안전관리자를 신규로 선임하는 경우 해당 특정소방대상물의 관계인은 특정소방대상물의 완공일로부터 며칠 이내에 소방안전관리자를 선임하여야 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 혼합기는 신호의 전송로가 분기되는 장소에 설치하는 장치를 말한다.
+② 분배기는 서로 다른 주파수의 합성된 신호를 분리하기 위해서 사용하는 장치를 말한다.
+③ 증폭기는 두 개 이상의 입력 신호를 원하는 비율로 조합한 출력이 발생되도록 하는 장치를 말한다.
+④ 누설동축케이블은 동축케이블 외부도체에 가느다란 홈을 만들어서 전파가 외부로 새어나갈 수 있도록 한 케이블을 말한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무선통신보조설비의 화재안전기준에서 사용하는 용어의 정의로 옳은 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화재속보설비 속보기의 예비전원을 병렬로 접속하는 경우 필요한 조치는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상벨설비 또는 자동식사이렌설비에 사용하는 벨 등의 음향장치의 설치기준이 틀린 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 음향장치용 전원은 교류전압의 옥내간선으로 하고 배선은 다른 설비와 겸용으로 할 것
+② 음향장치는 정격전압의 80% 전압에서 음향을 발할 수 있도록 할 것
+③ 음향장치의 음량은 부착된 음향장치의 중심으로부터 1m 떨어진 위치에서 90dB 이상일 것
+④ 지구음향장치는 특정소방대상물의 층마다 설치하되, 해당 특정소방대상물의 각 부분으로부터 하나의 음향장치까지의 수평거리가 25m 이하가 되도록 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상콘센트설비의 화재안전기준에서 정하고 있는 저압의 정의는?(2022년 09월 확인된 규정 적용됨)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부착높이가 6m 이고 주요구조부를 내화구조로 한 특정소방 대상물 또는 그 부분에 정온식 스포트형감지기 특종을 설치하고자 하는 경우 바닥면적 몇 m² 마다 1개 이상 설치해야 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 습도가 높은 장소
+② 온도의 변화가급격한 장소
+③ 고주파 발생회로 등에 따른 영향을 받을 우려가 있는 장소
+④ 부식성의 증기ㆍ가스 등이 체류하지 않는 장소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상방송설비는 기동장치에 의한 화재신고를 수신한 후 필요한 음량으로 화재발생상황 및 피난에 유효한 방송이 자동으로 개시될 때까지의 소요시간은 몇 초 이하가 되도록 하여야 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 차동식분포형감지기는 그 기판면을 부착한 정위치로 45° 를 경사시킨 경우 그 기능에 이상이 생기지 않아야 한다.
+② 연기를 감지하는 감지기는 감시챔버로 1.3±0.05mm 크기의 물체가 침입할 수 없는 구조이어야 한다.
+③ 방사성물질을 사용하는 감지기는 그 방사성물질을 밀봉 선원으로 하여 외부에서 직접 접촉할 수 없도록 하여야 한다.
+④ 차동식분포형 감지기로서 공기관식 공기관의 두께는 0.3mm 이상, 바깥지름은 1.9mm 이상이어야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16270a</t>
+  </si>
+  <si>
+    <t>① 배선은 다른 용도의 전선과 동일한 관, 덕트, 몰드 또는 풀박스 등에 설치할 것
+② 전원회로의 배선은 옥내소화전설비의 화재안전기준에 따른 내화배선을 설치할 것
+③ 화재로 인하여 하나의 층의 확성기 또는 배선이 단락 또는 단선되어도 다른 층의 화재통보에 지장이 없도록 할 것
+④ 부속회로의 전로와 대지사이 및 배선상호간의 절연저항은 1경계구역마다 직류 250V 의 절연저항측정기를 사용 하여 측정한 절연저항이 0.1MΩ 이상이 되도록 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 누설동축케이블 또는 동축케이블의 임피던스 50Ω 으로 한다.
+② 누설동축케이블 및 공중선은 고압의 전로로부터 0.5m 이상 떨어진 위치에 설치한다. 거리 300m 이내마다 설치한다.
+③ 무선기기 접속단자 중 지상에 설치하는 접속단자는 보행거리 300m 이내마다 설치한다.
+④ 누설동축케이블의 끝부분에는 무반사 종단저항을 견고하게 설치한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>누전경보기의 수신부의 절연된 충전부와 외함간의 절연저항은 DC 500V의 절연저항계로 측정하는 경우 몇 MΩ 이상이어야 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상콘센트설비의 전원회로에서 하나의 전용회로에 설치하는 비상콘센트는 최대 몇 개 이하로 하여야 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바닥면적이 450m²일 경우 단독경보형감지기의 최소 설치계수는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 30V
+② 60V
+③ 70V
+④ 100V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>누전경보기의 정격전압이 몇 V를 넘는 기구의 금속제 외함에는 접지단자를 설치해야 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>청정소화약제 중 HCFC-22를 82% 포함하고 있는 것은?</t>
+  </si>
+  <si>
+    <t>① IG-541
+② HFC-227ea
+③ IG-55
+④ HCFC BLEND A</t>
+  </si>
+  <si>
+    <t>니트로셀룰로오스에 대한 설명으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>① 질화도가 낮을수록 위험성이 크다.
+② 물을 첨가하여 습윤시켜 운반한다.
+③ 화약의 원료로 쓰인다.
+④ 고체이다.</t>
+  </si>
+  <si>
+    <t>화재실 혹은 화재공간의 단위바닥면적에 대한 등가가연물량 의 값을 화재하중이라 하며 식으로 표시할 경우에는 Q=∑(Gt ㆍ Ht)/H ㆍ A와 같이 표현할 수 있다. 여기에서 H는 무엇을 나타내는가?</t>
+  </si>
+  <si>
+    <t>① 목재의 단위발열량
+② 가연물의 단위발열량
+③ 화재실내 가연물의 전체 발열량
+④ 목재의 단위발열량과 가연물의 단위발열량을 합한 것</t>
+  </si>
+  <si>
+    <t>위험물안전관리법상 위험물의 적재 시 혼재기중 혼재가 가능 한 위험물로 짝지어진 것은? (단, 각 위험물은 지정수량의 10배로 가정한다.)</t>
+  </si>
+  <si>
+    <t>① 질산칼륨과 가솔린
+② 과산화수소와 황린
+③ 철분과 유기과산화물
+④ 등유와 과염소산</t>
+  </si>
+  <si>
+    <t>자연발화의 예방을 위한 대책이 아닌 것은?</t>
+  </si>
+  <si>
+    <t>① 열의 축적을 방지한다.
+② 주위 온도를 낮게 유지한다.
+③ 열전도성을 나쁘게 한다.
+④ 산소와의 접촉을 차단한다.</t>
+  </si>
+  <si>
+    <t>제1종 분말소화약제인 탄산수소나트륨은 어떤색으로 착색되 어 있는가?</t>
+  </si>
+  <si>
+    <t>① 담회색
+② 담홍색
+③ 회색
+④ 백색</t>
+  </si>
+  <si>
+    <t>밀폐된 내화건물의 실내에 화재가 발생했을 때 그 실내의 환 경변화에 대한 설명 중 틀린 것은?</t>
+  </si>
+  <si>
+    <t>① 기압이 강하한다.
+② 산소가 감소된다.
+③ 일산화탄소가 증가한다.
+④ 이산화탄소가 증가한다.</t>
+  </si>
+  <si>
+    <t>할로겐 화합물 소화설비에서 Halon 1211 약제의 분자식은?</t>
+  </si>
+  <si>
+    <t>① CBr ClF
+② CF ClBr 2 2
+③ COl BrF
+④ BrC ClF 2 2</t>
+  </si>
+  <si>
+    <t>조연성가스로만 나열되어 있는 것은?</t>
+  </si>
+  <si>
+    <t>① 질소, 불소, 수증기
+② 산소, 불소, 염소
+③ 산소, 이산화탄소, 오존
+④ 질소, 이산화탄소, 염소</t>
+  </si>
+  <si>
+    <t>다음 중 제거소화 방법과 무관한 것은?</t>
+  </si>
+  <si>
+    <t>① 산불의 확산방지를 위하여 산림의 일부를 벌채한다.
+② 화학반응기의 화재 시 원료 공급관의 밸브를 잠근다.
+④ 유류탱크 화재 시 주변에 있는 유류탱크의 유류를 다른 곳으로 이동시킨다.</t>
+  </si>
+  <si>
+    <t>실내에서 화재가 발생하여 실내의 온도가 21℃에서 650℃ 로 되었다면, 공기의 팽창은 처음의 약 몇 배가 되는가? (단, 대기압은 공기가 유동하여 화재 전후가 같다고 가정한 다.)</t>
+  </si>
+  <si>
+    <t>① 3.14
+② 4.27
+③ 5.69
+④ 6.01</t>
+  </si>
+  <si>
+    <t>연기에 의한 감광계수가 0.1m-1, 가시거리가 20~30m일 때 의 상황을 옳게 설명한 것은?</t>
+  </si>
+  <si>
+    <t>① 건물 내부에 익숙한 사람이 피난에 지장을 느낄 정도
+② 연기감지기가 작동할 정도
+③ 어두운 것을 느낄 정도
+④ 앞이 거의 보이지 않을 정도</t>
+  </si>
+  <si>
+    <t>물의 물리ㆍ화학적 성질로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>① 증발잠열은 539.6cal/g으로 다른 물질에 비해 매우 큰 편이다.
+② 대기압하에서 100℃의 물이 액체에서 수증기로 바뀌면 체적은 약 1603배 정도 증가한다.
+③ 수소 1분자와 산소 1/2분자로 이루어져 있으며 이들 사 이의 화학결합은 극성 공유결합이다.
+④ 분자간의 결합은 쌍극자-쌍극자 상호작용의 일종인 산소 결합에 의해 이루어진다.</t>
+  </si>
+  <si>
+    <t>다음 중 증기비중이 가장 큰 것은?</t>
+  </si>
+  <si>
+    <t>① 이산화탄소
+② 할론 1301
+③ 할론 1211
+④ 할론 2402</t>
+  </si>
+  <si>
+    <t>보일 오버(Boil over)현상에 대한 설명으로 옳은 것은?</t>
+  </si>
+  <si>
+    <t>① 아래층에서 발생한 화재가 위층으로 급격히 옮겨 가는 현상
+② 연소유의 표면이 급격히 증발하는 현상
+③ 기름이 뜨거운 표면 아래에서 끓는 현상
+④ 탱크 저부의 물이 급격히 증발하여 기름이 탱크밖으로 화재를 동반하여 방출하는 현상</t>
+  </si>
+  <si>
+    <t>건축물의 화재성상 중 내화건축물의 화재성상으로 옳은 것 은?</t>
+  </si>
+  <si>
+    <t>① 저온 장기형
+② 고온 단기형
+③ 고온 장기형
+④ 저온 단기형</t>
+  </si>
+  <si>
+    <t>정전기에 의한 발화과정으로 옳은 것은?</t>
+  </si>
+  <si>
+    <t>① 방전→전하의 축적→전하의 발생→발화
+② 전하의 발생→전하의 축적→방전→발화
+③ 전하의 발생→방전→전하의 축적→발화
+④ .전하의 축적→방전→전하의 발생→발화</t>
+  </si>
+  <si>
+    <t>피난계획의 일반원칙 중 Fool proof 원칙에 해당하는 것은?</t>
+  </si>
+  <si>
+    <t>① 저지능인 상태에서도 쉽게 식별이 가능하도록 그림이나 색채를 이용하는 원칙
+② 피난설비를 반드시 이동식으로 하는 원칙
+③ 한 가지 피난기구가 고장이 나도 다른 수단을 이용할 수
+④ 피난설비를 첨단화된 전자식으로 하는 원칙</t>
+  </si>
+  <si>
+    <t>칼륨에 화재가 발생할 경우에 주수를 하면 안되는 이유로 가장 옳은 것은?</t>
+  </si>
+  <si>
+    <t>① 산소가 발생하기 때문에
+② 질소가 발생하기 때문에
+③ 수소가 발생하기 때문에
+④ 수증기가 발생하기 때문에</t>
+  </si>
+  <si>
+    <t>분말소화약제의 열분해 반응식 중 다음 ( )안에 알맞은 화학 식은?</t>
+  </si>
+  <si>
+    <t>① CO
+② CO 2
+③ Na
+④ Na 2</t>
+  </si>
+  <si>
+    <t>전원과 부하가 다같이 △결선된 3상 평형회로가 있다. 전원 전압이 200V, 부하 1상의 임피던스가 4+j3Ω인 경우 선전류 는 몇 A 인가?</t>
+  </si>
+  <si>
+    <t>① 40/√3
+② 40/3
+③ 40
+④ 40√3</t>
+  </si>
+  <si>
+    <t>온도 측정을 위하여 사용하는 소자로서 온도-저항 부특성을 가지는 일반적인 소자는?</t>
+  </si>
+  <si>
+    <t>① 노즐플래퍼
+② 서미스터
+③ 앰플리다인
+④ 트랜지스터</t>
+  </si>
+  <si>
+    <t>자기장 내에 있는 도체에 전류를 흘리면 힘이 작용한다. 이 힘을 무엇이라고 하는가?</t>
+  </si>
+  <si>
+    <t>① 자속력
+② 기전력
+③ 전기력
+④ 전자력</t>
+  </si>
+  <si>
+    <t>히스테리시스 곡선의 종축과 횡축은?</t>
+  </si>
+  <si>
+    <t>① 종축 : 자속밀도, 횡축 : 투자율
+② 종축 : 자계의 세기, 횡축 : 투자율
+③ 종축 : 자계의 세기, 횡축 : 자속밀도
+④ 종축 : 자속밀도, 횡축 :자계의 세기</t>
+  </si>
+  <si>
+    <t>4단자 정수 A=5/3, B=800, C=1/450, D=5/3 일 때 영상 임피던스 Z01과 Z02는 각각 몇 Ω인가?</t>
+  </si>
+  <si>
+    <t>① Z =300, Z =300
+② Z =600, Z =600 01 02 01 02
+③ Z =800, Z =800
+④ Z =1000, Z =1000 01 02 01 02</t>
+  </si>
+  <si>
+    <t>200Ω의 저항을 가진 경종 10개와 50Ω의 저항을 가진 표시 등 3개가 있다. 이들을 모두 직렬로 접속할 때의 합성저항 은 몇 Ω인가?</t>
+  </si>
+  <si>
+    <t>① 250
+② 1250
+③ 1750
+④ 2150</t>
+  </si>
+  <si>
+    <t>그림과 같은 무접점회로는 어떤 논리회로인가?</t>
+  </si>
+  <si>
+    <t>① NOR
+② OR
+③ NAND
+④ AND</t>
+  </si>
+  <si>
+    <t>지시계기에 대한 동작원리가 틀린 것은?</t>
+  </si>
+  <si>
+    <t>① 열전형 계기 - 대전된 도체 사이에 작용하는 정전력을 이용
+② 가동 철편형 계기 - 전류에 의한 자기장이 연철편에 작 용하는 힘을 이용
+③ 전류력계형 계기 - 전류 상호간에 작용하는 힘을 이용
+④ 유도형 계기 - 회전 자기장 또는 이동 자기장과 이것에 의한 유도정류와의 상호작용을 이용</t>
+  </si>
+  <si>
+    <t>다음 중 쌍방향성 사이리스터인 것은?</t>
+  </si>
+  <si>
+    <t>① 브리지 정류기
+② SCR
+③ IGBT
+④ TRIAC</t>
+  </si>
+  <si>
+    <t>SCR의 양극 전류가 10A 일 때 게이트 전류를 반으로 줄이 면 양극 전류는 몇 A 인가?</t>
+  </si>
+  <si>
+    <t>① 20
+② 10
+③ 5
+④ 0.1</t>
+  </si>
+  <si>
+    <t>어떤 측정계기의 지시값을 M, 참값을 T라 할 때 보정율은?</t>
+  </si>
+  <si>
+    <t>자기인덕턴스 L , L 가 각각 4mH, 9mH 인 두 코일이 이 1 2 상적인 결합이 되었다면 상호인덕턴스는 몇 mH인가? (단, 결합계수는 1 이다.)</t>
+  </si>
+  <si>
+    <t>① 6
+② 12
+③ 24
+④ 36</t>
+  </si>
+  <si>
+    <t>국제 표준 연동 고유저항은 몇 Ωㆍm인가?</t>
+  </si>
+  <si>
+    <t>① 1.7241×10-9
+② 1.7241×10-8
+③ 1.7241×10-7
+④ 1.7241×10-6</t>
+  </si>
+  <si>
+    <t>도너(donor)와 억셉터(acceptor)의 설명 중 틀린 것은?</t>
+  </si>
+  <si>
+    <t>① 반도체 결정에서 Ge이나 Si에 넣는 5가의 불순물을 도 너라고 한다.
+② 반도체 결정에서 Ge이나 Si에 넣는 3가의 불순물에는 In, Ga, B 등이 있다.
+③ 진성반도체는 불순물이 전혀 섞이지 않은 반도체이다.</t>
+  </si>
+  <si>
+    <t>변압기의 철심구조를 여러 겹으로 성층시켜 사용하는 이유 는 무엇인가?</t>
+  </si>
+  <si>
+    <t>① 와전류로 인한 전력손실을 감소시키기 위해
+② 전력공급 능력을 높이기 위해
+③ 변압비를 크게 하기 위해
+④ 변압기의 중량을 적게 하기 위해</t>
+  </si>
+  <si>
+    <t>자동제어계를 제어목적에 의해 분류한 경우를 설명한 것 중 틀린 것은?</t>
+  </si>
+  <si>
+    <t>① 정치제어 : 제어량을 주어진 일정목표로 유지시키기 위 한 제어
+② 추종제어 : 목표치가 시간에 따라 일정한 변화를 하는 제어
+③ 프로그램제어 : 목표치가 프로그램대로 변하는 제어
+④ 서보제어 : 선박의 방향제어계인 서보제어는 정치제어와 같은 성질</t>
+  </si>
+  <si>
+    <t>V=141sin377t[V]인 정현파 전압의 주파수는 몇 Hz인가?</t>
+  </si>
+  <si>
+    <t>① 50
+② 55
+③ 60
+④ 65</t>
+  </si>
+  <si>
+    <t>그림과 같은 정류회로에서 부하 R에 흐르는 직류전류의 크 기는 약 몇 A인가? (단, V=200V, R=20√2Ω이며, 이상적인 다이오드이다.)</t>
+  </si>
+  <si>
+    <t>① 3.2
+② 3.8
+③ 4.4
+④ 5.2</t>
+  </si>
+  <si>
+    <t>계단변화에 대하여 잔류편차가 없는 것이 장점이며, 간헐현 상이 있는 제어계는?</t>
+  </si>
+  <si>
+    <t>① 비례제어계
+② 비례미분제어계
+③ 비례적분제어계
+④ 비례적분미분제어계</t>
+  </si>
+  <si>
+    <t>그림과 같은 트랜지스터를 사용한 정전압회로에서 Q 의 역 1 할로서 옳은 것은?</t>
+  </si>
+  <si>
+    <t>① 증폭용
+② 비교부용
+③ 제어용
+④ 기준부용
+① 황화린 - 100kg
+② 유황 - 300kg
+③ 철분 - 500kg
+④ 인화성고체 - 1000kg</t>
+  </si>
+  <si>
+    <t>소방시설공사업법상 소방시설업 등록신청 신청서 및 첨부서 류에 기재되어야 할 내용이 명확하지 아니한 경우 서류의 보완 기간은 며칠 이내인가?</t>
+  </si>
+  <si>
+    <t>① 14
+② 10
+③ 7
+④ 5</t>
+  </si>
+  <si>
+    <t>특정소방대상물 중 의료시설에 해당되지 않는 것은?</t>
+  </si>
+  <si>
+    <t>① 노숙인 재활시설
+② 장애인 의료재활시선
+③ 정신의료기관
+④ 마약진료소</t>
+  </si>
+  <si>
+    <t>소방용품의 형식승인을 반드시 취소하여야 하는 경우가 아 닌 것은?</t>
+  </si>
+  <si>
+    <t>① 거짓 또는 부정한 방법으로 형식승인을 받은 경우
+② 시험시설의 시설기준에 미달되는 경우
+③ 거짓 또는 부정한 방법으로 제품검사를 받은 경우
+④ 변경승인을 받지 아니한 경우</t>
+  </si>
+  <si>
+    <t>위험물 제조소 게시판의 바탕 및 문자의 색으로 올바르게 연결된 것은?</t>
+  </si>
+  <si>
+    <t>① 바탕- 백색, 문자 -청색
+② 바탕- 청색, 문자 -흑색
+③ 바탕- 흑색, 문자 -백색
+④ 바탕- 백색, 문자 -흑색</t>
+  </si>
+  <si>
+    <t>소방기본법상 소방용수시설의 저수조는 비면으로부터 낙차 가 몇 m 이하가 되어야 하는가?</t>
+  </si>
+  <si>
+    <t>① 3.5
+② 4
+③ 4.5
+④ 6</t>
+  </si>
+  <si>
+    <t>화재예방, 소방시설 설치ㆍ유지 및 안전관리에 관한 법률에 따른 소방안전관리 업무를 하지 아니한 특정소방대상물의 관계인에게는 몇 만원 이하의 과태료를 부과하는가?(2021년 12월 28일 개정된 규정 적용됨)</t>
+  </si>
+  <si>
+    <t>작동기능점검을 실시한 자는 작동기능점검 실시결과 보고서 를 며칠 이내에 소방본부장 또는 소방서장에게 제출해야 하 는가?(2020년 8월 14일 변경된 규정 적용됨)</t>
+  </si>
+  <si>
+    <t>① 7
+② 10
+③ 20
+④ 30</t>
+  </si>
+  <si>
+    <t>고형알코올 그 밖에 1기압 상태에서 인화점이 40℃ 미만인 고체에 해당하는 것은?</t>
+  </si>
+  <si>
+    <t>① 가연성 고체
+② 산화성 고체
+③ 인화성 고체
+④ 자연발화성물질</t>
+  </si>
+  <si>
+    <t>소방기본법상의 벌칙으로 5년이하의 징역 또는 3000만원 이하의 벌금에 해당하지 않는 것은?(관련 규정 개정전 문제 로 여기서는 기존 정답인 2번을 누르면 정답 처리됩니다.)</t>
+  </si>
+  <si>
+    <t>① 소방자동차가 화재진압 및 구조ㆍ구급활동을 위하여 출 동할 때 그 출동을 방해한 자
+② 사람을 구출하거나 불이 번지는 것을 막기 위하여 불이 번질 우려가 있는 소방대상물의 사용제한의 강제처분을 방해한 자
+④ 정당한 사유 없이 소방용수시설의 효용을 해치거나 그 정당한 사용을 방해한 자</t>
+  </si>
+  <si>
+    <t>일반 소방시설 설계업(기계분야)의 영업범위는 공장의 경우 연면적 몇 m2미만의 특정소방대상물에 설치되는 기계분야 소방시설의 설계에 한하는가? (단, 제연설비가 설치되는 특 정소방대상물은 제외한다.)</t>
+  </si>
+  <si>
+    <t>① 10000m2
+② 20000m2
+③ 30000m2
+④ 40000m2</t>
+  </si>
+  <si>
+    <t>소방본부장이 소방특별조사위원회 위원으로 임명하거나 위 촉할 수 있는 사람이 아닌 것은?</t>
+  </si>
+  <si>
+    <t>① 소방시설관리사
+② 과장급 직위 이상의 소방공무원
+③ 소방 관련 분야의 석사학위 이상을 취득한 사람
+④ 소방 관련 법인 또는 단체에서 소방 관련 업무에 3년 이 상 종사한 사람</t>
+  </si>
+  <si>
+    <t>교육연구시설 중 학교 지하층은 바닥면적의 합계가 몇 m2이 상인 경우 연결살수설비를 설치해야 하는가?</t>
+  </si>
+  <si>
+    <t>① 500
+② 600
+③ 700
+④ 1000</t>
+  </si>
+  <si>
+    <t>소방체험관의 설립ㆍ운영권자는?</t>
+  </si>
+  <si>
+    <t>① 국무총리
+② 국민안전처장관
+③ 시ㆍ도지사
+④ 소방본부장 및 소방서장</t>
+  </si>
+  <si>
+    <t>위험물안전관리법상 행정처분을 하고자 하는 경우 청문을 실시해야 하는 것은?</t>
+  </si>
+  <si>
+    <t>① 제조소등 설치허가의 취소
+② 제조소등 영업정지 처분
+③ 탱크시험자의 영업정지
+④ 과징금 부과처분</t>
+  </si>
+  <si>
+    <t>소방장비 등에 대한 국고보조 대상사업의 범위와 기준보조 율은 무엇으로 정하는가?</t>
+  </si>
+  <si>
+    <t>① 총리령
+② 대통령령
+③ 시ㆍ도의 조례
+④ 국토교통부령</t>
+  </si>
+  <si>
+    <t>하자보수 대상 소방시설 중 하자보수 보증기간이 2년이 아 닌 것은?</t>
+  </si>
+  <si>
+    <t>① 유도표시
+② 비상경보설비
+③ 무선통신보조설비
+④ 자동화재탐지설비</t>
+  </si>
+  <si>
+    <t>정기점검의 대상인 제조소등에 해당하지 않는 것은?</t>
+  </si>
+  <si>
+    <t>① 이송취급소
+② 이동탱크저장소
+③ 암반탱크저장소
+④ 판매취급소</t>
+  </si>
+  <si>
+    <t>소방용수시설 중 소화전과 급수탑의 설치기준으로 틀린 것 은?</t>
+  </si>
+  <si>
+    <t>① 소화전은 상수도와 연결하려 지하식 또는 지상식의 구조 로 할 것
+② 소방용호스와 연결하는 소화전의 연결금속구의 구경은 65mm로 할 것
+③ 급수탑 급수배관의 구경은 100mm 이상으로 할 것
+④ 급수탑의 개폐밸브는 지상에서 1.5m 이상 1.8m 이하의 위치에 설치할 것 중 유황만을 저장ㆍ취급하는 옥내탱크저장소에 설치해야 하 는 소화설비는?
+① 옥내소화전설비
+② 옥외소화전설비
+③ 물분무소화설비
+④ 고정식 포소화설비</t>
+  </si>
+  <si>
+    <t>통로유도등의 설치기준 중 틀린 것은?</t>
+  </si>
+  <si>
+    <t>① 거실의 통로가 벽체 등으로 구획된 경우에는 거실통로유 도등을 설치한다.
+② 거실통로유도등은 거실통로에 기둥이 설치된 경우에는 기둥부분의 바닥으로부터 높이 1.5m 이하의 위치에 설 치할 수 있다.
+③ 복도통로유도등은 구부러진 모퉁이 및 보행거리 20m 마 다 설치한다.
+④ 계단통로유도등은 바닥으로부터 높이 1m이하의 위치에 설치한다.</t>
+  </si>
+  <si>
+    <t>비상콘센트설비의 전원회로의 공급용량은 최소 몇 kVA 이상 인 것으로 설치해야 하는가?</t>
+  </si>
+  <si>
+    <t>① 1.5
+② 2
+③ 2.5
+④ 3</t>
+  </si>
+  <si>
+    <t>비상조명등 비상점등 회로의 보호를 위한 기준중 다음 ( )안 에 알맞은 것은?</t>
+  </si>
+  <si>
+    <t>① ㉠ 2, ㉡ 1
+② ㉠ 1.2, ㉡ 3
+③ ㉠ 3, ㉡ 1
+④ ㉠ 2.1, ㉡ 5</t>
+  </si>
+  <si>
+    <t>무선통신보조설비의 누설동축케이블 및 공중선은 고압의 전 류로부터 1.5m 이상 떨어진 위치에 설치해야 하나 그렇게 하지 않아도 되는 경우는?</t>
+  </si>
+  <si>
+    <t>① 해당 전로에 정전기 차폐장치를 유효하게 설치한 경우
+② 금속제 등의 지지금구로 일정한 간격으로 고정한 경우
+③ 끝부분에 무반사 종단저항을 설치한 경우
+④ 불연재료로 구획된 반자 안에 설치한 경우</t>
+  </si>
+  <si>
+    <t>유도등의 전기회로에 점멸기를 설치할 수 있는 장소에 해당 되지 않는 것은? (단, 유도등은 3선식 배선에 따라 상시 충 전되는 구조이다.)</t>
+  </si>
+  <si>
+    <t>① 공연장으로서 어두워야 할 필요가 있는 장소
+② 특정소방대상물의 관계인이 주로 사용하는 장소
+③ 외부광에 따라 피난구 또는 피난방향을 쉽게 식별할 수 있는 장소
+④ 지하층을 제외한 층수가 11층 이상의 장소</t>
+  </si>
+  <si>
+    <t>각 실별 실내의 바닥면적이 25m2인 4개의 실에 단독경보형 감지기를 설치 시 몇 개의 실로 보아야 하는가? (단, 각 실 은 이웃하고 있으며, 벽체 상부가 일부 개방되어 이웃하는</t>
+  </si>
+  <si>
+    <t>③ 3
+④ 4</t>
+  </si>
+  <si>
+    <t>피난기구 중 다수인 피난장비의 설치기준 중 틀린 것은?</t>
+  </si>
+  <si>
+    <t>① 사용 시에 보관실 외측 문이 먼저 열리고 탑승기가 외측 으로 자동으로 전개될 것
+② 하강 시에 탑승기가 건물 외벽이나 돌출물에 충돌하지 않도록 설치할 것
+③ 상ㆍ하층에 설치할 경우에는 탑승기의 하강경로가 중첩 되도록 할 것
+④ 보관실은 건물 외측보다 돌출되지 아니하고, 빗물ㆍ먼지 등으로 부터 장비를 보호할 수 있는 구조 일 것</t>
+  </si>
+  <si>
+    <t>누전경보기 수신부의 기능검사 항목이 아닌 것은?</t>
+  </si>
+  <si>
+    <t>① 충격시험
+② 절연저항실험
+③ 내식성시험
+④ 전원전압 변동시험</t>
+  </si>
+  <si>
+    <t>아파트형 공장의 지하 주차장에 설치된 비상방송용 스피커 의 음량조정기 배선방식은?</t>
+  </si>
+  <si>
+    <t>① 단선식
+② 2선식
+③ 3선식
+④ 복합식</t>
+  </si>
+  <si>
+    <t>공동주택 4층 이상 10층 이하에 적응성이 있는 피난기구 는?(단, 공동주택은 공동주택 관리법 시행령 제 2조의 규정 에 해당하는 공동주택이다.)</t>
+  </si>
+  <si>
+    <t>① 간이완강기
+② 피난용트랩
+③ 미끄럼대
+④ 공기안전매트</t>
+  </si>
+  <si>
+    <t>감지기의 설치기준 중 부착높이 20m이상에 설치되는 광전 식 중 아날로그장식의 감지기는 공칭감지농도 하한값이 감 광율 몇 %/m 미만인 것으로 하는가?</t>
+  </si>
+  <si>
+    <t>연기감지기 설치 시 천장 또는 반자부근에 배기구가 있는 경우에 감지기의 설치위치로 옳은 것은?</t>
+  </si>
+  <si>
+    <t>① 배기구가 있는 그 부근
+② 배기구로부터 가장 먼 곳
+③ 배기구로부터 0.6m 이상 떨어진 곳
+④ 배기구로부터 1.5m 이상 떨어진 곳</t>
+  </si>
+  <si>
+    <t>자동화재탐지설비 배선의 설치기준 중 다음 ( )안에 알맞은 것은?</t>
+  </si>
+  <si>
+    <t>① ㉠ 50Ω 이상, ㉡ 70
+② ㉠ 50Ω 이하, ㉡ 80
+③ ㉠ 40Ω 이상, ㉡ 70
+④ ㉠ 40Ω 이하, ㉡ 80</t>
+  </si>
+  <si>
+    <t>누전경보기의 변류기는 경계전로에 정격전류를 흘리는 경우 그 경계전로의 전압강하는 몇 V 이하여야 하는가? (단, 경 계전로의 전선을 그 변류기에 관통시키는 것은 제외한다.)</t>
+  </si>
+  <si>
+    <t>① 0.3
+② 0.5</t>
+  </si>
+  <si>
+    <t>무선통신보조설비 증폭기의 설치기준으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>① 증폭기는 비상전원이 부착된 것으로 한다.
+② 증폭기의 전면에는 표시등 및 전류계를 설치한다.
+③ 전원은 전기가 정상적으로 공급되는 축전지 또는 교류전 압 옥내간선으로 하고 전원까지의 배선은 전용으로 한 다,
+④ 증폭기의 비상전원용량은 무선통신보조설비 유효하게 30 분 이상 작동시킬 수 있는 것으로 한다.</t>
+  </si>
+  <si>
+    <t>비상콘센트의 배치는 아파트 또는 바닥면적이 1000m2 미만 인 층은 계단의 출입구로부터 몇 m 이내에 설치해야 하는 가? (단. 계단의 부속실을 포함하며 계단이 2 이상 있는 경 우에는 그 중 1개의 계단을 말한다.)</t>
+  </si>
+  <si>
+    <t>① 10
+② 8
+③ 5
+④ 3</t>
+  </si>
+  <si>
+    <t>비상방송설비는 기동장치에 따른 화재신고를 수신한 후 필 요한 음량으로 화재발생 상황 및 피난에 유효한 방송이 자 동으로 개시될 때까지의 소요시간은 몇 초 이하여야 하는 가?</t>
+  </si>
+  <si>
+    <t>① 5
+② 10
+③ 30
+④ 60</t>
+  </si>
+  <si>
+    <t>누전경보기 음향장치의 설치위치로 옳은 것은?</t>
+  </si>
+  <si>
+    <t>① 옥내의 점검에 편리한 장소
+② 옥외 인입선의 제1지점의 부하측의 점검이 쉬운 위치
+③ 수위실 등 상시 사람이 근무하는 장소
+④ 옥외인입선의 제2종 접지선측의 점검이 쉬운 위치</t>
+  </si>
+  <si>
+    <t>광전식 분리형감지기의 설치기준 중 틀린 것은?</t>
+  </si>
+  <si>
+    <t>① 감지기의 광축의 길이는 공칭감시거리 범위 이내 일것
+② 감지기의 송광부와 수광부는 설치된 뒷벽으로부터 1m 이내 위치에 설치할 것
+③ 광축의 높이는 천장 등 (천장의 실내에 면한 부분 또는 상층의 바닥하부면) 높이의 80% 이상일 것
+④ 광축은 나란한 벽으로부터 0.5m 이상 이격하여 설치할 것</t>
+  </si>
+  <si>
+    <t>자동화재속보설비 속보기의 구조에 대한 설명 중 틀린 것 은?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 수동통화용 송수화장치를 설치하여야 한다.
+② 접지전극에 직류전류를 통하는 회로방식을 사용하여야 한다.
+③ 작동 시 그 작동시간과 작동회수를 표시할 수 있는 장치 를 하여야 한다.
+④ 부식에 의한 기계적 기능에 영향을 초래할 우려가 있는 부분은 기계식 내식가공을 하거나 방청가공을 아여야 한 다. 전자문제집 CBT 홈페이지 : www.comcbt.com 기출문제 및 해설집 다운로드 : www.comcbt.com/xe 전자문제집 CBT 앱(구글플레이) : [다운로드] 전자문제집 CBT란? 종이 문제집이 아닌 인터넷으로 문제를 풀고 자동으로 채점하며 모의고사, 오답 노트, 해설까지 제공하는 무료 기출문제 학습 프 로그램으로 실제 시험에서 사용하는 OMR 형식의 CBT를 제공합 니다. PC 버전 및 모바일 버전 완벽 연동 교사용/학생용 관리기능도 제공합니다. 오답 및 오탈자가 수정된 최신 자료와 해설은 전자문제집 CBT 에서 확인하세요. 1 2 3 4 5 6 7 8 9 10
+④ 
+① 
+① 
+③ 
+③ 
+④ 
+① 
+② 
+② 
+③ 11 12 13 14 15 16 17 18 19 20
+① 
+② 
+④ 
+④ 
+④ 
+① 
+② 
+① 
+③ 
+② 21 22 23 24 25 26 27 28 29 30
+④ 
+② 
+④ 
+④ 
+② 
+④ 
+③ 
+① 
+④ 
+② 31 32 33 34 35 36 37 38 39 40
+① 
+① 
+② 
+④ 
+① 
+④ 
+③ 
+① 
+③ 
+③ 41 42 43 44 45 46 47 48 49 50
+② 
+② 
+① 
+② 
+④ 
+③ 
+③ 
+① 
+③ 
+② 51 52 53 54 55 56 57 58 59 60
+① 
+④ 
+③ 
+③ 
+① 
+② 
+④ 
+④ 
+④ 
+③ 61 62 63 64 65 66 67 68 69 70
+① 
+① 
+② 
+① 
+④ 
+① 
+③ 
+③ 
+③ 
+④ 71 72 73 74 75 76 77 78 79 80
+② 
+① 
+② 
+② 
+② 
+③ 
+② 
+③ 
+④ 
+② </t>
   </si>
 </sst>
 </file>
@@ -3290,7 +4827,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3327,11 +4864,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4763,7 +6309,7 @@
     </row>
     <row r="13" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>190</v>
@@ -4775,7 +6321,7 @@
     </row>
     <row r="14" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>191</v>
@@ -4874,7 +6420,7 @@
         <v>205</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C22" s="4">
         <v>1</v>
@@ -4895,10 +6441,10 @@
     </row>
     <row r="24" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C24" s="4">
         <v>4</v>
@@ -4907,10 +6453,10 @@
     </row>
     <row r="25" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A25" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C25" s="4">
         <v>1</v>
@@ -4919,10 +6465,10 @@
     </row>
     <row r="26" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A26" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C26" s="4">
         <v>2</v>
@@ -4931,10 +6477,10 @@
     </row>
     <row r="27" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A27" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C27" s="4">
         <v>4</v>
@@ -4943,10 +6489,10 @@
     </row>
     <row r="28" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A28" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C28" s="4">
         <v>2</v>
@@ -4955,10 +6501,10 @@
     </row>
     <row r="29" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A29" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C29" s="4">
         <v>2</v>
@@ -4967,10 +6513,10 @@
     </row>
     <row r="30" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A30" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C30" s="4">
         <v>3</v>
@@ -4979,10 +6525,10 @@
     </row>
     <row r="31" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A31" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C31" s="4">
         <v>1</v>
@@ -4991,10 +6537,10 @@
     </row>
     <row r="32" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A32" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C32" s="4">
         <v>2</v>
@@ -5003,10 +6549,10 @@
     </row>
     <row r="33" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A33" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C33" s="4">
         <v>3</v>
@@ -5015,24 +6561,24 @@
     </row>
     <row r="34" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A34" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C34" s="4">
         <v>2</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A35" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C35" s="4">
         <v>2</v>
@@ -5041,10 +6587,10 @@
     </row>
     <row r="36" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A36" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C36" s="4">
         <v>1</v>
@@ -5053,10 +6599,10 @@
     </row>
     <row r="37" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A37" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C37" s="4">
         <v>3</v>
@@ -5065,10 +6611,10 @@
     </row>
     <row r="38" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A38" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C38" s="4">
         <v>1</v>
@@ -5077,10 +6623,10 @@
     </row>
     <row r="39" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A39" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C39" s="4">
         <v>1</v>
@@ -5089,10 +6635,10 @@
     </row>
     <row r="40" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A40" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C40" s="4">
         <v>4</v>
@@ -5101,7 +6647,7 @@
     </row>
     <row r="41" spans="1:4" s="11" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A41" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B41" s="10">
         <v>15240</v>
@@ -5110,15 +6656,15 @@
         <v>3</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A42" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C42" s="4">
         <v>4</v>
@@ -5127,7 +6673,7 @@
     </row>
     <row r="43" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A43" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>108</v>
@@ -5139,10 +6685,10 @@
     </row>
     <row r="44" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A44" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C44" s="4">
         <v>3</v>
@@ -5151,10 +6697,10 @@
     </row>
     <row r="45" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A45" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C45" s="4">
         <v>2</v>
@@ -5163,10 +6709,10 @@
     </row>
     <row r="46" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A46" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C46" s="4">
         <v>4</v>
@@ -5175,10 +6721,10 @@
     </row>
     <row r="47" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A47" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C47" s="4">
         <v>1</v>
@@ -5187,24 +6733,24 @@
     </row>
     <row r="48" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A48" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C48" s="4">
         <v>3</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A49" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C49" s="4">
         <v>3</v>
@@ -5213,10 +6759,10 @@
     </row>
     <row r="50" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A50" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C50" s="4">
         <v>2</v>
@@ -5225,10 +6771,10 @@
     </row>
     <row r="51" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A51" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C51" s="4">
         <v>3</v>
@@ -5237,10 +6783,10 @@
     </row>
     <row r="52" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A52" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C52" s="4">
         <v>3</v>
@@ -5249,10 +6795,10 @@
     </row>
     <row r="53" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A53" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C53" s="4">
         <v>2</v>
@@ -5261,10 +6807,10 @@
     </row>
     <row r="54" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A54" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C54" s="4">
         <v>3</v>
@@ -5273,10 +6819,10 @@
     </row>
     <row r="55" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A55" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C55" s="4">
         <v>3</v>
@@ -5285,10 +6831,10 @@
     </row>
     <row r="56" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A56" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C56" s="4">
         <v>1</v>
@@ -5297,10 +6843,10 @@
     </row>
     <row r="57" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A57" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C57" s="4">
         <v>1</v>
@@ -5309,10 +6855,10 @@
     </row>
     <row r="58" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A58" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C58" s="4">
         <v>4</v>
@@ -5321,10 +6867,10 @@
     </row>
     <row r="59" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A59" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C59" s="4">
         <v>2</v>
@@ -5333,10 +6879,10 @@
     </row>
     <row r="60" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A60" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C60" s="4">
         <v>4</v>
@@ -5345,10 +6891,10 @@
     </row>
     <row r="61" spans="1:4" s="11" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A61" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C61" s="10">
         <v>1</v>
@@ -5357,10 +6903,10 @@
     </row>
     <row r="62" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A62" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C62" s="4">
         <v>1</v>
@@ -5369,10 +6915,10 @@
     </row>
     <row r="63" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A63" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C63" s="4">
         <v>3</v>
@@ -5381,10 +6927,10 @@
     </row>
     <row r="64" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A64" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C64" s="4">
         <v>2</v>
@@ -5393,10 +6939,10 @@
     </row>
     <row r="65" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A65" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C65" s="4">
         <v>2</v>
@@ -5405,10 +6951,10 @@
     </row>
     <row r="66" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A66" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C66" s="4">
         <v>1</v>
@@ -5417,10 +6963,10 @@
     </row>
     <row r="67" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A67" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C67" s="4">
         <v>3</v>
@@ -5429,10 +6975,10 @@
     </row>
     <row r="68" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A68" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C68" s="4">
         <v>4</v>
@@ -5441,10 +6987,10 @@
     </row>
     <row r="69" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A69" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C69" s="4">
         <v>2</v>
@@ -5453,10 +6999,10 @@
     </row>
     <row r="70" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A70" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="B70" s="4" t="s">
         <v>320</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>319</v>
       </c>
       <c r="C70" s="4">
         <v>4</v>
@@ -5465,10 +7011,10 @@
     </row>
     <row r="71" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A71" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C71" s="4">
         <v>4</v>
@@ -5477,10 +7023,10 @@
     </row>
     <row r="72" spans="1:4" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A72" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C72" s="4">
         <v>3</v>
@@ -5489,10 +7035,10 @@
     </row>
     <row r="73" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A73" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C73" s="4">
         <v>3</v>
@@ -5501,10 +7047,10 @@
     </row>
     <row r="74" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A74" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C74" s="4">
         <v>4</v>
@@ -5513,10 +7059,10 @@
     </row>
     <row r="75" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A75" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C75" s="4">
         <v>4</v>
@@ -5525,7 +7071,7 @@
     </row>
     <row r="76" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A76" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B76" s="4">
         <v>15275</v>
@@ -5537,24 +7083,24 @@
     </row>
     <row r="77" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A77" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C77" s="4">
         <v>2</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A78" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C78" s="4">
         <v>2</v>
@@ -5563,10 +7109,10 @@
     </row>
     <row r="79" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A79" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C79" s="4">
         <v>2</v>
@@ -5575,24 +7121,24 @@
     </row>
     <row r="80" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A80" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C80" s="4">
         <v>3</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A81" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C81" s="4">
         <v>1</v>
@@ -5632,10 +7178,10 @@
     </row>
     <row r="2" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -5643,10 +7189,10 @@
     </row>
     <row r="3" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -5654,10 +7200,10 @@
     </row>
     <row r="4" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -5665,10 +7211,10 @@
     </row>
     <row r="5" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -5676,10 +7222,10 @@
     </row>
     <row r="6" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -5687,10 +7233,10 @@
     </row>
     <row r="7" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -5698,10 +7244,10 @@
     </row>
     <row r="8" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -5709,10 +7255,10 @@
     </row>
     <row r="9" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -5720,10 +7266,10 @@
     </row>
     <row r="10" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -5731,10 +7277,10 @@
     </row>
     <row r="11" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -5742,10 +7288,10 @@
     </row>
     <row r="12" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -5753,10 +7299,10 @@
     </row>
     <row r="13" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -5764,10 +7310,10 @@
     </row>
     <row r="14" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -5775,10 +7321,10 @@
     </row>
     <row r="15" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A15" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -5786,10 +7332,10 @@
     </row>
     <row r="16" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C16">
         <v>2</v>
@@ -5797,10 +7343,10 @@
     </row>
     <row r="17" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -5808,10 +7354,10 @@
     </row>
     <row r="18" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -5819,10 +7365,10 @@
     </row>
     <row r="19" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C19">
         <v>4</v>
@@ -5830,46 +7376,46 @@
     </row>
     <row r="20" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C20">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:4" s="13" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A21" s="12" t="s">
+    <row r="21" spans="1:4" s="14" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A21" s="13" t="s">
+        <v>461</v>
+      </c>
+      <c r="B21" s="13" t="s">
         <v>460</v>
       </c>
-      <c r="B21" s="12" t="s">
-        <v>459</v>
-      </c>
-      <c r="C21" s="13">
+      <c r="C21" s="14">
         <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C22">
         <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A23" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C23">
         <v>3</v>
@@ -5877,10 +7423,10 @@
     </row>
     <row r="24" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -5888,10 +7434,10 @@
     </row>
     <row r="25" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A25" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C25">
         <v>4</v>
@@ -5899,24 +7445,24 @@
     </row>
     <row r="26" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A26" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A27" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C27">
         <v>3</v>
@@ -5924,10 +7470,10 @@
     </row>
     <row r="28" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A28" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C28">
         <v>2</v>
@@ -5935,10 +7481,10 @@
     </row>
     <row r="29" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A29" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -5946,10 +7492,10 @@
     </row>
     <row r="30" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A30" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C30">
         <v>2</v>
@@ -5957,10 +7503,10 @@
     </row>
     <row r="31" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A31" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C31">
         <v>3</v>
@@ -5968,10 +7514,10 @@
     </row>
     <row r="32" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A32" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -5979,10 +7525,10 @@
     </row>
     <row r="33" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A33" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C33">
         <v>3</v>
@@ -5990,10 +7536,10 @@
     </row>
     <row r="34" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A34" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -6001,10 +7547,10 @@
     </row>
     <row r="35" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A35" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -6012,10 +7558,10 @@
     </row>
     <row r="36" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A36" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -6023,10 +7569,10 @@
     </row>
     <row r="37" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A37" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C37">
         <v>2</v>
@@ -6034,10 +7580,10 @@
     </row>
     <row r="38" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A38" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C38">
         <v>3</v>
@@ -6045,24 +7591,24 @@
     </row>
     <row r="39" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A39" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C39">
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A40" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C40">
         <v>2</v>
@@ -6070,10 +7616,10 @@
     </row>
     <row r="41" spans="1:4" s="11" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A41" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C41" s="11">
         <v>3</v>
@@ -6081,10 +7627,10 @@
     </row>
     <row r="42" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A42" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -6092,10 +7638,10 @@
     </row>
     <row r="43" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A43" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C43">
         <v>2</v>
@@ -6103,10 +7649,10 @@
     </row>
     <row r="44" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A44" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C44">
         <v>4</v>
@@ -6114,10 +7660,10 @@
     </row>
     <row r="45" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A45" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C45">
         <v>4</v>
@@ -6125,10 +7671,10 @@
     </row>
     <row r="46" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A46" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C46">
         <v>3</v>
@@ -6136,10 +7682,10 @@
     </row>
     <row r="47" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A47" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C47">
         <v>2</v>
@@ -6147,10 +7693,10 @@
     </row>
     <row r="48" spans="1:4" ht="243.6" x14ac:dyDescent="0.4">
       <c r="A48" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C48">
         <v>2</v>
@@ -6158,10 +7704,10 @@
     </row>
     <row r="49" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A49" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C49">
         <v>2</v>
@@ -6169,10 +7715,10 @@
     </row>
     <row r="50" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A50" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -6180,10 +7726,10 @@
     </row>
     <row r="51" spans="1:3" ht="174" x14ac:dyDescent="0.4">
       <c r="A51" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C51">
         <v>4</v>
@@ -6191,10 +7737,10 @@
     </row>
     <row r="52" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A52" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C52">
         <v>3</v>
@@ -6202,10 +7748,10 @@
     </row>
     <row r="53" spans="1:3" ht="87" x14ac:dyDescent="0.4">
       <c r="A53" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C53">
         <v>2</v>
@@ -6213,10 +7759,10 @@
     </row>
     <row r="54" spans="1:3" ht="87" x14ac:dyDescent="0.4">
       <c r="A54" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C54">
         <v>4</v>
@@ -6224,10 +7770,10 @@
     </row>
     <row r="55" spans="1:3" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A55" s="4" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C55">
         <v>3</v>
@@ -6235,10 +7781,10 @@
     </row>
     <row r="56" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A56" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C56">
         <v>2</v>
@@ -6246,10 +7792,10 @@
     </row>
     <row r="57" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A57" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C57">
         <v>2</v>
@@ -6257,10 +7803,10 @@
     </row>
     <row r="58" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A58" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C58">
         <v>4</v>
@@ -6268,10 +7814,10 @@
     </row>
     <row r="59" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A59" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C59">
         <v>4</v>
@@ -6279,10 +7825,10 @@
     </row>
     <row r="60" spans="1:3" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A60" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -6290,10 +7836,10 @@
     </row>
     <row r="61" spans="1:3" s="11" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A61" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C61" s="11">
         <v>1</v>
@@ -6301,10 +7847,10 @@
     </row>
     <row r="62" spans="1:3" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A62" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C62">
         <v>4</v>
@@ -6312,10 +7858,10 @@
     </row>
     <row r="63" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A63" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C63">
         <v>2</v>
@@ -6323,10 +7869,10 @@
     </row>
     <row r="64" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A64" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C64">
         <v>2</v>
@@ -6334,10 +7880,10 @@
     </row>
     <row r="65" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A65" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="B65" s="4" t="s">
         <v>482</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>481</v>
       </c>
       <c r="C65">
         <v>4</v>
@@ -6345,10 +7891,10 @@
     </row>
     <row r="66" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A66" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -6356,10 +7902,10 @@
     </row>
     <row r="67" spans="1:3" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A67" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C67">
         <v>2</v>
@@ -6367,10 +7913,10 @@
     </row>
     <row r="68" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A68" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C68">
         <v>3</v>
@@ -6378,10 +7924,10 @@
     </row>
     <row r="69" spans="1:3" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A69" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C69">
         <v>4</v>
@@ -6389,10 +7935,10 @@
     </row>
     <row r="70" spans="1:3" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A70" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C70">
         <v>2</v>
@@ -6400,10 +7946,10 @@
     </row>
     <row r="71" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A71" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -6411,10 +7957,10 @@
     </row>
     <row r="72" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A72" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -6422,10 +7968,10 @@
     </row>
     <row r="73" spans="1:3" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A73" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -6433,10 +7979,10 @@
     </row>
     <row r="74" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A74" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -6444,10 +7990,10 @@
     </row>
     <row r="75" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A75" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -6455,10 +8001,10 @@
     </row>
     <row r="76" spans="1:3" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A76" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C76">
         <v>2</v>
@@ -6466,10 +8012,10 @@
     </row>
     <row r="77" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A77" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C77">
         <v>4</v>
@@ -6477,10 +8023,10 @@
     </row>
     <row r="78" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A78" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C78">
         <v>2</v>
@@ -6488,10 +8034,10 @@
     </row>
     <row r="79" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A79" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C79">
         <v>4</v>
@@ -6499,10 +8045,10 @@
     </row>
     <row r="80" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A80" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C80">
         <v>3</v>
@@ -6510,16 +8056,16 @@
     </row>
     <row r="81" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A81" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C81">
         <v>4</v>
       </c>
       <c r="D81" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -6556,10 +8102,10 @@
     </row>
     <row r="2" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C2" s="4">
         <v>1</v>
@@ -6567,10 +8113,10 @@
     </row>
     <row r="3" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C3" s="4">
         <v>4</v>
@@ -6578,10 +8124,10 @@
     </row>
     <row r="4" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C4" s="4">
         <v>3</v>
@@ -6589,10 +8135,10 @@
     </row>
     <row r="5" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C5" s="4">
         <v>1</v>
@@ -6600,10 +8146,10 @@
     </row>
     <row r="6" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C6" s="4">
         <v>3</v>
@@ -6611,10 +8157,10 @@
     </row>
     <row r="7" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C7" s="4">
         <v>4</v>
@@ -6622,10 +8168,10 @@
     </row>
     <row r="8" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C8" s="4">
         <v>2</v>
@@ -6633,10 +8179,10 @@
     </row>
     <row r="9" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C9" s="4">
         <v>3</v>
@@ -6644,10 +8190,10 @@
     </row>
     <row r="10" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C10" s="4">
         <v>1</v>
@@ -6655,10 +8201,10 @@
     </row>
     <row r="11" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>573</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>572</v>
       </c>
       <c r="C11" s="4">
         <v>1</v>
@@ -6666,7 +8212,7 @@
     </row>
     <row r="12" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B12" s="4">
         <v>16111</v>
@@ -6677,10 +8223,10 @@
     </row>
     <row r="13" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C13" s="4">
         <v>2</v>
@@ -6688,10 +8234,10 @@
     </row>
     <row r="14" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C14" s="4">
         <v>4</v>
@@ -6699,10 +8245,10 @@
     </row>
     <row r="15" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A15" s="4" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C15" s="4">
         <v>4</v>
@@ -6710,10 +8256,10 @@
     </row>
     <row r="16" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C16" s="4">
         <v>4</v>
@@ -6721,7 +8267,7 @@
     </row>
     <row r="17" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B17" s="4">
         <v>16116</v>
@@ -6732,10 +8278,10 @@
     </row>
     <row r="18" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C18" s="4">
         <v>1</v>
@@ -6743,10 +8289,10 @@
     </row>
     <row r="19" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C19" s="4">
         <v>4</v>
@@ -6754,10 +8300,10 @@
     </row>
     <row r="20" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C20" s="4">
         <v>1</v>
@@ -6765,10 +8311,10 @@
     </row>
     <row r="21" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C21" s="4">
         <v>3</v>
@@ -6776,10 +8322,10 @@
     </row>
     <row r="22" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C22" s="4">
         <v>1</v>
@@ -6787,24 +8333,24 @@
     </row>
     <row r="23" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A23" s="4" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C23" s="4">
         <v>1</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C24" s="4">
         <v>3</v>
@@ -6812,10 +8358,10 @@
     </row>
     <row r="25" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A25" s="4" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C25" s="4">
         <v>4</v>
@@ -6823,10 +8369,10 @@
     </row>
     <row r="26" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A26" s="4" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C26" s="4">
         <v>1</v>
@@ -6834,10 +8380,10 @@
     </row>
     <row r="27" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A27" s="4" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C27" s="4">
         <v>3</v>
@@ -6845,10 +8391,10 @@
     </row>
     <row r="28" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A28" s="4" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C28" s="4">
         <v>4</v>
@@ -6856,7 +8402,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29" s="4" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B29" s="4">
         <v>16128</v>
@@ -6867,10 +8413,10 @@
     </row>
     <row r="30" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A30" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C30" s="4">
         <v>4</v>
@@ -6878,10 +8424,10 @@
     </row>
     <row r="31" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A31" s="4" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C31" s="4">
         <v>1</v>
@@ -6889,10 +8435,10 @@
     </row>
     <row r="32" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A32" s="4" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C32" s="4">
         <v>2</v>
@@ -6900,10 +8446,10 @@
     </row>
     <row r="33" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A33" s="4" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C33" s="4">
         <v>3</v>
@@ -6911,10 +8457,10 @@
     </row>
     <row r="34" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A34" s="4" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C34" s="4">
         <v>1</v>
@@ -6922,10 +8468,10 @@
     </row>
     <row r="35" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A35" s="4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C35" s="4">
         <v>4</v>
@@ -6933,7 +8479,7 @@
     </row>
     <row r="36" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A36" s="4" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B36" s="4">
         <v>16135</v>
@@ -6944,10 +8490,10 @@
     </row>
     <row r="37" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A37" s="4" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C37" s="4">
         <v>2</v>
@@ -6955,10 +8501,10 @@
     </row>
     <row r="38" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A38" s="4" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C38" s="4">
         <v>1</v>
@@ -6966,10 +8512,10 @@
     </row>
     <row r="39" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A39" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C39" s="4">
         <v>2</v>
@@ -6977,10 +8523,10 @@
     </row>
     <row r="40" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A40" s="4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C40" s="4">
         <v>3</v>
@@ -6991,7 +8537,7 @@
     </row>
     <row r="41" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A41" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B41" s="4">
         <v>16140</v>
@@ -7000,15 +8546,15 @@
         <v>4</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A42" s="4" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C42" s="4">
         <v>3</v>
@@ -7016,10 +8562,10 @@
     </row>
     <row r="43" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A43" s="4" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C43" s="4">
         <v>2</v>
@@ -7027,7 +8573,7 @@
     </row>
     <row r="44" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A44" s="4" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>185</v>
@@ -7036,15 +8582,15 @@
         <v>4</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A45" s="4" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C45" s="4">
         <v>4</v>
@@ -7052,10 +8598,10 @@
     </row>
     <row r="46" spans="1:4" ht="226.2" x14ac:dyDescent="0.4">
       <c r="A46" s="4" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C46" s="4">
         <v>3</v>
@@ -7063,10 +8609,10 @@
     </row>
     <row r="47" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A47" s="4" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C47" s="4">
         <v>4</v>
@@ -7074,10 +8620,10 @@
     </row>
     <row r="48" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A48" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C48" s="4">
         <v>3</v>
@@ -7085,10 +8631,10 @@
     </row>
     <row r="49" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A49" s="4" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C49" s="4">
         <v>1</v>
@@ -7096,10 +8642,10 @@
     </row>
     <row r="50" spans="1:3" ht="87" x14ac:dyDescent="0.4">
       <c r="A50" s="4" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C50" s="4">
         <v>4</v>
@@ -7107,10 +8653,10 @@
     </row>
     <row r="51" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A51" s="4" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C51" s="4">
         <v>2</v>
@@ -7118,10 +8664,10 @@
     </row>
     <row r="52" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A52" s="4" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C52" s="4">
         <v>3</v>
@@ -7129,10 +8675,10 @@
     </row>
     <row r="53" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A53" s="4" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C53" s="4">
         <v>2</v>
@@ -7140,10 +8686,10 @@
     </row>
     <row r="54" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A54" s="4" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C54" s="4">
         <v>4</v>
@@ -7151,10 +8697,10 @@
     </row>
     <row r="55" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A55" s="4" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C55" s="4">
         <v>2</v>
@@ -7162,10 +8708,10 @@
     </row>
     <row r="56" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A56" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C56" s="4">
         <v>4</v>
@@ -7173,10 +8719,10 @@
     </row>
     <row r="57" spans="1:3" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A57" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>625</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>624</v>
       </c>
       <c r="C57" s="4">
         <v>2</v>
@@ -7184,10 +8730,10 @@
     </row>
     <row r="58" spans="1:3" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A58" s="4" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C58" s="4">
         <v>2</v>
@@ -7195,10 +8741,10 @@
     </row>
     <row r="59" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A59" s="4" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C59" s="4">
         <v>1</v>
@@ -7206,10 +8752,10 @@
     </row>
     <row r="60" spans="1:3" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A60" s="4" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C60" s="4">
         <v>2</v>
@@ -7217,10 +8763,10 @@
     </row>
     <row r="61" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A61" s="4" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C61" s="4">
         <v>2</v>
@@ -7228,10 +8774,10 @@
     </row>
     <row r="62" spans="1:3" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A62" s="4" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C62" s="4">
         <v>2</v>
@@ -7239,10 +8785,10 @@
     </row>
     <row r="63" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A63" s="4" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C63" s="4">
         <v>2</v>
@@ -7250,10 +8796,10 @@
     </row>
     <row r="64" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A64" s="4" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C64" s="4">
         <v>1</v>
@@ -7261,10 +8807,10 @@
     </row>
     <row r="65" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A65" s="4" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C65" s="4">
         <v>2</v>
@@ -7272,10 +8818,10 @@
     </row>
     <row r="66" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A66" s="4" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C66" s="4">
         <v>4</v>
@@ -7283,10 +8829,10 @@
     </row>
     <row r="67" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A67" s="4" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C67" s="4">
         <v>2</v>
@@ -7294,10 +8840,10 @@
     </row>
     <row r="68" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A68" s="4" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C68" s="4">
         <v>3</v>
@@ -7305,52 +8851,52 @@
     </row>
     <row r="69" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A69" s="4" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C69" s="4">
         <v>2</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A70" s="4" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C70" s="4">
         <v>3</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A71" s="4" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C71" s="4">
         <v>1</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A72" s="4" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C72" s="4">
         <v>4</v>
@@ -7358,10 +8904,10 @@
     </row>
     <row r="73" spans="1:4" ht="174" x14ac:dyDescent="0.4">
       <c r="A73" s="4" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C73" s="4">
         <v>2</v>
@@ -7369,10 +8915,10 @@
     </row>
     <row r="74" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A74" s="4" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C74" s="4">
         <v>3</v>
@@ -7380,10 +8926,10 @@
     </row>
     <row r="75" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A75" s="4" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C75" s="4">
         <v>3</v>
@@ -7391,10 +8937,10 @@
     </row>
     <row r="76" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A76" s="4" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C76" s="4">
         <v>4</v>
@@ -7402,10 +8948,10 @@
     </row>
     <row r="77" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A77" s="4" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C77" s="4">
         <v>2</v>
@@ -7413,10 +8959,10 @@
     </row>
     <row r="78" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A78" s="4" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C78" s="4">
         <v>2</v>
@@ -7424,10 +8970,10 @@
     </row>
     <row r="79" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A79" s="4" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C79" s="4">
         <v>4</v>
@@ -7435,10 +8981,10 @@
     </row>
     <row r="80" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A80" s="4" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C80" s="4">
         <v>2</v>
@@ -7446,10 +8992,10 @@
     </row>
     <row r="81" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A81" s="4" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C81" s="4">
         <v>1</v>
@@ -7463,21 +9009,1654 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B064E4E4-586D-4AE9-88BE-75A9B8DB12F8}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="42.8984375" customWidth="1"/>
+    <col min="2" max="2" width="31.796875" customWidth="1"/>
+    <col min="3" max="3" width="4.69921875" customWidth="1"/>
+    <col min="4" max="4" width="10.09765625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" ht="16.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="15" t="s">
         <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A2" s="15" t="s">
+        <v>653</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>654</v>
+      </c>
+      <c r="C2" s="12">
+        <v>4</v>
+      </c>
+      <c r="D2" s="12"/>
+    </row>
+    <row r="3" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A3" s="15" t="s">
+        <v>655</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>656</v>
+      </c>
+      <c r="C3" s="12">
+        <v>1</v>
+      </c>
+      <c r="D3" s="12"/>
+    </row>
+    <row r="4" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A4" s="15" t="s">
+        <v>657</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>751</v>
+      </c>
+      <c r="C4" s="12">
+        <v>3</v>
+      </c>
+      <c r="D4" s="12"/>
+    </row>
+    <row r="5" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A5" s="15" t="s">
+        <v>752</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>658</v>
+      </c>
+      <c r="C5" s="12">
+        <v>3</v>
+      </c>
+      <c r="D5" s="12"/>
+    </row>
+    <row r="6" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A6" s="15" t="s">
+        <v>753</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>659</v>
+      </c>
+      <c r="C6" s="12">
+        <v>4</v>
+      </c>
+      <c r="D6" s="12"/>
+    </row>
+    <row r="7" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A7" s="15" t="s">
+        <v>660</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>661</v>
+      </c>
+      <c r="C7" s="12">
+        <v>2</v>
+      </c>
+      <c r="D7" s="12"/>
+    </row>
+    <row r="8" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A8" s="15" t="s">
+        <v>662</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>663</v>
+      </c>
+      <c r="C8" s="12">
+        <v>4</v>
+      </c>
+      <c r="D8" s="12"/>
+    </row>
+    <row r="9" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A9" s="15" t="s">
+        <v>664</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>665</v>
+      </c>
+      <c r="C9" s="12">
+        <v>3</v>
+      </c>
+      <c r="D9" s="12"/>
+    </row>
+    <row r="10" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A10" s="15" t="s">
+        <v>666</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="C10" s="12">
+        <v>3</v>
+      </c>
+      <c r="D10" s="12"/>
+    </row>
+    <row r="11" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A11" s="15" t="s">
+        <v>668</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>669</v>
+      </c>
+      <c r="C11" s="12">
+        <v>3</v>
+      </c>
+      <c r="D11" s="12"/>
+    </row>
+    <row r="12" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A12" s="15" t="s">
+        <v>670</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>754</v>
+      </c>
+      <c r="C12" s="12">
+        <v>3</v>
+      </c>
+      <c r="D12" s="12"/>
+    </row>
+    <row r="13" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A13" s="15" t="s">
+        <v>755</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>671</v>
+      </c>
+      <c r="C13" s="12">
+        <v>3</v>
+      </c>
+      <c r="D13" s="12"/>
+    </row>
+    <row r="14" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A14" s="15" t="s">
+        <v>756</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="C14" s="12">
+        <v>4</v>
+      </c>
+      <c r="D14" s="12"/>
+    </row>
+    <row r="15" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A15" s="15" t="s">
+        <v>672</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>673</v>
+      </c>
+      <c r="C15" s="12">
+        <v>1</v>
+      </c>
+      <c r="D15" s="12"/>
+    </row>
+    <row r="16" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A16" s="15" t="s">
+        <v>674</v>
+      </c>
+      <c r="B16" s="15">
+        <v>16215</v>
+      </c>
+      <c r="C16" s="12">
+        <v>1</v>
+      </c>
+      <c r="D16" s="12"/>
+    </row>
+    <row r="17" spans="1:4" ht="191.4" x14ac:dyDescent="0.4">
+      <c r="A17" s="15" t="s">
+        <v>675</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>757</v>
+      </c>
+      <c r="C17" s="12">
+        <v>2</v>
+      </c>
+      <c r="D17" s="12"/>
+    </row>
+    <row r="18" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A18" s="15" t="s">
+        <v>676</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>677</v>
+      </c>
+      <c r="C18" s="12">
+        <v>3</v>
+      </c>
+      <c r="D18" s="12"/>
+    </row>
+    <row r="19" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A19" s="15" t="s">
+        <v>678</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>758</v>
+      </c>
+      <c r="C19" s="12">
+        <v>1</v>
+      </c>
+      <c r="D19" s="12"/>
+    </row>
+    <row r="20" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A20" s="15" t="s">
+        <v>679</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>680</v>
+      </c>
+      <c r="C20" s="12">
+        <v>1</v>
+      </c>
+      <c r="D20" s="12"/>
+    </row>
+    <row r="21" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A21" s="15" t="s">
+        <v>681</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>759</v>
+      </c>
+      <c r="C21" s="12">
+        <v>3</v>
+      </c>
+      <c r="D21" s="12"/>
+    </row>
+    <row r="22" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A22" s="15" t="s">
+        <v>682</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>683</v>
+      </c>
+      <c r="C22" s="12">
+        <v>2</v>
+      </c>
+      <c r="D22" s="12"/>
+    </row>
+    <row r="23" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A23" s="15" t="s">
+        <v>684</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>685</v>
+      </c>
+      <c r="C23" s="12">
+        <v>1</v>
+      </c>
+      <c r="D23" s="12"/>
+    </row>
+    <row r="24" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A24" s="15" t="s">
+        <v>760</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>686</v>
+      </c>
+      <c r="C24" s="12">
+        <v>2</v>
+      </c>
+      <c r="D24" s="12"/>
+    </row>
+    <row r="25" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A25" s="15" t="s">
+        <v>761</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>687</v>
+      </c>
+      <c r="C25" s="12">
+        <v>3</v>
+      </c>
+      <c r="D25" s="12"/>
+    </row>
+    <row r="26" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A26" s="15" t="s">
+        <v>762</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>688</v>
+      </c>
+      <c r="C26" s="12">
+        <v>4</v>
+      </c>
+      <c r="D26" s="12"/>
+    </row>
+    <row r="27" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A27" s="15" t="s">
+        <v>689</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>690</v>
+      </c>
+      <c r="C27" s="12">
+        <v>1</v>
+      </c>
+      <c r="D27" s="12"/>
+    </row>
+    <row r="28" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A28" s="15" t="s">
+        <v>691</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>692</v>
+      </c>
+      <c r="C28" s="12">
+        <v>1</v>
+      </c>
+      <c r="D28" s="12"/>
+    </row>
+    <row r="29" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A29" s="15" t="s">
+        <v>693</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>694</v>
+      </c>
+      <c r="C29" s="12">
+        <v>1</v>
+      </c>
+      <c r="D29" s="12"/>
+    </row>
+    <row r="30" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A30" s="15" t="s">
+        <v>763</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>695</v>
+      </c>
+      <c r="C30" s="12">
+        <v>4</v>
+      </c>
+      <c r="D30" s="12"/>
+    </row>
+    <row r="31" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A31" s="15" t="s">
+        <v>696</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>764</v>
+      </c>
+      <c r="C31" s="12">
+        <v>2</v>
+      </c>
+      <c r="D31" s="12"/>
+    </row>
+    <row r="32" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A32" s="15" t="s">
+        <v>765</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>697</v>
+      </c>
+      <c r="C32" s="12">
+        <v>1</v>
+      </c>
+      <c r="D32" s="12"/>
+    </row>
+    <row r="33" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A33" s="15" t="s">
+        <v>698</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>699</v>
+      </c>
+      <c r="C33" s="12">
+        <v>3</v>
+      </c>
+      <c r="D33" s="12"/>
+    </row>
+    <row r="34" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A34" s="15" t="s">
+        <v>767</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="C34" s="12">
+        <v>4</v>
+      </c>
+      <c r="D34" s="12"/>
+    </row>
+    <row r="35" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A35" s="15" t="s">
+        <v>770</v>
+      </c>
+      <c r="B35" s="15">
+        <v>16234</v>
+      </c>
+      <c r="C35" s="12">
+        <v>1</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A36" s="15" t="s">
+        <v>700</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>701</v>
+      </c>
+      <c r="C36" s="12">
+        <v>3</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A37" s="15" t="s">
+        <v>702</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>703</v>
+      </c>
+      <c r="C37" s="12">
+        <v>1</v>
+      </c>
+      <c r="D37" s="12"/>
+    </row>
+    <row r="38" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A38" s="15" t="s">
+        <v>771</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>772</v>
+      </c>
+      <c r="C38" s="12">
+        <v>4</v>
+      </c>
+      <c r="D38" s="12"/>
+    </row>
+    <row r="39" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A39" s="15" t="s">
+        <v>704</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>705</v>
+      </c>
+      <c r="C39" s="12">
+        <v>2</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A40" s="15" t="s">
+        <v>706</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>707</v>
+      </c>
+      <c r="C40" s="12">
+        <v>2</v>
+      </c>
+      <c r="D40" s="12"/>
+    </row>
+    <row r="41" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A41" s="15" t="s">
+        <v>708</v>
+      </c>
+      <c r="B41" s="15">
+        <v>16240</v>
+      </c>
+      <c r="C41" s="12">
+        <v>1</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A42" s="15" t="s">
+        <v>709</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>776</v>
+      </c>
+      <c r="C42" s="12">
+        <v>2</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A43" s="15" t="s">
+        <v>778</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>775</v>
+      </c>
+      <c r="C43" s="12">
+        <v>2</v>
+      </c>
+      <c r="D43" s="12"/>
+    </row>
+    <row r="44" spans="1:4" ht="87" x14ac:dyDescent="0.4">
+      <c r="A44" s="15" t="s">
+        <v>779</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>710</v>
+      </c>
+      <c r="C44" s="12">
+        <v>1</v>
+      </c>
+      <c r="D44" s="12"/>
+    </row>
+    <row r="45" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A45" s="15" t="s">
+        <v>780</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>711</v>
+      </c>
+      <c r="C45" s="12">
+        <v>3</v>
+      </c>
+      <c r="D45" s="12"/>
+    </row>
+    <row r="46" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A46" s="15" t="s">
+        <v>712</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>713</v>
+      </c>
+      <c r="C46" s="12">
+        <v>3</v>
+      </c>
+      <c r="D46" s="12"/>
+    </row>
+    <row r="47" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A47" s="15" t="s">
+        <v>714</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>715</v>
+      </c>
+      <c r="C47" s="12">
+        <v>2</v>
+      </c>
+      <c r="D47" s="12"/>
+    </row>
+    <row r="48" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A48" s="15" t="s">
+        <v>781</v>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>716</v>
+      </c>
+      <c r="C48" s="12">
+        <v>1</v>
+      </c>
+      <c r="D48" s="12"/>
+    </row>
+    <row r="49" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A49" s="15" t="s">
+        <v>717</v>
+      </c>
+      <c r="B49" s="15" t="s">
+        <v>718</v>
+      </c>
+      <c r="C49" s="12">
+        <v>2</v>
+      </c>
+      <c r="D49" s="12"/>
+    </row>
+    <row r="50" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A50" s="15" t="s">
+        <v>719</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>720</v>
+      </c>
+      <c r="C50" s="12">
+        <v>4</v>
+      </c>
+      <c r="D50" s="12"/>
+    </row>
+    <row r="51" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A51" s="15" t="s">
+        <v>721</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>722</v>
+      </c>
+      <c r="C51" s="12">
+        <v>4</v>
+      </c>
+      <c r="D51" s="12"/>
+    </row>
+    <row r="52" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A52" s="15" t="s">
+        <v>784</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>783</v>
+      </c>
+      <c r="C52" s="12">
+        <v>2</v>
+      </c>
+      <c r="D52" s="12"/>
+    </row>
+    <row r="53" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A53" s="15" t="s">
+        <v>785</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>782</v>
+      </c>
+      <c r="C53" s="12">
+        <v>4</v>
+      </c>
+      <c r="D53" s="12"/>
+    </row>
+    <row r="54" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A54" s="15" t="s">
+        <v>786</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>723</v>
+      </c>
+      <c r="C54" s="12">
+        <v>1</v>
+      </c>
+      <c r="D54" s="12"/>
+    </row>
+    <row r="55" spans="1:4" ht="208.8" x14ac:dyDescent="0.4">
+      <c r="A55" s="15" t="s">
+        <v>787</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>788</v>
+      </c>
+      <c r="C55" s="12">
+        <v>3</v>
+      </c>
+      <c r="D55" s="12"/>
+    </row>
+    <row r="56" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A56" s="15" t="s">
+        <v>789</v>
+      </c>
+      <c r="B56" s="15" t="s">
+        <v>790</v>
+      </c>
+      <c r="C56" s="12">
+        <v>3</v>
+      </c>
+      <c r="D56" s="12"/>
+    </row>
+    <row r="57" spans="1:4" ht="87" x14ac:dyDescent="0.4">
+      <c r="A57" s="15" t="s">
+        <v>791</v>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>724</v>
+      </c>
+      <c r="C57" s="12">
+        <v>3</v>
+      </c>
+      <c r="D57" s="12"/>
+    </row>
+    <row r="58" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A58" s="15" t="s">
+        <v>792</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>725</v>
+      </c>
+      <c r="C58" s="12">
+        <v>4</v>
+      </c>
+      <c r="D58" s="12"/>
+    </row>
+    <row r="59" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A59" s="15" t="s">
+        <v>726</v>
+      </c>
+      <c r="B59" s="15" t="s">
+        <v>727</v>
+      </c>
+      <c r="C59" s="12">
+        <v>2</v>
+      </c>
+      <c r="D59" s="12"/>
+    </row>
+    <row r="60" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A60" s="15" t="s">
+        <v>728</v>
+      </c>
+      <c r="B60" s="15" t="s">
+        <v>793</v>
+      </c>
+      <c r="C60" s="12">
+        <v>4</v>
+      </c>
+      <c r="D60" s="12"/>
+    </row>
+    <row r="61" spans="1:4" ht="87" x14ac:dyDescent="0.4">
+      <c r="A61" s="15" t="s">
+        <v>794</v>
+      </c>
+      <c r="B61" s="15" t="s">
+        <v>729</v>
+      </c>
+      <c r="C61" s="12">
+        <v>3</v>
+      </c>
+      <c r="D61" s="12"/>
+    </row>
+    <row r="62" spans="1:4" ht="208.8" x14ac:dyDescent="0.4">
+      <c r="A62" s="15" t="s">
+        <v>796</v>
+      </c>
+      <c r="B62" s="15" t="s">
+        <v>795</v>
+      </c>
+      <c r="C62" s="12">
+        <v>4</v>
+      </c>
+      <c r="D62" s="12"/>
+    </row>
+    <row r="63" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A63" s="15" t="s">
+        <v>797</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>730</v>
+      </c>
+      <c r="C63" s="12">
+        <v>1</v>
+      </c>
+      <c r="D63" s="12"/>
+    </row>
+    <row r="64" spans="1:4" ht="226.2" x14ac:dyDescent="0.4">
+      <c r="A64" s="15" t="s">
+        <v>798</v>
+      </c>
+      <c r="B64" s="15" t="s">
+        <v>799</v>
+      </c>
+      <c r="C64" s="12">
+        <v>1</v>
+      </c>
+      <c r="D64" s="12"/>
+    </row>
+    <row r="65" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A65" s="15" t="s">
+        <v>800</v>
+      </c>
+      <c r="B65" s="15" t="s">
+        <v>731</v>
+      </c>
+      <c r="C65" s="12">
+        <v>1</v>
+      </c>
+      <c r="D65" s="12"/>
+    </row>
+    <row r="66" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A66" s="15" t="s">
+        <v>801</v>
+      </c>
+      <c r="B66" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="C66" s="12">
+        <v>3</v>
+      </c>
+      <c r="D66" s="12"/>
+    </row>
+    <row r="67" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A67" s="15" t="s">
+        <v>733</v>
+      </c>
+      <c r="B67" s="15" t="s">
+        <v>802</v>
+      </c>
+      <c r="C67" s="12">
+        <v>4</v>
+      </c>
+      <c r="D67" s="12"/>
+    </row>
+    <row r="68" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A68" s="15" t="s">
+        <v>803</v>
+      </c>
+      <c r="B68" s="15" t="s">
+        <v>607</v>
+      </c>
+      <c r="C68" s="12">
+        <v>2</v>
+      </c>
+      <c r="D68" s="12"/>
+    </row>
+    <row r="69" spans="1:4" ht="226.2" x14ac:dyDescent="0.4">
+      <c r="A69" s="15" t="s">
+        <v>734</v>
+      </c>
+      <c r="B69" s="15" t="s">
+        <v>804</v>
+      </c>
+      <c r="C69" s="12">
+        <v>1</v>
+      </c>
+      <c r="D69" s="12"/>
+    </row>
+    <row r="70" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A70" s="15" t="s">
+        <v>735</v>
+      </c>
+      <c r="B70" s="15" t="s">
+        <v>736</v>
+      </c>
+      <c r="C70" s="12">
+        <v>4</v>
+      </c>
+      <c r="D70" s="12"/>
+    </row>
+    <row r="71" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A71" s="15" t="s">
+        <v>737</v>
+      </c>
+      <c r="B71" s="15" t="s">
+        <v>738</v>
+      </c>
+      <c r="C71" s="12">
+        <v>2</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="261" x14ac:dyDescent="0.4">
+      <c r="A72" s="15" t="s">
+        <v>739</v>
+      </c>
+      <c r="B72" s="15" t="s">
+        <v>806</v>
+      </c>
+      <c r="C72" s="12">
+        <v>1</v>
+      </c>
+      <c r="D72" s="12"/>
+    </row>
+    <row r="73" spans="1:4" ht="191.4" x14ac:dyDescent="0.4">
+      <c r="A73" s="15" t="s">
+        <v>740</v>
+      </c>
+      <c r="B73" s="15" t="s">
+        <v>807</v>
+      </c>
+      <c r="C73" s="12">
+        <v>2</v>
+      </c>
+      <c r="D73" s="12"/>
+    </row>
+    <row r="74" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A74" s="15" t="s">
+        <v>808</v>
+      </c>
+      <c r="B74" s="15" t="s">
+        <v>741</v>
+      </c>
+      <c r="C74" s="12">
+        <v>2</v>
+      </c>
+      <c r="D74" s="12"/>
+    </row>
+    <row r="75" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A75" s="15" t="s">
+        <v>742</v>
+      </c>
+      <c r="B75" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="C75" s="12">
+        <v>4</v>
+      </c>
+      <c r="D75" s="12"/>
+    </row>
+    <row r="76" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A76" s="15" t="s">
+        <v>744</v>
+      </c>
+      <c r="B76" s="15" t="s">
+        <v>745</v>
+      </c>
+      <c r="C76" s="12">
+        <v>4</v>
+      </c>
+      <c r="D76" s="12"/>
+    </row>
+    <row r="77" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A77" s="15" t="s">
+        <v>809</v>
+      </c>
+      <c r="B77" s="15" t="s">
+        <v>746</v>
+      </c>
+      <c r="C77" s="12">
+        <v>3</v>
+      </c>
+      <c r="D77" s="12"/>
+    </row>
+    <row r="78" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A78" s="15" t="s">
+        <v>747</v>
+      </c>
+      <c r="B78" s="15" t="s">
+        <v>748</v>
+      </c>
+      <c r="C78" s="12">
+        <v>4</v>
+      </c>
+      <c r="D78" s="12"/>
+    </row>
+    <row r="79" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A79" s="15" t="s">
+        <v>749</v>
+      </c>
+      <c r="B79" s="15" t="s">
+        <v>467</v>
+      </c>
+      <c r="C79" s="12">
+        <v>2</v>
+      </c>
+      <c r="D79" s="12"/>
+    </row>
+    <row r="80" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A80" s="15" t="s">
+        <v>810</v>
+      </c>
+      <c r="B80" s="15" t="s">
+        <v>750</v>
+      </c>
+      <c r="C80" s="12">
+        <v>3</v>
+      </c>
+      <c r="D80" s="12"/>
+    </row>
+    <row r="81" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A81" s="15" t="s">
+        <v>812</v>
+      </c>
+      <c r="B81" s="15" t="s">
+        <v>811</v>
+      </c>
+      <c r="C81" s="12">
+        <v>2</v>
+      </c>
+      <c r="D81" s="12"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8CB800D-DA44-4550-BA4F-B9F940DFC761}">
+  <dimension ref="A1:D79"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="39.59765625" customWidth="1"/>
+    <col min="2" max="2" width="35.19921875" customWidth="1"/>
+    <col min="3" max="3" width="5.09765625" customWidth="1"/>
+    <col min="4" max="4" width="9.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="1" customFormat="1" ht="16.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A2" s="15" t="s">
+        <v>813</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A3" s="15" t="s">
+        <v>815</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="87" x14ac:dyDescent="0.4">
+      <c r="A4" s="15" t="s">
+        <v>817</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A5" s="15" t="s">
+        <v>819</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A6" s="15" t="s">
+        <v>821</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A7" s="15" t="s">
+        <v>823</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A8" s="15" t="s">
+        <v>825</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A9" s="15" t="s">
+        <v>827</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A10" s="15" t="s">
+        <v>829</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A11" s="15" t="s">
+        <v>831</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A12" s="15" t="s">
+        <v>833</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="87" x14ac:dyDescent="0.4">
+      <c r="A13" s="15" t="s">
+        <v>835</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="174" x14ac:dyDescent="0.4">
+      <c r="A14" s="15" t="s">
+        <v>837</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A15" s="15" t="s">
+        <v>839</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A16" s="15" t="s">
+        <v>841</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A17" s="15" t="s">
+        <v>843</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A18" s="15" t="s">
+        <v>845</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A19" s="15" t="s">
+        <v>847</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A20" s="15" t="s">
+        <v>849</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A21" s="15" t="s">
+        <v>851</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A22" s="15" t="s">
+        <v>853</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A23" s="15" t="s">
+        <v>855</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A24" s="15" t="s">
+        <v>857</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A25" s="15" t="s">
+        <v>859</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A26" s="15" t="s">
+        <v>861</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A27" s="15" t="s">
+        <v>863</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A28" s="15" t="s">
+        <v>865</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A29" s="15" t="s">
+        <v>867</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A30" s="15" t="s">
+        <v>869</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A31" s="15" t="s">
+        <v>871</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A32" s="15" t="s">
+        <v>873</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A33" s="15" t="s">
+        <v>874</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A34" s="15" t="s">
+        <v>876</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A35" s="15" t="s">
+        <v>878</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="87" x14ac:dyDescent="0.4">
+      <c r="A36" s="15" t="s">
+        <v>880</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A37" s="15" t="s">
+        <v>882</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A38" s="15" t="s">
+        <v>884</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A39" s="15" t="s">
+        <v>886</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A40" s="15" t="s">
+        <v>888</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A41" s="15" t="s">
+        <v>890</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A42" s="15" t="s">
+        <v>892</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A43" s="15" t="s">
+        <v>894</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A44" s="15" t="s">
+        <v>896</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A45" s="15" t="s">
+        <v>898</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A46" s="15" t="s">
+        <v>900</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="87" x14ac:dyDescent="0.4">
+      <c r="A47" s="15" t="s">
+        <v>902</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A48" s="15" t="s">
+        <v>903</v>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A49" s="15" t="s">
+        <v>905</v>
+      </c>
+      <c r="B49" s="15" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A50" s="15" t="s">
+        <v>907</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="87" x14ac:dyDescent="0.4">
+      <c r="A51" s="15" t="s">
+        <v>909</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A52" s="15" t="s">
+        <v>911</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A53" s="15" t="s">
+        <v>913</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A54" s="15" t="s">
+        <v>915</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A55" s="15" t="s">
+        <v>917</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A56" s="15" t="s">
+        <v>919</v>
+      </c>
+      <c r="B56" s="15" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A57" s="15" t="s">
+        <v>921</v>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A58" s="15" t="s">
+        <v>923</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="243.6" x14ac:dyDescent="0.4">
+      <c r="A59" s="15" t="s">
+        <v>925</v>
+      </c>
+      <c r="B59" s="15" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A60" s="15" t="s">
+        <v>927</v>
+      </c>
+      <c r="B60" s="15" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A61" s="15" t="s">
+        <v>929</v>
+      </c>
+      <c r="B61" s="15" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A62" s="15" t="s">
+        <v>931</v>
+      </c>
+      <c r="B62" s="15" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A63" s="15" t="s">
+        <v>933</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A64" s="15" t="s">
+        <v>935</v>
+      </c>
+      <c r="B64" s="15" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A65" s="15" t="s">
+        <v>937</v>
+      </c>
+      <c r="B65" s="15" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A66" s="15" t="s">
+        <v>939</v>
+      </c>
+      <c r="B66" s="15" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A67" s="15" t="s">
+        <v>941</v>
+      </c>
+      <c r="B67" s="15" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A68" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="B68" s="15" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A69" s="15" t="s">
+        <v>945</v>
+      </c>
+      <c r="B69" s="15" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A70" s="15" t="s">
+        <v>947</v>
+      </c>
+      <c r="B70" s="15" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A71" s="15" t="s">
+        <v>948</v>
+      </c>
+      <c r="B71" s="15" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A72" s="15" t="s">
+        <v>950</v>
+      </c>
+      <c r="B72" s="15" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A73" s="15" t="s">
+        <v>952</v>
+      </c>
+      <c r="B73" s="15" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="174" x14ac:dyDescent="0.4">
+      <c r="A74" s="15" t="s">
+        <v>954</v>
+      </c>
+      <c r="B74" s="15" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="87" x14ac:dyDescent="0.4">
+      <c r="A75" s="15" t="s">
+        <v>956</v>
+      </c>
+      <c r="B75" s="15" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A76" s="15" t="s">
+        <v>958</v>
+      </c>
+      <c r="B76" s="15" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A77" s="15" t="s">
+        <v>960</v>
+      </c>
+      <c r="B77" s="15" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A78" s="15" t="s">
+        <v>962</v>
+      </c>
+      <c r="B78" s="15" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="409.6" x14ac:dyDescent="0.4">
+      <c r="A79" s="15" t="s">
+        <v>964</v>
+      </c>
+      <c r="B79" s="15" t="s">
+        <v>965</v>
       </c>
     </row>
   </sheetData>

--- a/소방설비기사_필기_문제은행.xlsx
+++ b/소방설비기사_필기_문제은행.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40C7E04-E3B8-49F4-BD87-E428F93BC6A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E304423-5C7E-4DF4-B4BA-E14F0CEE775C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="3" activeTab="5" xr2:uid="{FB57838C-1CAD-4D08-9B84-85A2A61E99B1}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="2" activeTab="2" xr2:uid="{FB57838C-1CAD-4D08-9B84-85A2A61E99B1}"/>
   </bookViews>
   <sheets>
     <sheet name="15년 1회" sheetId="1" r:id="rId1"/>
     <sheet name="15년 2회" sheetId="2" r:id="rId2"/>
-    <sheet name="15년 3회" sheetId="3" r:id="rId3"/>
+    <sheet name="15년 4회" sheetId="3" r:id="rId3"/>
     <sheet name="16년 1회" sheetId="4" r:id="rId4"/>
     <sheet name="16년 2회" sheetId="5" r:id="rId5"/>
-    <sheet name="Sheet5" sheetId="6" r:id="rId6"/>
+    <sheet name="16년 4회" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="966">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="973">
   <si>
     <t>문제</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1000,12 +1000,6 @@
   </si>
   <si>
     <t>반파 정류 정현파의 최대값이 1일 때, 실효값과 평균값은?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">① 
-② 
-③ 
-④ </t>
   </si>
   <si>
     <t>한 코일의 전류가 매초 150A 의 비율로 변화할 때 다른 코 일에 10V 기전력이 발생하였다면 두 코일 상호 인덕턴스(H) 는?</t>
@@ -3992,18 +3986,12 @@
 ④ 고체이다.</t>
   </si>
   <si>
-    <t>화재실 혹은 화재공간의 단위바닥면적에 대한 등가가연물량 의 값을 화재하중이라 하며 식으로 표시할 경우에는 Q=∑(Gt ㆍ Ht)/H ㆍ A와 같이 표현할 수 있다. 여기에서 H는 무엇을 나타내는가?</t>
-  </si>
-  <si>
     <t>① 목재의 단위발열량
 ② 가연물의 단위발열량
 ③ 화재실내 가연물의 전체 발열량
 ④ 목재의 단위발열량과 가연물의 단위발열량을 합한 것</t>
   </si>
   <si>
-    <t>위험물안전관리법상 위험물의 적재 시 혼재기중 혼재가 가능 한 위험물로 짝지어진 것은? (단, 각 위험물은 지정수량의 10배로 가정한다.)</t>
-  </si>
-  <si>
     <t>① 질산칼륨과 가솔린
 ② 과산화수소와 황린
 ③ 철분과 유기과산화물
@@ -4040,12 +4028,6 @@
     <t>할로겐 화합물 소화설비에서 Halon 1211 약제의 분자식은?</t>
   </si>
   <si>
-    <t>① CBr ClF
-② CF ClBr 2 2
-③ COl BrF
-④ BrC ClF 2 2</t>
-  </si>
-  <si>
     <t>조연성가스로만 나열되어 있는 것은?</t>
   </si>
   <si>
@@ -4058,11 +4040,6 @@
     <t>다음 중 제거소화 방법과 무관한 것은?</t>
   </si>
   <si>
-    <t>① 산불의 확산방지를 위하여 산림의 일부를 벌채한다.
-② 화학반응기의 화재 시 원료 공급관의 밸브를 잠근다.
-④ 유류탱크 화재 시 주변에 있는 유류탱크의 유류를 다른 곳으로 이동시킨다.</t>
-  </si>
-  <si>
     <t>실내에서 화재가 발생하여 실내의 온도가 21℃에서 650℃ 로 되었다면, 공기의 팽창은 처음의 약 몇 배가 되는가? (단, 대기압은 공기가 유동하여 화재 전후가 같다고 가정한 다.)</t>
   </si>
   <si>
@@ -4072,9 +4049,6 @@
 ④ 6.01</t>
   </si>
   <si>
-    <t>연기에 의한 감광계수가 0.1m-1, 가시거리가 20~30m일 때 의 상황을 옳게 설명한 것은?</t>
-  </si>
-  <si>
     <t>① 건물 내부에 익숙한 사람이 피난에 지장을 느낄 정도
 ② 연기감지기가 작동할 정도
 ③ 어두운 것을 느낄 정도
@@ -4084,12 +4058,6 @@
     <t>물의 물리ㆍ화학적 성질로 틀린 것은?</t>
   </si>
   <si>
-    <t>① 증발잠열은 539.6cal/g으로 다른 물질에 비해 매우 큰 편이다.
-② 대기압하에서 100℃의 물이 액체에서 수증기로 바뀌면 체적은 약 1603배 정도 증가한다.
-③ 수소 1분자와 산소 1/2분자로 이루어져 있으며 이들 사 이의 화학결합은 극성 공유결합이다.
-④ 분자간의 결합은 쌍극자-쌍극자 상호작용의 일종인 산소 결합에 의해 이루어진다.</t>
-  </si>
-  <si>
     <t>다음 중 증기비중이 가장 큰 것은?</t>
   </si>
   <si>
@@ -4108,9 +4076,6 @@
 ④ 탱크 저부의 물이 급격히 증발하여 기름이 탱크밖으로 화재를 동반하여 방출하는 현상</t>
   </si>
   <si>
-    <t>건축물의 화재성상 중 내화건축물의 화재성상으로 옳은 것 은?</t>
-  </si>
-  <si>
     <t>① 저온 장기형
 ② 고온 단기형
 ③ 고온 장기형
@@ -4120,19 +4085,7 @@
     <t>정전기에 의한 발화과정으로 옳은 것은?</t>
   </si>
   <si>
-    <t>① 방전→전하의 축적→전하의 발생→발화
-② 전하의 발생→전하의 축적→방전→발화
-③ 전하의 발생→방전→전하의 축적→발화
-④ .전하의 축적→방전→전하의 발생→발화</t>
-  </si>
-  <si>
     <t>피난계획의 일반원칙 중 Fool proof 원칙에 해당하는 것은?</t>
-  </si>
-  <si>
-    <t>① 저지능인 상태에서도 쉽게 식별이 가능하도록 그림이나 색채를 이용하는 원칙
-② 피난설비를 반드시 이동식으로 하는 원칙
-③ 한 가지 피난기구가 고장이 나도 다른 수단을 이용할 수
-④ 피난설비를 첨단화된 전자식으로 하는 원칙</t>
   </si>
   <si>
     <t>칼륨에 화재가 발생할 경우에 주수를 하면 안되는 이유로 가장 옳은 것은?</t>
@@ -4144,18 +4097,6 @@
 ④ 수증기가 발생하기 때문에</t>
   </si>
   <si>
-    <t>분말소화약제의 열분해 반응식 중 다음 ( )안에 알맞은 화학 식은?</t>
-  </si>
-  <si>
-    <t>① CO
-② CO 2
-③ Na
-④ Na 2</t>
-  </si>
-  <si>
-    <t>전원과 부하가 다같이 △결선된 3상 평형회로가 있다. 전원 전압이 200V, 부하 1상의 임피던스가 4+j3Ω인 경우 선전류 는 몇 A 인가?</t>
-  </si>
-  <si>
     <t>① 40/√3
 ② 40/3
 ③ 40
@@ -4189,18 +4130,6 @@
 ④ 종축 : 자속밀도, 횡축 :자계의 세기</t>
   </si>
   <si>
-    <t>4단자 정수 A=5/3, B=800, C=1/450, D=5/3 일 때 영상 임피던스 Z01과 Z02는 각각 몇 Ω인가?</t>
-  </si>
-  <si>
-    <t>① Z =300, Z =300
-② Z =600, Z =600 01 02 01 02
-③ Z =800, Z =800
-④ Z =1000, Z =1000 01 02 01 02</t>
-  </si>
-  <si>
-    <t>200Ω의 저항을 가진 경종 10개와 50Ω의 저항을 가진 표시 등 3개가 있다. 이들을 모두 직렬로 접속할 때의 합성저항 은 몇 Ω인가?</t>
-  </si>
-  <si>
     <t>① 250
 ② 1250
 ③ 1750
@@ -4219,12 +4148,6 @@
     <t>지시계기에 대한 동작원리가 틀린 것은?</t>
   </si>
   <si>
-    <t>① 열전형 계기 - 대전된 도체 사이에 작용하는 정전력을 이용
-② 가동 철편형 계기 - 전류에 의한 자기장이 연철편에 작 용하는 힘을 이용
-③ 전류력계형 계기 - 전류 상호간에 작용하는 힘을 이용
-④ 유도형 계기 - 회전 자기장 또는 이동 자기장과 이것에 의한 유도정류와의 상호작용을 이용</t>
-  </si>
-  <si>
     <t>다음 중 쌍방향성 사이리스터인 것은?</t>
   </si>
   <si>
@@ -4234,9 +4157,6 @@
 ④ TRIAC</t>
   </si>
   <si>
-    <t>SCR의 양극 전류가 10A 일 때 게이트 전류를 반으로 줄이 면 양극 전류는 몇 A 인가?</t>
-  </si>
-  <si>
     <t>① 20
 ② 10
 ③ 5
@@ -4246,9 +4166,6 @@
     <t>어떤 측정계기의 지시값을 M, 참값을 T라 할 때 보정율은?</t>
   </si>
   <si>
-    <t>자기인덕턴스 L , L 가 각각 4mH, 9mH 인 두 코일이 이 1 2 상적인 결합이 되었다면 상호인덕턴스는 몇 mH인가? (단, 결합계수는 1 이다.)</t>
-  </si>
-  <si>
     <t>① 6
 ② 12
 ③ 24
@@ -4258,21 +4175,7 @@
     <t>국제 표준 연동 고유저항은 몇 Ωㆍm인가?</t>
   </si>
   <si>
-    <t>① 1.7241×10-9
-② 1.7241×10-8
-③ 1.7241×10-7
-④ 1.7241×10-6</t>
-  </si>
-  <si>
     <t>도너(donor)와 억셉터(acceptor)의 설명 중 틀린 것은?</t>
-  </si>
-  <si>
-    <t>① 반도체 결정에서 Ge이나 Si에 넣는 5가의 불순물을 도 너라고 한다.
-② 반도체 결정에서 Ge이나 Si에 넣는 3가의 불순물에는 In, Ga, B 등이 있다.
-③ 진성반도체는 불순물이 전혀 섞이지 않은 반도체이다.</t>
-  </si>
-  <si>
-    <t>변압기의 철심구조를 여러 겹으로 성층시켜 사용하는 이유 는 무엇인가?</t>
   </si>
   <si>
     <t>① 와전류로 인한 전력손실을 감소시키기 위해
@@ -4299,40 +4202,18 @@
 ④ 65</t>
   </si>
   <si>
-    <t>그림과 같은 정류회로에서 부하 R에 흐르는 직류전류의 크 기는 약 몇 A인가? (단, V=200V, R=20√2Ω이며, 이상적인 다이오드이다.)</t>
-  </si>
-  <si>
     <t>① 3.2
 ② 3.8
 ③ 4.4
 ④ 5.2</t>
   </si>
   <si>
-    <t>계단변화에 대하여 잔류편차가 없는 것이 장점이며, 간헐현 상이 있는 제어계는?</t>
-  </si>
-  <si>
     <t>① 비례제어계
 ② 비례미분제어계
 ③ 비례적분제어계
 ④ 비례적분미분제어계</t>
   </si>
   <si>
-    <t>그림과 같은 트랜지스터를 사용한 정전압회로에서 Q 의 역 1 할로서 옳은 것은?</t>
-  </si>
-  <si>
-    <t>① 증폭용
-② 비교부용
-③ 제어용
-④ 기준부용
-① 황화린 - 100kg
-② 유황 - 300kg
-③ 철분 - 500kg
-④ 인화성고체 - 1000kg</t>
-  </si>
-  <si>
-    <t>소방시설공사업법상 소방시설업 등록신청 신청서 및 첨부서 류에 기재되어야 할 내용이 명확하지 아니한 경우 서류의 보완 기간은 며칠 이내인가?</t>
-  </si>
-  <si>
     <t>① 14
 ② 10
 ③ 7
@@ -4348,9 +4229,6 @@
 ④ 마약진료소</t>
   </si>
   <si>
-    <t>소방용품의 형식승인을 반드시 취소하여야 하는 경우가 아 닌 것은?</t>
-  </si>
-  <si>
     <t>① 거짓 또는 부정한 방법으로 형식승인을 받은 경우
 ② 시험시설의 시설기준에 미달되는 경우
 ③ 거짓 또는 부정한 방법으로 제품검사를 받은 경우
@@ -4375,12 +4253,6 @@
 ④ 6</t>
   </si>
   <si>
-    <t>화재예방, 소방시설 설치ㆍ유지 및 안전관리에 관한 법률에 따른 소방안전관리 업무를 하지 아니한 특정소방대상물의 관계인에게는 몇 만원 이하의 과태료를 부과하는가?(2021년 12월 28일 개정된 규정 적용됨)</t>
-  </si>
-  <si>
-    <t>작동기능점검을 실시한 자는 작동기능점검 실시결과 보고서 를 며칠 이내에 소방본부장 또는 소방서장에게 제출해야 하 는가?(2020년 8월 14일 변경된 규정 적용됨)</t>
-  </si>
-  <si>
     <t>① 7
 ② 10
 ③ 20
@@ -4396,35 +4268,6 @@
 ④ 자연발화성물질</t>
   </si>
   <si>
-    <t>소방기본법상의 벌칙으로 5년이하의 징역 또는 3000만원 이하의 벌금에 해당하지 않는 것은?(관련 규정 개정전 문제 로 여기서는 기존 정답인 2번을 누르면 정답 처리됩니다.)</t>
-  </si>
-  <si>
-    <t>① 소방자동차가 화재진압 및 구조ㆍ구급활동을 위하여 출 동할 때 그 출동을 방해한 자
-② 사람을 구출하거나 불이 번지는 것을 막기 위하여 불이 번질 우려가 있는 소방대상물의 사용제한의 강제처분을 방해한 자
-④ 정당한 사유 없이 소방용수시설의 효용을 해치거나 그 정당한 사용을 방해한 자</t>
-  </si>
-  <si>
-    <t>일반 소방시설 설계업(기계분야)의 영업범위는 공장의 경우 연면적 몇 m2미만의 특정소방대상물에 설치되는 기계분야 소방시설의 설계에 한하는가? (단, 제연설비가 설치되는 특 정소방대상물은 제외한다.)</t>
-  </si>
-  <si>
-    <t>① 10000m2
-② 20000m2
-③ 30000m2
-④ 40000m2</t>
-  </si>
-  <si>
-    <t>소방본부장이 소방특별조사위원회 위원으로 임명하거나 위 촉할 수 있는 사람이 아닌 것은?</t>
-  </si>
-  <si>
-    <t>① 소방시설관리사
-② 과장급 직위 이상의 소방공무원
-③ 소방 관련 분야의 석사학위 이상을 취득한 사람
-④ 소방 관련 법인 또는 단체에서 소방 관련 업무에 3년 이 상 종사한 사람</t>
-  </si>
-  <si>
-    <t>교육연구시설 중 학교 지하층은 바닥면적의 합계가 몇 m2이 상인 경우 연결살수설비를 설치해야 하는가?</t>
-  </si>
-  <si>
     <t>① 500
 ② 600
 ③ 700
@@ -4449,18 +4292,12 @@
 ④ 과징금 부과처분</t>
   </si>
   <si>
-    <t>소방장비 등에 대한 국고보조 대상사업의 범위와 기준보조 율은 무엇으로 정하는가?</t>
-  </si>
-  <si>
     <t>① 총리령
 ② 대통령령
 ③ 시ㆍ도의 조례
 ④ 국토교통부령</t>
   </si>
   <si>
-    <t>하자보수 대상 소방시설 중 하자보수 보증기간이 2년이 아 닌 것은?</t>
-  </si>
-  <si>
     <t>① 유도표시
 ② 비상경보설비
 ③ 무선통신보조설비
@@ -4476,29 +4313,7 @@
 ④ 판매취급소</t>
   </si>
   <si>
-    <t>소방용수시설 중 소화전과 급수탑의 설치기준으로 틀린 것 은?</t>
-  </si>
-  <si>
-    <t>① 소화전은 상수도와 연결하려 지하식 또는 지상식의 구조 로 할 것
-② 소방용호스와 연결하는 소화전의 연결금속구의 구경은 65mm로 할 것
-③ 급수탑 급수배관의 구경은 100mm 이상으로 할 것
-④ 급수탑의 개폐밸브는 지상에서 1.5m 이상 1.8m 이하의 위치에 설치할 것 중 유황만을 저장ㆍ취급하는 옥내탱크저장소에 설치해야 하 는 소화설비는?
-① 옥내소화전설비
-② 옥외소화전설비
-③ 물분무소화설비
-④ 고정식 포소화설비</t>
-  </si>
-  <si>
     <t>통로유도등의 설치기준 중 틀린 것은?</t>
-  </si>
-  <si>
-    <t>① 거실의 통로가 벽체 등으로 구획된 경우에는 거실통로유 도등을 설치한다.
-② 거실통로유도등은 거실통로에 기둥이 설치된 경우에는 기둥부분의 바닥으로부터 높이 1.5m 이하의 위치에 설 치할 수 있다.
-③ 복도통로유도등은 구부러진 모퉁이 및 보행거리 20m 마 다 설치한다.
-④ 계단통로유도등은 바닥으로부터 높이 1m이하의 위치에 설치한다.</t>
-  </si>
-  <si>
-    <t>비상콘센트설비의 전원회로의 공급용량은 최소 몇 kVA 이상 인 것으로 설치해야 하는가?</t>
   </si>
   <si>
     <t>① 1.5
@@ -4516,38 +4331,19 @@
 ④ ㉠ 2.1, ㉡ 5</t>
   </si>
   <si>
-    <t>무선통신보조설비의 누설동축케이블 및 공중선은 고압의 전 류로부터 1.5m 이상 떨어진 위치에 설치해야 하나 그렇게 하지 않아도 되는 경우는?</t>
-  </si>
-  <si>
     <t>① 해당 전로에 정전기 차폐장치를 유효하게 설치한 경우
 ② 금속제 등의 지지금구로 일정한 간격으로 고정한 경우
 ③ 끝부분에 무반사 종단저항을 설치한 경우
 ④ 불연재료로 구획된 반자 안에 설치한 경우</t>
   </si>
   <si>
-    <t>유도등의 전기회로에 점멸기를 설치할 수 있는 장소에 해당 되지 않는 것은? (단, 유도등은 3선식 배선에 따라 상시 충 전되는 구조이다.)</t>
-  </si>
-  <si>
     <t>① 공연장으로서 어두워야 할 필요가 있는 장소
 ② 특정소방대상물의 관계인이 주로 사용하는 장소
 ③ 외부광에 따라 피난구 또는 피난방향을 쉽게 식별할 수 있는 장소
 ④ 지하층을 제외한 층수가 11층 이상의 장소</t>
   </si>
   <si>
-    <t>각 실별 실내의 바닥면적이 25m2인 4개의 실에 단독경보형 감지기를 설치 시 몇 개의 실로 보아야 하는가? (단, 각 실 은 이웃하고 있으며, 벽체 상부가 일부 개방되어 이웃하는</t>
-  </si>
-  <si>
-    <t>③ 3
-④ 4</t>
-  </si>
-  <si>
     <t>피난기구 중 다수인 피난장비의 설치기준 중 틀린 것은?</t>
-  </si>
-  <si>
-    <t>① 사용 시에 보관실 외측 문이 먼저 열리고 탑승기가 외측 으로 자동으로 전개될 것
-② 하강 시에 탑승기가 건물 외벽이나 돌출물에 충돌하지 않도록 설치할 것
-③ 상ㆍ하층에 설치할 경우에는 탑승기의 하강경로가 중첩 되도록 할 것
-④ 보관실은 건물 외측보다 돌출되지 아니하고, 빗물ㆍ먼지 등으로 부터 장비를 보호할 수 있는 구조 일 것</t>
   </si>
   <si>
     <t>누전경보기 수신부의 기능검사 항목이 아닌 것은?</t>
@@ -4559,27 +4355,18 @@
 ④ 전원전압 변동시험</t>
   </si>
   <si>
-    <t>아파트형 공장의 지하 주차장에 설치된 비상방송용 스피커 의 음량조정기 배선방식은?</t>
-  </si>
-  <si>
     <t>① 단선식
 ② 2선식
 ③ 3선식
 ④ 복합식</t>
   </si>
   <si>
-    <t>공동주택 4층 이상 10층 이하에 적응성이 있는 피난기구 는?(단, 공동주택은 공동주택 관리법 시행령 제 2조의 규정 에 해당하는 공동주택이다.)</t>
-  </si>
-  <si>
     <t>① 간이완강기
 ② 피난용트랩
 ③ 미끄럼대
 ④ 공기안전매트</t>
   </si>
   <si>
-    <t>감지기의 설치기준 중 부착높이 20m이상에 설치되는 광전 식 중 아날로그장식의 감지기는 공칭감지농도 하한값이 감 광율 몇 %/m 미만인 것으로 하는가?</t>
-  </si>
-  <si>
     <t>연기감지기 설치 시 천장 또는 반자부근에 배기구가 있는 경우에 감지기의 설치위치로 옳은 것은?</t>
   </si>
   <si>
@@ -4598,23 +4385,7 @@
 ④ ㉠ 40Ω 이하, ㉡ 80</t>
   </si>
   <si>
-    <t>누전경보기의 변류기는 경계전로에 정격전류를 흘리는 경우 그 경계전로의 전압강하는 몇 V 이하여야 하는가? (단, 경 계전로의 전선을 그 변류기에 관통시키는 것은 제외한다.)</t>
-  </si>
-  <si>
-    <t>① 0.3
-② 0.5</t>
-  </si>
-  <si>
     <t>무선통신보조설비 증폭기의 설치기준으로 틀린 것은?</t>
-  </si>
-  <si>
-    <t>① 증폭기는 비상전원이 부착된 것으로 한다.
-② 증폭기의 전면에는 표시등 및 전류계를 설치한다.
-③ 전원은 전기가 정상적으로 공급되는 축전지 또는 교류전 압 옥내간선으로 하고 전원까지의 배선은 전용으로 한 다,
-④ 증폭기의 비상전원용량은 무선통신보조설비 유효하게 30 분 이상 작동시킬 수 있는 것으로 한다.</t>
-  </si>
-  <si>
-    <t>비상콘센트의 배치는 아파트 또는 바닥면적이 1000m2 미만 인 층은 계단의 출입구로부터 몇 m 이내에 설치해야 하는 가? (단. 계단의 부속실을 포함하며 계단이 2 이상 있는 경 우에는 그 중 1개의 계단을 말한다.)</t>
   </si>
   <si>
     <t>① 10
@@ -4623,9 +4394,6 @@
 ④ 3</t>
   </si>
   <si>
-    <t>비상방송설비는 기동장치에 따른 화재신고를 수신한 후 필 요한 음량으로 화재발생 상황 및 피난에 유효한 방송이 자 동으로 개시될 때까지의 소요시간은 몇 초 이하여야 하는 가?</t>
-  </si>
-  <si>
     <t>① 5
 ② 10
 ③ 30
@@ -4650,93 +4418,322 @@
 ④ 광축은 나란한 벽으로부터 0.5m 이상 이격하여 설치할 것</t>
   </si>
   <si>
-    <t>자동화재속보설비 속보기의 구조에 대한 설명 중 틀린 것 은?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">① 수동통화용 송수화장치를 설치하여야 한다.
+    <t>화재실 혹은 화재공간의 단위바닥면적에 대한 등가가연물량의 값을 화재하중이라 하며 식으로 표시할 경우에는 Q=∑(Gt ㆍ Ht)/H ㆍ A와 같이 표현할 수 있다. 여기에서 H는 무엇을 나타내는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위험물안전관리법상 위험물의 적재 시 혼재기중 혼재가 가능한 위험물로 짝지어진 것은? (단, 각 위험물은 지정수량의 10배로 가정한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 산불의 확산방지를 위하여 산림의 일부를 벌채한다.
+② 화학반응기의 화재 시 원료 공급관의 밸브를 잠근다.
+③ 유류화재 시 가연물을 포로 덮는다.
+④ 유류탱크 화재 시 주변에 있는 유류탱크의 유류를 다른 곳으로 이동시킨다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연기에 의한 감광계수가 0.1m^-1, 가시거리가 20~30m일 때 의 상황을 옳게 설명한 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 증발잠열은 539.6cal/g으로 다른 물질에 비해 매우 큰 편이다.
+② 대기압하에서 100℃의 물이 액체에서 수증기로 바뀌면 체적은 약 1603배 정도 증가한다.
+③ 수소 1분자와 산소 1/2분자로 이루어져 있으며 이들 사이의 화학결합은 극성 공유결합이다.
+④ 분자간의 결합은 쌍극자-쌍극자 상호작용의 일종인 산소결합에 의해 이루어진다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>건축물의 화재성상 중 내화건축물의 화재성상으로 옳은 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 방전→전하의 축적→전하의 발생→발화
+② 전하의 발생→전하의 축적→방전→발화
+③ 전하의 발생→방전→전하의 축적→발화
+④ 전하의 축적→방전→전하의 발생→발화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 저지능인 상태에서도 쉽게 식별이 가능하도록 그림이나 색채를 이용하는 원칙
+② 피난설비를 반드시 이동식으로 하는 원칙
+③ 한 가지 피난기구가 고장이 나도 다른 수단을 이용할 수 있도록 고려하는 원칙
+④ 피난설비를 첨단화된 전자식으로 하는 원칙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① CO
+② CO₂
+③ Na
+④ Na₂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>분말소화약제의 열분해 반응식 중 다음 ( )안에 알맞은 화학식은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16420a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전원과 부하가 다같이 △결선된 3상 평형회로가 있다. 전원 전압이 200V, 부하 1상의 임피던스가 4+j3Ω인 경우 선전류는 몇 A 인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① Z₁ =300, Z₂ =300
+② Z₁ =600, Z₂ =600
+③ Z₁ =800, Z₂ =800
+④ Z₁ =1000, Z₂ =1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4단자 정수 A=5/3, B=800, C=1/450, D=5/3 일 때 영상 임피던스 Z₁과 Z₂는 각각 몇 Ω인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200Ω의 저항을 가진 경종 10개와 50Ω의 저항을 가진 표시등 3개가 있다. 이들을 모두 직렬로 접속할 때의 합성저항은 몇 Ω인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16427a</t>
+  </si>
+  <si>
+    <t>① 열전형 계기 - 대전된 도체 사이에 작용하는 정전력을 이용
+② 가동 철편형 계기 - 전류에 의한 자기장이 연철편에 작용하는 힘을 이용
+③ 전류력계형 계기 - 전류 상호간에 작용하는 힘을 이용
+④ 유도형 계기 - 회전 자기장 또는 이동 자기장과 이것에 의한 유도정류와의 상호작용을 이용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCR의 양극 전류가 10A 일 때 게이트 전류를 반으로 줄이면 양극 전류는 몇 A 인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자기인덕턴스 L₁ , L₂ 가 각각 4mH, 9mH 인 두 코일이 이상적인 결합이 되었다면 상호인덕턴스는 몇 mH인가? (단, 결합계수는 1 이다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 1.7241×10^-9
+② 1.7241×10^-8
+③ 1.7241×10^-7
+④ 1.7241×10^-6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 반도체 결정에서 Ge이나 Si에 넣는 5가의 불순물을 도너라고 한다.
+② 반도체 결정에서 Ge이나 Si에 넣는 3가의 불순물에는 In, Ga, B 등이 있다.
+③ 진성반도체는 불순물이 전혀 섞이지 않은 반도체이다.
+④ N형 반도체의 불순물이 억셉터이고, P형 반도체의 불순물이 도너이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>변압기의 철심구조를 여러 겹으로 성층시켜 사용하는 이유는 무엇인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16438a</t>
+  </si>
+  <si>
+    <t>그림과 같은 정류회로에서 부하 R에 흐르는 직류전류의 크기는 약 몇 A인가? (단, V=200V, R=20√2Ω이며, 이상적인 다이오드이다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>계단변화에 대하여 잔류편차가 없는 것이 장점이며, 간헐현 상이 있는 제어계는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 황화린 - 100kg
+② 유황 - 300kg
+③ 철분 - 500kg
+④ 인화성고체 - 1000kg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 증폭용
+② 비교부용
+③ 제어용
+④ 기준부용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그림과 같은 트랜지스터를 사용한 정전압회로에서 Q₁ 의 역할로서 옳은 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16440a</t>
+  </si>
+  <si>
+    <t>제2류 위험물의 품명에 따른 지정수량의 연결이 틀린 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소방시설공사업법상 소방시설업 등록신청 신청서 및 첨부서류에 기재되어야 할 내용이 명확하지 아니한 경우 서류의 보완 기간은 며칠 이내인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소방용품의 형식승인을 반드시 취소하여야 하는 경우가 아닌 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화재예방, 소방시설 설치ㆍ유지 및 안전관리에 관한 법률에 따른 소방안전관리 업무를 하지 아니한 특정소방대상물의 관계인에게는 몇 만원 이하의 과태료를 부과하는가?(2021년 12월 28일 개정된 규정 적용됨)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작동기능점검을 실시한 자는 작동기능점검 실시결과 보고서를 며칠 이내에 소방본부장 또는 소방서장에게 제출해야 하는가?(2020년 8월 14일 변경된 규정 적용됨)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소방기본법상의 벌칙으로 5년이하의 징역 또는 3000만원 이하의 벌금에 해당하지 않는 것은?(관련 규정 개정전 문제로 여기서는 기존 정답인 2번을 누르면 정답 처리됩니다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 소방자동차가 화재진압 및 구조ㆍ구급활동을 위하여 출동할 때 그 출동을 방해한 자
+② 사람을 구출하거나 불이 번지는 것을 막기 위하여 불이 번질 우려가 있는 소방대상물의 사용제한의 강제처분을 방해한 자
+③ 출동한 소방대의 소방장비를 파손하거나 그 효용을 해하며 화재진압ㆍ인명구조 또는 구급활동을 방해한 자
+④ 정당한 사유 없이 소방용수시설의 효용을 해치거나 그 정당한 사용을 방해한 자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반 소방시설 설계업(기계분야)의 영업범위는 공장의 경우 연면적 몇 m²미만의 특정소방대상물에 설치되는 기계분야 소방시설의 설계에 한하는가? (단, 제연설비가 설치되는 특정소방대상물은 제외한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 10000m²
+② 20000m²
+③ 30000m²
+④ 40000m²</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소방본부장이 소방특별조사위원회 위원으로 임명하거나 위촉할 수 있는 사람이 아닌 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 소방시설관리사
+② 과장급 직위 이상의 소방공무원
+③ 소방 관련 분야의 석사학위 이상을 취득한 사람
+④ 소방 관련 법인 또는 단체에서 소방 관련 업무에 3년 이상 종사한 사람</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>교육연구시설 중 학교 지하층은 바닥면적의 합계가 몇 m²이상인 경우 연결살수설비를 설치해야 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소방장비 등에 대한 국고보조 대상사업의 범위와 기준보조율은 무엇으로 정하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하자보수 대상 소방시설 중 하자보수 보증기간이 2년이 아닌 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소방용수시설 중 소화전과 급수탑의 설치기준으로 틀린 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 소화전은 상수도와 연결하려 지하식 또는 지상식의 구조로 할 것
+② 소방용호스와 연결하는 소화전의 연결금속구의 구경은 65mm로 할 것
+③ 급수탑 급수배관의 구경은 100mm 이상으로 할 것
+④ 급수탑의 개폐밸브는 지상에서 1.5m 이상 1.8m 이하의 위치에 설치할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 옥내소화전설비
+② 옥외소화전설비
+③ 물분무소화설비
+④ 고정식 포소화설</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소화난이도등급 I의 제조소등에 설치해야 하는 소화설비기준 중 유황만을 저장ㆍ취급하는 옥내탱크저장소에 설치해야 하는 소화설비는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 거실의 통로가 벽체 등으로 구획된 경우에는 거실통로유도등을 설치한다.
+② 거실통로유도등은 거실통로에 기둥이 설치된 경우에는 기둥부분의 바닥으로부터 높이 1.5m 이하의 위치에 설치할 수 있다.
+③ 복도통로유도등은 구부러진 모퉁이 및 보행거리 20m 마다 설치한다.
+④ 계단통로유도등은 바닥으로부터 높이 1m이하의 위치에 설치한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상콘센트설비의 전원회로의 공급용량은 최소 몇 kVA 이상인 것으로 설치해야 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16463a</t>
+  </si>
+  <si>
+    <t>무선통신보조설비의 누설동축케이블 및 공중선은 고압의 전류로부터 1.5m 이상 떨어진 위치에 설치해야 하나 그렇게 하지 않아도 되는 경우는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유도등의 전기회로에 점멸기를 설치할 수 있는 장소에 해당 되지 않는 것은? (단, 유도등은 3선식 배선에 따라 상시 충전되는 구조이다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>각 실별 실내의 바닥면적이 25m²인 4개의 실에 단독경보형 감지기를 설치 시 몇 개의 실로 보아야 하는가? (단, 각 실은 이웃하고 있으며, 벽체 상부가 일부 개방되어 이웃하는 실내와 공기가 상호유통되는 경우이다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 사용 시에 보관실 외측 문이 먼저 열리고 탑승기가 외측으로 자동으로 전개될 것
+② 하강 시에 탑승기가 건물 외벽이나 돌출물에 충돌하지 않도록 설치할 것
+③ 상ㆍ하층에 설치할 경우에는 탑승기의 하강경로가 중첩되도록 할 것
+④ 보관실은 건물 외측보다 돌출되지 아니하고, 빗물ㆍ먼지 등으로 부터 장비를 보호할 수 있는 구조 일 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아파트형 공장의 지하 주차장에 설치된 비상방송용 스피커의 음량조정기 배선방식은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공동주택 4층 이상 10층 이하에 적응성이 있는 피난기구는?(단, 공동주택은 공동주택 관리법 시행령 제 2조의 규정에 해당하는 공동주택이다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>감지기의 설치기준 중 부착높이 20m이상에 설치되는 광전식 중 아날로그장식의 감지기는 공칭감지농도 하한값이 감광율 몇 %/m 미만인 것으로 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16473a</t>
+  </si>
+  <si>
+    <t>누전경보기의 변류기는 경계전로에 정격전류를 흘리는 경우 그 경계전로의 전압강하는 몇 V 이하여야 하는가? (단, 경계전로의 전선을 그 변류기에 관통시키는 것은 제외한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 0.3
+② 0.5
+③ 1.0
+④ 3.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 증폭기는 비상전원이 부착된 것으로 한다.
+② 증폭기의 전면에는 표시등 및 전류계를 설치한다.
+③ 전원은 전기가 정상적으로 공급되는 축전지 또는 교류전압 옥내간선으로 하고 전원까지의 배선은 전용으로 한다,
+④ 증폭기의 비상전원용량은 무선통신보조설비 유효하게 30분 이상 작동시킬 수 있는 것으로 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상콘센트의 배치는 아파트 또는 바닥면적이 1000m² 미만인 층은 계단의 출입구로부터 몇 m 이내에 설치해야 하는가? (단. 계단의 부속실을 포함하며 계단이 2 이상 있는 경우에는 그 중 1개의 계단을 말한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상방송설비는 기동장치에 따른 화재신고를 수신한 후 필요한 음량으로 화재발생 상황 및 피난에 유효한 방송이 자동으로 개시될 때까지의 소요시간은 몇 초 이하여야 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 수동통화용 송수화장치를 설치하여야 한다.
 ② 접지전극에 직류전류를 통하는 회로방식을 사용하여야 한다.
-③ 작동 시 그 작동시간과 작동회수를 표시할 수 있는 장치 를 하여야 한다.
-④ 부식에 의한 기계적 기능에 영향을 초래할 우려가 있는 부분은 기계식 내식가공을 하거나 방청가공을 아여야 한 다. 전자문제집 CBT 홈페이지 : www.comcbt.com 기출문제 및 해설집 다운로드 : www.comcbt.com/xe 전자문제집 CBT 앱(구글플레이) : [다운로드] 전자문제집 CBT란? 종이 문제집이 아닌 인터넷으로 문제를 풀고 자동으로 채점하며 모의고사, 오답 노트, 해설까지 제공하는 무료 기출문제 학습 프 로그램으로 실제 시험에서 사용하는 OMR 형식의 CBT를 제공합 니다. PC 버전 및 모바일 버전 완벽 연동 교사용/학생용 관리기능도 제공합니다. 오답 및 오탈자가 수정된 최신 자료와 해설은 전자문제집 CBT 에서 확인하세요. 1 2 3 4 5 6 7 8 9 10
-④ 
-① 
-① 
-③ 
-③ 
-④ 
-① 
-② 
-② 
-③ 11 12 13 14 15 16 17 18 19 20
-① 
-② 
-④ 
-④ 
-④ 
-① 
-② 
-① 
-③ 
-② 21 22 23 24 25 26 27 28 29 30
-④ 
-② 
-④ 
-④ 
-② 
-④ 
-③ 
-① 
-④ 
-② 31 32 33 34 35 36 37 38 39 40
-① 
-① 
-② 
-④ 
-① 
-④ 
-③ 
-① 
-③ 
-③ 41 42 43 44 45 46 47 48 49 50
-② 
-② 
-① 
-② 
-④ 
-③ 
-③ 
-① 
-③ 
-② 51 52 53 54 55 56 57 58 59 60
-① 
-④ 
-③ 
-③ 
-① 
-② 
-④ 
-④ 
-④ 
-③ 61 62 63 64 65 66 67 68 69 70
-① 
-① 
-② 
-① 
-④ 
-① 
-③ 
-③ 
-③ 
-④ 71 72 73 74 75 76 77 78 79 80
-② 
-① 
-② 
-② 
-② 
-③ 
-② 
-③ 
-④ 
-② </t>
+③ 작동 시 그 작동시간과 작동회수를 표시할 수 있는 장치를 하여야 한다.
+④ 부식에 의한 기계적 기능에 영향을 초래할 우려가 있는 부분은 기계식 내식가공을 하거나 방청가공을 아여야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화재속보설비 속보기의 구조에 대한 설명 중 틀린 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -6309,7 +6306,7 @@
     </row>
     <row r="13" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>190</v>
@@ -6321,7 +6318,7 @@
     </row>
     <row r="14" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>191</v>
@@ -6420,7 +6417,7 @@
         <v>205</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C22" s="4">
         <v>1</v>
@@ -6441,10 +6438,10 @@
     </row>
     <row r="24" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>208</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>209</v>
       </c>
       <c r="C24" s="4">
         <v>4</v>
@@ -6453,10 +6450,10 @@
     </row>
     <row r="25" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A25" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>210</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>211</v>
       </c>
       <c r="C25" s="4">
         <v>1</v>
@@ -6465,10 +6462,10 @@
     </row>
     <row r="26" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A26" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>212</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>213</v>
       </c>
       <c r="C26" s="4">
         <v>2</v>
@@ -6477,10 +6474,10 @@
     </row>
     <row r="27" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A27" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>214</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>215</v>
       </c>
       <c r="C27" s="4">
         <v>4</v>
@@ -6489,10 +6486,10 @@
     </row>
     <row r="28" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A28" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>216</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>217</v>
       </c>
       <c r="C28" s="4">
         <v>2</v>
@@ -6501,10 +6498,10 @@
     </row>
     <row r="29" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A29" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>218</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>219</v>
       </c>
       <c r="C29" s="4">
         <v>2</v>
@@ -6513,10 +6510,10 @@
     </row>
     <row r="30" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A30" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>220</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>221</v>
       </c>
       <c r="C30" s="4">
         <v>3</v>
@@ -6525,10 +6522,10 @@
     </row>
     <row r="31" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A31" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>222</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>223</v>
       </c>
       <c r="C31" s="4">
         <v>1</v>
@@ -6537,10 +6534,10 @@
     </row>
     <row r="32" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A32" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C32" s="4">
         <v>2</v>
@@ -6549,10 +6546,10 @@
     </row>
     <row r="33" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A33" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B33" s="4" t="s">
         <v>225</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>226</v>
       </c>
       <c r="C33" s="4">
         <v>3</v>
@@ -6561,24 +6558,24 @@
     </row>
     <row r="34" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A34" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B34" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>228</v>
-      </c>
       <c r="C34" s="4">
         <v>2</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A35" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>229</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>230</v>
       </c>
       <c r="C35" s="4">
         <v>2</v>
@@ -6587,10 +6584,10 @@
     </row>
     <row r="36" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A36" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>231</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>232</v>
       </c>
       <c r="C36" s="4">
         <v>1</v>
@@ -6599,10 +6596,10 @@
     </row>
     <row r="37" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A37" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B37" s="4" t="s">
         <v>233</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>234</v>
       </c>
       <c r="C37" s="4">
         <v>3</v>
@@ -6611,10 +6608,10 @@
     </row>
     <row r="38" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A38" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B38" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>236</v>
       </c>
       <c r="C38" s="4">
         <v>1</v>
@@ -6623,10 +6620,10 @@
     </row>
     <row r="39" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A39" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B39" s="4" t="s">
         <v>237</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>238</v>
       </c>
       <c r="C39" s="4">
         <v>1</v>
@@ -6635,10 +6632,10 @@
     </row>
     <row r="40" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A40" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B40" s="4" t="s">
         <v>239</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>240</v>
       </c>
       <c r="C40" s="4">
         <v>4</v>
@@ -6647,7 +6644,7 @@
     </row>
     <row r="41" spans="1:4" s="11" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A41" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B41" s="10">
         <v>15240</v>
@@ -6656,15 +6653,15 @@
         <v>3</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A42" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C42" s="4">
         <v>4</v>
@@ -6673,7 +6670,7 @@
     </row>
     <row r="43" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A43" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>108</v>
@@ -6685,10 +6682,10 @@
     </row>
     <row r="44" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A44" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>244</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>245</v>
       </c>
       <c r="C44" s="4">
         <v>3</v>
@@ -6697,10 +6694,10 @@
     </row>
     <row r="45" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A45" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B45" s="4" t="s">
         <v>246</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>247</v>
       </c>
       <c r="C45" s="4">
         <v>2</v>
@@ -6709,10 +6706,10 @@
     </row>
     <row r="46" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A46" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C46" s="4">
         <v>4</v>
@@ -6721,10 +6718,10 @@
     </row>
     <row r="47" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A47" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C47" s="4">
         <v>1</v>
@@ -6733,24 +6730,24 @@
     </row>
     <row r="48" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A48" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B48" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="B48" s="4" t="s">
-        <v>251</v>
-      </c>
       <c r="C48" s="4">
         <v>3</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A49" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C49" s="4">
         <v>3</v>
@@ -6759,10 +6756,10 @@
     </row>
     <row r="50" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A50" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>253</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>254</v>
       </c>
       <c r="C50" s="4">
         <v>2</v>
@@ -6771,10 +6768,10 @@
     </row>
     <row r="51" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A51" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C51" s="4">
         <v>3</v>
@@ -6783,10 +6780,10 @@
     </row>
     <row r="52" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A52" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B52" s="4" t="s">
         <v>256</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>257</v>
       </c>
       <c r="C52" s="4">
         <v>3</v>
@@ -6795,10 +6792,10 @@
     </row>
     <row r="53" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A53" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C53" s="4">
         <v>2</v>
@@ -6807,10 +6804,10 @@
     </row>
     <row r="54" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A54" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B54" s="4" t="s">
         <v>259</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>260</v>
       </c>
       <c r="C54" s="4">
         <v>3</v>
@@ -6819,10 +6816,10 @@
     </row>
     <row r="55" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A55" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C55" s="4">
         <v>3</v>
@@ -6831,10 +6828,10 @@
     </row>
     <row r="56" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A56" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B56" s="4" t="s">
         <v>262</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>263</v>
       </c>
       <c r="C56" s="4">
         <v>1</v>
@@ -6843,10 +6840,10 @@
     </row>
     <row r="57" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A57" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B57" s="4" t="s">
         <v>264</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>265</v>
       </c>
       <c r="C57" s="4">
         <v>1</v>
@@ -6855,10 +6852,10 @@
     </row>
     <row r="58" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A58" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B58" s="4" t="s">
         <v>266</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>267</v>
       </c>
       <c r="C58" s="4">
         <v>4</v>
@@ -6867,10 +6864,10 @@
     </row>
     <row r="59" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A59" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B59" s="4" t="s">
         <v>268</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>269</v>
       </c>
       <c r="C59" s="4">
         <v>2</v>
@@ -6879,10 +6876,10 @@
     </row>
     <row r="60" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A60" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B60" s="4" t="s">
         <v>270</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>271</v>
       </c>
       <c r="C60" s="4">
         <v>4</v>
@@ -6891,10 +6888,10 @@
     </row>
     <row r="61" spans="1:4" s="11" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A61" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="B61" s="10" t="s">
         <v>272</v>
-      </c>
-      <c r="B61" s="10" t="s">
-        <v>273</v>
       </c>
       <c r="C61" s="10">
         <v>1</v>
@@ -6903,10 +6900,10 @@
     </row>
     <row r="62" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A62" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C62" s="4">
         <v>1</v>
@@ -6915,10 +6912,10 @@
     </row>
     <row r="63" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A63" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B63" s="4" t="s">
         <v>275</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>276</v>
       </c>
       <c r="C63" s="4">
         <v>3</v>
@@ -6927,10 +6924,10 @@
     </row>
     <row r="64" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A64" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C64" s="4">
         <v>2</v>
@@ -6939,10 +6936,10 @@
     </row>
     <row r="65" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A65" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C65" s="4">
         <v>2</v>
@@ -6951,10 +6948,10 @@
     </row>
     <row r="66" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A66" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B66" s="4" t="s">
         <v>279</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>280</v>
       </c>
       <c r="C66" s="4">
         <v>1</v>
@@ -6963,10 +6960,10 @@
     </row>
     <row r="67" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A67" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B67" s="4" t="s">
         <v>281</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>282</v>
       </c>
       <c r="C67" s="4">
         <v>3</v>
@@ -6975,10 +6972,10 @@
     </row>
     <row r="68" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A68" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B68" s="4" t="s">
         <v>283</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>284</v>
       </c>
       <c r="C68" s="4">
         <v>4</v>
@@ -6987,10 +6984,10 @@
     </row>
     <row r="69" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A69" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C69" s="4">
         <v>2</v>
@@ -6999,10 +6996,10 @@
     </row>
     <row r="70" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A70" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C70" s="4">
         <v>4</v>
@@ -7011,10 +7008,10 @@
     </row>
     <row r="71" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A71" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B71" s="4" t="s">
         <v>286</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>287</v>
       </c>
       <c r="C71" s="4">
         <v>4</v>
@@ -7023,10 +7020,10 @@
     </row>
     <row r="72" spans="1:4" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A72" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C72" s="4">
         <v>3</v>
@@ -7035,10 +7032,10 @@
     </row>
     <row r="73" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A73" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C73" s="4">
         <v>3</v>
@@ -7047,10 +7044,10 @@
     </row>
     <row r="74" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A74" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B74" s="4" t="s">
         <v>290</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>291</v>
       </c>
       <c r="C74" s="4">
         <v>4</v>
@@ -7059,10 +7056,10 @@
     </row>
     <row r="75" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A75" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="B75" s="4" t="s">
         <v>292</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>293</v>
       </c>
       <c r="C75" s="4">
         <v>4</v>
@@ -7071,7 +7068,7 @@
     </row>
     <row r="76" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A76" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B76" s="4">
         <v>15275</v>
@@ -7083,24 +7080,24 @@
     </row>
     <row r="77" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A77" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B77" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="B77" s="4" t="s">
-        <v>296</v>
-      </c>
       <c r="C77" s="4">
         <v>2</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A78" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C78" s="4">
         <v>2</v>
@@ -7109,10 +7106,10 @@
     </row>
     <row r="79" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A79" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C79" s="4">
         <v>2</v>
@@ -7121,24 +7118,24 @@
     </row>
     <row r="80" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A80" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="B80" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="B80" s="4" t="s">
-        <v>300</v>
-      </c>
       <c r="C80" s="4">
         <v>3</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A81" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C81" s="4">
         <v>1</v>
@@ -7178,10 +7175,10 @@
     </row>
     <row r="2" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -7189,10 +7186,10 @@
     </row>
     <row r="3" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -7200,10 +7197,10 @@
     </row>
     <row r="4" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -7211,10 +7208,10 @@
     </row>
     <row r="5" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -7222,10 +7219,10 @@
     </row>
     <row r="6" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -7233,10 +7230,10 @@
     </row>
     <row r="7" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -7244,10 +7241,10 @@
     </row>
     <row r="8" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -7255,10 +7252,10 @@
     </row>
     <row r="9" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -7266,10 +7263,10 @@
     </row>
     <row r="10" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -7277,10 +7274,10 @@
     </row>
     <row r="11" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -7288,10 +7285,10 @@
     </row>
     <row r="12" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -7299,10 +7296,10 @@
     </row>
     <row r="13" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -7310,10 +7307,10 @@
     </row>
     <row r="14" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -7321,10 +7318,10 @@
     </row>
     <row r="15" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A15" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -7332,10 +7329,10 @@
     </row>
     <row r="16" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C16">
         <v>2</v>
@@ -7343,10 +7340,10 @@
     </row>
     <row r="17" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -7354,10 +7351,10 @@
     </row>
     <row r="18" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -7365,10 +7362,10 @@
     </row>
     <row r="19" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C19">
         <v>4</v>
@@ -7376,10 +7373,10 @@
     </row>
     <row r="20" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C20">
         <v>4</v>
@@ -7387,10 +7384,10 @@
     </row>
     <row r="21" spans="1:4" s="14" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A21" s="13" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C21" s="14">
         <v>2</v>
@@ -7398,24 +7395,24 @@
     </row>
     <row r="22" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22" t="s">
         <v>462</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>459</v>
-      </c>
-      <c r="C22">
-        <v>2</v>
-      </c>
-      <c r="D22" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A23" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C23">
         <v>3</v>
@@ -7423,10 +7420,10 @@
     </row>
     <row r="24" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -7434,10 +7431,10 @@
     </row>
     <row r="25" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A25" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C25">
         <v>4</v>
@@ -7445,24 +7442,24 @@
     </row>
     <row r="26" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A26" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
         <v>465</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A27" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C27">
         <v>3</v>
@@ -7470,10 +7467,10 @@
     </row>
     <row r="28" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A28" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C28">
         <v>2</v>
@@ -7481,10 +7478,10 @@
     </row>
     <row r="29" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A29" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -7492,10 +7489,10 @@
     </row>
     <row r="30" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A30" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C30">
         <v>2</v>
@@ -7503,10 +7500,10 @@
     </row>
     <row r="31" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A31" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C31">
         <v>3</v>
@@ -7514,10 +7511,10 @@
     </row>
     <row r="32" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A32" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -7525,10 +7522,10 @@
     </row>
     <row r="33" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A33" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C33">
         <v>3</v>
@@ -7536,10 +7533,10 @@
     </row>
     <row r="34" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A34" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -7547,10 +7544,10 @@
     </row>
     <row r="35" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A35" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -7558,10 +7555,10 @@
     </row>
     <row r="36" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A36" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -7569,10 +7566,10 @@
     </row>
     <row r="37" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A37" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C37">
         <v>2</v>
@@ -7580,10 +7577,10 @@
     </row>
     <row r="38" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A38" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C38">
         <v>3</v>
@@ -7591,24 +7588,24 @@
     </row>
     <row r="39" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A39" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C39">
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A40" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C40">
         <v>2</v>
@@ -7616,10 +7613,10 @@
     </row>
     <row r="41" spans="1:4" s="11" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A41" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C41" s="11">
         <v>3</v>
@@ -7627,10 +7624,10 @@
     </row>
     <row r="42" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A42" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -7638,10 +7635,10 @@
     </row>
     <row r="43" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A43" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C43">
         <v>2</v>
@@ -7649,10 +7646,10 @@
     </row>
     <row r="44" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A44" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C44">
         <v>4</v>
@@ -7660,10 +7657,10 @@
     </row>
     <row r="45" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A45" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C45">
         <v>4</v>
@@ -7671,10 +7668,10 @@
     </row>
     <row r="46" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A46" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C46">
         <v>3</v>
@@ -7682,10 +7679,10 @@
     </row>
     <row r="47" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A47" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C47">
         <v>2</v>
@@ -7693,10 +7690,10 @@
     </row>
     <row r="48" spans="1:4" ht="243.6" x14ac:dyDescent="0.4">
       <c r="A48" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="B48" s="4" t="s">
         <v>474</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>475</v>
       </c>
       <c r="C48">
         <v>2</v>
@@ -7704,10 +7701,10 @@
     </row>
     <row r="49" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A49" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C49">
         <v>2</v>
@@ -7715,10 +7712,10 @@
     </row>
     <row r="50" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A50" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -7726,10 +7723,10 @@
     </row>
     <row r="51" spans="1:3" ht="174" x14ac:dyDescent="0.4">
       <c r="A51" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C51">
         <v>4</v>
@@ -7737,10 +7734,10 @@
     </row>
     <row r="52" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A52" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C52">
         <v>3</v>
@@ -7748,10 +7745,10 @@
     </row>
     <row r="53" spans="1:3" ht="87" x14ac:dyDescent="0.4">
       <c r="A53" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C53">
         <v>2</v>
@@ -7759,10 +7756,10 @@
     </row>
     <row r="54" spans="1:3" ht="87" x14ac:dyDescent="0.4">
       <c r="A54" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C54">
         <v>4</v>
@@ -7770,10 +7767,10 @@
     </row>
     <row r="55" spans="1:3" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A55" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="B55" s="4" t="s">
         <v>479</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>480</v>
       </c>
       <c r="C55">
         <v>3</v>
@@ -7781,10 +7778,10 @@
     </row>
     <row r="56" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A56" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C56">
         <v>2</v>
@@ -7792,10 +7789,10 @@
     </row>
     <row r="57" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A57" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C57">
         <v>2</v>
@@ -7803,10 +7800,10 @@
     </row>
     <row r="58" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A58" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C58">
         <v>4</v>
@@ -7814,10 +7811,10 @@
     </row>
     <row r="59" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A59" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C59">
         <v>4</v>
@@ -7825,10 +7822,10 @@
     </row>
     <row r="60" spans="1:3" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A60" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -7836,10 +7833,10 @@
     </row>
     <row r="61" spans="1:3" s="11" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A61" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C61" s="11">
         <v>1</v>
@@ -7847,10 +7844,10 @@
     </row>
     <row r="62" spans="1:3" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A62" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C62">
         <v>4</v>
@@ -7858,10 +7855,10 @@
     </row>
     <row r="63" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A63" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C63">
         <v>2</v>
@@ -7869,10 +7866,10 @@
     </row>
     <row r="64" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A64" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C64">
         <v>2</v>
@@ -7880,10 +7877,10 @@
     </row>
     <row r="65" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A65" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C65">
         <v>4</v>
@@ -7891,10 +7888,10 @@
     </row>
     <row r="66" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A66" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -7902,10 +7899,10 @@
     </row>
     <row r="67" spans="1:3" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A67" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C67">
         <v>2</v>
@@ -7913,10 +7910,10 @@
     </row>
     <row r="68" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A68" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C68">
         <v>3</v>
@@ -7924,10 +7921,10 @@
     </row>
     <row r="69" spans="1:3" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A69" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C69">
         <v>4</v>
@@ -7935,10 +7932,10 @@
     </row>
     <row r="70" spans="1:3" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A70" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C70">
         <v>2</v>
@@ -7946,10 +7943,10 @@
     </row>
     <row r="71" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A71" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -7957,10 +7954,10 @@
     </row>
     <row r="72" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A72" s="4" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -7968,10 +7965,10 @@
     </row>
     <row r="73" spans="1:3" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A73" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -7979,10 +7976,10 @@
     </row>
     <row r="74" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A74" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -7990,10 +7987,10 @@
     </row>
     <row r="75" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A75" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -8001,10 +7998,10 @@
     </row>
     <row r="76" spans="1:3" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A76" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C76">
         <v>2</v>
@@ -8012,10 +8009,10 @@
     </row>
     <row r="77" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A77" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C77">
         <v>4</v>
@@ -8023,10 +8020,10 @@
     </row>
     <row r="78" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A78" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C78">
         <v>2</v>
@@ -8034,10 +8031,10 @@
     </row>
     <row r="79" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A79" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C79">
         <v>4</v>
@@ -8045,10 +8042,10 @@
     </row>
     <row r="80" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A80" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C80">
         <v>3</v>
@@ -8056,16 +8053,16 @@
     </row>
     <row r="81" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A81" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B81" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="C81">
+        <v>4</v>
+      </c>
+      <c r="D81" t="s">
         <v>489</v>
-      </c>
-      <c r="C81">
-        <v>4</v>
-      </c>
-      <c r="D81" t="s">
-        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -8102,10 +8099,10 @@
     </row>
     <row r="2" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C2" s="4">
         <v>1</v>
@@ -8113,10 +8110,10 @@
     </row>
     <row r="3" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C3" s="4">
         <v>4</v>
@@ -8124,10 +8121,10 @@
     </row>
     <row r="4" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C4" s="4">
         <v>3</v>
@@ -8135,10 +8132,10 @@
     </row>
     <row r="5" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C5" s="4">
         <v>1</v>
@@ -8146,10 +8143,10 @@
     </row>
     <row r="6" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C6" s="4">
         <v>3</v>
@@ -8157,10 +8154,10 @@
     </row>
     <row r="7" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C7" s="4">
         <v>4</v>
@@ -8168,10 +8165,10 @@
     </row>
     <row r="8" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>570</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>571</v>
       </c>
       <c r="C8" s="4">
         <v>2</v>
@@ -8179,10 +8176,10 @@
     </row>
     <row r="9" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C9" s="4">
         <v>3</v>
@@ -8190,10 +8187,10 @@
     </row>
     <row r="10" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C10" s="4">
         <v>1</v>
@@ -8201,10 +8198,10 @@
     </row>
     <row r="11" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C11" s="4">
         <v>1</v>
@@ -8212,7 +8209,7 @@
     </row>
     <row r="12" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B12" s="4">
         <v>16111</v>
@@ -8223,10 +8220,10 @@
     </row>
     <row r="13" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C13" s="4">
         <v>2</v>
@@ -8234,10 +8231,10 @@
     </row>
     <row r="14" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C14" s="4">
         <v>4</v>
@@ -8245,10 +8242,10 @@
     </row>
     <row r="15" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A15" s="4" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C15" s="4">
         <v>4</v>
@@ -8256,10 +8253,10 @@
     </row>
     <row r="16" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C16" s="4">
         <v>4</v>
@@ -8267,7 +8264,7 @@
     </row>
     <row r="17" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B17" s="4">
         <v>16116</v>
@@ -8278,10 +8275,10 @@
     </row>
     <row r="18" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C18" s="4">
         <v>1</v>
@@ -8289,10 +8286,10 @@
     </row>
     <row r="19" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C19" s="4">
         <v>4</v>
@@ -8300,10 +8297,10 @@
     </row>
     <row r="20" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C20" s="4">
         <v>1</v>
@@ -8311,10 +8308,10 @@
     </row>
     <row r="21" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C21" s="4">
         <v>3</v>
@@ -8322,10 +8319,10 @@
     </row>
     <row r="22" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C22" s="4">
         <v>1</v>
@@ -8333,24 +8330,24 @@
     </row>
     <row r="23" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A23" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C23" s="4">
         <v>1</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C24" s="4">
         <v>3</v>
@@ -8358,10 +8355,10 @@
     </row>
     <row r="25" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A25" s="4" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C25" s="4">
         <v>4</v>
@@ -8369,10 +8366,10 @@
     </row>
     <row r="26" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A26" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C26" s="4">
         <v>1</v>
@@ -8380,10 +8377,10 @@
     </row>
     <row r="27" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A27" s="4" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C27" s="4">
         <v>3</v>
@@ -8391,10 +8388,10 @@
     </row>
     <row r="28" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A28" s="4" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C28" s="4">
         <v>4</v>
@@ -8402,7 +8399,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29" s="4" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B29" s="4">
         <v>16128</v>
@@ -8413,10 +8410,10 @@
     </row>
     <row r="30" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A30" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C30" s="4">
         <v>4</v>
@@ -8424,10 +8421,10 @@
     </row>
     <row r="31" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A31" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C31" s="4">
         <v>1</v>
@@ -8435,10 +8432,10 @@
     </row>
     <row r="32" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A32" s="4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C32" s="4">
         <v>2</v>
@@ -8446,10 +8443,10 @@
     </row>
     <row r="33" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A33" s="4" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C33" s="4">
         <v>3</v>
@@ -8457,10 +8454,10 @@
     </row>
     <row r="34" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A34" s="4" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C34" s="4">
         <v>1</v>
@@ -8468,10 +8465,10 @@
     </row>
     <row r="35" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A35" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C35" s="4">
         <v>4</v>
@@ -8479,7 +8476,7 @@
     </row>
     <row r="36" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A36" s="4" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B36" s="4">
         <v>16135</v>
@@ -8490,10 +8487,10 @@
     </row>
     <row r="37" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A37" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C37" s="4">
         <v>2</v>
@@ -8501,10 +8498,10 @@
     </row>
     <row r="38" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A38" s="4" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C38" s="4">
         <v>1</v>
@@ -8512,10 +8509,10 @@
     </row>
     <row r="39" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A39" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C39" s="4">
         <v>2</v>
@@ -8523,10 +8520,10 @@
     </row>
     <row r="40" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A40" s="4" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C40" s="4">
         <v>3</v>
@@ -8537,7 +8534,7 @@
     </row>
     <row r="41" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A41" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B41" s="4">
         <v>16140</v>
@@ -8546,15 +8543,15 @@
         <v>4</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A42" s="4" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C42" s="4">
         <v>3</v>
@@ -8562,10 +8559,10 @@
     </row>
     <row r="43" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A43" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C43" s="4">
         <v>2</v>
@@ -8573,7 +8570,7 @@
     </row>
     <row r="44" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A44" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>185</v>
@@ -8582,15 +8579,15 @@
         <v>4</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A45" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>615</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>616</v>
       </c>
       <c r="C45" s="4">
         <v>4</v>
@@ -8598,10 +8595,10 @@
     </row>
     <row r="46" spans="1:4" ht="226.2" x14ac:dyDescent="0.4">
       <c r="A46" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C46" s="4">
         <v>3</v>
@@ -8609,10 +8606,10 @@
     </row>
     <row r="47" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A47" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C47" s="4">
         <v>4</v>
@@ -8620,10 +8617,10 @@
     </row>
     <row r="48" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A48" s="4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C48" s="4">
         <v>3</v>
@@ -8631,10 +8628,10 @@
     </row>
     <row r="49" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A49" s="4" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C49" s="4">
         <v>1</v>
@@ -8642,10 +8639,10 @@
     </row>
     <row r="50" spans="1:3" ht="87" x14ac:dyDescent="0.4">
       <c r="A50" s="4" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C50" s="4">
         <v>4</v>
@@ -8653,10 +8650,10 @@
     </row>
     <row r="51" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A51" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C51" s="4">
         <v>2</v>
@@ -8664,10 +8661,10 @@
     </row>
     <row r="52" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A52" s="4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C52" s="4">
         <v>3</v>
@@ -8675,10 +8672,10 @@
     </row>
     <row r="53" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A53" s="4" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C53" s="4">
         <v>2</v>
@@ -8686,10 +8683,10 @@
     </row>
     <row r="54" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A54" s="4" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C54" s="4">
         <v>4</v>
@@ -8697,10 +8694,10 @@
     </row>
     <row r="55" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A55" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C55" s="4">
         <v>2</v>
@@ -8708,10 +8705,10 @@
     </row>
     <row r="56" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A56" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C56" s="4">
         <v>4</v>
@@ -8719,10 +8716,10 @@
     </row>
     <row r="57" spans="1:3" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A57" s="4" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C57" s="4">
         <v>2</v>
@@ -8730,10 +8727,10 @@
     </row>
     <row r="58" spans="1:3" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A58" s="4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C58" s="4">
         <v>2</v>
@@ -8741,10 +8738,10 @@
     </row>
     <row r="59" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A59" s="4" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C59" s="4">
         <v>1</v>
@@ -8752,10 +8749,10 @@
     </row>
     <row r="60" spans="1:3" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A60" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C60" s="4">
         <v>2</v>
@@ -8763,10 +8760,10 @@
     </row>
     <row r="61" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A61" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C61" s="4">
         <v>2</v>
@@ -8774,10 +8771,10 @@
     </row>
     <row r="62" spans="1:3" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A62" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C62" s="4">
         <v>2</v>
@@ -8785,10 +8782,10 @@
     </row>
     <row r="63" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A63" s="4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C63" s="4">
         <v>2</v>
@@ -8796,10 +8793,10 @@
     </row>
     <row r="64" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A64" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C64" s="4">
         <v>1</v>
@@ -8807,10 +8804,10 @@
     </row>
     <row r="65" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A65" s="4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C65" s="4">
         <v>2</v>
@@ -8818,10 +8815,10 @@
     </row>
     <row r="66" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A66" s="4" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C66" s="4">
         <v>4</v>
@@ -8829,10 +8826,10 @@
     </row>
     <row r="67" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A67" s="4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C67" s="4">
         <v>2</v>
@@ -8840,10 +8837,10 @@
     </row>
     <row r="68" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A68" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C68" s="4">
         <v>3</v>
@@ -8851,52 +8848,52 @@
     </row>
     <row r="69" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A69" s="4" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C69" s="4">
         <v>2</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A70" s="4" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C70" s="4">
         <v>3</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A71" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C71" s="4">
         <v>1</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A72" s="4" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C72" s="4">
         <v>4</v>
@@ -8904,10 +8901,10 @@
     </row>
     <row r="73" spans="1:4" ht="174" x14ac:dyDescent="0.4">
       <c r="A73" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>643</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>644</v>
       </c>
       <c r="C73" s="4">
         <v>2</v>
@@ -8915,10 +8912,10 @@
     </row>
     <row r="74" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A74" s="4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C74" s="4">
         <v>3</v>
@@ -8926,10 +8923,10 @@
     </row>
     <row r="75" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A75" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C75" s="4">
         <v>3</v>
@@ -8937,10 +8934,10 @@
     </row>
     <row r="76" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A76" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C76" s="4">
         <v>4</v>
@@ -8948,10 +8945,10 @@
     </row>
     <row r="77" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A77" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C77" s="4">
         <v>2</v>
@@ -8959,10 +8956,10 @@
     </row>
     <row r="78" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A78" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C78" s="4">
         <v>2</v>
@@ -8970,10 +8967,10 @@
     </row>
     <row r="79" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A79" s="4" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C79" s="4">
         <v>4</v>
@@ -8981,10 +8978,10 @@
     </row>
     <row r="80" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A80" s="4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C80" s="4">
         <v>2</v>
@@ -8992,10 +8989,10 @@
     </row>
     <row r="81" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A81" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>651</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>652</v>
       </c>
       <c r="C81" s="4">
         <v>1</v>
@@ -9034,10 +9031,10 @@
     </row>
     <row r="2" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
+        <v>652</v>
+      </c>
+      <c r="B2" s="15" t="s">
         <v>653</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>654</v>
       </c>
       <c r="C2" s="12">
         <v>4</v>
@@ -9046,10 +9043,10 @@
     </row>
     <row r="3" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
+        <v>654</v>
+      </c>
+      <c r="B3" s="15" t="s">
         <v>655</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>656</v>
       </c>
       <c r="C3" s="12">
         <v>1</v>
@@ -9058,10 +9055,10 @@
     </row>
     <row r="4" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C4" s="12">
         <v>3</v>
@@ -9070,10 +9067,10 @@
     </row>
     <row r="5" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C5" s="12">
         <v>3</v>
@@ -9082,10 +9079,10 @@
     </row>
     <row r="6" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A6" s="15" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C6" s="12">
         <v>4</v>
@@ -9094,10 +9091,10 @@
     </row>
     <row r="7" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
+        <v>659</v>
+      </c>
+      <c r="B7" s="15" t="s">
         <v>660</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>661</v>
       </c>
       <c r="C7" s="12">
         <v>2</v>
@@ -9106,10 +9103,10 @@
     </row>
     <row r="8" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
+        <v>661</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>662</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>663</v>
       </c>
       <c r="C8" s="12">
         <v>4</v>
@@ -9118,10 +9115,10 @@
     </row>
     <row r="9" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
+        <v>663</v>
+      </c>
+      <c r="B9" s="15" t="s">
         <v>664</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>665</v>
       </c>
       <c r="C9" s="12">
         <v>3</v>
@@ -9130,10 +9127,10 @@
     </row>
     <row r="10" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
+        <v>665</v>
+      </c>
+      <c r="B10" s="15" t="s">
         <v>666</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>667</v>
       </c>
       <c r="C10" s="12">
         <v>3</v>
@@ -9142,10 +9139,10 @@
     </row>
     <row r="11" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="B11" s="15" t="s">
         <v>668</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>669</v>
       </c>
       <c r="C11" s="12">
         <v>3</v>
@@ -9154,10 +9151,10 @@
     </row>
     <row r="12" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C12" s="12">
         <v>3</v>
@@ -9166,10 +9163,10 @@
     </row>
     <row r="13" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C13" s="12">
         <v>3</v>
@@ -9178,7 +9175,7 @@
     </row>
     <row r="14" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>181</v>
@@ -9190,10 +9187,10 @@
     </row>
     <row r="15" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
+        <v>671</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>672</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>673</v>
       </c>
       <c r="C15" s="12">
         <v>1</v>
@@ -9202,7 +9199,7 @@
     </row>
     <row r="16" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A16" s="15" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B16" s="15">
         <v>16215</v>
@@ -9214,10 +9211,10 @@
     </row>
     <row r="17" spans="1:4" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A17" s="15" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C17" s="12">
         <v>2</v>
@@ -9226,10 +9223,10 @@
     </row>
     <row r="18" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A18" s="15" t="s">
+        <v>675</v>
+      </c>
+      <c r="B18" s="15" t="s">
         <v>676</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>677</v>
       </c>
       <c r="C18" s="12">
         <v>3</v>
@@ -9238,10 +9235,10 @@
     </row>
     <row r="19" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A19" s="15" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C19" s="12">
         <v>1</v>
@@ -9250,10 +9247,10 @@
     </row>
     <row r="20" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A20" s="15" t="s">
+        <v>678</v>
+      </c>
+      <c r="B20" s="15" t="s">
         <v>679</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>680</v>
       </c>
       <c r="C20" s="12">
         <v>1</v>
@@ -9262,10 +9259,10 @@
     </row>
     <row r="21" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A21" s="15" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C21" s="12">
         <v>3</v>
@@ -9274,10 +9271,10 @@
     </row>
     <row r="22" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A22" s="15" t="s">
+        <v>681</v>
+      </c>
+      <c r="B22" s="15" t="s">
         <v>682</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>683</v>
       </c>
       <c r="C22" s="12">
         <v>2</v>
@@ -9286,10 +9283,10 @@
     </row>
     <row r="23" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A23" s="15" t="s">
+        <v>683</v>
+      </c>
+      <c r="B23" s="15" t="s">
         <v>684</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>685</v>
       </c>
       <c r="C23" s="12">
         <v>1</v>
@@ -9298,10 +9295,10 @@
     </row>
     <row r="24" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A24" s="15" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C24" s="12">
         <v>2</v>
@@ -9310,10 +9307,10 @@
     </row>
     <row r="25" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A25" s="15" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C25" s="12">
         <v>3</v>
@@ -9322,10 +9319,10 @@
     </row>
     <row r="26" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A26" s="15" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C26" s="12">
         <v>4</v>
@@ -9334,10 +9331,10 @@
     </row>
     <row r="27" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A27" s="15" t="s">
+        <v>688</v>
+      </c>
+      <c r="B27" s="15" t="s">
         <v>689</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>690</v>
       </c>
       <c r="C27" s="12">
         <v>1</v>
@@ -9346,10 +9343,10 @@
     </row>
     <row r="28" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A28" s="15" t="s">
+        <v>690</v>
+      </c>
+      <c r="B28" s="15" t="s">
         <v>691</v>
-      </c>
-      <c r="B28" s="15" t="s">
-        <v>692</v>
       </c>
       <c r="C28" s="12">
         <v>1</v>
@@ -9358,10 +9355,10 @@
     </row>
     <row r="29" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A29" s="15" t="s">
+        <v>692</v>
+      </c>
+      <c r="B29" s="15" t="s">
         <v>693</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>694</v>
       </c>
       <c r="C29" s="12">
         <v>1</v>
@@ -9370,10 +9367,10 @@
     </row>
     <row r="30" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A30" s="15" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C30" s="12">
         <v>4</v>
@@ -9382,10 +9379,10 @@
     </row>
     <row r="31" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A31" s="15" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C31" s="12">
         <v>2</v>
@@ -9394,10 +9391,10 @@
     </row>
     <row r="32" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A32" s="15" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C32" s="12">
         <v>1</v>
@@ -9406,10 +9403,10 @@
     </row>
     <row r="33" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A33" s="15" t="s">
+        <v>697</v>
+      </c>
+      <c r="B33" s="15" t="s">
         <v>698</v>
-      </c>
-      <c r="B33" s="15" t="s">
-        <v>699</v>
       </c>
       <c r="C33" s="12">
         <v>3</v>
@@ -9418,10 +9415,10 @@
     </row>
     <row r="34" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A34" s="15" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C34" s="12">
         <v>4</v>
@@ -9430,7 +9427,7 @@
     </row>
     <row r="35" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A35" s="15" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B35" s="15">
         <v>16234</v>
@@ -9439,29 +9436,29 @@
         <v>1</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A36" s="15" t="s">
+        <v>699</v>
+      </c>
+      <c r="B36" s="15" t="s">
         <v>700</v>
       </c>
-      <c r="B36" s="15" t="s">
-        <v>701</v>
-      </c>
       <c r="C36" s="12">
         <v>3</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A37" s="15" t="s">
+        <v>701</v>
+      </c>
+      <c r="B37" s="15" t="s">
         <v>702</v>
-      </c>
-      <c r="B37" s="15" t="s">
-        <v>703</v>
       </c>
       <c r="C37" s="12">
         <v>1</v>
@@ -9470,10 +9467,10 @@
     </row>
     <row r="38" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A38" s="15" t="s">
+        <v>770</v>
+      </c>
+      <c r="B38" s="15" t="s">
         <v>771</v>
-      </c>
-      <c r="B38" s="15" t="s">
-        <v>772</v>
       </c>
       <c r="C38" s="12">
         <v>4</v>
@@ -9482,24 +9479,24 @@
     </row>
     <row r="39" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A39" s="15" t="s">
+        <v>703</v>
+      </c>
+      <c r="B39" s="15" t="s">
         <v>704</v>
       </c>
-      <c r="B39" s="15" t="s">
-        <v>705</v>
-      </c>
       <c r="C39" s="12">
         <v>2</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A40" s="15" t="s">
+        <v>705</v>
+      </c>
+      <c r="B40" s="15" t="s">
         <v>706</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>707</v>
       </c>
       <c r="C40" s="12">
         <v>2</v>
@@ -9508,7 +9505,7 @@
     </row>
     <row r="41" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A41" s="15" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B41" s="15">
         <v>16240</v>
@@ -9517,29 +9514,29 @@
         <v>1</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A42" s="15" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B42" s="15" t="s">
+        <v>775</v>
+      </c>
+      <c r="C42" s="12">
+        <v>2</v>
+      </c>
+      <c r="D42" s="12" t="s">
         <v>776</v>
-      </c>
-      <c r="C42" s="12">
-        <v>2</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A43" s="15" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C43" s="12">
         <v>2</v>
@@ -9548,10 +9545,10 @@
     </row>
     <row r="44" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A44" s="15" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C44" s="12">
         <v>1</v>
@@ -9560,10 +9557,10 @@
     </row>
     <row r="45" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A45" s="15" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C45" s="12">
         <v>3</v>
@@ -9572,10 +9569,10 @@
     </row>
     <row r="46" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A46" s="15" t="s">
+        <v>711</v>
+      </c>
+      <c r="B46" s="15" t="s">
         <v>712</v>
-      </c>
-      <c r="B46" s="15" t="s">
-        <v>713</v>
       </c>
       <c r="C46" s="12">
         <v>3</v>
@@ -9584,10 +9581,10 @@
     </row>
     <row r="47" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A47" s="15" t="s">
+        <v>713</v>
+      </c>
+      <c r="B47" s="15" t="s">
         <v>714</v>
-      </c>
-      <c r="B47" s="15" t="s">
-        <v>715</v>
       </c>
       <c r="C47" s="12">
         <v>2</v>
@@ -9596,10 +9593,10 @@
     </row>
     <row r="48" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A48" s="15" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C48" s="12">
         <v>1</v>
@@ -9608,10 +9605,10 @@
     </row>
     <row r="49" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A49" s="15" t="s">
+        <v>716</v>
+      </c>
+      <c r="B49" s="15" t="s">
         <v>717</v>
-      </c>
-      <c r="B49" s="15" t="s">
-        <v>718</v>
       </c>
       <c r="C49" s="12">
         <v>2</v>
@@ -9620,10 +9617,10 @@
     </row>
     <row r="50" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A50" s="15" t="s">
+        <v>718</v>
+      </c>
+      <c r="B50" s="15" t="s">
         <v>719</v>
-      </c>
-      <c r="B50" s="15" t="s">
-        <v>720</v>
       </c>
       <c r="C50" s="12">
         <v>4</v>
@@ -9632,10 +9629,10 @@
     </row>
     <row r="51" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A51" s="15" t="s">
+        <v>720</v>
+      </c>
+      <c r="B51" s="15" t="s">
         <v>721</v>
-      </c>
-      <c r="B51" s="15" t="s">
-        <v>722</v>
       </c>
       <c r="C51" s="12">
         <v>4</v>
@@ -9644,10 +9641,10 @@
     </row>
     <row r="52" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A52" s="15" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C52" s="12">
         <v>2</v>
@@ -9656,10 +9653,10 @@
     </row>
     <row r="53" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A53" s="15" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C53" s="12">
         <v>4</v>
@@ -9668,10 +9665,10 @@
     </row>
     <row r="54" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A54" s="15" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C54" s="12">
         <v>1</v>
@@ -9680,10 +9677,10 @@
     </row>
     <row r="55" spans="1:4" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A55" s="15" t="s">
+        <v>786</v>
+      </c>
+      <c r="B55" s="15" t="s">
         <v>787</v>
-      </c>
-      <c r="B55" s="15" t="s">
-        <v>788</v>
       </c>
       <c r="C55" s="12">
         <v>3</v>
@@ -9692,10 +9689,10 @@
     </row>
     <row r="56" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A56" s="15" t="s">
+        <v>788</v>
+      </c>
+      <c r="B56" s="15" t="s">
         <v>789</v>
-      </c>
-      <c r="B56" s="15" t="s">
-        <v>790</v>
       </c>
       <c r="C56" s="12">
         <v>3</v>
@@ -9704,10 +9701,10 @@
     </row>
     <row r="57" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A57" s="15" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C57" s="12">
         <v>3</v>
@@ -9716,10 +9713,10 @@
     </row>
     <row r="58" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A58" s="15" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C58" s="12">
         <v>4</v>
@@ -9728,10 +9725,10 @@
     </row>
     <row r="59" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A59" s="15" t="s">
+        <v>725</v>
+      </c>
+      <c r="B59" s="15" t="s">
         <v>726</v>
-      </c>
-      <c r="B59" s="15" t="s">
-        <v>727</v>
       </c>
       <c r="C59" s="12">
         <v>2</v>
@@ -9740,10 +9737,10 @@
     </row>
     <row r="60" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A60" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C60" s="12">
         <v>4</v>
@@ -9752,10 +9749,10 @@
     </row>
     <row r="61" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A61" s="15" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C61" s="12">
         <v>3</v>
@@ -9764,10 +9761,10 @@
     </row>
     <row r="62" spans="1:4" ht="208.8" x14ac:dyDescent="0.4">
       <c r="A62" s="15" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="C62" s="12">
         <v>4</v>
@@ -9776,10 +9773,10 @@
     </row>
     <row r="63" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A63" s="15" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C63" s="12">
         <v>1</v>
@@ -9788,10 +9785,10 @@
     </row>
     <row r="64" spans="1:4" ht="226.2" x14ac:dyDescent="0.4">
       <c r="A64" s="15" t="s">
+        <v>797</v>
+      </c>
+      <c r="B64" s="15" t="s">
         <v>798</v>
-      </c>
-      <c r="B64" s="15" t="s">
-        <v>799</v>
       </c>
       <c r="C64" s="12">
         <v>1</v>
@@ -9800,10 +9797,10 @@
     </row>
     <row r="65" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
       <c r="A65" s="15" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C65" s="12">
         <v>1</v>
@@ -9812,10 +9809,10 @@
     </row>
     <row r="66" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A66" s="15" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C66" s="12">
         <v>3</v>
@@ -9824,10 +9821,10 @@
     </row>
     <row r="67" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A67" s="15" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C67" s="12">
         <v>4</v>
@@ -9836,10 +9833,10 @@
     </row>
     <row r="68" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A68" s="15" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C68" s="12">
         <v>2</v>
@@ -9848,10 +9845,10 @@
     </row>
     <row r="69" spans="1:4" ht="226.2" x14ac:dyDescent="0.4">
       <c r="A69" s="15" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C69" s="12">
         <v>1</v>
@@ -9860,10 +9857,10 @@
     </row>
     <row r="70" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A70" s="15" t="s">
+        <v>734</v>
+      </c>
+      <c r="B70" s="15" t="s">
         <v>735</v>
-      </c>
-      <c r="B70" s="15" t="s">
-        <v>736</v>
       </c>
       <c r="C70" s="12">
         <v>4</v>
@@ -9872,24 +9869,24 @@
     </row>
     <row r="71" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A71" s="15" t="s">
+        <v>736</v>
+      </c>
+      <c r="B71" s="15" t="s">
         <v>737</v>
       </c>
-      <c r="B71" s="15" t="s">
-        <v>738</v>
-      </c>
       <c r="C71" s="12">
         <v>2</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="261" x14ac:dyDescent="0.4">
       <c r="A72" s="15" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C72" s="12">
         <v>1</v>
@@ -9898,10 +9895,10 @@
     </row>
     <row r="73" spans="1:4" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A73" s="15" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B73" s="15" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C73" s="12">
         <v>2</v>
@@ -9910,10 +9907,10 @@
     </row>
     <row r="74" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A74" s="15" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C74" s="12">
         <v>2</v>
@@ -9922,10 +9919,10 @@
     </row>
     <row r="75" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A75" s="15" t="s">
+        <v>741</v>
+      </c>
+      <c r="B75" s="15" t="s">
         <v>742</v>
-      </c>
-      <c r="B75" s="15" t="s">
-        <v>743</v>
       </c>
       <c r="C75" s="12">
         <v>4</v>
@@ -9934,10 +9931,10 @@
     </row>
     <row r="76" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A76" s="15" t="s">
+        <v>743</v>
+      </c>
+      <c r="B76" s="15" t="s">
         <v>744</v>
-      </c>
-      <c r="B76" s="15" t="s">
-        <v>745</v>
       </c>
       <c r="C76" s="12">
         <v>4</v>
@@ -9946,10 +9943,10 @@
     </row>
     <row r="77" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A77" s="15" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B77" s="15" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C77" s="12">
         <v>3</v>
@@ -9958,10 +9955,10 @@
     </row>
     <row r="78" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A78" s="15" t="s">
+        <v>746</v>
+      </c>
+      <c r="B78" s="15" t="s">
         <v>747</v>
-      </c>
-      <c r="B78" s="15" t="s">
-        <v>748</v>
       </c>
       <c r="C78" s="12">
         <v>4</v>
@@ -9970,10 +9967,10 @@
     </row>
     <row r="79" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A79" s="15" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B79" s="15" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C79" s="12">
         <v>2</v>
@@ -9982,10 +9979,10 @@
     </row>
     <row r="80" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A80" s="15" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B80" s="15" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C80" s="12">
         <v>3</v>
@@ -9994,10 +9991,10 @@
     </row>
     <row r="81" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A81" s="15" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B81" s="15" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C81" s="12">
         <v>2</v>
@@ -10012,7 +10009,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8CB800D-DA44-4550-BA4F-B9F940DFC761}">
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="39.59765625" customWidth="1"/>
@@ -10037,626 +10034,900 @@
     </row>
     <row r="2" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
+        <v>812</v>
+      </c>
+      <c r="B2" s="15" t="s">
         <v>813</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>814</v>
+      <c r="C2">
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A3" s="15" t="s">
+        <v>814</v>
+      </c>
+      <c r="B3" s="15" t="s">
         <v>815</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>816</v>
+      <c r="C3">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>817</v>
+        <v>908</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>818</v>
+        <v>816</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>819</v>
+        <v>909</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>820</v>
+        <v>817</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A6" s="15" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>822</v>
+        <v>819</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>824</v>
+        <v>821</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+        <v>823</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>827</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>828</v>
+        <v>824</v>
+      </c>
+      <c r="B9" s="15">
+        <v>16408</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A10" s="15" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
+        <v>826</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A11" s="15" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>832</v>
+        <v>910</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A12" s="15" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>834</v>
+        <v>829</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A13" s="15" t="s">
-        <v>835</v>
+        <v>911</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>836</v>
+        <v>830</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="174" x14ac:dyDescent="0.4">
       <c r="A14" s="15" t="s">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>838</v>
+        <v>912</v>
+      </c>
+      <c r="C14">
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A15" s="15" t="s">
-        <v>839</v>
+        <v>832</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>840</v>
+        <v>833</v>
+      </c>
+      <c r="C15">
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A16" s="15" t="s">
+        <v>834</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>835</v>
+      </c>
+      <c r="C16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A17" s="15" t="s">
+        <v>913</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>836</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A18" s="15" t="s">
+        <v>837</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>914</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A19" s="15" t="s">
+        <v>838</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>915</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A20" s="15" t="s">
+        <v>839</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>840</v>
+      </c>
+      <c r="C20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A21" s="15" t="s">
+        <v>917</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>916</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A22" s="15" t="s">
+        <v>919</v>
+      </c>
+      <c r="B22" s="15" t="s">
         <v>841</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="C22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A23" s="15" t="s">
         <v>842</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A17" s="15" t="s">
+      <c r="B23" s="15" t="s">
         <v>843</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="C23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A24" s="15" t="s">
         <v>844</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A18" s="15" t="s">
+      <c r="B24" s="15" t="s">
         <v>845</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="C24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A25" s="15" t="s">
         <v>846</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="139.19999999999999" x14ac:dyDescent="0.4">
-      <c r="A19" s="15" t="s">
+      <c r="B25" s="15" t="s">
         <v>847</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="C25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A26" s="15" t="s">
+        <v>921</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>920</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A27" s="15" t="s">
+        <v>922</v>
+      </c>
+      <c r="B27" s="15" t="s">
         <v>848</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A20" s="15" t="s">
+      <c r="C27">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A28" s="15" t="s">
         <v>849</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B28" s="15" t="s">
         <v>850</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A21" s="15" t="s">
+      <c r="C28">
+        <v>3</v>
+      </c>
+      <c r="D28" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A29" s="15" t="s">
         <v>851</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B29" s="15" t="s">
+        <v>924</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A30" s="15" t="s">
         <v>852</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A22" s="15" t="s">
+      <c r="B30" s="15" t="s">
         <v>853</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="C30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A31" s="15" t="s">
+        <v>925</v>
+      </c>
+      <c r="B31" s="15" t="s">
         <v>854</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A23" s="15" t="s">
+      <c r="C31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A32" s="15" t="s">
         <v>855</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B32" s="15">
+        <v>16431</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A33" s="15" t="s">
+        <v>926</v>
+      </c>
+      <c r="B33" s="15" t="s">
         <v>856</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A24" s="15" t="s">
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A34" s="15" t="s">
         <v>857</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B34" s="15" t="s">
+        <v>927</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A35" s="15" t="s">
         <v>858</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A25" s="15" t="s">
+      <c r="B35" s="15" t="s">
+        <v>928</v>
+      </c>
+      <c r="C35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="87" x14ac:dyDescent="0.4">
+      <c r="A36" s="15" t="s">
+        <v>929</v>
+      </c>
+      <c r="B36" s="15" t="s">
         <v>859</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A37" s="15" t="s">
         <v>860</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A26" s="15" t="s">
+      <c r="B37" s="15" t="s">
         <v>861</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="C37">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A38" s="15" t="s">
         <v>862</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A27" s="15" t="s">
+      <c r="B38" s="15" t="s">
         <v>863</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="C38">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A39" s="15" t="s">
+        <v>931</v>
+      </c>
+      <c r="B39" s="15" t="s">
         <v>864</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A28" s="15" t="s">
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A40" s="15" t="s">
+        <v>932</v>
+      </c>
+      <c r="B40" s="15" t="s">
         <v>865</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="C40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A41" s="15" t="s">
+        <v>935</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>934</v>
+      </c>
+      <c r="C41">
+        <v>3</v>
+      </c>
+      <c r="D41" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A42" s="15" t="s">
+        <v>937</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>933</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A43" s="15" t="s">
+        <v>938</v>
+      </c>
+      <c r="B43" s="15" t="s">
         <v>866</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" ht="156.6" x14ac:dyDescent="0.4">
-      <c r="A29" s="15" t="s">
+      <c r="C43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A44" s="15" t="s">
         <v>867</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B44" s="15" t="s">
         <v>868</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A30" s="15" t="s">
+      <c r="C44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A45" s="15" t="s">
+        <v>939</v>
+      </c>
+      <c r="B45" s="15" t="s">
         <v>869</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="C45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A46" s="15" t="s">
         <v>870</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A31" s="15" t="s">
+      <c r="B46" s="15" t="s">
         <v>871</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="C46">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A47" s="15" t="s">
         <v>872</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A32" s="15" t="s">
+      <c r="B47" s="15" t="s">
         <v>873</v>
       </c>
-      <c r="B32" s="15" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A33" s="15" t="s">
+      <c r="C47">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="87" x14ac:dyDescent="0.4">
+      <c r="A48" s="15" t="s">
+        <v>940</v>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C48">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A49" s="15" t="s">
+        <v>941</v>
+      </c>
+      <c r="B49" s="15" t="s">
         <v>874</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="C49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A50" s="15" t="s">
         <v>875</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A34" s="15" t="s">
+      <c r="B50" s="15" t="s">
         <v>876</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="C50">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="191.4" x14ac:dyDescent="0.4">
+      <c r="A51" s="15" t="s">
+        <v>942</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>943</v>
+      </c>
+      <c r="C51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="87" x14ac:dyDescent="0.4">
+      <c r="A52" s="15" t="s">
+        <v>944</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>945</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A53" s="15" t="s">
+        <v>946</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>947</v>
+      </c>
+      <c r="C53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A54" s="15" t="s">
+        <v>948</v>
+      </c>
+      <c r="B54" s="15" t="s">
         <v>877</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" ht="104.4" x14ac:dyDescent="0.4">
-      <c r="A35" s="15" t="s">
+      <c r="C54">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A55" s="15" t="s">
         <v>878</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B55" s="15" t="s">
         <v>879</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" ht="87" x14ac:dyDescent="0.4">
-      <c r="A36" s="15" t="s">
+      <c r="C55">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A56" s="15" t="s">
         <v>880</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="B56" s="15" t="s">
         <v>881</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" ht="139.19999999999999" x14ac:dyDescent="0.4">
-      <c r="A37" s="15" t="s">
+      <c r="C56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A57" s="15" t="s">
+        <v>949</v>
+      </c>
+      <c r="B57" s="15" t="s">
         <v>882</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="C57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A58" s="15" t="s">
+        <v>950</v>
+      </c>
+      <c r="B58" s="15" t="s">
         <v>883</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A38" s="15" t="s">
+      <c r="C58">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A59" s="15" t="s">
         <v>884</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="B59" s="15" t="s">
         <v>885</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A39" s="15" t="s">
+      <c r="C59">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A60" s="15" t="s">
+        <v>951</v>
+      </c>
+      <c r="B60" s="15" t="s">
+        <v>952</v>
+      </c>
+      <c r="C60">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A61" s="15" t="s">
+        <v>954</v>
+      </c>
+      <c r="B61" s="15" t="s">
+        <v>953</v>
+      </c>
+      <c r="C61">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A62" s="15" t="s">
         <v>886</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="B62" s="15" t="s">
+        <v>955</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A63" s="15" t="s">
+        <v>956</v>
+      </c>
+      <c r="B63" s="15" t="s">
         <v>887</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A40" s="15" t="s">
+      <c r="C63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A64" s="15" t="s">
         <v>888</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B64" s="15" t="s">
         <v>889</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" ht="139.19999999999999" x14ac:dyDescent="0.4">
-      <c r="A41" s="15" t="s">
+      <c r="C64">
+        <v>2</v>
+      </c>
+      <c r="D64" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A65" s="15" t="s">
+        <v>958</v>
+      </c>
+      <c r="B65" s="15" t="s">
         <v>890</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="C65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A66" s="15" t="s">
+        <v>959</v>
+      </c>
+      <c r="B66" s="15" t="s">
         <v>891</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A42" s="15" t="s">
+      <c r="C66">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="87" x14ac:dyDescent="0.4">
+      <c r="A67" s="15" t="s">
+        <v>960</v>
+      </c>
+      <c r="B67" s="15" t="s">
+        <v>467</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A68" s="15" t="s">
         <v>892</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B68" s="15" t="s">
+        <v>961</v>
+      </c>
+      <c r="C68">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A69" s="15" t="s">
         <v>893</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A43" s="15" t="s">
+      <c r="B69" s="15" t="s">
         <v>894</v>
       </c>
-      <c r="B43" s="15" t="s">
+      <c r="C69">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A70" s="15" t="s">
+        <v>962</v>
+      </c>
+      <c r="B70" s="15" t="s">
         <v>895</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" ht="104.4" x14ac:dyDescent="0.4">
-      <c r="A44" s="15" t="s">
+      <c r="C70">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A71" s="15" t="s">
+        <v>963</v>
+      </c>
+      <c r="B71" s="15" t="s">
         <v>896</v>
       </c>
-      <c r="B44" s="15" t="s">
+      <c r="C71">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A72" s="15" t="s">
+        <v>964</v>
+      </c>
+      <c r="B72" s="15" t="s">
+        <v>634</v>
+      </c>
+      <c r="C72">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A73" s="15" t="s">
         <v>897</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A45" s="15" t="s">
+      <c r="B73" s="15" t="s">
         <v>898</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="C73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A74" s="15" t="s">
         <v>899</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A46" s="15" t="s">
+      <c r="B74" s="15" t="s">
         <v>900</v>
       </c>
-      <c r="B46" s="15" t="s">
+      <c r="C74">
+        <v>2</v>
+      </c>
+      <c r="D74" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A75" s="15" t="s">
+        <v>966</v>
+      </c>
+      <c r="B75" s="15" t="s">
+        <v>967</v>
+      </c>
+      <c r="C75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="174" x14ac:dyDescent="0.4">
+      <c r="A76" s="15" t="s">
         <v>901</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" ht="87" x14ac:dyDescent="0.4">
-      <c r="A47" s="15" t="s">
+      <c r="B76" s="15" t="s">
+        <v>968</v>
+      </c>
+      <c r="C76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="87" x14ac:dyDescent="0.4">
+      <c r="A77" s="15" t="s">
+        <v>969</v>
+      </c>
+      <c r="B77" s="15" t="s">
         <v>902</v>
       </c>
-      <c r="B47" s="15" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A48" s="15" t="s">
+      <c r="C77">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A78" s="15" t="s">
+        <v>970</v>
+      </c>
+      <c r="B78" s="15" t="s">
         <v>903</v>
       </c>
-      <c r="B48" s="15" t="s">
+      <c r="C78">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A79" s="15" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A49" s="15" t="s">
+      <c r="B79" s="15" t="s">
         <v>905</v>
       </c>
-      <c r="B49" s="15" t="s">
+      <c r="C79">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A80" s="15" t="s">
         <v>906</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" ht="139.19999999999999" x14ac:dyDescent="0.4">
-      <c r="A50" s="15" t="s">
+      <c r="B80" s="15" t="s">
         <v>907</v>
       </c>
-      <c r="B50" s="15" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" ht="87" x14ac:dyDescent="0.4">
-      <c r="A51" s="15" t="s">
-        <v>909</v>
-      </c>
-      <c r="B51" s="15" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" ht="104.4" x14ac:dyDescent="0.4">
-      <c r="A52" s="15" t="s">
-        <v>911</v>
-      </c>
-      <c r="B52" s="15" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A53" s="15" t="s">
-        <v>913</v>
-      </c>
-      <c r="B53" s="15" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A54" s="15" t="s">
-        <v>915</v>
-      </c>
-      <c r="B54" s="15" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A55" s="15" t="s">
-        <v>917</v>
-      </c>
-      <c r="B55" s="15" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A56" s="15" t="s">
-        <v>919</v>
-      </c>
-      <c r="B56" s="15" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A57" s="15" t="s">
-        <v>921</v>
-      </c>
-      <c r="B57" s="15" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A58" s="15" t="s">
-        <v>923</v>
-      </c>
-      <c r="B58" s="15" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" ht="243.6" x14ac:dyDescent="0.4">
-      <c r="A59" s="15" t="s">
-        <v>925</v>
-      </c>
-      <c r="B59" s="15" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" ht="156.6" x14ac:dyDescent="0.4">
-      <c r="A60" s="15" t="s">
-        <v>927</v>
-      </c>
-      <c r="B60" s="15" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A61" s="15" t="s">
-        <v>929</v>
-      </c>
-      <c r="B61" s="15" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A62" s="15" t="s">
-        <v>931</v>
-      </c>
-      <c r="B62" s="15" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" ht="139.19999999999999" x14ac:dyDescent="0.4">
-      <c r="A63" s="15" t="s">
-        <v>933</v>
-      </c>
-      <c r="B63" s="15" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" ht="139.19999999999999" x14ac:dyDescent="0.4">
-      <c r="A64" s="15" t="s">
-        <v>935</v>
-      </c>
-      <c r="B64" s="15" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A65" s="15" t="s">
-        <v>937</v>
-      </c>
-      <c r="B65" s="15" t="s">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" ht="156.6" x14ac:dyDescent="0.4">
-      <c r="A66" s="15" t="s">
-        <v>939</v>
-      </c>
-      <c r="B66" s="15" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A67" s="15" t="s">
-        <v>941</v>
-      </c>
-      <c r="B67" s="15" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A68" s="15" t="s">
-        <v>943</v>
-      </c>
-      <c r="B68" s="15" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A69" s="15" t="s">
-        <v>945</v>
-      </c>
-      <c r="B69" s="15" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A70" s="15" t="s">
-        <v>947</v>
-      </c>
-      <c r="B70" s="15" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A71" s="15" t="s">
-        <v>948</v>
-      </c>
-      <c r="B71" s="15" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A72" s="15" t="s">
-        <v>950</v>
-      </c>
-      <c r="B72" s="15" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A73" s="15" t="s">
-        <v>952</v>
-      </c>
-      <c r="B73" s="15" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" ht="174" x14ac:dyDescent="0.4">
-      <c r="A74" s="15" t="s">
-        <v>954</v>
-      </c>
-      <c r="B74" s="15" t="s">
-        <v>955</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" ht="87" x14ac:dyDescent="0.4">
-      <c r="A75" s="15" t="s">
-        <v>956</v>
-      </c>
-      <c r="B75" s="15" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A76" s="15" t="s">
-        <v>958</v>
-      </c>
-      <c r="B76" s="15" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" ht="104.4" x14ac:dyDescent="0.4">
-      <c r="A77" s="15" t="s">
-        <v>960</v>
-      </c>
-      <c r="B77" s="15" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" ht="156.6" x14ac:dyDescent="0.4">
-      <c r="A78" s="15" t="s">
-        <v>962</v>
-      </c>
-      <c r="B78" s="15" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" ht="409.6" x14ac:dyDescent="0.4">
-      <c r="A79" s="15" t="s">
-        <v>964</v>
-      </c>
-      <c r="B79" s="15" t="s">
-        <v>965</v>
+      <c r="C80">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A81" s="15" t="s">
+        <v>972</v>
+      </c>
+      <c r="B81" s="15" t="s">
+        <v>971</v>
+      </c>
+      <c r="C81">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/소방설비기사_필기_문제은행.xlsx
+++ b/소방설비기사_필기_문제은행.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E304423-5C7E-4DF4-B4BA-E14F0CEE775C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4A7C9D-31E8-40E4-BF42-968C19D5C92B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="2" activeTab="2" xr2:uid="{FB57838C-1CAD-4D08-9B84-85A2A61E99B1}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="13008" windowHeight="12336" firstSheet="4" activeTab="6" xr2:uid="{FB57838C-1CAD-4D08-9B84-85A2A61E99B1}"/>
   </bookViews>
   <sheets>
     <sheet name="15년 1회" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="16년 1회" sheetId="4" r:id="rId4"/>
     <sheet name="16년 2회" sheetId="5" r:id="rId5"/>
     <sheet name="16년 4회" sheetId="6" r:id="rId6"/>
+    <sheet name="17년 1회" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="973">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="1139">
   <si>
     <t>문제</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4735,12 +4736,804 @@
     <t>자동화재속보설비 속보기의 구조에 대한 설명 중 틀린 것은?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>고층 건축물 내 연기거동 중 굴뚝효과에 영향을 미치는 요소 가 아닌 것은?</t>
+  </si>
+  <si>
+    <t>섭씨 30도는 랭킨(Rankine)온도로 나타내면 몇 도인가?</t>
+  </si>
+  <si>
+    <t>물질의 연소범위와 화재 위험도에 대한 설명으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>A급, B급, C급 화재에 사용이 가능한 제3종 분말 소화약제의 분자식은?</t>
+  </si>
+  <si>
+    <t>할론 (Halon) 1301의 분자식은?</t>
+  </si>
+  <si>
+    <t>소화약제의 방출수단에 대한 설명으로 가장 옳은 것은?</t>
+  </si>
+  <si>
+    <t>다음 중 가연성 가스가 아닌 것은?</t>
+  </si>
+  <si>
+    <t>1기압, 100℃에서의 물 1g의 기화잠열은 약 몇 cal 인가?</t>
+  </si>
+  <si>
+    <t>건축물의 화재 시 피난자들의 집중으로 패닉(panic) 현상이 일어날 수 있는 피난방향은?</t>
+  </si>
+  <si>
+    <t>위험물의 저장 방법으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>건축방화계획에서 건축구조 및 재료를 불연화하여 화재를 미연에 방지하고자 하는 공간적 대응방법은?</t>
+  </si>
+  <si>
+    <t>할론 가스 45kg과 함께 기동가스로 질소2kg을 충전하였다. 이 때 질소가스의 몰분율은? (단, 할론 가스의 분자량은 149이다.)</t>
+  </si>
+  <si>
+    <t>다음 중 착화온도가 가장 낮은 것은?</t>
+  </si>
+  <si>
+    <t>B급 화재 시 사용할 수 없는 소화방법은?</t>
+  </si>
+  <si>
+    <t>가연물의 제거와 가장 관련이 없는 소화방법은?</t>
+  </si>
+  <si>
+    <t>유류 저장탱크의 화재에서 일어날 수 있는 현상이 아닌 것 은?</t>
+  </si>
+  <si>
+    <t>인화성 액체의 연소점, 인화점, 발화점을 온도가 높은 것부 터 옳게 나열한 것은?</t>
+  </si>
+  <si>
+    <t>최대눈금이 70V 인 직류전압계에 5kΩ 의 배율기를 접속하 여 전압의 최대측정치가 350V 라면 내부 저항은 몇 kΩ 인 가?</t>
+  </si>
+  <si>
+    <t>발전기에서 유도기전력의 방향을 나타내는 법칙은?</t>
+  </si>
+  <si>
+    <t>다음은 논리식들 중 틀린 것은?</t>
+  </si>
+  <si>
+    <t>빛이 닿으면 전류가 흐르는 다이오드로 광량의 변화를 전류 값으로 대치하므로 광센서에 주로 사용하는 다이오드는?</t>
+  </si>
+  <si>
+    <t>3상 직권 정류자 전동기에서 중간 변압기를 사용하는 이유 중 틀린 것은?</t>
+  </si>
+  <si>
+    <t>피드백제어계에서 제어요소에 대한 설명 중 옳은 것은?</t>
+  </si>
+  <si>
+    <t>균등 눈금을 사용하며 소비전력이 적게 소요되고 정확도가 높은 지시계기는?</t>
+  </si>
+  <si>
+    <t>그림과 같은 유접점 회로의 논리식은?</t>
+  </si>
+  <si>
+    <t>50kW의 전력의 안테나에서 사방으로 균일하게 방사될 때, 안테나에서 1km 거리에 있는 점에서의 전계의 실효값은 약 몇 V/m 인가?</t>
+  </si>
+  <si>
+    <t>MOSFET(금속-산화물 반도체 전계효과 트랜지스터)의 특성 으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>인덕턴스가 0.5H 인 코일의 리액턴스가 753.6Ω일 때 주파 수는 약 몇 Hz 인가?</t>
+  </si>
+  <si>
+    <t>페루프 제어의 특징에 대한 설명으로 옳은 것은?</t>
+  </si>
+  <si>
+    <t>PD(비례 미분) 제어 동작의 특징으로 옳은 것은?</t>
+  </si>
+  <si>
+    <t>정현파 전압의 평균값과 최대값의 관계식 중 옳은 것은?</t>
+  </si>
+  <si>
+    <t>열팽창식 온도계가 아닌 것은?</t>
+  </si>
+  <si>
+    <t>동기발전기의 병렬조건으로 틀린 것은?</t>
+  </si>
+  <si>
+    <t>대통령령으로 정하는 특정소방대상물 소방시설공사의 완공 검사를 위하여 소방본부장이나 소방서장의 현장확인 대상 범위가 아닌 것은?</t>
+  </si>
+  <si>
+    <t>국민안전처장관, 소방본부장 또는 소방서장이 소방특별조사 조치명령서를 해당 소방대상물의 관계인에게 발급하는 경우 가 아닌 것은?</t>
+  </si>
+  <si>
+    <t>화재예방, 소방시설 설치ㆍ유지 및 안전관리에 관한 법률상 특정소방대상물 중 오피스텔이 해당하는 것은?</t>
+  </si>
+  <si>
+    <t>지정수량 미만인 위험물의 저장 또는 취급에 관한 기술상의 기준은 무엇으로 정하는가?</t>
+  </si>
+  <si>
+    <t>소방용수시설 급수탑 개폐밸브의 설치기준으로 옳은 것은?</t>
+  </si>
+  <si>
+    <t>다음 조건을 참고하여 숙박시설이 있는 특정소방대상물의 수용인원 산정 수로 옳은 것은?</t>
+  </si>
+  <si>
+    <t>감지기의 설치기준 중 옳은 것은?</t>
+  </si>
+  <si>
+    <t>휴대용비상조명등의 설치기준 중 틀린 것은?</t>
+  </si>
+  <si>
+    <t>경사강하식 구조대의 구조 기준 중 틀린 것은?</t>
+  </si>
+  <si>
+    <t>전기사업자로부터 저압으로 수전하는 경우 비상전원설비로 옳은 것은?</t>
+  </si>
+  <si>
+    <t>광원점등방식 피난유도선의 설치기준 중 틀린 것은?</t>
+  </si>
+  <si>
+    <t>무선통신보조설비의 설치제외 기준 중 다음 ( )안에 알맞은 것으로 연결된 것은?</t>
+  </si>
+  <si>
+    <t>5~10회로까지 사용할 수 있는 누전경보기의 집합형 수신기 내부결선도에서 그 구성요소가 아닌 것은?</t>
+  </si>
+  <si>
+    <t>무선통신보조설비의 증폭기 전면에 주회로의 전원이 정상 인지의 여부를 표시할 수 있도록 설치하는 것으로 옳은 것 은?</t>
+  </si>
+  <si>
+    <t>피난기구의 설치개수 기준 중 틀린 것은?</t>
+  </si>
+  <si>
+    <t>비상콘센트설비의 전원회로의 설치기준 중 틀린 것은?</t>
+  </si>
+  <si>
+    <t>자동화재탐지설비의 경계구역 설정 기준으로 옳은 것 은?(2021년 01월 15일 개정된 규정 적용됨)</t>
+  </si>
+  <si>
+    <t>피난구유도등의 설치제외 기준 중 틀린 것은?</t>
+  </si>
+  <si>
+    <t>각 설비와 비상전원의 최소용량 연결이 틀린 것은?</t>
+  </si>
+  <si>
+    <t>① 건물 내ㆍ외의 온도차
+② 화재실의 온도
+③ 건물의 높이
+④ 층의 면적</t>
+  </si>
+  <si>
+    <t>① 546도
+② 515도
+③ 498도
+④ 463도</t>
+  </si>
+  <si>
+    <t>① 연소범위의 폭이 클수록 화재 위험이 높다.
+② 연소범위의 하한계가 낮을수록 화재 위험이 높다.
+③ 연소범위의 상한계가 높을수록 화재 위험이 높다.
+④ 연소범위의 하한계가 높을수록 화재 위험이 높다.</t>
+  </si>
+  <si>
+    <t>① 액체 화학반응을 이용하여 발생되는 열로 방출한다.
+② 기체의 압력으로 폭발, 기화작용 등을 이용하여 방출한다.
+③ 외기의 온도, 습도, 기압 등을 이용하여 방출한다.
+④ 가스압력, 동력, 사람의 손 등에 의하여 방출한다.</t>
+  </si>
+  <si>
+    <t>① 일산화탄소
+② 프로판
+③ 아르곤
+④ 수소</t>
+  </si>
+  <si>
+    <t>① 425
+② 539
+③ 647
+④ 734</t>
+  </si>
+  <si>
+    <t>① 0.5는 거의 앞이 보이지 않을 정도이다.
+② 10은 화재 최성기 때의 농도이다.
+③ 0.5는 가시거리가 20~30m 정도이다.
+④ 10은 연기감지기가 작동하기 직전의 농도이다.</t>
+  </si>
+  <si>
+    <t>① 회피성 대응
+② 도피성 대응
+③ 대항성 대응
+④ 설비적 대응</t>
+  </si>
+  <si>
+    <t>① 0.19
+② 0.24
+③ 0.31
+④ 0.39</t>
+  </si>
+  <si>
+    <t>① 에틸알코올
+② 톨루엔
+③ 등유
+④ 가솔린</t>
+  </si>
+  <si>
+    <t>① 촛불을 입김으로 불어서 끈다.
+② 산불 화재 시 나무를 잘라 없앤다.
+③ 팽창 진주암을 사용하여 진화한다.
+④ 가스화재 시 중간밸브를 잠근다.</t>
+  </si>
+  <si>
+    <t>① 플래시 오버(Flash Over)
+② 보일 오버(Boil Over)
+③ 슬롭 오버(Slop Over)
+④ 후로스 오버(Froth Over)</t>
+  </si>
+  <si>
+    <t>① 제1종 분말
+② 제2종 분말
+③ 제3종 분말
+④ 제4종 분말</t>
+  </si>
+  <si>
+    <t>① 이산화탄소
+② 아세틸렌
+③ Halon 1211
+④ Halon 1301</t>
+  </si>
+  <si>
+    <t>① 발화점&gt; 연소점&gt; 인화점
+② 연소점&gt; 인화점&gt; 발화점
+③ 인화점&gt; 발화점&gt; 연소점
+④ 인화점&gt; 연소점&gt; 발화점</t>
+  </si>
+  <si>
+    <t>① 0.8
+② 1
+③ 1.25
+④ 20</t>
+  </si>
+  <si>
+    <t>① 페러데이의 전자유도법칙
+② 플레밍의 오른손법칙
+③ 암페어의 오른나사법칙
+④ 플레밍의 왼손법칙</t>
+  </si>
+  <si>
+    <t>① 1.4
+② 1.7
+③ 2.4
+④ 2.7</t>
+  </si>
+  <si>
+    <t>① 제너다이오드
+② 터널다이오드
+③ 발광다이오드
+④ 포토다이오드</t>
+  </si>
+  <si>
+    <t>① 경부하시 속도의 이상 상승 방지
+② 실효 권수비 선정 조정
+③ 전원전압의 크기에 관계없이, 정류에 알맞은 회전자전압 선택
+④ 회전자 상수의 감소</t>
+  </si>
+  <si>
+    <t>① 조작부와 검출부로 구성되어 있다.
+② 조절부와 변환부로 구성되어 있다.
+③ 동작신호를 조작량으로 변화시키는 요소이다.
+④ 목표값에 비례하는 신호를 발생하는 요소이다.</t>
+  </si>
+  <si>
+    <t>① 가동 코일형 계기
+② 전류력계형 계기
+③ 정전형 계기
+④ 열전형 계기</t>
+  </si>
+  <si>
+    <t>① A + BC
+② AB + C
+③ B + AC
+④ AB + BC</t>
+  </si>
+  <si>
+    <t>① 0.87
+② 1.22
+③ 1.73
+④ 3.98</t>
+  </si>
+  <si>
+    <t>① 12π
+② 24π
+③ 12√2
+④ 24√2</t>
+  </si>
+  <si>
+    <t>① 2차 항복이 없다.
+② 직접도가 낮다.
+③ 소전력으로 작동한다.
+④ 큰 입력저항으로 게이트 전류가 거의 흐르지 않는다.</t>
+  </si>
+  <si>
+    <t>① 120
+② 240
+③ 360
+④ 480</t>
+  </si>
+  <si>
+    <t>① 외부의 변화에 대한 영향을 증가시킬 수 있다.
+② 제어기 부품의 성능 차이에 따라 영향을 많이 받는다.
+③ 대역폭이 증가한다.
+④ 정확도와 전체 이득이 증가한다.</t>
+  </si>
+  <si>
+    <t>① 27
+② 59
+③ 77
+④ 89</t>
+  </si>
+  <si>
+    <t>① 잔류편차 제거
+② 간헐현상 제거
+③ 불연속 제어
+④ 응답 속응성 개선</t>
+  </si>
+  <si>
+    <t>① 열전대 온도계
+② 유리 온도계
+③ 바이메탈 온도계
+④ 압력식 온도계</t>
+  </si>
+  <si>
+    <t>① 기전력의 크기가 같을 것
+② 기전력의 위상이 같을 것
+③ 기전력의 주파수가 같을 것
+④ 극수가 같을 것</t>
+  </si>
+  <si>
+    <t>① 20만원 이하
+② 50만원 이하
+③ 100만원 이하
+④ 200만원 이하</t>
+  </si>
+  <si>
+    <t>① 비상경보설비
+② 비상콘센트설비
+③ 비상방송설비
+④ 옥내소화전설비</t>
+  </si>
+  <si>
+    <t>① 숙박시설
+② 업무시설
+③ 공동주택
+④ 근린생활시설</t>
+  </si>
+  <si>
+    <t>① 대통령령
+② 총리령
+③ 국민안전처장관령
+④ 시ㆍ도의 조례</t>
+  </si>
+  <si>
+    <t>① 옥외소화전 및 연결살수설비
+② 연결송수관설비 및 연결살수설비
+③ 자동화재탐지설비, 상수도소화용수설비 및 연결살수설비
+④ 스프링클러설비, 상수도소화용수설비 및 연결살수설비</t>
+  </si>
+  <si>
+    <t>① 지상에서 1.0m 이상 1.5m 이하
+② 지상에서 1.5m 이상 1.7m 이하
+③ 지상에서 1.2m 이상 1.8m 이하
+④ 지상에서 1.5m 이상 2.0m 이하</t>
+  </si>
+  <si>
+    <t>① 10배
+② 20배
+③ 30배
+④ 40배</t>
+  </si>
+  <si>
+    <t>① 300만원 이하의 벌금
+② 500만원 이하의 벌금
+③ 1000만원 이하의 벌금
+④ 2000만원 이하의 벌금</t>
+  </si>
+  <si>
+    <t>① 33
+② 40
+③ 43
+④ 46</t>
+  </si>
+  <si>
+    <t>① 5일
+② 7일
+③ 10일
+④ 15일</t>
+  </si>
+  <si>
+    <t>① 영화상영관에는 보행거리 50m 이내마다 3개이상 설치할 것
+② 지하상가 및 지하역사에는 보행거리 30m 이내마다 3개 이상 설치할 것
+③ 숙박시설 또는 다중이용업소에는 객실 또는 영업장안의 구획된 실마다 잘 보이는 곳에 1개 이상 설치할 것
+④ 건전지 및 충전식 밧데리의 용량은 20분 이상 유효하게 사용할 수 있는 것으로 할 것</t>
+  </si>
+  <si>
+    <t>① 방화구획형
+② 전용배전반(1ㆍ2종)
+③ 큐비클형
+④ 옥외개방형</t>
+  </si>
+  <si>
+    <t>① 1.5
+② 5
+③ 7
+④ 10</t>
+  </si>
+  <si>
+    <t>① 3회
+② 5회
+③ 10회
+④ 20회</t>
+  </si>
+  <si>
+    <t>① ㉠ 2, ㉡ 1
+② ㉠ 2, ㉡ 2
+③ ㉠ 3, ㉡ 1
+④ ㉠ 3, ㉡ 2</t>
+  </si>
+  <si>
+    <t>① 제어부
+② 조작부
+③ 증폭부
+④ 도통시험 및 동작시험부</t>
+  </si>
+  <si>
+    <t>① 전력계 및 전류계
+② 전류계 및 전압계
+③ 표시등 및 전압계
+④ 표시등 및 전력계</t>
+  </si>
+  <si>
+    <t>① 6개
+② 7개
+③ 8개
+④ 9개</t>
+  </si>
+  <si>
+    <t>① 비상콘센트 설비 - 20분 이상
+② 제연설비 - 20분 이상
+③ 비상경보설비 - 20분 이상
+④ 무선통신보조설비의 증폭기 - 30분 이상</t>
+  </si>
+  <si>
+    <t>① 0.1
+② 0.2
+③ 10
+④ 20</t>
+  </si>
+  <si>
+    <t>① 불꽃감지기
+② 축적방식의 감지기
+③ 정온식 감지선형 감지기
+④ 광전식 스포트형 감지기</t>
+  </si>
+  <si>
+    <t>① ㉠2층, ㉡1층, ㉢지하층
+② ㉠1층, ㉡2층, ㉢지하층
+③ ㉠2층, ㉡지하층, ㉢1층
+④ ㉠2층, ㉡1층, ㉢모든 층</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>17109(1), 17109(2)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연기의 감광계수(m^-1)에 대한 설명으로 옳은 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 금속나트륨 - 석유류에 저장
+② 이황화탄소 - 수조 물탱크에 저장
+③ 알킬알루미늄 - 벤젠액에 희석하여 저장
+④ 산화프로필렌 - 구리 용기에 넣고 불연성 가스를 봉입하여 저장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① CO₂ 소화약제로 소화한다.
+② 봉상 주수로 소화한다.
+③ 3종 분말약제로 소화한다.
+④ 단백포로 소화한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>분말소화약제 중 탄산수소칼륨(KHCO₃)과 요소(CO(NH₂)₂)와의 반응물을 주성분으로 하는 소화약제는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소화효과를 고려하였을 경우 화재 시 사용할 수 있는 물질이 아닌 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">길이 1m의 철심(비투자율 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>㎲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> =700) 자기회로에 2mm 의 공극이 생겼다면 자기저항은 몇 배 증가하는가? (단, 각 부의 단면적은 일정하다.)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17129a</t>
+  </si>
+  <si>
+    <t>그림과 같은 반파정류회로에 스위치 A를 사용하여 부하 저항 R 을 떼어 냈을 경우, 콘덴서 C의 충전전압은 몇 V 인 L 가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17131a</t>
+  </si>
+  <si>
+    <t>17132a</t>
+  </si>
+  <si>
+    <t>그림과 같은 교류브리지의 평형조건으로 옳은 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① R₂C₄ = R₁C₃ , R₂C₁ = R₄C₃ 
+② R₁C₁ = R₄C₄ , R₂C₃ = R₁C₁
+③ R₂C₄ = R₄C₃ , R₁C₃ = R₂C₁
+④ R₁C₁ = R₄C₄ , R₂C₃ = R₁C₄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20℃의 물 2L를 64℃가 되도록 가열하기 위해 400W의 온수기를 20분 사용하였을 때 이 온수기의 효율은 약 몇 %인 가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① Vav = 0.707Vm
+② Vav = 0.840Vm 
+③ Vav = 0.637Vm
+④ Vav = 0.956Vm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>관계인이 예방규정을 정하여야 하는 제조소등의 기준이 아닌 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 지정수량의 10배 이상의 위험물을 취급하는 제조소
+② 지정수량의 50배 이상의 위험물을 취급하는 옥외저장소
+③ 지정수량의 150배 이상의 위험물을 취급하는 옥내저장소
+④ 지정수량의 200배 이상의 위험물을 취급하는 옥외탱크저장소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정소방대상물이 증축 되는 경우 기존 부분에 대해서 증축당시의 소방시설의 설치에 관한 대통령령 또는 화재안전기준을 적용하지 않는 경우가 아닌 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 문화 및 집회시설
+② 수계 소화설비가 설치되는 것
+③ 연면적 10000m² 이상이거나 11층 이상인 특정소방대상 물(아파트는 제외)
+④ 가연성가스를 제조ㆍ저장 또는 취급하는 시설중 지상에 노출된 가연성가스탱크의 저장용량의 합계가 1000톤 이상인 시설</t>
+  </si>
+  <si>
+    <t>① 증축으로 인하여 천장ㆍ바닥ㆍ벽 등에 고정되어 있는가 연성 물질의 양이 줄어드는 경우
+② 자동차 생산공장 등 화재 위험이 낮은 특정소방대상물 내부에 연면적 33m² 이하의 직원 휴게실을 증축하는 경우
+③ 기존 부분과 증축 부분이 갑종 방화문(국토교통부장관이 정하는 기준에 적합한 자동방화셔터를 포함)으로 구획되어 있는 경우
+④ 자동차 생산공장 등 화재 위험이 낮은 특정소방대상물에 캐노피(3면 이상에 벽이 없는 구조의 캐노피)를 설치하는 경우</t>
+  </si>
+  <si>
+    <t>① 연면적 5000m² 이상 30000m² 미만인 특정소방대상물의 공사 현장
+② 연면적 30000m² 이상 200000m² 미만인 아파트의 공사 현장
+③ 연면적 30000m² 이상 200000m² 미만인 특정소방대상 물(아파트는 제외)의 공사 현장
+④ 연면적 200000m² 이상인 특정소방대상물의 공사 현장</t>
+  </si>
+  <si>
+    <t>비상콘센트의 배치 기준 중 바닥면적이 1000m²미만인 층은 계단의 출입구로부터 몇m 이내에 설치하여야 하는가?</t>
+  </si>
+  <si>
+    <t>① 능력단위 수치가 3 이상의 소형 수동식소화기등 1개 이상
+② 능력단위 수치가 3 이상의 소형 수동식소화기등 2개 이상
+③ 능력단위 수치가 2 이상의 소형 수동식소화기등 1개 이상
+④ 능력단위 수치가 2 이상의 소형 수동식소화기등 2개 이상</t>
+  </si>
+  <si>
+    <t>소화난이도등급 Ⅲ인 지하탱크저장소에 설치하여야 하는 소화설비의 설치기준으로 옳은 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소방특별조사의 연기를 신청하려는 자는 소방특별조사 시작 며칠 전까지 국민안전처장관, 소방본부장 또는 소방서장에게 소방특별조사 연기신청서에 증명서류를 첨부하여 제출해야 하는가? (단, 천재지변 및 그 밖에 대통령령으로 정하는 사유로 소방특별조사를 받기 곤란한 경우이다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시장지역에서 화재로 오인할 만한 우려가 있는 불을 피우거나 연막소독을 하려는 자가 소방본부장 또는 소방서장에게 신고를 하지 아니하여 소방자동차를 출동하게 한 자에 대한 과태료 부과금액 기준으로 옳은 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 소방대상물의 신축
+② 소방대상물의 개수
+③ 소방대상물의 이전
+④ 소방대상물의 제거</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대통령령 또는 화재안전기준이 변경되어 그 기준이 강화되는 경우에 기존 특정소방대상물의 소방시설에 대하여 변경으로 강화된 기준을 적용하여야 하는 소방시설은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>출동한 소방대의 화재진압 및 인명구조ㆍ구급 등 소방활동방해에 따른 벌칙이 5년이하의 징역 또는 5000만원 이하의 벌금에 처하는 행위가 아닌 것은?(2018년 03월 27일 개정된 규정 적용됨)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 위력을 사용하여 출동한 소방대의 구급활동을 방해하는 행위
+② 화재진압을 마치고 소방서로 복귀 중인 소방자동차의 통행을 고의로 방해하는 행위
+③ 출동한 소방대원에게 협박을 행사하여 구급활동을 방해 하는 행위
+④ 출동한 소방대의 소방장비를 파손하거나 그 효용을 해하여 구급활동을 방해하는 행위</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소방시설업에 대한 행정처분 기준 중 1차처분이 영업정지 3개월이 아닌 경우는?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 국가, 지방자치단체 또는 공공기관이 발주하는 소방시설의 설계ㆍ감리업자 선정에 따른 사업수행능력 평가에 관한 서류를 위조하거나 변조하는 등 거짓이나 그 밖의 부정한 방법으로 입찰에 참여한 경우
+② 소방시설업의 감독을 위하여 필요한 보고나 자료제출 명령을 위반하여 보고 또는 자료 제출을 하지 아니하고나 거짓으로 보고 또는 자료 제출을 한 경우
+③ 정당한 사유 없이 출입ㆍ검사업무에 따른 관계 공무원의 출입 또는 검사ㆍ조사를 거부ㆍ방해 또는 기피한 경우
+④ 감리업자의 감리 시 소방시설공사가 설계도서에 맞지 아니하여 공사업자에게 공사의 시정 또는 보완 등의 요구를 하였으나 따르지 아니한 경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소방시설기준 적용의 특례 중 특정소방대상물의 관계인이 소방시설을 갖추어야 함에도 불구하고 관련 소방시설을 설치하지 아니할 수 있는 소방시설의 범위로 옳은 것은? (단, 화재 위험도가 낮은 특정소방대상물로서 석재, 불연성금속, 불연성 건축재료 등의 가공공장ㆍ기계조립공장ㆍ주물공장 또는 불연성 물품을 저장하는 창고이다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>옥내저장소의 위치ㆍ구조 및 설비의 기준 중 지정수량의 몇 배 이상의 저장창고(제6류 위험물의 저장창고 제외)에 피뢰침을 설치해야 하는가? (단, 저장창고 주위의 상황이 안전상 지장이 없는 경우는 제외한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우수품질인증을 받지 아니한 제품에 우수품질 인증표시를 하거나 우수품질인증 표시를 위조 또는 변조하여 사용한 자에 대한 벌칙기준은?(2017년 12월 26일 개정된 규정 적용 됨)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17157a</t>
+  </si>
+  <si>
+    <t>성능위주설계를 실시하여야 하는 특정소방대상물의 범위 기준으로 틀린 것은?(2021년 08월 24일 변경된 기준 적용됨]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 연면적 200000m² 이상인 특정소방대상물 (아파트등은 제외)
+② 지하층을 포함한 층수가 30층 이상인 특정소방대상물 (아파트등은 제외)
+③ 건축물의 높이가 120m 이상인 특정소방대상물 (아파트등은 제외)
+④ 하나의 건축물에 영화상영관이 5개 이상인 특정소방대상물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소방본부장 또는 소방서장은 건축허가등의 동의요구서류를 접수한 날부터 최대 며칠 이내에 건축허가등의 동의여부를 회신하여야 하는가? (단, 허가 신청한 건축물은 지상으로부터 높이가 200m 인 아파트이다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총리령으로 정하는 고급감리원 이상의 소방공사 감리원의 소방시설공사 배치 현장기준으로 옳은 것은?(관련 규정 개 정전 문제로 여기서는 기존 정답인 2번을 누르면 정답 처리 됩니다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 보상식 스포트형 감지기는 정온점이 감지기 주위의 평상시 최고 온도보다 20℃ 이상 높은 것으로 설치할 것
+② 정온식 감지기는 주방ㆍ보일러실 등으로서 다량의 화기를 취급하는 장소에 설치하되, 공칭작동온도가 최고주위 온도보다 30℃ 이상 높은 것으로 설치할 것
+③ 스포트형 감지기는 15°이상 경사되지 아니하도록 부착할 것
+④ 공기관식 차동식분포형 감지기의 검출부는 45°이상 경사 되지 아니하도록 부착할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 손잡이는 출구 부근에 좌우 각 3개 이상 균일한 간격으로 견고하게 부착하여야 한다.
+② 입구틀 및 취부틀의 입구는 지름 30cm 이상의 구체가 통과할 수 있어야 한다.
+③ 구조대 본체의 활강부는 낙하방지를 위해 포를 2중구조로 하거나 또는 망목의 변의 길이가 8cm 이하인 망을 설치하여야 한다.
+④ 구조대본체의 끝부분에는 길이 4m 이상, 지름4mm 이상의 유도선을 부착하여야 하며, 유도선 끝에는 중량 3N(300g) 이상의 모래주머니 등을 설치하여야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 피난유도 표시부는 50cm 이내의 간격으로 연속되도록 설치하되 실내장식물 등으로 설치가 곤란할 경우 2m 이내로 설치할 것
+② 피난유도 표시부는 바닥으로부터 높이 1m 이하의 위치 또는 바닥 면에 설치할 것
+③ 피난유도 제어부는 조작 및 관리가 용이 하도록 바닥으로부터 0.8m 이상 1.5m 이하의 높이에 설치할 것
+④ 구획된 각 실로부터 주 출입구 또는 비상구까지 설치할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동화재속보설비의 속보기는 연동 또는 수동작동에 의한 다이얼링 후 소방관서와 전화접속이 이루어지지 않는 경우 에는 최초 다이얼링을 포함하여 몇 회 이상 반복적으로 접속을 위한 다이얼링이 이루어져야 하는가? (단, 이 경우 매 회 다이얼링 완료 후 호출은 30초 이상 지속한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17168a</t>
+  </si>
+  <si>
+    <t>① 설치한 피난기구 외에 아파트의 경우에는 하나의 관리주체가 관리하는 아파트 구역마다 공기안전매트 1개 이상을 추가로 설치할 것
+② 휴양콘도미니엄을 제외한 숙박시설의 경우에는 추가로 객실마다 완강기 또는 1개이상의 간이완강기를 설치할 것
+③ 층마다 설치하되, 숙박시설ㆍ노유자시설 및 의료시설로 사용되는 층에 있어서는 그 층의 바닥면적 500m² 마다 1개 이상 설치할 것
+④ 층마다 설치하되, 위락시설ㆍ문화집회 및 운동시설ㆍ판매시설로 사용되는 층 또는 복합용도의 층에 있어서는 그 층은 바닥면적 800m² 마다 1개 이상 설치할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 비상콘센트용 풀박스 등은 방청도장을 한 것으로서, 두께 1.6mm 이상의 철판으로 할 것
+② 하나의 전용회로에 설치하는 비상콘센트는 10개 이하로 할 것
+③ 콘센트마다 배선용 차단기(KS C 8321)를 설치하여야 하며, 충전부가 노출되지 아니하도록 할 것
+④ 전원회로는 단상교류 220V인 것으로서, 그 공급용량은 3kVA 이상인 것으로 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정소방대상물의 그 부분에서 피난층에 이르는 부분의 비상조명등을 60분 이상 유효하게 작동시킬 수 있는 용량으로 하여야 하는 경우가 아닌 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 지하층을 제외한 층수가 11층 이상의 층
+② 지하층 또는 무창층으로서 용도가 도매시장ㆍ소매시장
+③ 지하층 또는 무창층으로서 용도가 여객자동차터미널ㆍ지하역사 또는 지하상가
+④ 지하가 터널로서 길이 500m 이상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주요구조부를 내화구조로 한 특정소방대상물의 바닥면적이 370m²인 부분에 설치해야 하는 감지기의 최소 수량은? (단, 감지기의 부착높이는 바닥으로부터 4.5m 이고, 보상식 스포트형 1종을 설치한다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 하나의 경계구역이 3개 이상의 건축물에 미치지 아니하도록 하여야 한다.
+② 하나의 경계구역의 면적은 500m² 이하로 하고 한 변의 길이는 60m 이하로 하여야 한다.
+③ 500m² 이하의 범위안에서는 2개의 층을 하나의 경계구역으로 할 수 있다
+④ 특정소방대상물의 주된 출입구에서 그 내부 전체가 보이는 것에 있어서는 한 변의 길이가 100m의 범위내에서 1500m² 이하로 할 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 거실 각 부분으로부터 하나의 출입구에 이르는 보행거리가 20m 이하이고 비상조명등과 유도표지가 설치된 거실의 출입구
+② 바닥면적이 500m² 미만인 층으로서 옥내로부터 직접 지상으로 통하는 출입구(외부의 식별이 용이하지 않은 경우에 한함)
+③ 출입구가 3 이상 있는 거실로서 그 거실 각 부분으로부터 하나의 출입구에 이르는 보행거리가 30m 이하인 경우에는 주된 출입구 2개소외의 출입구 (유도표지가 부착된 출입구)
+④ 거실 각 부분으로부터 쉽게 도달할 수 있는 출입구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상방송설비의 배선의 설치기준 중 부속회로의 전로와 대지 사이 및 배선상호간의 절연저항은 1경계구역마다 직류 250V의 절연저항측정기를 사용하여 측정한 절연저항이 몇 MΩ 이상이 되도록 해야 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>감지기의 부착면과 실내 바닥과의 거리가 2.3m 이하인 곳 으로서 일시적으로 발생한 열ㆍ연기 또는 먼지 등으로 인하여 화재신호를 발신할 우려가 있는 장소에 적응성이 있는 감지기가 아닌 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상방송설비의 음향장치의 설치기준 중 다음 ( )안에 알맞은 것으로 연결된 것은?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17180a</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4776,6 +5569,13 @@
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -4861,20 +5661,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6220,7 +7020,7 @@
       </c>
       <c r="D5" s="4"/>
     </row>
-    <row r="6" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
         <v>176</v>
       </c>
@@ -7272,7 +8072,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
         <v>337</v>
       </c>
@@ -7382,14 +8182,14 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:4" s="14" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A21" s="13" t="s">
+    <row r="21" spans="1:4" s="11" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A21" s="12" t="s">
         <v>460</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="12" t="s">
         <v>459</v>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="11">
         <v>2</v>
       </c>
     </row>
@@ -7520,7 +8320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:4" ht="87" x14ac:dyDescent="0.4">
       <c r="A33" s="4" t="s">
         <v>355</v>
       </c>
@@ -7622,7 +8422,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
       <c r="A42" s="4" t="s">
         <v>361</v>
       </c>
@@ -7633,7 +8433,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
       <c r="A43" s="4" t="s">
         <v>362</v>
       </c>
@@ -7644,7 +8444,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A44" s="4" t="s">
         <v>363</v>
       </c>
@@ -7688,7 +8488,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="243.6" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:4" ht="191.4" x14ac:dyDescent="0.4">
       <c r="A48" s="4" t="s">
         <v>473</v>
       </c>
@@ -7721,7 +8521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="174" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:3" ht="156.6" x14ac:dyDescent="0.4">
       <c r="A51" s="4" t="s">
         <v>367</v>
       </c>
@@ -7820,7 +8620,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="121.8" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:3" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A60" s="4" t="s">
         <v>373</v>
       </c>
@@ -7842,7 +8642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="121.8" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:3" ht="87" x14ac:dyDescent="0.4">
       <c r="A62" s="4" t="s">
         <v>375</v>
       </c>
@@ -7930,7 +8730,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="121.8" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:3" ht="104.4" x14ac:dyDescent="0.4">
       <c r="A70" s="4" t="s">
         <v>381</v>
       </c>
@@ -9016,990 +9816,916 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" ht="16.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="13" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="13" t="s">
         <v>652</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="13" t="s">
         <v>653</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2">
         <v>4</v>
       </c>
-      <c r="D2" s="12"/>
     </row>
     <row r="3" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="13" t="s">
         <v>654</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="13" t="s">
         <v>655</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3" s="12"/>
     </row>
     <row r="4" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="13" t="s">
         <v>656</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="13" t="s">
         <v>750</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4" s="12"/>
     </row>
     <row r="5" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="13" t="s">
         <v>751</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="13" t="s">
         <v>657</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5">
         <v>3</v>
       </c>
-      <c r="D5" s="12"/>
     </row>
     <row r="6" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="13" t="s">
         <v>752</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="13" t="s">
         <v>658</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6">
         <v>4</v>
       </c>
-      <c r="D6" s="12"/>
     </row>
     <row r="7" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="13" t="s">
         <v>659</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="13" t="s">
         <v>660</v>
       </c>
-      <c r="C7" s="12">
-        <v>2</v>
-      </c>
-      <c r="D7" s="12"/>
+      <c r="C7">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="13" t="s">
         <v>661</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="13" t="s">
         <v>662</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8">
         <v>4</v>
       </c>
-      <c r="D8" s="12"/>
     </row>
     <row r="9" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="13" t="s">
         <v>663</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="13" t="s">
         <v>664</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9">
         <v>3</v>
       </c>
-      <c r="D9" s="12"/>
     </row>
     <row r="10" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="13" t="s">
         <v>665</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="13" t="s">
         <v>666</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10">
         <v>3</v>
       </c>
-      <c r="D10" s="12"/>
     </row>
     <row r="11" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="13" t="s">
         <v>667</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="13" t="s">
         <v>668</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11">
         <v>3</v>
       </c>
-      <c r="D11" s="12"/>
     </row>
     <row r="12" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="13" t="s">
         <v>669</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="13" t="s">
         <v>753</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12">
         <v>3</v>
       </c>
-      <c r="D12" s="12"/>
     </row>
     <row r="13" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="13" t="s">
         <v>754</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="13" t="s">
         <v>670</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13">
         <v>3</v>
       </c>
-      <c r="D13" s="12"/>
     </row>
     <row r="14" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="13" t="s">
         <v>755</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14">
         <v>4</v>
       </c>
-      <c r="D14" s="12"/>
     </row>
     <row r="15" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="13" t="s">
         <v>671</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="13" t="s">
         <v>672</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15">
         <v>1</v>
       </c>
-      <c r="D15" s="12"/>
     </row>
     <row r="16" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="13" t="s">
         <v>673</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="13">
         <v>16215</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16">
         <v>1</v>
       </c>
-      <c r="D16" s="12"/>
-    </row>
-    <row r="17" spans="1:4" ht="191.4" x14ac:dyDescent="0.4">
-      <c r="A17" s="15" t="s">
+    </row>
+    <row r="17" spans="1:3" ht="191.4" x14ac:dyDescent="0.4">
+      <c r="A17" s="13" t="s">
         <v>674</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="13" t="s">
         <v>756</v>
       </c>
-      <c r="C17" s="12">
-        <v>2</v>
-      </c>
-      <c r="D17" s="12"/>
-    </row>
-    <row r="18" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A18" s="15" t="s">
+      <c r="C17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A18" s="13" t="s">
         <v>675</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="13" t="s">
         <v>676</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18">
         <v>3</v>
       </c>
-      <c r="D18" s="12"/>
-    </row>
-    <row r="19" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
-      <c r="A19" s="15" t="s">
+    </row>
+    <row r="19" spans="1:3" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A19" s="13" t="s">
         <v>677</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="13" t="s">
         <v>757</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19">
         <v>1</v>
       </c>
-      <c r="D19" s="12"/>
-    </row>
-    <row r="20" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
-      <c r="A20" s="15" t="s">
+    </row>
+    <row r="20" spans="1:3" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A20" s="13" t="s">
         <v>678</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="13" t="s">
         <v>679</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20">
         <v>1</v>
       </c>
-      <c r="D20" s="12"/>
-    </row>
-    <row r="21" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A21" s="15" t="s">
+    </row>
+    <row r="21" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A21" s="13" t="s">
         <v>680</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="13" t="s">
         <v>758</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21">
         <v>3</v>
       </c>
-      <c r="D21" s="12"/>
-    </row>
-    <row r="22" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A22" s="15" t="s">
+    </row>
+    <row r="22" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A22" s="13" t="s">
         <v>681</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="13" t="s">
         <v>682</v>
       </c>
-      <c r="C22" s="12">
-        <v>2</v>
-      </c>
-      <c r="D22" s="12"/>
-    </row>
-    <row r="23" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A23" s="15" t="s">
+      <c r="C22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A23" s="13" t="s">
         <v>683</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="13" t="s">
         <v>684</v>
       </c>
-      <c r="C23" s="12">
+      <c r="C23">
         <v>1</v>
       </c>
-      <c r="D23" s="12"/>
-    </row>
-    <row r="24" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A24" s="15" t="s">
+    </row>
+    <row r="24" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A24" s="13" t="s">
         <v>759</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="13" t="s">
         <v>685</v>
       </c>
-      <c r="C24" s="12">
-        <v>2</v>
-      </c>
-      <c r="D24" s="12"/>
-    </row>
-    <row r="25" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A25" s="15" t="s">
+      <c r="C24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A25" s="13" t="s">
         <v>760</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="13" t="s">
         <v>686</v>
       </c>
-      <c r="C25" s="12">
+      <c r="C25">
         <v>3</v>
       </c>
-      <c r="D25" s="12"/>
-    </row>
-    <row r="26" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A26" s="15" t="s">
+    </row>
+    <row r="26" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A26" s="13" t="s">
         <v>761</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="13" t="s">
         <v>687</v>
       </c>
-      <c r="C26" s="12">
+      <c r="C26">
         <v>4</v>
       </c>
-      <c r="D26" s="12"/>
-    </row>
-    <row r="27" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A27" s="15" t="s">
+    </row>
+    <row r="27" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A27" s="13" t="s">
         <v>688</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="13" t="s">
         <v>689</v>
       </c>
-      <c r="C27" s="12">
+      <c r="C27">
         <v>1</v>
       </c>
-      <c r="D27" s="12"/>
-    </row>
-    <row r="28" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A28" s="15" t="s">
+    </row>
+    <row r="28" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A28" s="13" t="s">
         <v>690</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="13" t="s">
         <v>691</v>
       </c>
-      <c r="C28" s="12">
+      <c r="C28">
         <v>1</v>
       </c>
-      <c r="D28" s="12"/>
-    </row>
-    <row r="29" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A29" s="15" t="s">
+    </row>
+    <row r="29" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A29" s="13" t="s">
         <v>692</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="13" t="s">
         <v>693</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29">
         <v>1</v>
       </c>
-      <c r="D29" s="12"/>
-    </row>
-    <row r="30" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A30" s="15" t="s">
+    </row>
+    <row r="30" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A30" s="13" t="s">
         <v>762</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="13" t="s">
         <v>694</v>
       </c>
-      <c r="C30" s="12">
+      <c r="C30">
         <v>4</v>
       </c>
-      <c r="D30" s="12"/>
-    </row>
-    <row r="31" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A31" s="15" t="s">
+    </row>
+    <row r="31" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A31" s="13" t="s">
         <v>695</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="13" t="s">
         <v>763</v>
       </c>
-      <c r="C31" s="12">
-        <v>2</v>
-      </c>
-      <c r="D31" s="12"/>
-    </row>
-    <row r="32" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A32" s="15" t="s">
+      <c r="C31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A32" s="13" t="s">
         <v>764</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="13" t="s">
         <v>696</v>
       </c>
-      <c r="C32" s="12">
+      <c r="C32">
         <v>1</v>
       </c>
-      <c r="D32" s="12"/>
     </row>
     <row r="33" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="13" t="s">
         <v>697</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="13" t="s">
         <v>698</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33">
         <v>3</v>
       </c>
-      <c r="D33" s="12"/>
     </row>
     <row r="34" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="13" t="s">
         <v>766</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="13" t="s">
         <v>765</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C34">
         <v>4</v>
       </c>
-      <c r="D34" s="12"/>
     </row>
     <row r="35" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="13" t="s">
         <v>769</v>
       </c>
-      <c r="B35" s="15">
+      <c r="B35" s="13">
         <v>16234</v>
       </c>
-      <c r="C35" s="12">
+      <c r="C35">
         <v>1</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" t="s">
         <v>767</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A36" s="15" t="s">
+      <c r="A36" s="13" t="s">
         <v>699</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="B36" s="13" t="s">
         <v>700</v>
       </c>
-      <c r="C36" s="12">
+      <c r="C36">
         <v>3</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" t="s">
         <v>768</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="13" t="s">
         <v>701</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="13" t="s">
         <v>702</v>
       </c>
-      <c r="C37" s="12">
+      <c r="C37">
         <v>1</v>
       </c>
-      <c r="D37" s="12"/>
     </row>
     <row r="38" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="13" t="s">
         <v>770</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="13" t="s">
         <v>771</v>
       </c>
-      <c r="C38" s="12">
+      <c r="C38">
         <v>4</v>
       </c>
-      <c r="D38" s="12"/>
     </row>
     <row r="39" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A39" s="15" t="s">
+      <c r="A39" s="13" t="s">
         <v>703</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="B39" s="13" t="s">
         <v>704</v>
       </c>
-      <c r="C39" s="12">
-        <v>2</v>
-      </c>
-      <c r="D39" s="12" t="s">
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39" t="s">
         <v>772</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A40" s="15" t="s">
+      <c r="A40" s="13" t="s">
         <v>705</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B40" s="13" t="s">
         <v>706</v>
       </c>
-      <c r="C40" s="12">
-        <v>2</v>
-      </c>
-      <c r="D40" s="12"/>
+      <c r="C40">
+        <v>2</v>
+      </c>
     </row>
     <row r="41" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A41" s="15" t="s">
+      <c r="A41" s="13" t="s">
         <v>707</v>
       </c>
-      <c r="B41" s="15">
+      <c r="B41" s="13">
         <v>16240</v>
       </c>
-      <c r="C41" s="12">
+      <c r="C41">
         <v>1</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" t="s">
         <v>773</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A42" s="15" t="s">
+      <c r="A42" s="13" t="s">
         <v>708</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="13" t="s">
         <v>775</v>
       </c>
-      <c r="C42" s="12">
-        <v>2</v>
-      </c>
-      <c r="D42" s="12" t="s">
+      <c r="C42">
+        <v>2</v>
+      </c>
+      <c r="D42" t="s">
         <v>776</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A43" s="15" t="s">
+      <c r="A43" s="13" t="s">
         <v>777</v>
       </c>
-      <c r="B43" s="15" t="s">
+      <c r="B43" s="13" t="s">
         <v>774</v>
       </c>
-      <c r="C43" s="12">
-        <v>2</v>
-      </c>
-      <c r="D43" s="12"/>
+      <c r="C43">
+        <v>2</v>
+      </c>
     </row>
     <row r="44" spans="1:4" ht="87" x14ac:dyDescent="0.4">
-      <c r="A44" s="15" t="s">
+      <c r="A44" s="13" t="s">
         <v>778</v>
       </c>
-      <c r="B44" s="15" t="s">
+      <c r="B44" s="13" t="s">
         <v>709</v>
       </c>
-      <c r="C44" s="12">
+      <c r="C44">
         <v>1</v>
       </c>
-      <c r="D44" s="12"/>
     </row>
     <row r="45" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A45" s="15" t="s">
+      <c r="A45" s="13" t="s">
         <v>779</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="B45" s="13" t="s">
         <v>710</v>
       </c>
-      <c r="C45" s="12">
+      <c r="C45">
         <v>3</v>
       </c>
-      <c r="D45" s="12"/>
     </row>
     <row r="46" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A46" s="15" t="s">
+      <c r="A46" s="13" t="s">
         <v>711</v>
       </c>
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="13" t="s">
         <v>712</v>
       </c>
-      <c r="C46" s="12">
+      <c r="C46">
         <v>3</v>
       </c>
-      <c r="D46" s="12"/>
     </row>
     <row r="47" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A47" s="15" t="s">
+      <c r="A47" s="13" t="s">
         <v>713</v>
       </c>
-      <c r="B47" s="15" t="s">
+      <c r="B47" s="13" t="s">
         <v>714</v>
       </c>
-      <c r="C47" s="12">
-        <v>2</v>
-      </c>
-      <c r="D47" s="12"/>
+      <c r="C47">
+        <v>2</v>
+      </c>
     </row>
     <row r="48" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A48" s="15" t="s">
+      <c r="A48" s="13" t="s">
         <v>780</v>
       </c>
-      <c r="B48" s="15" t="s">
+      <c r="B48" s="13" t="s">
         <v>715</v>
       </c>
-      <c r="C48" s="12">
+      <c r="C48">
         <v>1</v>
       </c>
-      <c r="D48" s="12"/>
-    </row>
-    <row r="49" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A49" s="15" t="s">
+    </row>
+    <row r="49" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A49" s="13" t="s">
         <v>716</v>
       </c>
-      <c r="B49" s="15" t="s">
+      <c r="B49" s="13" t="s">
         <v>717</v>
       </c>
-      <c r="C49" s="12">
-        <v>2</v>
-      </c>
-      <c r="D49" s="12"/>
-    </row>
-    <row r="50" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A50" s="15" t="s">
+      <c r="C49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A50" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="13" t="s">
         <v>719</v>
       </c>
-      <c r="C50" s="12">
+      <c r="C50">
         <v>4</v>
       </c>
-      <c r="D50" s="12"/>
-    </row>
-    <row r="51" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A51" s="15" t="s">
+    </row>
+    <row r="51" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A51" s="13" t="s">
         <v>720</v>
       </c>
-      <c r="B51" s="15" t="s">
+      <c r="B51" s="13" t="s">
         <v>721</v>
       </c>
-      <c r="C51" s="12">
+      <c r="C51">
         <v>4</v>
       </c>
-      <c r="D51" s="12"/>
-    </row>
-    <row r="52" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A52" s="15" t="s">
+    </row>
+    <row r="52" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A52" s="13" t="s">
         <v>783</v>
       </c>
-      <c r="B52" s="15" t="s">
+      <c r="B52" s="13" t="s">
         <v>782</v>
       </c>
-      <c r="C52" s="12">
-        <v>2</v>
-      </c>
-      <c r="D52" s="12"/>
-    </row>
-    <row r="53" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A53" s="15" t="s">
+      <c r="C52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A53" s="13" t="s">
         <v>784</v>
       </c>
-      <c r="B53" s="15" t="s">
+      <c r="B53" s="13" t="s">
         <v>781</v>
       </c>
-      <c r="C53" s="12">
+      <c r="C53">
         <v>4</v>
       </c>
-      <c r="D53" s="12"/>
-    </row>
-    <row r="54" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A54" s="15" t="s">
+    </row>
+    <row r="54" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A54" s="13" t="s">
         <v>785</v>
       </c>
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="13" t="s">
         <v>722</v>
       </c>
-      <c r="C54" s="12">
+      <c r="C54">
         <v>1</v>
       </c>
-      <c r="D54" s="12"/>
-    </row>
-    <row r="55" spans="1:4" ht="208.8" x14ac:dyDescent="0.4">
-      <c r="A55" s="15" t="s">
+    </row>
+    <row r="55" spans="1:3" ht="208.8" x14ac:dyDescent="0.4">
+      <c r="A55" s="13" t="s">
         <v>786</v>
       </c>
-      <c r="B55" s="15" t="s">
+      <c r="B55" s="13" t="s">
         <v>787</v>
       </c>
-      <c r="C55" s="12">
+      <c r="C55">
         <v>3</v>
       </c>
-      <c r="D55" s="12"/>
-    </row>
-    <row r="56" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
-      <c r="A56" s="15" t="s">
+    </row>
+    <row r="56" spans="1:3" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A56" s="13" t="s">
         <v>788</v>
       </c>
-      <c r="B56" s="15" t="s">
+      <c r="B56" s="13" t="s">
         <v>789</v>
       </c>
-      <c r="C56" s="12">
+      <c r="C56">
         <v>3</v>
       </c>
-      <c r="D56" s="12"/>
-    </row>
-    <row r="57" spans="1:4" ht="87" x14ac:dyDescent="0.4">
-      <c r="A57" s="15" t="s">
+    </row>
+    <row r="57" spans="1:3" ht="87" x14ac:dyDescent="0.4">
+      <c r="A57" s="13" t="s">
         <v>790</v>
       </c>
-      <c r="B57" s="15" t="s">
+      <c r="B57" s="13" t="s">
         <v>723</v>
       </c>
-      <c r="C57" s="12">
+      <c r="C57">
         <v>3</v>
       </c>
-      <c r="D57" s="12"/>
-    </row>
-    <row r="58" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
-      <c r="A58" s="15" t="s">
+    </row>
+    <row r="58" spans="1:3" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A58" s="13" t="s">
         <v>791</v>
       </c>
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="13" t="s">
         <v>724</v>
       </c>
-      <c r="C58" s="12">
+      <c r="C58">
         <v>4</v>
       </c>
-      <c r="D58" s="12"/>
-    </row>
-    <row r="59" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A59" s="15" t="s">
+    </row>
+    <row r="59" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A59" s="13" t="s">
         <v>725</v>
       </c>
-      <c r="B59" s="15" t="s">
+      <c r="B59" s="13" t="s">
         <v>726</v>
       </c>
-      <c r="C59" s="12">
-        <v>2</v>
-      </c>
-      <c r="D59" s="12"/>
-    </row>
-    <row r="60" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A60" s="15" t="s">
+      <c r="C59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A60" s="13" t="s">
         <v>727</v>
       </c>
-      <c r="B60" s="15" t="s">
+      <c r="B60" s="13" t="s">
         <v>792</v>
       </c>
-      <c r="C60" s="12">
+      <c r="C60">
         <v>4</v>
       </c>
-      <c r="D60" s="12"/>
-    </row>
-    <row r="61" spans="1:4" ht="87" x14ac:dyDescent="0.4">
-      <c r="A61" s="15" t="s">
+    </row>
+    <row r="61" spans="1:3" ht="87" x14ac:dyDescent="0.4">
+      <c r="A61" s="13" t="s">
         <v>793</v>
       </c>
-      <c r="B61" s="15" t="s">
+      <c r="B61" s="13" t="s">
         <v>728</v>
       </c>
-      <c r="C61" s="12">
+      <c r="C61">
         <v>3</v>
       </c>
-      <c r="D61" s="12"/>
-    </row>
-    <row r="62" spans="1:4" ht="208.8" x14ac:dyDescent="0.4">
-      <c r="A62" s="15" t="s">
+    </row>
+    <row r="62" spans="1:3" ht="208.8" x14ac:dyDescent="0.4">
+      <c r="A62" s="13" t="s">
         <v>795</v>
       </c>
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="13" t="s">
         <v>794</v>
       </c>
-      <c r="C62" s="12">
+      <c r="C62">
         <v>4</v>
       </c>
-      <c r="D62" s="12"/>
-    </row>
-    <row r="63" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A63" s="15" t="s">
+    </row>
+    <row r="63" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A63" s="13" t="s">
         <v>796</v>
       </c>
-      <c r="B63" s="15" t="s">
+      <c r="B63" s="13" t="s">
         <v>729</v>
       </c>
-      <c r="C63" s="12">
+      <c r="C63">
         <v>1</v>
       </c>
-      <c r="D63" s="12"/>
-    </row>
-    <row r="64" spans="1:4" ht="226.2" x14ac:dyDescent="0.4">
-      <c r="A64" s="15" t="s">
+    </row>
+    <row r="64" spans="1:3" ht="226.2" x14ac:dyDescent="0.4">
+      <c r="A64" s="13" t="s">
         <v>797</v>
       </c>
-      <c r="B64" s="15" t="s">
+      <c r="B64" s="13" t="s">
         <v>798</v>
       </c>
-      <c r="C64" s="12">
+      <c r="C64">
         <v>1</v>
       </c>
-      <c r="D64" s="12"/>
     </row>
     <row r="65" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
-      <c r="A65" s="15" t="s">
+      <c r="A65" s="13" t="s">
         <v>799</v>
       </c>
-      <c r="B65" s="15" t="s">
+      <c r="B65" s="13" t="s">
         <v>730</v>
       </c>
-      <c r="C65" s="12">
+      <c r="C65">
         <v>1</v>
       </c>
-      <c r="D65" s="12"/>
     </row>
     <row r="66" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A66" s="15" t="s">
+      <c r="A66" s="13" t="s">
         <v>800</v>
       </c>
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="13" t="s">
         <v>731</v>
       </c>
-      <c r="C66" s="12">
+      <c r="C66">
         <v>3</v>
       </c>
-      <c r="D66" s="12"/>
     </row>
     <row r="67" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
-      <c r="A67" s="15" t="s">
+      <c r="A67" s="13" t="s">
         <v>732</v>
       </c>
-      <c r="B67" s="15" t="s">
+      <c r="B67" s="13" t="s">
         <v>801</v>
       </c>
-      <c r="C67" s="12">
+      <c r="C67">
         <v>4</v>
       </c>
-      <c r="D67" s="12"/>
     </row>
     <row r="68" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A68" s="15" t="s">
+      <c r="A68" s="13" t="s">
         <v>802</v>
       </c>
-      <c r="B68" s="15" t="s">
+      <c r="B68" s="13" t="s">
         <v>606</v>
       </c>
-      <c r="C68" s="12">
-        <v>2</v>
-      </c>
-      <c r="D68" s="12"/>
+      <c r="C68">
+        <v>2</v>
+      </c>
     </row>
     <row r="69" spans="1:4" ht="226.2" x14ac:dyDescent="0.4">
-      <c r="A69" s="15" t="s">
+      <c r="A69" s="13" t="s">
         <v>733</v>
       </c>
-      <c r="B69" s="15" t="s">
+      <c r="B69" s="13" t="s">
         <v>803</v>
       </c>
-      <c r="C69" s="12">
+      <c r="C69">
         <v>1</v>
       </c>
-      <c r="D69" s="12"/>
     </row>
     <row r="70" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A70" s="15" t="s">
+      <c r="A70" s="13" t="s">
         <v>734</v>
       </c>
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="13" t="s">
         <v>735</v>
       </c>
-      <c r="C70" s="12">
+      <c r="C70">
         <v>4</v>
       </c>
-      <c r="D70" s="12"/>
     </row>
     <row r="71" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A71" s="15" t="s">
+      <c r="A71" s="13" t="s">
         <v>736</v>
       </c>
-      <c r="B71" s="15" t="s">
+      <c r="B71" s="13" t="s">
         <v>737</v>
       </c>
-      <c r="C71" s="12">
-        <v>2</v>
-      </c>
-      <c r="D71" s="12" t="s">
+      <c r="C71">
+        <v>2</v>
+      </c>
+      <c r="D71" t="s">
         <v>804</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="261" x14ac:dyDescent="0.4">
-      <c r="A72" s="15" t="s">
+      <c r="A72" s="13" t="s">
         <v>738</v>
       </c>
-      <c r="B72" s="15" t="s">
+      <c r="B72" s="13" t="s">
         <v>805</v>
       </c>
-      <c r="C72" s="12">
+      <c r="C72">
         <v>1</v>
       </c>
-      <c r="D72" s="12"/>
     </row>
     <row r="73" spans="1:4" ht="191.4" x14ac:dyDescent="0.4">
-      <c r="A73" s="15" t="s">
+      <c r="A73" s="13" t="s">
         <v>739</v>
       </c>
-      <c r="B73" s="15" t="s">
+      <c r="B73" s="13" t="s">
         <v>806</v>
       </c>
-      <c r="C73" s="12">
-        <v>2</v>
-      </c>
-      <c r="D73" s="12"/>
+      <c r="C73">
+        <v>2</v>
+      </c>
     </row>
     <row r="74" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A74" s="15" t="s">
+      <c r="A74" s="13" t="s">
         <v>807</v>
       </c>
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="13" t="s">
         <v>740</v>
       </c>
-      <c r="C74" s="12">
-        <v>2</v>
-      </c>
-      <c r="D74" s="12"/>
+      <c r="C74">
+        <v>2</v>
+      </c>
     </row>
     <row r="75" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A75" s="15" t="s">
+      <c r="A75" s="13" t="s">
         <v>741</v>
       </c>
-      <c r="B75" s="15" t="s">
+      <c r="B75" s="13" t="s">
         <v>742</v>
       </c>
-      <c r="C75" s="12">
+      <c r="C75">
         <v>4</v>
       </c>
-      <c r="D75" s="12"/>
     </row>
     <row r="76" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A76" s="15" t="s">
+      <c r="A76" s="13" t="s">
         <v>743</v>
       </c>
-      <c r="B76" s="15" t="s">
+      <c r="B76" s="13" t="s">
         <v>744</v>
       </c>
-      <c r="C76" s="12">
+      <c r="C76">
         <v>4</v>
       </c>
-      <c r="D76" s="12"/>
     </row>
     <row r="77" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A77" s="15" t="s">
+      <c r="A77" s="13" t="s">
         <v>808</v>
       </c>
-      <c r="B77" s="15" t="s">
+      <c r="B77" s="13" t="s">
         <v>745</v>
       </c>
-      <c r="C77" s="12">
+      <c r="C77">
         <v>3</v>
       </c>
-      <c r="D77" s="12"/>
     </row>
     <row r="78" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A78" s="15" t="s">
+      <c r="A78" s="13" t="s">
         <v>746</v>
       </c>
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="13" t="s">
         <v>747</v>
       </c>
-      <c r="C78" s="12">
+      <c r="C78">
         <v>4</v>
       </c>
-      <c r="D78" s="12"/>
     </row>
     <row r="79" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A79" s="15" t="s">
+      <c r="A79" s="13" t="s">
         <v>748</v>
       </c>
-      <c r="B79" s="15" t="s">
+      <c r="B79" s="13" t="s">
         <v>466</v>
       </c>
-      <c r="C79" s="12">
-        <v>2</v>
-      </c>
-      <c r="D79" s="12"/>
+      <c r="C79">
+        <v>2</v>
+      </c>
     </row>
     <row r="80" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A80" s="15" t="s">
+      <c r="A80" s="13" t="s">
         <v>809</v>
       </c>
-      <c r="B80" s="15" t="s">
+      <c r="B80" s="13" t="s">
         <v>749</v>
       </c>
-      <c r="C80" s="12">
+      <c r="C80">
         <v>3</v>
       </c>
-      <c r="D80" s="12"/>
-    </row>
-    <row r="81" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A81" s="15" t="s">
+    </row>
+    <row r="81" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A81" s="13" t="s">
         <v>811</v>
       </c>
-      <c r="B81" s="15" t="s">
+      <c r="B81" s="13" t="s">
         <v>810</v>
       </c>
-      <c r="C81" s="12">
-        <v>2</v>
-      </c>
-      <c r="D81" s="12"/>
+      <c r="C81">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10019,24 +10745,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" ht="16.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="13" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="13" t="s">
         <v>812</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="13" t="s">
         <v>813</v>
       </c>
       <c r="C2">
@@ -10044,10 +10770,10 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="13" t="s">
         <v>814</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="13" t="s">
         <v>815</v>
       </c>
       <c r="C3">
@@ -10055,10 +10781,10 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="87" x14ac:dyDescent="0.4">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="13" t="s">
         <v>908</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="13" t="s">
         <v>816</v>
       </c>
       <c r="C4">
@@ -10066,10 +10792,10 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="13" t="s">
         <v>909</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="13" t="s">
         <v>817</v>
       </c>
       <c r="C5">
@@ -10077,10 +10803,10 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="13" t="s">
         <v>818</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="13" t="s">
         <v>819</v>
       </c>
       <c r="C6">
@@ -10088,10 +10814,10 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="13" t="s">
         <v>820</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="13" t="s">
         <v>821</v>
       </c>
       <c r="C7">
@@ -10099,10 +10825,10 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="13" t="s">
         <v>822</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="13" t="s">
         <v>823</v>
       </c>
       <c r="C8">
@@ -10110,10 +10836,10 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="13" t="s">
         <v>824</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="13">
         <v>16408</v>
       </c>
       <c r="C9">
@@ -10121,10 +10847,10 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="13" t="s">
         <v>825</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="13" t="s">
         <v>826</v>
       </c>
       <c r="C10">
@@ -10132,10 +10858,10 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="13" t="s">
         <v>827</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="13" t="s">
         <v>910</v>
       </c>
       <c r="C11">
@@ -10143,10 +10869,10 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="13" t="s">
         <v>828</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="13" t="s">
         <v>829</v>
       </c>
       <c r="C12">
@@ -10154,10 +10880,10 @@
       </c>
     </row>
     <row r="13" spans="1:4" ht="87" x14ac:dyDescent="0.4">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="13" t="s">
         <v>911</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="13" t="s">
         <v>830</v>
       </c>
       <c r="C13">
@@ -10165,10 +10891,10 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="174" x14ac:dyDescent="0.4">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="13" t="s">
         <v>831</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="13" t="s">
         <v>912</v>
       </c>
       <c r="C14">
@@ -10176,10 +10902,10 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="13" t="s">
         <v>832</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="13" t="s">
         <v>833</v>
       </c>
       <c r="C15">
@@ -10187,10 +10913,10 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="121.8" x14ac:dyDescent="0.4">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="13" t="s">
         <v>834</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="13" t="s">
         <v>835</v>
       </c>
       <c r="C16">
@@ -10198,10 +10924,10 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="13" t="s">
         <v>913</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="13" t="s">
         <v>836</v>
       </c>
       <c r="C17">
@@ -10209,10 +10935,10 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="13" t="s">
         <v>837</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="13" t="s">
         <v>914</v>
       </c>
       <c r="C18">
@@ -10220,10 +10946,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="13" t="s">
         <v>838</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="13" t="s">
         <v>915</v>
       </c>
       <c r="C19">
@@ -10231,10 +10957,10 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="13" t="s">
         <v>839</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="13" t="s">
         <v>840</v>
       </c>
       <c r="C20">
@@ -10242,10 +10968,10 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="13" t="s">
         <v>917</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="13" t="s">
         <v>916</v>
       </c>
       <c r="C21">
@@ -10256,10 +10982,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="13" t="s">
         <v>919</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="13" t="s">
         <v>841</v>
       </c>
       <c r="C22">
@@ -10267,10 +10993,10 @@
       </c>
     </row>
     <row r="23" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="13" t="s">
         <v>842</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="13" t="s">
         <v>843</v>
       </c>
       <c r="C23">
@@ -10278,10 +11004,10 @@
       </c>
     </row>
     <row r="24" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="13" t="s">
         <v>844</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="13" t="s">
         <v>845</v>
       </c>
       <c r="C24">
@@ -10289,10 +11015,10 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="13" t="s">
         <v>846</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="13" t="s">
         <v>847</v>
       </c>
       <c r="C25">
@@ -10300,10 +11026,10 @@
       </c>
     </row>
     <row r="26" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="13" t="s">
         <v>921</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="13" t="s">
         <v>920</v>
       </c>
       <c r="C26">
@@ -10311,10 +11037,10 @@
       </c>
     </row>
     <row r="27" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="13" t="s">
         <v>922</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="13" t="s">
         <v>848</v>
       </c>
       <c r="C27">
@@ -10322,10 +11048,10 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="13" t="s">
         <v>849</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="13" t="s">
         <v>850</v>
       </c>
       <c r="C28">
@@ -10336,10 +11062,10 @@
       </c>
     </row>
     <row r="29" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="13" t="s">
         <v>851</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="13" t="s">
         <v>924</v>
       </c>
       <c r="C29">
@@ -10347,10 +11073,10 @@
       </c>
     </row>
     <row r="30" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A30" s="15" t="s">
+      <c r="A30" s="13" t="s">
         <v>852</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="13" t="s">
         <v>853</v>
       </c>
       <c r="C30">
@@ -10358,10 +11084,10 @@
       </c>
     </row>
     <row r="31" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="13" t="s">
         <v>925</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="13" t="s">
         <v>854</v>
       </c>
       <c r="C31">
@@ -10369,10 +11095,10 @@
       </c>
     </row>
     <row r="32" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="13" t="s">
         <v>855</v>
       </c>
-      <c r="B32" s="15">
+      <c r="B32" s="13">
         <v>16431</v>
       </c>
       <c r="C32">
@@ -10380,10 +11106,10 @@
       </c>
     </row>
     <row r="33" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="13" t="s">
         <v>926</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="13" t="s">
         <v>856</v>
       </c>
       <c r="C33">
@@ -10391,10 +11117,10 @@
       </c>
     </row>
     <row r="34" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="13" t="s">
         <v>857</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="13" t="s">
         <v>927</v>
       </c>
       <c r="C34">
@@ -10402,10 +11128,10 @@
       </c>
     </row>
     <row r="35" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="13" t="s">
         <v>858</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="13" t="s">
         <v>928</v>
       </c>
       <c r="C35">
@@ -10413,10 +11139,10 @@
       </c>
     </row>
     <row r="36" spans="1:4" ht="87" x14ac:dyDescent="0.4">
-      <c r="A36" s="15" t="s">
+      <c r="A36" s="13" t="s">
         <v>929</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="B36" s="13" t="s">
         <v>859</v>
       </c>
       <c r="C36">
@@ -10424,10 +11150,10 @@
       </c>
     </row>
     <row r="37" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="13" t="s">
         <v>860</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="13" t="s">
         <v>861</v>
       </c>
       <c r="C37">
@@ -10435,10 +11161,10 @@
       </c>
     </row>
     <row r="38" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="13" t="s">
         <v>862</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="13" t="s">
         <v>863</v>
       </c>
       <c r="C38">
@@ -10446,10 +11172,10 @@
       </c>
     </row>
     <row r="39" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A39" s="15" t="s">
+      <c r="A39" s="13" t="s">
         <v>931</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="B39" s="13" t="s">
         <v>864</v>
       </c>
       <c r="C39">
@@ -10460,10 +11186,10 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A40" s="15" t="s">
+      <c r="A40" s="13" t="s">
         <v>932</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B40" s="13" t="s">
         <v>865</v>
       </c>
       <c r="C40">
@@ -10471,10 +11197,10 @@
       </c>
     </row>
     <row r="41" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A41" s="15" t="s">
+      <c r="A41" s="13" t="s">
         <v>935</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="B41" s="13" t="s">
         <v>934</v>
       </c>
       <c r="C41">
@@ -10485,10 +11211,10 @@
       </c>
     </row>
     <row r="42" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A42" s="15" t="s">
+      <c r="A42" s="13" t="s">
         <v>937</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="13" t="s">
         <v>933</v>
       </c>
       <c r="C42">
@@ -10496,10 +11222,10 @@
       </c>
     </row>
     <row r="43" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A43" s="15" t="s">
+      <c r="A43" s="13" t="s">
         <v>938</v>
       </c>
-      <c r="B43" s="15" t="s">
+      <c r="B43" s="13" t="s">
         <v>866</v>
       </c>
       <c r="C43">
@@ -10507,10 +11233,10 @@
       </c>
     </row>
     <row r="44" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A44" s="15" t="s">
+      <c r="A44" s="13" t="s">
         <v>867</v>
       </c>
-      <c r="B44" s="15" t="s">
+      <c r="B44" s="13" t="s">
         <v>868</v>
       </c>
       <c r="C44">
@@ -10518,10 +11244,10 @@
       </c>
     </row>
     <row r="45" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
-      <c r="A45" s="15" t="s">
+      <c r="A45" s="13" t="s">
         <v>939</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="B45" s="13" t="s">
         <v>869</v>
       </c>
       <c r="C45">
@@ -10529,10 +11255,10 @@
       </c>
     </row>
     <row r="46" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A46" s="15" t="s">
+      <c r="A46" s="13" t="s">
         <v>870</v>
       </c>
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="13" t="s">
         <v>871</v>
       </c>
       <c r="C46">
@@ -10540,10 +11266,10 @@
       </c>
     </row>
     <row r="47" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A47" s="15" t="s">
+      <c r="A47" s="13" t="s">
         <v>872</v>
       </c>
-      <c r="B47" s="15" t="s">
+      <c r="B47" s="13" t="s">
         <v>873</v>
       </c>
       <c r="C47">
@@ -10551,10 +11277,10 @@
       </c>
     </row>
     <row r="48" spans="1:4" ht="87" x14ac:dyDescent="0.4">
-      <c r="A48" s="15" t="s">
+      <c r="A48" s="13" t="s">
         <v>940</v>
       </c>
-      <c r="B48" s="15" t="s">
+      <c r="B48" s="13" t="s">
         <v>108</v>
       </c>
       <c r="C48">
@@ -10562,10 +11288,10 @@
       </c>
     </row>
     <row r="49" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A49" s="15" t="s">
+      <c r="A49" s="13" t="s">
         <v>941</v>
       </c>
-      <c r="B49" s="15" t="s">
+      <c r="B49" s="13" t="s">
         <v>874</v>
       </c>
       <c r="C49">
@@ -10573,10 +11299,10 @@
       </c>
     </row>
     <row r="50" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A50" s="15" t="s">
+      <c r="A50" s="13" t="s">
         <v>875</v>
       </c>
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="13" t="s">
         <v>876</v>
       </c>
       <c r="C50">
@@ -10584,10 +11310,10 @@
       </c>
     </row>
     <row r="51" spans="1:4" ht="191.4" x14ac:dyDescent="0.4">
-      <c r="A51" s="15" t="s">
+      <c r="A51" s="13" t="s">
         <v>942</v>
       </c>
-      <c r="B51" s="15" t="s">
+      <c r="B51" s="13" t="s">
         <v>943</v>
       </c>
       <c r="C51">
@@ -10595,10 +11321,10 @@
       </c>
     </row>
     <row r="52" spans="1:4" ht="87" x14ac:dyDescent="0.4">
-      <c r="A52" s="15" t="s">
+      <c r="A52" s="13" t="s">
         <v>944</v>
       </c>
-      <c r="B52" s="15" t="s">
+      <c r="B52" s="13" t="s">
         <v>945</v>
       </c>
       <c r="C52">
@@ -10606,10 +11332,10 @@
       </c>
     </row>
     <row r="53" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
-      <c r="A53" s="15" t="s">
+      <c r="A53" s="13" t="s">
         <v>946</v>
       </c>
-      <c r="B53" s="15" t="s">
+      <c r="B53" s="13" t="s">
         <v>947</v>
       </c>
       <c r="C53">
@@ -10617,10 +11343,10 @@
       </c>
     </row>
     <row r="54" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A54" s="15" t="s">
+      <c r="A54" s="13" t="s">
         <v>948</v>
       </c>
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="13" t="s">
         <v>877</v>
       </c>
       <c r="C54">
@@ -10628,10 +11354,10 @@
       </c>
     </row>
     <row r="55" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A55" s="15" t="s">
+      <c r="A55" s="13" t="s">
         <v>878</v>
       </c>
-      <c r="B55" s="15" t="s">
+      <c r="B55" s="13" t="s">
         <v>879</v>
       </c>
       <c r="C55">
@@ -10639,10 +11365,10 @@
       </c>
     </row>
     <row r="56" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A56" s="15" t="s">
+      <c r="A56" s="13" t="s">
         <v>880</v>
       </c>
-      <c r="B56" s="15" t="s">
+      <c r="B56" s="13" t="s">
         <v>881</v>
       </c>
       <c r="C56">
@@ -10650,10 +11376,10 @@
       </c>
     </row>
     <row r="57" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A57" s="15" t="s">
+      <c r="A57" s="13" t="s">
         <v>949</v>
       </c>
-      <c r="B57" s="15" t="s">
+      <c r="B57" s="13" t="s">
         <v>882</v>
       </c>
       <c r="C57">
@@ -10661,10 +11387,10 @@
       </c>
     </row>
     <row r="58" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A58" s="15" t="s">
+      <c r="A58" s="13" t="s">
         <v>950</v>
       </c>
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="13" t="s">
         <v>883</v>
       </c>
       <c r="C58">
@@ -10672,10 +11398,10 @@
       </c>
     </row>
     <row r="59" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A59" s="15" t="s">
+      <c r="A59" s="13" t="s">
         <v>884</v>
       </c>
-      <c r="B59" s="15" t="s">
+      <c r="B59" s="13" t="s">
         <v>885</v>
       </c>
       <c r="C59">
@@ -10683,10 +11409,10 @@
       </c>
     </row>
     <row r="60" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
-      <c r="A60" s="15" t="s">
+      <c r="A60" s="13" t="s">
         <v>951</v>
       </c>
-      <c r="B60" s="15" t="s">
+      <c r="B60" s="13" t="s">
         <v>952</v>
       </c>
       <c r="C60">
@@ -10694,10 +11420,10 @@
       </c>
     </row>
     <row r="61" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A61" s="15" t="s">
+      <c r="A61" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="B61" s="15" t="s">
+      <c r="B61" s="13" t="s">
         <v>953</v>
       </c>
       <c r="C61">
@@ -10705,10 +11431,10 @@
       </c>
     </row>
     <row r="62" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
-      <c r="A62" s="15" t="s">
+      <c r="A62" s="13" t="s">
         <v>886</v>
       </c>
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="13" t="s">
         <v>955</v>
       </c>
       <c r="C62">
@@ -10716,10 +11442,10 @@
       </c>
     </row>
     <row r="63" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A63" s="15" t="s">
+      <c r="A63" s="13" t="s">
         <v>956</v>
       </c>
-      <c r="B63" s="15" t="s">
+      <c r="B63" s="13" t="s">
         <v>887</v>
       </c>
       <c r="C63">
@@ -10727,10 +11453,10 @@
       </c>
     </row>
     <row r="64" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A64" s="15" t="s">
+      <c r="A64" s="13" t="s">
         <v>888</v>
       </c>
-      <c r="B64" s="15" t="s">
+      <c r="B64" s="13" t="s">
         <v>889</v>
       </c>
       <c r="C64">
@@ -10741,10 +11467,10 @@
       </c>
     </row>
     <row r="65" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
-      <c r="A65" s="15" t="s">
+      <c r="A65" s="13" t="s">
         <v>958</v>
       </c>
-      <c r="B65" s="15" t="s">
+      <c r="B65" s="13" t="s">
         <v>890</v>
       </c>
       <c r="C65">
@@ -10752,10 +11478,10 @@
       </c>
     </row>
     <row r="66" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
-      <c r="A66" s="15" t="s">
+      <c r="A66" s="13" t="s">
         <v>959</v>
       </c>
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="13" t="s">
         <v>891</v>
       </c>
       <c r="C66">
@@ -10763,10 +11489,10 @@
       </c>
     </row>
     <row r="67" spans="1:4" ht="87" x14ac:dyDescent="0.4">
-      <c r="A67" s="15" t="s">
+      <c r="A67" s="13" t="s">
         <v>960</v>
       </c>
-      <c r="B67" s="15" t="s">
+      <c r="B67" s="13" t="s">
         <v>467</v>
       </c>
       <c r="C67">
@@ -10774,10 +11500,10 @@
       </c>
     </row>
     <row r="68" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
-      <c r="A68" s="15" t="s">
+      <c r="A68" s="13" t="s">
         <v>892</v>
       </c>
-      <c r="B68" s="15" t="s">
+      <c r="B68" s="13" t="s">
         <v>961</v>
       </c>
       <c r="C68">
@@ -10785,10 +11511,10 @@
       </c>
     </row>
     <row r="69" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A69" s="15" t="s">
+      <c r="A69" s="13" t="s">
         <v>893</v>
       </c>
-      <c r="B69" s="15" t="s">
+      <c r="B69" s="13" t="s">
         <v>894</v>
       </c>
       <c r="C69">
@@ -10796,10 +11522,10 @@
       </c>
     </row>
     <row r="70" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A70" s="15" t="s">
+      <c r="A70" s="13" t="s">
         <v>962</v>
       </c>
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="13" t="s">
         <v>895</v>
       </c>
       <c r="C70">
@@ -10807,10 +11533,10 @@
       </c>
     </row>
     <row r="71" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A71" s="15" t="s">
+      <c r="A71" s="13" t="s">
         <v>963</v>
       </c>
-      <c r="B71" s="15" t="s">
+      <c r="B71" s="13" t="s">
         <v>896</v>
       </c>
       <c r="C71">
@@ -10818,10 +11544,10 @@
       </c>
     </row>
     <row r="72" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A72" s="15" t="s">
+      <c r="A72" s="13" t="s">
         <v>964</v>
       </c>
-      <c r="B72" s="15" t="s">
+      <c r="B72" s="13" t="s">
         <v>634</v>
       </c>
       <c r="C72">
@@ -10829,10 +11555,10 @@
       </c>
     </row>
     <row r="73" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A73" s="15" t="s">
+      <c r="A73" s="13" t="s">
         <v>897</v>
       </c>
-      <c r="B73" s="15" t="s">
+      <c r="B73" s="13" t="s">
         <v>898</v>
       </c>
       <c r="C73">
@@ -10840,10 +11566,10 @@
       </c>
     </row>
     <row r="74" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A74" s="15" t="s">
+      <c r="A74" s="13" t="s">
         <v>899</v>
       </c>
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="13" t="s">
         <v>900</v>
       </c>
       <c r="C74">
@@ -10854,10 +11580,10 @@
       </c>
     </row>
     <row r="75" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A75" s="15" t="s">
+      <c r="A75" s="13" t="s">
         <v>966</v>
       </c>
-      <c r="B75" s="15" t="s">
+      <c r="B75" s="13" t="s">
         <v>967</v>
       </c>
       <c r="C75">
@@ -10865,10 +11591,10 @@
       </c>
     </row>
     <row r="76" spans="1:4" ht="174" x14ac:dyDescent="0.4">
-      <c r="A76" s="15" t="s">
+      <c r="A76" s="13" t="s">
         <v>901</v>
       </c>
-      <c r="B76" s="15" t="s">
+      <c r="B76" s="13" t="s">
         <v>968</v>
       </c>
       <c r="C76">
@@ -10876,10 +11602,10 @@
       </c>
     </row>
     <row r="77" spans="1:4" ht="87" x14ac:dyDescent="0.4">
-      <c r="A77" s="15" t="s">
+      <c r="A77" s="13" t="s">
         <v>969</v>
       </c>
-      <c r="B77" s="15" t="s">
+      <c r="B77" s="13" t="s">
         <v>902</v>
       </c>
       <c r="C77">
@@ -10887,10 +11613,10 @@
       </c>
     </row>
     <row r="78" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A78" s="15" t="s">
+      <c r="A78" s="13" t="s">
         <v>970</v>
       </c>
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="13" t="s">
         <v>903</v>
       </c>
       <c r="C78">
@@ -10898,10 +11624,10 @@
       </c>
     </row>
     <row r="79" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
-      <c r="A79" s="15" t="s">
+      <c r="A79" s="13" t="s">
         <v>904</v>
       </c>
-      <c r="B79" s="15" t="s">
+      <c r="B79" s="13" t="s">
         <v>905</v>
       </c>
       <c r="C79">
@@ -10909,10 +11635,10 @@
       </c>
     </row>
     <row r="80" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
-      <c r="A80" s="15" t="s">
+      <c r="A80" s="13" t="s">
         <v>906</v>
       </c>
-      <c r="B80" s="15" t="s">
+      <c r="B80" s="13" t="s">
         <v>907</v>
       </c>
       <c r="C80">
@@ -10920,14 +11646,1016 @@
       </c>
     </row>
     <row r="81" spans="1:3" ht="156.6" x14ac:dyDescent="0.4">
-      <c r="A81" s="15" t="s">
+      <c r="A81" s="13" t="s">
         <v>972</v>
       </c>
-      <c r="B81" s="15" t="s">
+      <c r="B81" s="13" t="s">
         <v>971</v>
       </c>
       <c r="C81">
         <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA271491-B8A6-4DE4-BB68-3B26D2B5A98E}">
+  <dimension ref="A1:D81"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="46.09765625" customWidth="1"/>
+    <col min="2" max="2" width="33.19921875" customWidth="1"/>
+    <col min="3" max="3" width="4.3984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="1" customFormat="1" ht="16.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A2" s="13" t="s">
+        <v>973</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D2" s="16"/>
+    </row>
+    <row r="3" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A3" s="13" t="s">
+        <v>974</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D3" s="16"/>
+    </row>
+    <row r="4" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A4" s="13" t="s">
+        <v>975</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D4" s="16"/>
+    </row>
+    <row r="5" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A5" s="13" t="s">
+        <v>976</v>
+      </c>
+      <c r="B5" s="13">
+        <v>17104</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D5" s="16"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A6" s="13" t="s">
+        <v>977</v>
+      </c>
+      <c r="B6" s="13">
+        <v>17105</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D6" s="16"/>
+    </row>
+    <row r="7" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A7" s="13" t="s">
+        <v>978</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D7" s="16"/>
+    </row>
+    <row r="8" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A8" s="13" t="s">
+        <v>979</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D8" s="16"/>
+    </row>
+    <row r="9" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A9" s="13" t="s">
+        <v>980</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D9" s="16"/>
+    </row>
+    <row r="10" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A10" s="13" t="s">
+        <v>981</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D10" s="16"/>
+    </row>
+    <row r="11" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A11" s="13" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D11" s="16"/>
+    </row>
+    <row r="12" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A12" s="13" t="s">
+        <v>982</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D12" s="16"/>
+    </row>
+    <row r="13" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A13" s="13" t="s">
+        <v>983</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D13" s="16"/>
+    </row>
+    <row r="14" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A14" s="13" t="s">
+        <v>984</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D14" s="16"/>
+    </row>
+    <row r="15" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A15" s="13" t="s">
+        <v>985</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D15" s="16"/>
+    </row>
+    <row r="16" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A16" s="13" t="s">
+        <v>986</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D16" s="16"/>
+    </row>
+    <row r="17" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A17" s="13" t="s">
+        <v>987</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D17" s="16"/>
+    </row>
+    <row r="18" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A18" s="13" t="s">
+        <v>988</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D18" s="16"/>
+    </row>
+    <row r="19" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A19" s="13" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D19" s="16"/>
+    </row>
+    <row r="20" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A20" s="13" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D20" s="16"/>
+    </row>
+    <row r="21" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A21" s="13" t="s">
+        <v>989</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D21" s="16"/>
+    </row>
+    <row r="22" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A22" s="13" t="s">
+        <v>990</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D22" s="16"/>
+    </row>
+    <row r="23" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A23" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D23" s="16"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A24" s="13" t="s">
+        <v>992</v>
+      </c>
+      <c r="B24" s="13">
+        <v>17123</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D24" s="16"/>
+    </row>
+    <row r="25" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A25" s="13" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D25" s="16"/>
+    </row>
+    <row r="26" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A26" s="13" t="s">
+        <v>993</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D26" s="16"/>
+    </row>
+    <row r="27" spans="1:4" ht="87" x14ac:dyDescent="0.4">
+      <c r="A27" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D27" s="16"/>
+    </row>
+    <row r="28" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A28" s="13" t="s">
+        <v>995</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D28" s="16"/>
+    </row>
+    <row r="29" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A29" s="13" t="s">
+        <v>996</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D29" s="16"/>
+    </row>
+    <row r="30" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A30" s="13" t="s">
+        <v>997</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A31" s="13" t="s">
+        <v>998</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D31" s="16"/>
+    </row>
+    <row r="32" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A32" s="13" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A33" s="13" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="87" x14ac:dyDescent="0.4">
+      <c r="A34" s="13" t="s">
+        <v>999</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D34" s="16"/>
+    </row>
+    <row r="35" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A35" s="13" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D35" s="16"/>
+    </row>
+    <row r="36" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A36" s="13" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D36" s="16"/>
+    </row>
+    <row r="37" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A37" s="13" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D37" s="16"/>
+    </row>
+    <row r="38" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A38" s="13" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D38" s="16"/>
+    </row>
+    <row r="39" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A39" s="13" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D39" s="16"/>
+    </row>
+    <row r="40" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A40" s="13" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D40" s="16"/>
+    </row>
+    <row r="41" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A41" s="13" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D41" s="16"/>
+    </row>
+    <row r="42" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A42" s="13" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D42" s="16"/>
+    </row>
+    <row r="43" spans="1:4" ht="226.2" x14ac:dyDescent="0.4">
+      <c r="A43" s="13" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D43" s="16"/>
+    </row>
+    <row r="44" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A44" s="13" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D44" s="16"/>
+    </row>
+    <row r="45" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A45" s="13" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D45" s="16"/>
+    </row>
+    <row r="46" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A46" s="13" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>634</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D46" s="16"/>
+    </row>
+    <row r="47" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A47" s="13" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D47" s="16"/>
+    </row>
+    <row r="48" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A48" s="13" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D48" s="16"/>
+    </row>
+    <row r="49" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A49" s="13" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D49" s="16"/>
+    </row>
+    <row r="50" spans="1:4" ht="174" x14ac:dyDescent="0.4">
+      <c r="A50" s="13" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D50" s="16"/>
+    </row>
+    <row r="51" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A51" s="13" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D51" s="16"/>
+    </row>
+    <row r="52" spans="1:4" ht="295.8" x14ac:dyDescent="0.4">
+      <c r="A52" s="13" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D52" s="16"/>
+    </row>
+    <row r="53" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A53" s="13" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D53" s="16"/>
+    </row>
+    <row r="54" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A54" s="13" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D54" s="16"/>
+    </row>
+    <row r="55" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A55" s="13" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B55" s="13" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D55" s="16"/>
+    </row>
+    <row r="56" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A56" s="13" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B56" s="13" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C56" s="15" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D56" s="16"/>
+    </row>
+    <row r="57" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A57" s="13" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B57" s="13" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D57" s="16"/>
+    </row>
+    <row r="58" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A58" s="13" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B58" s="13" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D58" s="16" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A59" s="13" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D59" s="16"/>
+    </row>
+    <row r="60" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A60" s="13" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C60" s="15" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D60" s="16"/>
+    </row>
+    <row r="61" spans="1:4" ht="156.6" x14ac:dyDescent="0.4">
+      <c r="A61" s="13" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D61" s="16"/>
+    </row>
+    <row r="62" spans="1:4" ht="208.8" x14ac:dyDescent="0.4">
+      <c r="A62" s="13" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B62" s="13" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D62" s="16"/>
+    </row>
+    <row r="63" spans="1:4" ht="174" x14ac:dyDescent="0.4">
+      <c r="A63" s="13" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B63" s="13" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D63" s="16"/>
+    </row>
+    <row r="64" spans="1:4" ht="261" x14ac:dyDescent="0.4">
+      <c r="A64" s="13" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B64" s="13" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C64" s="15" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D64" s="16"/>
+    </row>
+    <row r="65" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A65" s="13" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B65" s="13" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C65" s="15" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D65" s="16"/>
+    </row>
+    <row r="66" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A66" s="13" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B66" s="13" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D66" s="16"/>
+    </row>
+    <row r="67" spans="1:4" ht="208.8" x14ac:dyDescent="0.4">
+      <c r="A67" s="13" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B67" s="13" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D67" s="16"/>
+    </row>
+    <row r="68" spans="1:4" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A68" s="13" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B68" s="13" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C68" s="15" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D68" s="16"/>
+    </row>
+    <row r="69" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A69" s="13" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B69" s="13" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D69" s="16" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A70" s="13" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B70" s="13" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C70" s="15" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D70" s="16"/>
+    </row>
+    <row r="71" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A71" s="13" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B71" s="13" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C71" s="15" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D71" s="16"/>
+    </row>
+    <row r="72" spans="1:4" ht="278.39999999999998" x14ac:dyDescent="0.4">
+      <c r="A72" s="13" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C72" s="15" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D72" s="16"/>
+    </row>
+    <row r="73" spans="1:4" ht="191.4" x14ac:dyDescent="0.4">
+      <c r="A73" s="13" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B73" s="13" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D73" s="16"/>
+    </row>
+    <row r="74" spans="1:4" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A74" s="13" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B74" s="13" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C74" s="15" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D74" s="16"/>
+    </row>
+    <row r="75" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A75" s="13" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B75" s="13" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C75" s="15" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D75" s="16"/>
+    </row>
+    <row r="76" spans="1:4" ht="191.4" x14ac:dyDescent="0.4">
+      <c r="A76" s="13" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B76" s="13" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C76" s="15" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D76" s="16"/>
+    </row>
+    <row r="77" spans="1:4" ht="261" x14ac:dyDescent="0.4">
+      <c r="A77" s="13" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B77" s="13" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C77" s="15" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D77" s="16"/>
+    </row>
+    <row r="78" spans="1:4" ht="87" x14ac:dyDescent="0.4">
+      <c r="A78" s="13" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B78" s="13" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C78" s="15" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D78" s="16"/>
+    </row>
+    <row r="79" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A79" s="13" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B79" s="13" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C79" s="15" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D79" s="16"/>
+    </row>
+    <row r="80" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A80" s="13" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B80" s="13" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C80" s="15" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D80" s="16"/>
+    </row>
+    <row r="81" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A81" s="13" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B81" s="13" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C81" s="15" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D81" s="16" t="s">
+        <v>1138</v>
       </c>
     </row>
   </sheetData>
